--- a/marsu-pwa-dashboard/py_scripts/PBB FY 2023.xlsx
+++ b/marsu-pwa-dashboard/py_scripts/PBB FY 2023.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\dev\ds-dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\marsu-dasboard-rev2\marsu-pwa-dashboard\py_scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5F91FB4-371E-4021-9D88-081439C4BA9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61C01BE-A0C4-444F-8107-8C1F974E523F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="90" windowWidth="14595" windowHeight="10800" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="690" yWindow="690" windowWidth="12030" windowHeight="10800" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reference Matrix" sheetId="1" r:id="rId1"/>
@@ -11638,6 +11638,11 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -11648,127 +11653,65 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="10" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="10" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11800,25 +11743,62 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -11827,25 +11807,36 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -11860,16 +11851,31 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="37" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -11879,45 +11885,14 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="7" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11941,52 +11916,62 @@
     <xf numFmtId="0" fontId="31" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="112" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="31" fillId="7" borderId="113" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="31" fillId="7" borderId="114" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="31" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -11999,27 +11984,49 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="112" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="31" fillId="7" borderId="113" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="31" fillId="7" borderId="114" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="31" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -12039,33 +12046,26 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -13136,24 +13136,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A1" s="575" t="s">
+      <c r="A1" s="578" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="576"/>
-      <c r="C1" s="576"/>
-      <c r="D1" s="576"/>
-      <c r="E1" s="576"/>
-      <c r="F1" s="577"/>
+      <c r="B1" s="579"/>
+      <c r="C1" s="579"/>
+      <c r="D1" s="579"/>
+      <c r="E1" s="579"/>
+      <c r="F1" s="580"/>
     </row>
     <row r="2" spans="1:12" ht="155.25" customHeight="1">
-      <c r="A2" s="578" t="s">
+      <c r="A2" s="581" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="579"/>
-      <c r="C2" s="579"/>
-      <c r="D2" s="579"/>
-      <c r="E2" s="579"/>
-      <c r="F2" s="580"/>
+      <c r="B2" s="582"/>
+      <c r="C2" s="582"/>
+      <c r="D2" s="582"/>
+      <c r="E2" s="582"/>
+      <c r="F2" s="583"/>
     </row>
     <row r="3" spans="1:12" ht="12.75" customHeight="1">
       <c r="A3" s="1"/>
@@ -13185,14 +13185,14 @@
       <c r="L4" s="3"/>
     </row>
     <row r="5" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A5" s="581" t="s">
+      <c r="A5" s="575" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="582"/>
-      <c r="C5" s="582"/>
-      <c r="D5" s="582"/>
-      <c r="E5" s="582"/>
-      <c r="F5" s="583"/>
+      <c r="B5" s="576"/>
+      <c r="C5" s="576"/>
+      <c r="D5" s="576"/>
+      <c r="E5" s="576"/>
+      <c r="F5" s="577"/>
       <c r="L5" s="3"/>
     </row>
     <row r="6" spans="1:12" ht="12.75" customHeight="1">
@@ -13280,14 +13280,14 @@
       <c r="L9" s="3"/>
     </row>
     <row r="10" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A10" s="581" t="s">
+      <c r="A10" s="575" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="582"/>
-      <c r="C10" s="582"/>
-      <c r="D10" s="582"/>
-      <c r="E10" s="582"/>
-      <c r="F10" s="583"/>
+      <c r="B10" s="576"/>
+      <c r="C10" s="576"/>
+      <c r="D10" s="576"/>
+      <c r="E10" s="576"/>
+      <c r="F10" s="577"/>
       <c r="L10" s="3"/>
     </row>
     <row r="11" spans="1:12" ht="12.75" customHeight="1">
@@ -13375,14 +13375,14 @@
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A15" s="581" t="s">
+      <c r="A15" s="575" t="s">
         <v>51</v>
       </c>
-      <c r="B15" s="582"/>
-      <c r="C15" s="582"/>
-      <c r="D15" s="582"/>
-      <c r="E15" s="582"/>
-      <c r="F15" s="583"/>
+      <c r="B15" s="576"/>
+      <c r="C15" s="576"/>
+      <c r="D15" s="576"/>
+      <c r="E15" s="576"/>
+      <c r="F15" s="577"/>
       <c r="L15" s="3"/>
     </row>
     <row r="16" spans="1:12" ht="12.75" customHeight="1">
@@ -13470,14 +13470,14 @@
       <c r="L19" s="3"/>
     </row>
     <row r="20" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A20" s="581" t="s">
+      <c r="A20" s="575" t="s">
         <v>72</v>
       </c>
-      <c r="B20" s="582"/>
-      <c r="C20" s="582"/>
-      <c r="D20" s="582"/>
-      <c r="E20" s="582"/>
-      <c r="F20" s="583"/>
+      <c r="B20" s="576"/>
+      <c r="C20" s="576"/>
+      <c r="D20" s="576"/>
+      <c r="E20" s="576"/>
+      <c r="F20" s="577"/>
       <c r="L20" s="3"/>
     </row>
     <row r="21" spans="1:12" ht="12.75" customHeight="1">
@@ -13565,14 +13565,14 @@
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="1:12" ht="12.75" customHeight="1">
-      <c r="A25" s="581" t="s">
+      <c r="A25" s="575" t="s">
         <v>92</v>
       </c>
-      <c r="B25" s="582"/>
-      <c r="C25" s="582"/>
-      <c r="D25" s="582"/>
-      <c r="E25" s="582"/>
-      <c r="F25" s="583"/>
+      <c r="B25" s="576"/>
+      <c r="C25" s="576"/>
+      <c r="D25" s="576"/>
+      <c r="E25" s="576"/>
+      <c r="F25" s="577"/>
       <c r="L25" s="3"/>
     </row>
     <row r="26" spans="1:12" ht="12.75" customHeight="1">
@@ -16255,15 +16255,15 @@
       <c r="B1" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="718" t="s">
+      <c r="C1" s="725" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="647"/>
-      <c r="E1" s="647"/>
-      <c r="F1" s="647"/>
-      <c r="G1" s="647"/>
-      <c r="H1" s="647"/>
-      <c r="I1" s="648"/>
+      <c r="D1" s="624"/>
+      <c r="E1" s="624"/>
+      <c r="F1" s="624"/>
+      <c r="G1" s="624"/>
+      <c r="H1" s="624"/>
+      <c r="I1" s="625"/>
       <c r="J1" s="398"/>
       <c r="K1" s="398"/>
       <c r="L1" s="398"/>
@@ -16275,7 +16275,7 @@
       <c r="B2" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="587" t="s">
+      <c r="C2" s="606" t="s">
         <v>72</v>
       </c>
       <c r="D2" s="588"/>
@@ -16288,14 +16288,14 @@
       <c r="K2" s="588"/>
       <c r="L2" s="588"/>
       <c r="M2" s="588"/>
-      <c r="N2" s="589"/>
+      <c r="N2" s="597"/>
     </row>
     <row r="3" spans="1:14" ht="12.75" customHeight="1">
       <c r="A3" s="14"/>
       <c r="B3" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="613" t="s">
+      <c r="C3" s="648" t="s">
         <v>1380</v>
       </c>
       <c r="D3" s="588"/>
@@ -16308,14 +16308,14 @@
       <c r="K3" s="588"/>
       <c r="L3" s="588"/>
       <c r="M3" s="588"/>
-      <c r="N3" s="589"/>
+      <c r="N3" s="597"/>
     </row>
     <row r="4" spans="1:14" ht="91.5" customHeight="1">
       <c r="A4" s="401"/>
       <c r="B4" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="613" t="s">
+      <c r="C4" s="648" t="s">
         <v>1381</v>
       </c>
       <c r="D4" s="588"/>
@@ -16328,7 +16328,7 @@
       <c r="K4" s="588"/>
       <c r="L4" s="588"/>
       <c r="M4" s="588"/>
-      <c r="N4" s="589"/>
+      <c r="N4" s="597"/>
     </row>
     <row r="5" spans="1:14" ht="195.75" customHeight="1">
       <c r="A5" s="12"/>
@@ -16375,20 +16375,20 @@
       <c r="B7" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="591" t="s">
+      <c r="C7" s="598" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="592"/>
-      <c r="E7" s="592"/>
-      <c r="F7" s="592"/>
-      <c r="G7" s="592"/>
-      <c r="H7" s="592"/>
-      <c r="I7" s="592"/>
-      <c r="J7" s="592"/>
-      <c r="K7" s="592"/>
-      <c r="L7" s="592"/>
-      <c r="M7" s="592"/>
-      <c r="N7" s="593"/>
+      <c r="D7" s="599"/>
+      <c r="E7" s="599"/>
+      <c r="F7" s="599"/>
+      <c r="G7" s="599"/>
+      <c r="H7" s="599"/>
+      <c r="I7" s="599"/>
+      <c r="J7" s="599"/>
+      <c r="K7" s="599"/>
+      <c r="L7" s="599"/>
+      <c r="M7" s="599"/>
+      <c r="N7" s="586"/>
     </row>
     <row r="8" spans="1:14" ht="14.25" customHeight="1">
       <c r="A8" s="405"/>
@@ -16407,36 +16407,36 @@
       <c r="N8" s="408"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A9" s="719" t="s">
+      <c r="A9" s="726" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="681"/>
-      <c r="C9" s="681"/>
-      <c r="D9" s="681"/>
-      <c r="E9" s="681"/>
-      <c r="F9" s="681"/>
-      <c r="G9" s="681"/>
-      <c r="H9" s="681"/>
-      <c r="I9" s="681"/>
-      <c r="J9" s="681"/>
-      <c r="K9" s="681"/>
-      <c r="L9" s="681"/>
-      <c r="M9" s="681"/>
-      <c r="N9" s="683"/>
+      <c r="B9" s="683"/>
+      <c r="C9" s="683"/>
+      <c r="D9" s="683"/>
+      <c r="E9" s="683"/>
+      <c r="F9" s="683"/>
+      <c r="G9" s="683"/>
+      <c r="H9" s="683"/>
+      <c r="I9" s="683"/>
+      <c r="J9" s="683"/>
+      <c r="K9" s="683"/>
+      <c r="L9" s="683"/>
+      <c r="M9" s="683"/>
+      <c r="N9" s="685"/>
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A10" s="720">
+      <c r="A10" s="727">
         <v>1</v>
       </c>
-      <c r="B10" s="595"/>
-      <c r="C10" s="721">
+      <c r="B10" s="591"/>
+      <c r="C10" s="728">
         <v>2</v>
       </c>
-      <c r="D10" s="595"/>
-      <c r="E10" s="713">
+      <c r="D10" s="591"/>
+      <c r="E10" s="729">
         <v>3</v>
       </c>
-      <c r="F10" s="595"/>
+      <c r="F10" s="591"/>
       <c r="G10" s="410">
         <v>4</v>
       </c>
@@ -16446,60 +16446,60 @@
       <c r="I10" s="411">
         <v>6</v>
       </c>
-      <c r="J10" s="713">
+      <c r="J10" s="729">
         <v>7</v>
       </c>
-      <c r="K10" s="585"/>
-      <c r="L10" s="585"/>
-      <c r="M10" s="585"/>
-      <c r="N10" s="586"/>
+      <c r="K10" s="595"/>
+      <c r="L10" s="595"/>
+      <c r="M10" s="595"/>
+      <c r="N10" s="605"/>
     </row>
     <row r="11" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A11" s="722" t="s">
+      <c r="A11" s="730" t="s">
         <v>1384</v>
       </c>
-      <c r="B11" s="653"/>
-      <c r="C11" s="723" t="s">
+      <c r="B11" s="655"/>
+      <c r="C11" s="731" t="s">
         <v>1385</v>
       </c>
-      <c r="D11" s="640"/>
-      <c r="E11" s="724" t="s">
+      <c r="D11" s="617"/>
+      <c r="E11" s="732" t="s">
         <v>1386</v>
       </c>
-      <c r="F11" s="724" t="s">
+      <c r="F11" s="732" t="s">
         <v>1387</v>
       </c>
-      <c r="G11" s="724" t="s">
+      <c r="G11" s="732" t="s">
         <v>1388</v>
       </c>
-      <c r="H11" s="710" t="s">
+      <c r="H11" s="733" t="s">
         <v>1389</v>
       </c>
-      <c r="I11" s="711" t="s">
+      <c r="I11" s="734" t="s">
         <v>1390</v>
       </c>
-      <c r="J11" s="714" t="s">
+      <c r="J11" s="736" t="s">
         <v>1391</v>
       </c>
-      <c r="K11" s="715"/>
-      <c r="L11" s="715"/>
-      <c r="M11" s="715"/>
-      <c r="N11" s="705"/>
+      <c r="K11" s="737"/>
+      <c r="L11" s="737"/>
+      <c r="M11" s="737"/>
+      <c r="N11" s="696"/>
     </row>
     <row r="12" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A12" s="652"/>
-      <c r="B12" s="653"/>
-      <c r="C12" s="663" t="s">
+      <c r="A12" s="654"/>
+      <c r="B12" s="655"/>
+      <c r="C12" s="679" t="s">
         <v>1392</v>
       </c>
-      <c r="D12" s="663" t="s">
+      <c r="D12" s="679" t="s">
         <v>1393</v>
       </c>
-      <c r="E12" s="653"/>
-      <c r="F12" s="653"/>
-      <c r="G12" s="653"/>
+      <c r="E12" s="655"/>
+      <c r="F12" s="655"/>
+      <c r="G12" s="655"/>
       <c r="H12" s="588"/>
-      <c r="I12" s="712"/>
+      <c r="I12" s="735"/>
       <c r="J12" s="412">
         <v>1</v>
       </c>
@@ -16517,15 +16517,15 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A13" s="615"/>
-      <c r="B13" s="616"/>
-      <c r="C13" s="645"/>
-      <c r="D13" s="645"/>
-      <c r="E13" s="616"/>
-      <c r="F13" s="616"/>
-      <c r="G13" s="616"/>
-      <c r="H13" s="579"/>
-      <c r="I13" s="688"/>
+      <c r="A13" s="609"/>
+      <c r="B13" s="610"/>
+      <c r="C13" s="622"/>
+      <c r="D13" s="622"/>
+      <c r="E13" s="610"/>
+      <c r="F13" s="610"/>
+      <c r="G13" s="610"/>
+      <c r="H13" s="582"/>
+      <c r="I13" s="687"/>
       <c r="J13" s="414" t="s">
         <v>1394</v>
       </c>
@@ -16760,18 +16760,18 @@
       <c r="N19" s="407"/>
     </row>
     <row r="20" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A20" s="737">
+      <c r="A20" s="711">
         <v>1</v>
       </c>
-      <c r="B20" s="595"/>
-      <c r="C20" s="738">
+      <c r="B20" s="591"/>
+      <c r="C20" s="712">
         <v>2</v>
       </c>
-      <c r="D20" s="595"/>
-      <c r="E20" s="738">
+      <c r="D20" s="591"/>
+      <c r="E20" s="712">
         <v>3</v>
       </c>
-      <c r="F20" s="595"/>
+      <c r="F20" s="591"/>
       <c r="G20" s="433">
         <v>4</v>
       </c>
@@ -16781,60 +16781,60 @@
       <c r="I20" s="431">
         <v>6</v>
       </c>
-      <c r="J20" s="716">
+      <c r="J20" s="738">
         <v>7</v>
       </c>
-      <c r="K20" s="576"/>
-      <c r="L20" s="576"/>
-      <c r="M20" s="576"/>
-      <c r="N20" s="577"/>
+      <c r="K20" s="579"/>
+      <c r="L20" s="579"/>
+      <c r="M20" s="579"/>
+      <c r="N20" s="580"/>
     </row>
     <row r="21" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A21" s="661" t="s">
+      <c r="A21" s="653" t="s">
         <v>1384</v>
       </c>
-      <c r="B21" s="604"/>
-      <c r="C21" s="717" t="s">
+      <c r="B21" s="593"/>
+      <c r="C21" s="710" t="s">
         <v>1385</v>
       </c>
-      <c r="D21" s="583"/>
-      <c r="E21" s="725" t="s">
+      <c r="D21" s="577"/>
+      <c r="E21" s="720" t="s">
         <v>1386</v>
       </c>
-      <c r="F21" s="725" t="s">
+      <c r="F21" s="720" t="s">
         <v>1387</v>
       </c>
-      <c r="G21" s="725" t="s">
+      <c r="G21" s="720" t="s">
         <v>1388</v>
       </c>
-      <c r="H21" s="726" t="s">
+      <c r="H21" s="721" t="s">
         <v>1389</v>
       </c>
-      <c r="I21" s="661" t="s">
+      <c r="I21" s="653" t="s">
         <v>1390</v>
       </c>
-      <c r="J21" s="717" t="s">
+      <c r="J21" s="710" t="s">
         <v>1391</v>
       </c>
-      <c r="K21" s="582"/>
-      <c r="L21" s="582"/>
-      <c r="M21" s="582"/>
-      <c r="N21" s="676"/>
+      <c r="K21" s="576"/>
+      <c r="L21" s="576"/>
+      <c r="M21" s="576"/>
+      <c r="N21" s="665"/>
     </row>
     <row r="22" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A22" s="652"/>
-      <c r="B22" s="653"/>
-      <c r="C22" s="729" t="s">
+      <c r="A22" s="654"/>
+      <c r="B22" s="655"/>
+      <c r="C22" s="724" t="s">
         <v>1403</v>
       </c>
-      <c r="D22" s="725" t="s">
+      <c r="D22" s="720" t="s">
         <v>1404</v>
       </c>
-      <c r="E22" s="664"/>
-      <c r="F22" s="664"/>
-      <c r="G22" s="664"/>
-      <c r="H22" s="727"/>
-      <c r="I22" s="652"/>
+      <c r="E22" s="673"/>
+      <c r="F22" s="673"/>
+      <c r="G22" s="673"/>
+      <c r="H22" s="722"/>
+      <c r="I22" s="654"/>
       <c r="J22" s="434">
         <v>1</v>
       </c>
@@ -16852,15 +16852,15 @@
       </c>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A23" s="615"/>
-      <c r="B23" s="616"/>
-      <c r="C23" s="616"/>
-      <c r="D23" s="645"/>
-      <c r="E23" s="645"/>
-      <c r="F23" s="645"/>
-      <c r="G23" s="645"/>
-      <c r="H23" s="728"/>
-      <c r="I23" s="615"/>
+      <c r="A23" s="609"/>
+      <c r="B23" s="610"/>
+      <c r="C23" s="610"/>
+      <c r="D23" s="622"/>
+      <c r="E23" s="622"/>
+      <c r="F23" s="622"/>
+      <c r="G23" s="622"/>
+      <c r="H23" s="723"/>
+      <c r="I23" s="609"/>
       <c r="J23" s="149" t="s">
         <v>1394</v>
       </c>
@@ -18911,19 +18911,19 @@
       <c r="B69" s="405"/>
       <c r="C69" s="405"/>
       <c r="D69" s="405"/>
-      <c r="E69" s="730" t="s">
+      <c r="E69" s="713" t="s">
         <v>1447</v>
       </c>
-      <c r="F69" s="731"/>
-      <c r="G69" s="732">
+      <c r="F69" s="714"/>
+      <c r="G69" s="715">
         <f t="shared" ref="G69:H69" si="6">SUM(G25:G68)</f>
         <v>2657</v>
       </c>
-      <c r="H69" s="733" t="e">
+      <c r="H69" s="716" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
       </c>
-      <c r="I69" s="734">
+      <c r="I69" s="717">
         <f>SUM(I24:I68)</f>
         <v>2657</v>
       </c>
@@ -18950,19 +18950,19 @@
       <c r="B70" s="475"/>
       <c r="C70" s="476"/>
       <c r="D70" s="476"/>
-      <c r="E70" s="615"/>
-      <c r="F70" s="636"/>
-      <c r="G70" s="638"/>
-      <c r="H70" s="638"/>
-      <c r="I70" s="735"/>
-      <c r="J70" s="736">
+      <c r="E70" s="609"/>
+      <c r="F70" s="613"/>
+      <c r="G70" s="615"/>
+      <c r="H70" s="615"/>
+      <c r="I70" s="718"/>
+      <c r="J70" s="719">
         <f>SUM(M69:N69)/I69</f>
         <v>1</v>
       </c>
-      <c r="K70" s="592"/>
-      <c r="L70" s="592"/>
-      <c r="M70" s="592"/>
-      <c r="N70" s="593"/>
+      <c r="K70" s="599"/>
+      <c r="L70" s="599"/>
+      <c r="M70" s="599"/>
+      <c r="N70" s="586"/>
     </row>
     <row r="71" spans="1:14" ht="15.75" customHeight="1">
       <c r="A71" s="249"/>
@@ -22862,30 +22862,7 @@
     </row>
   </sheetData>
   <mergeCells count="39">
-    <mergeCell ref="A21:B23"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="E69:F70"/>
-    <mergeCell ref="G69:G70"/>
-    <mergeCell ref="H69:H70"/>
-    <mergeCell ref="I69:I70"/>
-    <mergeCell ref="J70:N70"/>
-    <mergeCell ref="F21:F23"/>
-    <mergeCell ref="G21:G23"/>
-    <mergeCell ref="H21:H23"/>
-    <mergeCell ref="I21:I23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="J21:N21"/>
-    <mergeCell ref="C1:I1"/>
-    <mergeCell ref="C2:N2"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="C4:N4"/>
-    <mergeCell ref="C7:N7"/>
+    <mergeCell ref="J20:N20"/>
     <mergeCell ref="A9:N9"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="C10:D10"/>
@@ -22895,12 +22872,35 @@
     <mergeCell ref="E11:E13"/>
     <mergeCell ref="F11:F13"/>
     <mergeCell ref="G11:G13"/>
-    <mergeCell ref="E21:E23"/>
     <mergeCell ref="H11:H13"/>
     <mergeCell ref="I11:I13"/>
     <mergeCell ref="J10:N10"/>
     <mergeCell ref="J11:N11"/>
-    <mergeCell ref="J20:N20"/>
+    <mergeCell ref="C1:I1"/>
+    <mergeCell ref="C2:N2"/>
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="C4:N4"/>
+    <mergeCell ref="C7:N7"/>
+    <mergeCell ref="J70:N70"/>
+    <mergeCell ref="F21:F23"/>
+    <mergeCell ref="G21:G23"/>
+    <mergeCell ref="H21:H23"/>
+    <mergeCell ref="I21:I23"/>
+    <mergeCell ref="J21:N21"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="E69:F70"/>
+    <mergeCell ref="G69:G70"/>
+    <mergeCell ref="H69:H70"/>
+    <mergeCell ref="I69:I70"/>
+    <mergeCell ref="E21:E23"/>
+    <mergeCell ref="A21:B23"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -22928,45 +22928,45 @@
       <c r="A1" s="484" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="584" t="s">
+      <c r="B1" s="604" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="585"/>
-      <c r="D1" s="585"/>
-      <c r="E1" s="586"/>
+      <c r="C1" s="595"/>
+      <c r="D1" s="595"/>
+      <c r="E1" s="605"/>
     </row>
     <row r="2" spans="1:5" ht="12.75" customHeight="1">
       <c r="A2" s="485" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="587" t="s">
+      <c r="B2" s="606" t="s">
         <v>72</v>
       </c>
       <c r="C2" s="588"/>
       <c r="D2" s="588"/>
-      <c r="E2" s="589"/>
+      <c r="E2" s="597"/>
     </row>
     <row r="3" spans="1:5" ht="29.25" customHeight="1">
       <c r="A3" s="79" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="613" t="s">
+      <c r="B3" s="648" t="s">
         <v>1448</v>
       </c>
       <c r="C3" s="588"/>
       <c r="D3" s="588"/>
-      <c r="E3" s="589"/>
+      <c r="E3" s="597"/>
     </row>
     <row r="4" spans="1:5" ht="42" customHeight="1">
       <c r="A4" s="485" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="613" t="s">
+      <c r="B4" s="648" t="s">
         <v>1449</v>
       </c>
       <c r="C4" s="588"/>
       <c r="D4" s="588"/>
-      <c r="E4" s="589"/>
+      <c r="E4" s="597"/>
     </row>
     <row r="5" spans="1:5" ht="182.25" customHeight="1">
       <c r="A5" s="485" t="s">
@@ -22994,12 +22994,12 @@
       <c r="A7" s="486" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="591" t="s">
+      <c r="B7" s="598" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="592"/>
-      <c r="D7" s="592"/>
-      <c r="E7" s="593"/>
+      <c r="C7" s="599"/>
+      <c r="D7" s="599"/>
+      <c r="E7" s="586"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="249"/>
@@ -23009,35 +23009,35 @@
       <c r="E8" s="249"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A9" s="748" t="s">
+      <c r="A9" s="741" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="576"/>
-      <c r="C9" s="576"/>
-      <c r="D9" s="576"/>
-      <c r="E9" s="577"/>
+      <c r="B9" s="579"/>
+      <c r="C9" s="579"/>
+      <c r="D9" s="579"/>
+      <c r="E9" s="580"/>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1">
       <c r="A10" s="487">
         <v>1</v>
       </c>
-      <c r="B10" s="739">
+      <c r="B10" s="742">
         <v>2</v>
       </c>
-      <c r="C10" s="740"/>
-      <c r="D10" s="739">
+      <c r="C10" s="743"/>
+      <c r="D10" s="742">
         <v>3</v>
       </c>
-      <c r="E10" s="683"/>
+      <c r="E10" s="685"/>
     </row>
     <row r="11" spans="1:5" ht="38.25" customHeight="1">
       <c r="A11" s="488" t="s">
         <v>1452</v>
       </c>
-      <c r="B11" s="741" t="s">
+      <c r="B11" s="744" t="s">
         <v>1453</v>
       </c>
-      <c r="C11" s="616"/>
+      <c r="C11" s="610"/>
       <c r="D11" s="414" t="s">
         <v>1454</v>
       </c>
@@ -23141,23 +23141,23 @@
       <c r="A18" s="500">
         <v>1</v>
       </c>
-      <c r="B18" s="742">
+      <c r="B18" s="745">
         <v>2</v>
       </c>
-      <c r="C18" s="743"/>
-      <c r="D18" s="744">
+      <c r="C18" s="746"/>
+      <c r="D18" s="747">
         <v>3</v>
       </c>
-      <c r="E18" s="683"/>
+      <c r="E18" s="685"/>
     </row>
     <row r="19" spans="1:5" ht="38.25" customHeight="1">
       <c r="A19" s="501" t="s">
         <v>1452</v>
       </c>
-      <c r="B19" s="745" t="s">
+      <c r="B19" s="748" t="s">
         <v>1453</v>
       </c>
-      <c r="C19" s="577"/>
+      <c r="C19" s="580"/>
       <c r="D19" s="502" t="s">
         <v>1463</v>
       </c>
@@ -23258,10 +23258,10 @@
       <c r="E25" s="378"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="746" t="s">
+      <c r="A26" s="739" t="s">
         <v>1469</v>
       </c>
-      <c r="B26" s="747"/>
+      <c r="B26" s="740"/>
       <c r="C26" s="522">
         <v>5</v>
       </c>
@@ -24379,51 +24379,51 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A1" s="749" t="s">
+      <c r="A1" s="754" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="648"/>
-      <c r="C1" s="584" t="s">
+      <c r="B1" s="625"/>
+      <c r="C1" s="604" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="585"/>
-      <c r="E1" s="586"/>
+      <c r="D1" s="595"/>
+      <c r="E1" s="605"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="750" t="s">
+      <c r="A2" s="751" t="s">
         <v>107</v>
       </c>
       <c r="B2" s="588"/>
-      <c r="C2" s="587" t="s">
+      <c r="C2" s="606" t="s">
         <v>72</v>
       </c>
       <c r="D2" s="588"/>
-      <c r="E2" s="589"/>
+      <c r="E2" s="597"/>
     </row>
     <row r="3" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A3" s="751" t="s">
+      <c r="A3" s="755" t="s">
         <v>108</v>
       </c>
       <c r="B3" s="588"/>
-      <c r="C3" s="613" t="s">
+      <c r="C3" s="648" t="s">
         <v>1470</v>
       </c>
       <c r="D3" s="588"/>
-      <c r="E3" s="589"/>
+      <c r="E3" s="597"/>
     </row>
     <row r="4" spans="1:5" ht="54.75" customHeight="1">
-      <c r="A4" s="750" t="s">
+      <c r="A4" s="751" t="s">
         <v>110</v>
       </c>
       <c r="B4" s="588"/>
-      <c r="C4" s="613" t="s">
+      <c r="C4" s="648" t="s">
         <v>1471</v>
       </c>
       <c r="D4" s="588"/>
-      <c r="E4" s="589"/>
+      <c r="E4" s="597"/>
     </row>
     <row r="5" spans="1:5" ht="24.75" customHeight="1">
-      <c r="A5" s="750" t="s">
+      <c r="A5" s="751" t="s">
         <v>112</v>
       </c>
       <c r="B5" s="588"/>
@@ -24434,7 +24434,7 @@
       <c r="E5" s="404"/>
     </row>
     <row r="6" spans="1:5" ht="51.75" customHeight="1">
-      <c r="A6" s="750" t="s">
+      <c r="A6" s="751" t="s">
         <v>113</v>
       </c>
       <c r="B6" s="588"/>
@@ -24445,15 +24445,15 @@
       <c r="E6" s="404"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A7" s="754" t="s">
+      <c r="A7" s="752" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="673"/>
-      <c r="C7" s="591" t="s">
+      <c r="B7" s="670"/>
+      <c r="C7" s="598" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="592"/>
-      <c r="E7" s="593"/>
+      <c r="D7" s="599"/>
+      <c r="E7" s="586"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="525"/>
@@ -24470,23 +24470,23 @@
       <c r="E9" s="525"/>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A10" s="755">
+      <c r="A10" s="753">
         <v>1</v>
       </c>
-      <c r="B10" s="683"/>
+      <c r="B10" s="685"/>
       <c r="C10" s="526">
         <v>2</v>
       </c>
-      <c r="D10" s="739">
+      <c r="D10" s="742">
         <v>3</v>
       </c>
-      <c r="E10" s="683"/>
+      <c r="E10" s="685"/>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A11" s="752" t="s">
+      <c r="A11" s="749" t="s">
         <v>1474</v>
       </c>
-      <c r="B11" s="580"/>
+      <c r="B11" s="583"/>
       <c r="C11" s="527" t="s">
         <v>1475</v>
       </c>
@@ -24556,23 +24556,23 @@
       <c r="E15" s="525"/>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A16" s="753">
+      <c r="A16" s="750">
         <v>1</v>
       </c>
-      <c r="B16" s="740"/>
+      <c r="B16" s="743"/>
       <c r="C16" s="531">
         <v>2</v>
       </c>
-      <c r="D16" s="744">
+      <c r="D16" s="747">
         <v>3</v>
       </c>
-      <c r="E16" s="683"/>
+      <c r="E16" s="685"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="745" t="s">
+      <c r="A17" s="748" t="s">
         <v>1474</v>
       </c>
-      <c r="B17" s="743"/>
+      <c r="B17" s="746"/>
       <c r="C17" s="532" t="s">
         <v>1475</v>
       </c>
@@ -26648,6 +26648,12 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="C3:E3"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="A11:B11"/>
     <mergeCell ref="A16:B16"/>
@@ -26660,12 +26666,6 @@
     <mergeCell ref="C7:E7"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="D10:E10"/>
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="C3:E3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
@@ -26694,110 +26694,110 @@
       <c r="B1" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="584" t="s">
+      <c r="C1" s="604" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="585"/>
-      <c r="E1" s="585"/>
-      <c r="F1" s="586"/>
+      <c r="D1" s="595"/>
+      <c r="E1" s="595"/>
+      <c r="F1" s="605"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1">
       <c r="A2" s="12"/>
       <c r="B2" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="587" t="s">
+      <c r="C2" s="606" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="588"/>
       <c r="E2" s="588"/>
-      <c r="F2" s="589"/>
+      <c r="F2" s="597"/>
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="14"/>
       <c r="B3" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="590" t="s">
+      <c r="C3" s="587" t="s">
         <v>109</v>
       </c>
       <c r="D3" s="588"/>
       <c r="E3" s="588"/>
-      <c r="F3" s="589"/>
+      <c r="F3" s="597"/>
     </row>
     <row r="4" spans="1:6" ht="105" customHeight="1">
       <c r="A4" s="17"/>
       <c r="B4" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="590" t="s">
+      <c r="C4" s="587" t="s">
         <v>111</v>
       </c>
       <c r="D4" s="588"/>
       <c r="E4" s="588"/>
-      <c r="F4" s="589"/>
+      <c r="F4" s="597"/>
     </row>
     <row r="5" spans="1:6" ht="15.75" customHeight="1">
       <c r="A5" s="12"/>
       <c r="B5" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="590" t="str">
+      <c r="C5" s="587" t="str">
         <f>'Reference Matrix'!$E6</f>
         <v>Summary Sheets</v>
       </c>
       <c r="D5" s="588"/>
       <c r="E5" s="588"/>
-      <c r="F5" s="589"/>
+      <c r="F5" s="597"/>
     </row>
     <row r="6" spans="1:6" ht="15.75" customHeight="1">
       <c r="A6" s="12"/>
       <c r="B6" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="590" t="str">
+      <c r="C6" s="587" t="str">
         <f>'Reference Matrix'!$F6</f>
         <v>1. PRC/MARINA licensure examination results</v>
       </c>
       <c r="D6" s="588"/>
       <c r="E6" s="588"/>
-      <c r="F6" s="589"/>
+      <c r="F6" s="597"/>
     </row>
     <row r="7" spans="1:6" ht="15.75" customHeight="1">
       <c r="A7" s="18"/>
       <c r="B7" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="591" t="s">
+      <c r="C7" s="598" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="592"/>
-      <c r="E7" s="592"/>
-      <c r="F7" s="593"/>
+      <c r="D7" s="599"/>
+      <c r="E7" s="599"/>
+      <c r="F7" s="586"/>
     </row>
     <row r="8" spans="1:6" ht="15.75" customHeight="1">
       <c r="A8" s="20"/>
       <c r="B8" s="20"/>
-      <c r="C8" s="590"/>
+      <c r="C8" s="587"/>
       <c r="D8" s="588"/>
       <c r="E8" s="588"/>
       <c r="F8" s="588"/>
     </row>
     <row r="9" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A9" s="601" t="s">
+      <c r="A9" s="589" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="576"/>
-      <c r="C9" s="576"/>
-      <c r="D9" s="576"/>
-      <c r="E9" s="576"/>
-      <c r="F9" s="577"/>
+      <c r="B9" s="579"/>
+      <c r="C9" s="579"/>
+      <c r="D9" s="579"/>
+      <c r="E9" s="579"/>
+      <c r="F9" s="580"/>
     </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A10" s="602">
+      <c r="A10" s="590">
         <v>1</v>
       </c>
-      <c r="B10" s="595"/>
+      <c r="B10" s="591"/>
       <c r="C10" s="21">
         <v>2</v>
       </c>
@@ -26812,10 +26812,10 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="40.5" customHeight="1">
-      <c r="A11" s="603" t="s">
+      <c r="A11" s="592" t="s">
         <v>117</v>
       </c>
-      <c r="B11" s="604"/>
+      <c r="B11" s="593"/>
       <c r="C11" s="24" t="s">
         <v>118</v>
       </c>
@@ -26830,13 +26830,13 @@
       </c>
     </row>
     <row r="12" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A12" s="605" t="s">
+      <c r="A12" s="594" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="585"/>
-      <c r="C12" s="585"/>
-      <c r="D12" s="585"/>
-      <c r="E12" s="595"/>
+      <c r="B12" s="595"/>
+      <c r="C12" s="595"/>
+      <c r="D12" s="595"/>
+      <c r="E12" s="591"/>
       <c r="F12" s="26"/>
     </row>
     <row r="13" spans="1:6" ht="15.75" customHeight="1">
@@ -26855,7 +26855,7 @@
       <c r="E13" s="30">
         <v>72</v>
       </c>
-      <c r="F13" s="606" t="s">
+      <c r="F13" s="596" t="s">
         <v>124</v>
       </c>
     </row>
@@ -26875,7 +26875,7 @@
       <c r="E14" s="30">
         <v>159</v>
       </c>
-      <c r="F14" s="589"/>
+      <c r="F14" s="597"/>
     </row>
     <row r="15" spans="1:6" ht="15.75" customHeight="1">
       <c r="A15" s="31">
@@ -26893,7 +26893,7 @@
       <c r="E15" s="30">
         <v>130</v>
       </c>
-      <c r="F15" s="589"/>
+      <c r="F15" s="597"/>
     </row>
     <row r="16" spans="1:6" ht="15.75" customHeight="1">
       <c r="A16" s="31">
@@ -26911,7 +26911,7 @@
       <c r="E16" s="30">
         <v>198</v>
       </c>
-      <c r="F16" s="589"/>
+      <c r="F16" s="597"/>
     </row>
     <row r="17" spans="1:6" ht="15.75" customHeight="1">
       <c r="A17" s="33">
@@ -26929,21 +26929,21 @@
       <c r="E17" s="36">
         <v>321</v>
       </c>
-      <c r="F17" s="580"/>
+      <c r="F17" s="583"/>
     </row>
     <row r="18" spans="1:6" ht="15.75" customHeight="1">
       <c r="A18" s="20"/>
       <c r="B18" s="20"/>
-      <c r="C18" s="590"/>
+      <c r="C18" s="587"/>
       <c r="D18" s="588"/>
       <c r="E18" s="588"/>
       <c r="F18" s="588"/>
     </row>
     <row r="19" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A19" s="594">
+      <c r="A19" s="600">
         <v>1</v>
       </c>
-      <c r="B19" s="595"/>
+      <c r="B19" s="591"/>
       <c r="C19" s="37">
         <v>2</v>
       </c>
@@ -26958,10 +26958,10 @@
       </c>
     </row>
     <row r="20" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A20" s="596" t="s">
+      <c r="A20" s="601" t="s">
         <v>117</v>
       </c>
-      <c r="B20" s="597"/>
+      <c r="B20" s="602"/>
       <c r="C20" s="40" t="s">
         <v>129</v>
       </c>
@@ -26976,13 +26976,13 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="16.5" customHeight="1">
-      <c r="A21" s="598" t="s">
+      <c r="A21" s="603" t="s">
         <v>130</v>
       </c>
-      <c r="B21" s="585"/>
-      <c r="C21" s="585"/>
-      <c r="D21" s="585"/>
-      <c r="E21" s="595"/>
+      <c r="B21" s="595"/>
+      <c r="C21" s="595"/>
+      <c r="D21" s="595"/>
+      <c r="E21" s="591"/>
       <c r="F21" s="42"/>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1">
@@ -27130,13 +27130,13 @@
       <c r="F29" s="47"/>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A30" s="599" t="s">
+      <c r="A30" s="584" t="s">
         <v>145</v>
       </c>
-      <c r="B30" s="582"/>
-      <c r="C30" s="582"/>
-      <c r="D30" s="582"/>
-      <c r="E30" s="583"/>
+      <c r="B30" s="576"/>
+      <c r="C30" s="576"/>
+      <c r="D30" s="576"/>
+      <c r="E30" s="577"/>
       <c r="F30" s="47"/>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1">
@@ -27158,13 +27158,13 @@
       <c r="F31" s="47"/>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1">
-      <c r="A32" s="599" t="s">
+      <c r="A32" s="584" t="s">
         <v>148</v>
       </c>
-      <c r="B32" s="582"/>
-      <c r="C32" s="582"/>
-      <c r="D32" s="582"/>
-      <c r="E32" s="583"/>
+      <c r="B32" s="576"/>
+      <c r="C32" s="576"/>
+      <c r="D32" s="576"/>
+      <c r="E32" s="577"/>
       <c r="F32" s="47"/>
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1">
@@ -27215,11 +27215,11 @@
       <c r="C36" s="63" t="s">
         <v>152</v>
       </c>
-      <c r="D36" s="600">
+      <c r="D36" s="585">
         <f>E35/D35</f>
         <v>0.7350427350427351</v>
       </c>
-      <c r="E36" s="593"/>
+      <c r="E36" s="586"/>
       <c r="F36" s="61"/>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1">
@@ -28299,6 +28299,16 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A21:E21"/>
     <mergeCell ref="A30:E30"/>
     <mergeCell ref="A32:E32"/>
     <mergeCell ref="D36:E36"/>
@@ -28309,16 +28319,6 @@
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="F13:F17"/>
     <mergeCell ref="C18:F18"/>
-    <mergeCell ref="C6:F6"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A21:E21"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C5:F5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -28348,21 +28348,21 @@
       <c r="A1" s="78" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="584" t="s">
+      <c r="B1" s="604" t="s">
         <v>160</v>
       </c>
-      <c r="C1" s="585"/>
-      <c r="D1" s="585"/>
-      <c r="E1" s="585"/>
-      <c r="F1" s="585"/>
-      <c r="G1" s="585"/>
-      <c r="H1" s="586"/>
+      <c r="C1" s="595"/>
+      <c r="D1" s="595"/>
+      <c r="E1" s="595"/>
+      <c r="F1" s="595"/>
+      <c r="G1" s="595"/>
+      <c r="H1" s="605"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="79" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="611" t="s">
+      <c r="B2" s="646" t="s">
         <v>8</v>
       </c>
       <c r="C2" s="588"/>
@@ -28370,13 +28370,13 @@
       <c r="E2" s="588"/>
       <c r="F2" s="588"/>
       <c r="G2" s="588"/>
-      <c r="H2" s="589"/>
+      <c r="H2" s="597"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="79" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="612" t="s">
+      <c r="B3" s="647" t="s">
         <v>161</v>
       </c>
       <c r="C3" s="588"/>
@@ -28384,13 +28384,13 @@
       <c r="E3" s="588"/>
       <c r="F3" s="588"/>
       <c r="G3" s="588"/>
-      <c r="H3" s="589"/>
+      <c r="H3" s="597"/>
     </row>
     <row r="4" spans="1:8" ht="78.75" customHeight="1">
       <c r="A4" s="79" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="613" t="s">
+      <c r="B4" s="648" t="s">
         <v>162</v>
       </c>
       <c r="C4" s="588"/>
@@ -28398,13 +28398,13 @@
       <c r="E4" s="588"/>
       <c r="F4" s="588"/>
       <c r="G4" s="588"/>
-      <c r="H4" s="589"/>
+      <c r="H4" s="597"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="79" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="612" t="str">
+      <c r="B5" s="647" t="str">
         <f>'Reference Matrix'!$E7</f>
         <v>Summary Sheets</v>
       </c>
@@ -28413,13 +28413,13 @@
       <c r="E5" s="588"/>
       <c r="F5" s="588"/>
       <c r="G5" s="588"/>
-      <c r="H5" s="589"/>
+      <c r="H5" s="597"/>
     </row>
     <row r="6" spans="1:8" ht="39.75" customHeight="1">
       <c r="A6" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="590" t="str">
+      <c r="B6" s="587" t="str">
         <f>'Reference Matrix'!$F7</f>
         <v>1. Graduate tracer study
 2. Result of survey of employed from the graduates in the 1st semester of FY 2021-2022, certified by the Registrar
@@ -28430,21 +28430,21 @@
       <c r="E6" s="588"/>
       <c r="F6" s="588"/>
       <c r="G6" s="588"/>
-      <c r="H6" s="589"/>
+      <c r="H6" s="597"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="591" t="s">
+      <c r="B7" s="598" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="592"/>
-      <c r="D7" s="592"/>
-      <c r="E7" s="592"/>
-      <c r="F7" s="592"/>
-      <c r="G7" s="592"/>
-      <c r="H7" s="593"/>
+      <c r="C7" s="599"/>
+      <c r="D7" s="599"/>
+      <c r="E7" s="599"/>
+      <c r="F7" s="599"/>
+      <c r="G7" s="599"/>
+      <c r="H7" s="586"/>
     </row>
     <row r="8" spans="1:8" ht="12.75" customHeight="1">
       <c r="A8" s="80"/>
@@ -28457,30 +28457,30 @@
       <c r="H8" s="64"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A9" s="601" t="s">
+      <c r="A9" s="589" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="576"/>
-      <c r="C9" s="576"/>
-      <c r="D9" s="576"/>
-      <c r="E9" s="576"/>
-      <c r="F9" s="576"/>
-      <c r="G9" s="576"/>
-      <c r="H9" s="577"/>
+      <c r="B9" s="579"/>
+      <c r="C9" s="579"/>
+      <c r="D9" s="579"/>
+      <c r="E9" s="579"/>
+      <c r="F9" s="579"/>
+      <c r="G9" s="579"/>
+      <c r="H9" s="580"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A10" s="623">
+      <c r="A10" s="636">
         <v>1</v>
       </c>
-      <c r="B10" s="583"/>
+      <c r="B10" s="577"/>
       <c r="C10" s="82">
         <v>2</v>
       </c>
-      <c r="D10" s="624">
+      <c r="D10" s="637">
         <v>3</v>
       </c>
-      <c r="E10" s="582"/>
-      <c r="F10" s="583"/>
+      <c r="E10" s="576"/>
+      <c r="F10" s="577"/>
       <c r="G10" s="82">
         <v>4</v>
       </c>
@@ -28489,18 +28489,18 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A11" s="625" t="s">
+      <c r="A11" s="638" t="s">
         <v>163</v>
       </c>
-      <c r="B11" s="597"/>
+      <c r="B11" s="602"/>
       <c r="C11" s="84" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="626" t="s">
+      <c r="D11" s="639" t="s">
         <v>165</v>
       </c>
-      <c r="E11" s="622"/>
-      <c r="F11" s="597"/>
+      <c r="E11" s="635"/>
+      <c r="F11" s="602"/>
       <c r="G11" s="84" t="s">
         <v>166</v>
       </c>
@@ -28509,16 +28509,16 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A12" s="627" t="s">
+      <c r="A12" s="640" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="628"/>
-      <c r="C12" s="628"/>
-      <c r="D12" s="628"/>
-      <c r="E12" s="628"/>
-      <c r="F12" s="628"/>
-      <c r="G12" s="629"/>
-      <c r="H12" s="630" t="s">
+      <c r="B12" s="641"/>
+      <c r="C12" s="641"/>
+      <c r="D12" s="641"/>
+      <c r="E12" s="641"/>
+      <c r="F12" s="641"/>
+      <c r="G12" s="642"/>
+      <c r="H12" s="643" t="s">
         <v>167</v>
       </c>
     </row>
@@ -28532,15 +28532,15 @@
       <c r="C13" s="87" t="s">
         <v>168</v>
       </c>
-      <c r="D13" s="608" t="s">
+      <c r="D13" s="649" t="s">
         <v>169</v>
       </c>
-      <c r="E13" s="582"/>
-      <c r="F13" s="583"/>
+      <c r="E13" s="576"/>
+      <c r="F13" s="577"/>
       <c r="G13" s="88" t="s">
         <v>170</v>
       </c>
-      <c r="H13" s="610"/>
+      <c r="H13" s="644"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="85" t="s">
@@ -28552,13 +28552,13 @@
       <c r="C14" s="87" t="s">
         <v>168</v>
       </c>
-      <c r="D14" s="608" t="s">
+      <c r="D14" s="649" t="s">
         <v>171</v>
       </c>
-      <c r="E14" s="582"/>
-      <c r="F14" s="583"/>
+      <c r="E14" s="576"/>
+      <c r="F14" s="577"/>
       <c r="G14" s="88"/>
-      <c r="H14" s="610"/>
+      <c r="H14" s="644"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="85" t="s">
@@ -28570,13 +28570,13 @@
       <c r="C15" s="87" t="s">
         <v>168</v>
       </c>
-      <c r="D15" s="608" t="s">
+      <c r="D15" s="649" t="s">
         <v>172</v>
       </c>
-      <c r="E15" s="582"/>
-      <c r="F15" s="583"/>
+      <c r="E15" s="576"/>
+      <c r="F15" s="577"/>
       <c r="G15" s="88"/>
-      <c r="H15" s="610"/>
+      <c r="H15" s="644"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="85" t="s">
@@ -28588,15 +28588,15 @@
       <c r="C16" s="87" t="s">
         <v>168</v>
       </c>
-      <c r="D16" s="608" t="s">
+      <c r="D16" s="649" t="s">
         <v>169</v>
       </c>
-      <c r="E16" s="582"/>
-      <c r="F16" s="583"/>
+      <c r="E16" s="576"/>
+      <c r="F16" s="577"/>
       <c r="G16" s="88" t="s">
         <v>173</v>
       </c>
-      <c r="H16" s="610"/>
+      <c r="H16" s="644"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="85" t="s">
@@ -28608,22 +28608,22 @@
       <c r="C17" s="87" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="608" t="s">
+      <c r="D17" s="649" t="s">
         <v>169</v>
       </c>
-      <c r="E17" s="582"/>
-      <c r="F17" s="583"/>
+      <c r="E17" s="576"/>
+      <c r="F17" s="577"/>
       <c r="G17" s="88" t="s">
         <v>174</v>
       </c>
-      <c r="H17" s="610"/>
+      <c r="H17" s="644"/>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A18" s="614" t="s">
+      <c r="A18" s="629" t="s">
         <v>175</v>
       </c>
-      <c r="B18" s="604"/>
-      <c r="C18" s="617">
+      <c r="B18" s="593"/>
+      <c r="C18" s="630">
         <f>COUNTIFS($A13:$A17,"*",$C13:$C17,"*",$D13:$D17,"*")</f>
         <v>5</v>
       </c>
@@ -28637,12 +28637,12 @@
         <v>178</v>
       </c>
       <c r="G18" s="91"/>
-      <c r="H18" s="610"/>
+      <c r="H18" s="644"/>
     </row>
     <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" s="615"/>
-      <c r="B19" s="616"/>
-      <c r="C19" s="618"/>
+      <c r="A19" s="609"/>
+      <c r="B19" s="610"/>
+      <c r="C19" s="631"/>
       <c r="D19" s="92">
         <f>COUNTIFS($A13:$A17,"*",$C13:$C17,"*",$D13:$D17, "Employed")</f>
         <v>3</v>
@@ -28656,7 +28656,7 @@
         <v>1</v>
       </c>
       <c r="G19" s="93"/>
-      <c r="H19" s="631"/>
+      <c r="H19" s="645"/>
     </row>
     <row r="20" spans="1:8" ht="13.5" customHeight="1">
       <c r="A20" s="77"/>
@@ -28669,18 +28669,18 @@
       <c r="H20" s="77"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A21" s="619">
+      <c r="A21" s="632">
         <v>1</v>
       </c>
-      <c r="B21" s="595"/>
+      <c r="B21" s="591"/>
       <c r="C21" s="94">
         <v>2</v>
       </c>
-      <c r="D21" s="620">
+      <c r="D21" s="633">
         <v>3</v>
       </c>
-      <c r="E21" s="585"/>
-      <c r="F21" s="595"/>
+      <c r="E21" s="595"/>
+      <c r="F21" s="591"/>
       <c r="G21" s="95">
         <v>4</v>
       </c>
@@ -28689,18 +28689,18 @@
       </c>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A22" s="596" t="s">
+      <c r="A22" s="601" t="s">
         <v>163</v>
       </c>
-      <c r="B22" s="597"/>
+      <c r="B22" s="602"/>
       <c r="C22" s="97" t="s">
         <v>164</v>
       </c>
-      <c r="D22" s="621" t="s">
+      <c r="D22" s="634" t="s">
         <v>179</v>
       </c>
-      <c r="E22" s="622"/>
-      <c r="F22" s="597"/>
+      <c r="E22" s="635"/>
+      <c r="F22" s="602"/>
       <c r="G22" s="97" t="s">
         <v>166</v>
       </c>
@@ -28709,16 +28709,16 @@
       </c>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A23" s="598" t="s">
+      <c r="A23" s="603" t="s">
         <v>130</v>
       </c>
-      <c r="B23" s="585"/>
-      <c r="C23" s="585"/>
-      <c r="D23" s="585"/>
-      <c r="E23" s="585"/>
-      <c r="F23" s="585"/>
-      <c r="G23" s="595"/>
-      <c r="H23" s="609"/>
+      <c r="B23" s="595"/>
+      <c r="C23" s="595"/>
+      <c r="D23" s="595"/>
+      <c r="E23" s="595"/>
+      <c r="F23" s="595"/>
+      <c r="G23" s="591"/>
+      <c r="H23" s="650"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="98" t="s">
@@ -28733,12 +28733,12 @@
       <c r="D24" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E24" s="582"/>
-      <c r="F24" s="583"/>
+      <c r="E24" s="576"/>
+      <c r="F24" s="577"/>
       <c r="G24" s="101" t="s">
         <v>181</v>
       </c>
-      <c r="H24" s="610"/>
+      <c r="H24" s="644"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="98" t="s">
@@ -28753,10 +28753,10 @@
       <c r="D25" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E25" s="582"/>
-      <c r="F25" s="583"/>
+      <c r="E25" s="576"/>
+      <c r="F25" s="577"/>
       <c r="G25" s="101"/>
-      <c r="H25" s="610"/>
+      <c r="H25" s="644"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="98" t="s">
@@ -28771,12 +28771,12 @@
       <c r="D26" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E26" s="582"/>
-      <c r="F26" s="583"/>
+      <c r="E26" s="576"/>
+      <c r="F26" s="577"/>
       <c r="G26" s="102" t="s">
         <v>184</v>
       </c>
-      <c r="H26" s="610"/>
+      <c r="H26" s="644"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="98" t="s">
@@ -28791,12 +28791,12 @@
       <c r="D27" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E27" s="582"/>
-      <c r="F27" s="583"/>
+      <c r="E27" s="576"/>
+      <c r="F27" s="577"/>
       <c r="G27" s="102" t="s">
         <v>186</v>
       </c>
-      <c r="H27" s="610"/>
+      <c r="H27" s="644"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="98" t="s">
@@ -28811,10 +28811,10 @@
       <c r="D28" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E28" s="582"/>
-      <c r="F28" s="583"/>
+      <c r="E28" s="576"/>
+      <c r="F28" s="577"/>
       <c r="G28" s="101"/>
-      <c r="H28" s="610"/>
+      <c r="H28" s="644"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" s="98" t="s">
@@ -28829,10 +28829,10 @@
       <c r="D29" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E29" s="582"/>
-      <c r="F29" s="583"/>
+      <c r="E29" s="576"/>
+      <c r="F29" s="577"/>
       <c r="G29" s="101"/>
-      <c r="H29" s="610"/>
+      <c r="H29" s="644"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="98" t="s">
@@ -28847,10 +28847,10 @@
       <c r="D30" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E30" s="582"/>
-      <c r="F30" s="583"/>
+      <c r="E30" s="576"/>
+      <c r="F30" s="577"/>
       <c r="G30" s="101"/>
-      <c r="H30" s="610"/>
+      <c r="H30" s="644"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" s="98" t="s">
@@ -28865,10 +28865,10 @@
       <c r="D31" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E31" s="582"/>
-      <c r="F31" s="583"/>
+      <c r="E31" s="576"/>
+      <c r="F31" s="577"/>
       <c r="G31" s="101"/>
-      <c r="H31" s="610"/>
+      <c r="H31" s="644"/>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1">
       <c r="A32" s="98" t="s">
@@ -28883,10 +28883,10 @@
       <c r="D32" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E32" s="582"/>
-      <c r="F32" s="583"/>
+      <c r="E32" s="576"/>
+      <c r="F32" s="577"/>
       <c r="G32" s="105"/>
-      <c r="H32" s="610"/>
+      <c r="H32" s="644"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1">
       <c r="A33" s="98" t="s">
@@ -28901,12 +28901,12 @@
       <c r="D33" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E33" s="582"/>
-      <c r="F33" s="583"/>
+      <c r="E33" s="576"/>
+      <c r="F33" s="577"/>
       <c r="G33" s="107" t="s">
         <v>195</v>
       </c>
-      <c r="H33" s="610"/>
+      <c r="H33" s="644"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1">
       <c r="A34" s="98" t="s">
@@ -28921,10 +28921,10 @@
       <c r="D34" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E34" s="582"/>
-      <c r="F34" s="583"/>
+      <c r="E34" s="576"/>
+      <c r="F34" s="577"/>
       <c r="G34" s="105"/>
-      <c r="H34" s="610"/>
+      <c r="H34" s="644"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1">
       <c r="A35" s="98" t="s">
@@ -28939,10 +28939,10 @@
       <c r="D35" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E35" s="582"/>
-      <c r="F35" s="583"/>
+      <c r="E35" s="576"/>
+      <c r="F35" s="577"/>
       <c r="G35" s="105"/>
-      <c r="H35" s="610"/>
+      <c r="H35" s="644"/>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1">
       <c r="A36" s="98" t="s">
@@ -28957,12 +28957,12 @@
       <c r="D36" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E36" s="582"/>
-      <c r="F36" s="583"/>
+      <c r="E36" s="576"/>
+      <c r="F36" s="577"/>
       <c r="G36" s="108" t="s">
         <v>200</v>
       </c>
-      <c r="H36" s="610"/>
+      <c r="H36" s="644"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1">
       <c r="A37" s="98" t="s">
@@ -28977,10 +28977,10 @@
       <c r="D37" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E37" s="582"/>
-      <c r="F37" s="583"/>
+      <c r="E37" s="576"/>
+      <c r="F37" s="577"/>
       <c r="G37" s="105"/>
-      <c r="H37" s="610"/>
+      <c r="H37" s="644"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1">
       <c r="A38" s="98" t="s">
@@ -28995,12 +28995,12 @@
       <c r="D38" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E38" s="582"/>
-      <c r="F38" s="583"/>
+      <c r="E38" s="576"/>
+      <c r="F38" s="577"/>
       <c r="G38" s="108" t="s">
         <v>204</v>
       </c>
-      <c r="H38" s="610"/>
+      <c r="H38" s="644"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1">
       <c r="A39" s="98" t="s">
@@ -29015,10 +29015,10 @@
       <c r="D39" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E39" s="582"/>
-      <c r="F39" s="583"/>
+      <c r="E39" s="576"/>
+      <c r="F39" s="577"/>
       <c r="G39" s="105"/>
-      <c r="H39" s="610"/>
+      <c r="H39" s="644"/>
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1">
       <c r="A40" s="98" t="s">
@@ -29033,12 +29033,12 @@
       <c r="D40" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E40" s="582"/>
-      <c r="F40" s="583"/>
+      <c r="E40" s="576"/>
+      <c r="F40" s="577"/>
       <c r="G40" s="108" t="s">
         <v>208</v>
       </c>
-      <c r="H40" s="610"/>
+      <c r="H40" s="644"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1">
       <c r="A41" s="98" t="s">
@@ -29053,12 +29053,12 @@
       <c r="D41" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E41" s="582"/>
-      <c r="F41" s="583"/>
+      <c r="E41" s="576"/>
+      <c r="F41" s="577"/>
       <c r="G41" s="108" t="s">
         <v>210</v>
       </c>
-      <c r="H41" s="610"/>
+      <c r="H41" s="644"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1">
       <c r="A42" s="98" t="s">
@@ -29073,12 +29073,12 @@
       <c r="D42" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E42" s="582"/>
-      <c r="F42" s="583"/>
+      <c r="E42" s="576"/>
+      <c r="F42" s="577"/>
       <c r="G42" s="108" t="s">
         <v>212</v>
       </c>
-      <c r="H42" s="610"/>
+      <c r="H42" s="644"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1">
       <c r="A43" s="98" t="s">
@@ -29093,10 +29093,10 @@
       <c r="D43" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E43" s="582"/>
-      <c r="F43" s="583"/>
+      <c r="E43" s="576"/>
+      <c r="F43" s="577"/>
       <c r="G43" s="105"/>
-      <c r="H43" s="610"/>
+      <c r="H43" s="644"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" customHeight="1">
       <c r="A44" s="98" t="s">
@@ -29111,10 +29111,10 @@
       <c r="D44" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E44" s="582"/>
-      <c r="F44" s="583"/>
+      <c r="E44" s="576"/>
+      <c r="F44" s="577"/>
       <c r="G44" s="109"/>
-      <c r="H44" s="610"/>
+      <c r="H44" s="644"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" customHeight="1">
       <c r="A45" s="98" t="s">
@@ -29129,12 +29129,12 @@
       <c r="D45" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E45" s="582"/>
-      <c r="F45" s="583"/>
+      <c r="E45" s="576"/>
+      <c r="F45" s="577"/>
       <c r="G45" s="108" t="s">
         <v>216</v>
       </c>
-      <c r="H45" s="610"/>
+      <c r="H45" s="644"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1">
       <c r="A46" s="98" t="s">
@@ -29149,12 +29149,12 @@
       <c r="D46" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E46" s="582"/>
-      <c r="F46" s="583"/>
+      <c r="E46" s="576"/>
+      <c r="F46" s="577"/>
       <c r="G46" s="108" t="s">
         <v>219</v>
       </c>
-      <c r="H46" s="610"/>
+      <c r="H46" s="644"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1">
       <c r="A47" s="98" t="s">
@@ -29169,12 +29169,12 @@
       <c r="D47" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E47" s="582"/>
-      <c r="F47" s="583"/>
+      <c r="E47" s="576"/>
+      <c r="F47" s="577"/>
       <c r="G47" s="108" t="s">
         <v>221</v>
       </c>
-      <c r="H47" s="610"/>
+      <c r="H47" s="644"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1">
       <c r="A48" s="98" t="s">
@@ -29186,13 +29186,13 @@
       <c r="C48" s="106" t="s">
         <v>222</v>
       </c>
-      <c r="D48" s="632" t="s">
+      <c r="D48" s="628" t="s">
         <v>172</v>
       </c>
-      <c r="E48" s="582"/>
-      <c r="F48" s="583"/>
+      <c r="E48" s="576"/>
+      <c r="F48" s="577"/>
       <c r="G48" s="110"/>
-      <c r="H48" s="610"/>
+      <c r="H48" s="644"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" customHeight="1">
       <c r="A49" s="98" t="s">
@@ -29207,12 +29207,12 @@
       <c r="D49" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E49" s="582"/>
-      <c r="F49" s="583"/>
+      <c r="E49" s="576"/>
+      <c r="F49" s="577"/>
       <c r="G49" s="108" t="s">
         <v>224</v>
       </c>
-      <c r="H49" s="610"/>
+      <c r="H49" s="644"/>
     </row>
     <row r="50" spans="1:8" ht="15.75" customHeight="1">
       <c r="A50" s="98" t="s">
@@ -29227,10 +29227,10 @@
       <c r="D50" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E50" s="582"/>
-      <c r="F50" s="583"/>
+      <c r="E50" s="576"/>
+      <c r="F50" s="577"/>
       <c r="G50" s="109"/>
-      <c r="H50" s="610"/>
+      <c r="H50" s="644"/>
     </row>
     <row r="51" spans="1:8" ht="15.75" customHeight="1">
       <c r="A51" s="98" t="s">
@@ -29245,12 +29245,12 @@
       <c r="D51" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E51" s="582"/>
-      <c r="F51" s="583"/>
+      <c r="E51" s="576"/>
+      <c r="F51" s="577"/>
       <c r="G51" s="107" t="s">
         <v>227</v>
       </c>
-      <c r="H51" s="610"/>
+      <c r="H51" s="644"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" customHeight="1">
       <c r="A52" s="98" t="s">
@@ -29265,12 +29265,12 @@
       <c r="D52" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E52" s="582"/>
-      <c r="F52" s="583"/>
+      <c r="E52" s="576"/>
+      <c r="F52" s="577"/>
       <c r="G52" s="108" t="s">
         <v>229</v>
       </c>
-      <c r="H52" s="610"/>
+      <c r="H52" s="644"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1">
       <c r="A53" s="98" t="s">
@@ -29285,10 +29285,10 @@
       <c r="D53" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E53" s="582"/>
-      <c r="F53" s="583"/>
+      <c r="E53" s="576"/>
+      <c r="F53" s="577"/>
       <c r="G53" s="105"/>
-      <c r="H53" s="610"/>
+      <c r="H53" s="644"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" customHeight="1">
       <c r="A54" s="98" t="s">
@@ -29303,12 +29303,12 @@
       <c r="D54" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E54" s="582"/>
-      <c r="F54" s="583"/>
+      <c r="E54" s="576"/>
+      <c r="F54" s="577"/>
       <c r="G54" s="108" t="s">
         <v>233</v>
       </c>
-      <c r="H54" s="610"/>
+      <c r="H54" s="644"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" customHeight="1">
       <c r="A55" s="98" t="s">
@@ -29323,12 +29323,12 @@
       <c r="D55" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E55" s="582"/>
-      <c r="F55" s="583"/>
+      <c r="E55" s="576"/>
+      <c r="F55" s="577"/>
       <c r="G55" s="108" t="s">
         <v>235</v>
       </c>
-      <c r="H55" s="610"/>
+      <c r="H55" s="644"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" customHeight="1">
       <c r="A56" s="98" t="s">
@@ -29343,10 +29343,10 @@
       <c r="D56" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E56" s="582"/>
-      <c r="F56" s="583"/>
+      <c r="E56" s="576"/>
+      <c r="F56" s="577"/>
       <c r="G56" s="105"/>
-      <c r="H56" s="610"/>
+      <c r="H56" s="644"/>
     </row>
     <row r="57" spans="1:8" ht="15.75" customHeight="1">
       <c r="A57" s="98" t="s">
@@ -29361,12 +29361,12 @@
       <c r="D57" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="582"/>
-      <c r="F57" s="583"/>
+      <c r="E57" s="576"/>
+      <c r="F57" s="577"/>
       <c r="G57" s="108" t="s">
         <v>238</v>
       </c>
-      <c r="H57" s="610"/>
+      <c r="H57" s="644"/>
     </row>
     <row r="58" spans="1:8" ht="15.75" customHeight="1">
       <c r="A58" s="98" t="s">
@@ -29381,12 +29381,12 @@
       <c r="D58" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E58" s="582"/>
-      <c r="F58" s="583"/>
+      <c r="E58" s="576"/>
+      <c r="F58" s="577"/>
       <c r="G58" s="108" t="s">
         <v>240</v>
       </c>
-      <c r="H58" s="610"/>
+      <c r="H58" s="644"/>
     </row>
     <row r="59" spans="1:8" ht="15.75" customHeight="1">
       <c r="A59" s="98" t="s">
@@ -29401,10 +29401,10 @@
       <c r="D59" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E59" s="582"/>
-      <c r="F59" s="583"/>
+      <c r="E59" s="576"/>
+      <c r="F59" s="577"/>
       <c r="G59" s="105"/>
-      <c r="H59" s="610"/>
+      <c r="H59" s="644"/>
     </row>
     <row r="60" spans="1:8" ht="15.75" customHeight="1">
       <c r="A60" s="98" t="s">
@@ -29419,12 +29419,12 @@
       <c r="D60" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E60" s="582"/>
-      <c r="F60" s="583"/>
+      <c r="E60" s="576"/>
+      <c r="F60" s="577"/>
       <c r="G60" s="107" t="s">
         <v>243</v>
       </c>
-      <c r="H60" s="610"/>
+      <c r="H60" s="644"/>
     </row>
     <row r="61" spans="1:8" ht="15.75" customHeight="1">
       <c r="A61" s="98" t="s">
@@ -29439,10 +29439,10 @@
       <c r="D61" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E61" s="582"/>
-      <c r="F61" s="583"/>
+      <c r="E61" s="576"/>
+      <c r="F61" s="577"/>
       <c r="G61" s="105"/>
-      <c r="H61" s="610"/>
+      <c r="H61" s="644"/>
     </row>
     <row r="62" spans="1:8" ht="15.75" customHeight="1">
       <c r="A62" s="98" t="s">
@@ -29457,10 +29457,10 @@
       <c r="D62" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E62" s="582"/>
-      <c r="F62" s="583"/>
+      <c r="E62" s="576"/>
+      <c r="F62" s="577"/>
       <c r="G62" s="105"/>
-      <c r="H62" s="610"/>
+      <c r="H62" s="644"/>
     </row>
     <row r="63" spans="1:8" ht="15.75" customHeight="1">
       <c r="A63" s="98" t="s">
@@ -29475,10 +29475,10 @@
       <c r="D63" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="582"/>
-      <c r="F63" s="583"/>
+      <c r="E63" s="576"/>
+      <c r="F63" s="577"/>
       <c r="G63" s="105"/>
-      <c r="H63" s="610"/>
+      <c r="H63" s="644"/>
     </row>
     <row r="64" spans="1:8" ht="15.75" customHeight="1">
       <c r="A64" s="98" t="s">
@@ -29493,12 +29493,12 @@
       <c r="D64" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E64" s="582"/>
-      <c r="F64" s="583"/>
+      <c r="E64" s="576"/>
+      <c r="F64" s="577"/>
       <c r="G64" s="108" t="s">
         <v>248</v>
       </c>
-      <c r="H64" s="610"/>
+      <c r="H64" s="644"/>
     </row>
     <row r="65" spans="1:8" ht="15.75" customHeight="1">
       <c r="A65" s="98" t="s">
@@ -29513,10 +29513,10 @@
       <c r="D65" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E65" s="582"/>
-      <c r="F65" s="583"/>
+      <c r="E65" s="576"/>
+      <c r="F65" s="577"/>
       <c r="G65" s="105"/>
-      <c r="H65" s="610"/>
+      <c r="H65" s="644"/>
     </row>
     <row r="66" spans="1:8" ht="15.75" customHeight="1">
       <c r="A66" s="98" t="s">
@@ -29531,12 +29531,12 @@
       <c r="D66" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E66" s="582"/>
-      <c r="F66" s="583"/>
+      <c r="E66" s="576"/>
+      <c r="F66" s="577"/>
       <c r="G66" s="108" t="s">
         <v>251</v>
       </c>
-      <c r="H66" s="610"/>
+      <c r="H66" s="644"/>
     </row>
     <row r="67" spans="1:8" ht="15.75" customHeight="1">
       <c r="A67" s="98" t="s">
@@ -29551,12 +29551,12 @@
       <c r="D67" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E67" s="582"/>
-      <c r="F67" s="583"/>
+      <c r="E67" s="576"/>
+      <c r="F67" s="577"/>
       <c r="G67" s="108" t="s">
         <v>253</v>
       </c>
-      <c r="H67" s="610"/>
+      <c r="H67" s="644"/>
     </row>
     <row r="68" spans="1:8" ht="15.75" customHeight="1">
       <c r="A68" s="98" t="s">
@@ -29571,10 +29571,10 @@
       <c r="D68" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E68" s="582"/>
-      <c r="F68" s="583"/>
+      <c r="E68" s="576"/>
+      <c r="F68" s="577"/>
       <c r="G68" s="105"/>
-      <c r="H68" s="610"/>
+      <c r="H68" s="644"/>
     </row>
     <row r="69" spans="1:8" ht="15.75" customHeight="1">
       <c r="A69" s="98" t="s">
@@ -29589,12 +29589,12 @@
       <c r="D69" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E69" s="582"/>
-      <c r="F69" s="583"/>
+      <c r="E69" s="576"/>
+      <c r="F69" s="577"/>
       <c r="G69" s="108" t="s">
         <v>256</v>
       </c>
-      <c r="H69" s="610"/>
+      <c r="H69" s="644"/>
     </row>
     <row r="70" spans="1:8" ht="15.75" customHeight="1">
       <c r="A70" s="98" t="s">
@@ -29609,10 +29609,10 @@
       <c r="D70" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E70" s="582"/>
-      <c r="F70" s="583"/>
+      <c r="E70" s="576"/>
+      <c r="F70" s="577"/>
       <c r="G70" s="105"/>
-      <c r="H70" s="610"/>
+      <c r="H70" s="644"/>
     </row>
     <row r="71" spans="1:8" ht="15.75" customHeight="1">
       <c r="A71" s="98" t="s">
@@ -29627,10 +29627,10 @@
       <c r="D71" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E71" s="582"/>
-      <c r="F71" s="583"/>
+      <c r="E71" s="576"/>
+      <c r="F71" s="577"/>
       <c r="G71" s="105"/>
-      <c r="H71" s="610"/>
+      <c r="H71" s="644"/>
     </row>
     <row r="72" spans="1:8" ht="15.75" customHeight="1">
       <c r="A72" s="98" t="s">
@@ -29645,12 +29645,12 @@
       <c r="D72" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E72" s="582"/>
-      <c r="F72" s="583"/>
+      <c r="E72" s="576"/>
+      <c r="F72" s="577"/>
       <c r="G72" s="108" t="s">
         <v>260</v>
       </c>
-      <c r="H72" s="610"/>
+      <c r="H72" s="644"/>
     </row>
     <row r="73" spans="1:8" ht="15.75" customHeight="1">
       <c r="A73" s="98" t="s">
@@ -29665,10 +29665,10 @@
       <c r="D73" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E73" s="582"/>
-      <c r="F73" s="583"/>
+      <c r="E73" s="576"/>
+      <c r="F73" s="577"/>
       <c r="G73" s="112"/>
-      <c r="H73" s="610"/>
+      <c r="H73" s="644"/>
     </row>
     <row r="74" spans="1:8" ht="15.75" customHeight="1">
       <c r="A74" s="98" t="s">
@@ -29683,12 +29683,12 @@
       <c r="D74" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E74" s="582"/>
-      <c r="F74" s="583"/>
+      <c r="E74" s="576"/>
+      <c r="F74" s="577"/>
       <c r="G74" s="108" t="s">
         <v>263</v>
       </c>
-      <c r="H74" s="610"/>
+      <c r="H74" s="644"/>
     </row>
     <row r="75" spans="1:8" ht="15.75" customHeight="1">
       <c r="A75" s="98" t="s">
@@ -29703,12 +29703,12 @@
       <c r="D75" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E75" s="582"/>
-      <c r="F75" s="583"/>
+      <c r="E75" s="576"/>
+      <c r="F75" s="577"/>
       <c r="G75" s="108" t="s">
         <v>265</v>
       </c>
-      <c r="H75" s="610"/>
+      <c r="H75" s="644"/>
     </row>
     <row r="76" spans="1:8" ht="15.75" customHeight="1">
       <c r="A76" s="98" t="s">
@@ -29723,12 +29723,12 @@
       <c r="D76" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E76" s="582"/>
-      <c r="F76" s="583"/>
+      <c r="E76" s="576"/>
+      <c r="F76" s="577"/>
       <c r="G76" s="108" t="s">
         <v>268</v>
       </c>
-      <c r="H76" s="610"/>
+      <c r="H76" s="644"/>
     </row>
     <row r="77" spans="1:8" ht="15.75" customHeight="1">
       <c r="A77" s="98" t="s">
@@ -29743,12 +29743,12 @@
       <c r="D77" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E77" s="582"/>
-      <c r="F77" s="583"/>
+      <c r="E77" s="576"/>
+      <c r="F77" s="577"/>
       <c r="G77" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="H77" s="610"/>
+      <c r="H77" s="644"/>
     </row>
     <row r="78" spans="1:8" ht="15.75" customHeight="1">
       <c r="A78" s="98" t="s">
@@ -29763,12 +29763,12 @@
       <c r="D78" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E78" s="582"/>
-      <c r="F78" s="583"/>
+      <c r="E78" s="576"/>
+      <c r="F78" s="577"/>
       <c r="G78" s="107" t="s">
         <v>272</v>
       </c>
-      <c r="H78" s="610"/>
+      <c r="H78" s="644"/>
     </row>
     <row r="79" spans="1:8" ht="15.75" customHeight="1">
       <c r="A79" s="98" t="s">
@@ -29783,12 +29783,12 @@
       <c r="D79" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E79" s="582"/>
-      <c r="F79" s="583"/>
+      <c r="E79" s="576"/>
+      <c r="F79" s="577"/>
       <c r="G79" s="105" t="s">
         <v>274</v>
       </c>
-      <c r="H79" s="610"/>
+      <c r="H79" s="644"/>
     </row>
     <row r="80" spans="1:8" ht="15.75" customHeight="1">
       <c r="A80" s="98" t="s">
@@ -29803,10 +29803,10 @@
       <c r="D80" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E80" s="582"/>
-      <c r="F80" s="583"/>
+      <c r="E80" s="576"/>
+      <c r="F80" s="577"/>
       <c r="G80" s="105"/>
-      <c r="H80" s="610"/>
+      <c r="H80" s="644"/>
     </row>
     <row r="81" spans="1:8" ht="15.75" customHeight="1">
       <c r="A81" s="98" t="s">
@@ -29818,15 +29818,15 @@
       <c r="C81" s="106" t="s">
         <v>277</v>
       </c>
-      <c r="D81" s="632" t="s">
+      <c r="D81" s="628" t="s">
         <v>169</v>
       </c>
-      <c r="E81" s="582"/>
-      <c r="F81" s="583"/>
+      <c r="E81" s="576"/>
+      <c r="F81" s="577"/>
       <c r="G81" s="107" t="s">
         <v>278</v>
       </c>
-      <c r="H81" s="610"/>
+      <c r="H81" s="644"/>
     </row>
     <row r="82" spans="1:8" ht="15.75" customHeight="1">
       <c r="A82" s="98" t="s">
@@ -29838,13 +29838,13 @@
       <c r="C82" s="106" t="s">
         <v>279</v>
       </c>
-      <c r="D82" s="632" t="s">
+      <c r="D82" s="628" t="s">
         <v>171</v>
       </c>
-      <c r="E82" s="582"/>
-      <c r="F82" s="583"/>
+      <c r="E82" s="576"/>
+      <c r="F82" s="577"/>
       <c r="G82" s="113"/>
-      <c r="H82" s="610"/>
+      <c r="H82" s="644"/>
     </row>
     <row r="83" spans="1:8" ht="15.75" customHeight="1">
       <c r="A83" s="98" t="s">
@@ -29859,12 +29859,12 @@
       <c r="D83" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E83" s="582"/>
-      <c r="F83" s="583"/>
+      <c r="E83" s="576"/>
+      <c r="F83" s="577"/>
       <c r="G83" s="108" t="s">
         <v>281</v>
       </c>
-      <c r="H83" s="610"/>
+      <c r="H83" s="644"/>
     </row>
     <row r="84" spans="1:8" ht="15.75" customHeight="1">
       <c r="A84" s="98" t="s">
@@ -29879,12 +29879,12 @@
       <c r="D84" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E84" s="582"/>
-      <c r="F84" s="583"/>
+      <c r="E84" s="576"/>
+      <c r="F84" s="577"/>
       <c r="G84" s="107" t="s">
         <v>283</v>
       </c>
-      <c r="H84" s="610"/>
+      <c r="H84" s="644"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" customHeight="1">
       <c r="A85" s="98" t="s">
@@ -29899,12 +29899,12 @@
       <c r="D85" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E85" s="582"/>
-      <c r="F85" s="583"/>
+      <c r="E85" s="576"/>
+      <c r="F85" s="577"/>
       <c r="G85" s="107" t="s">
         <v>285</v>
       </c>
-      <c r="H85" s="610"/>
+      <c r="H85" s="644"/>
     </row>
     <row r="86" spans="1:8" ht="15.75" customHeight="1">
       <c r="A86" s="98" t="s">
@@ -29919,10 +29919,10 @@
       <c r="D86" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E86" s="582"/>
-      <c r="F86" s="583"/>
+      <c r="E86" s="576"/>
+      <c r="F86" s="577"/>
       <c r="G86" s="105"/>
-      <c r="H86" s="610"/>
+      <c r="H86" s="644"/>
     </row>
     <row r="87" spans="1:8" ht="15.75" customHeight="1">
       <c r="A87" s="98" t="s">
@@ -29937,10 +29937,10 @@
       <c r="D87" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E87" s="582"/>
-      <c r="F87" s="583"/>
+      <c r="E87" s="576"/>
+      <c r="F87" s="577"/>
       <c r="G87" s="105"/>
-      <c r="H87" s="610"/>
+      <c r="H87" s="644"/>
     </row>
     <row r="88" spans="1:8" ht="15.75" customHeight="1">
       <c r="A88" s="98" t="s">
@@ -29955,10 +29955,10 @@
       <c r="D88" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E88" s="582"/>
-      <c r="F88" s="583"/>
+      <c r="E88" s="576"/>
+      <c r="F88" s="577"/>
       <c r="G88" s="105"/>
-      <c r="H88" s="610"/>
+      <c r="H88" s="644"/>
     </row>
     <row r="89" spans="1:8" ht="15.75" customHeight="1">
       <c r="A89" s="98" t="s">
@@ -29973,12 +29973,12 @@
       <c r="D89" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E89" s="582"/>
-      <c r="F89" s="583"/>
+      <c r="E89" s="576"/>
+      <c r="F89" s="577"/>
       <c r="G89" s="107" t="s">
         <v>290</v>
       </c>
-      <c r="H89" s="610"/>
+      <c r="H89" s="644"/>
     </row>
     <row r="90" spans="1:8" ht="15.75" customHeight="1">
       <c r="A90" s="98" t="s">
@@ -29993,12 +29993,12 @@
       <c r="D90" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E90" s="582"/>
-      <c r="F90" s="583"/>
+      <c r="E90" s="576"/>
+      <c r="F90" s="577"/>
       <c r="G90" s="107" t="s">
         <v>292</v>
       </c>
-      <c r="H90" s="610"/>
+      <c r="H90" s="644"/>
     </row>
     <row r="91" spans="1:8" ht="15.75" customHeight="1">
       <c r="A91" s="98" t="s">
@@ -30013,10 +30013,10 @@
       <c r="D91" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E91" s="582"/>
-      <c r="F91" s="583"/>
+      <c r="E91" s="576"/>
+      <c r="F91" s="577"/>
       <c r="G91" s="105"/>
-      <c r="H91" s="610"/>
+      <c r="H91" s="644"/>
     </row>
     <row r="92" spans="1:8" ht="15.75" customHeight="1">
       <c r="A92" s="98" t="s">
@@ -30031,10 +30031,10 @@
       <c r="D92" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E92" s="582"/>
-      <c r="F92" s="583"/>
+      <c r="E92" s="576"/>
+      <c r="F92" s="577"/>
       <c r="G92" s="105"/>
-      <c r="H92" s="610"/>
+      <c r="H92" s="644"/>
     </row>
     <row r="93" spans="1:8" ht="15.75" customHeight="1">
       <c r="A93" s="98" t="s">
@@ -30049,10 +30049,10 @@
       <c r="D93" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E93" s="582"/>
-      <c r="F93" s="583"/>
+      <c r="E93" s="576"/>
+      <c r="F93" s="577"/>
       <c r="G93" s="105"/>
-      <c r="H93" s="610"/>
+      <c r="H93" s="644"/>
     </row>
     <row r="94" spans="1:8" ht="15.75" customHeight="1">
       <c r="A94" s="98" t="s">
@@ -30067,10 +30067,10 @@
       <c r="D94" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E94" s="582"/>
-      <c r="F94" s="583"/>
+      <c r="E94" s="576"/>
+      <c r="F94" s="577"/>
       <c r="G94" s="105"/>
-      <c r="H94" s="610"/>
+      <c r="H94" s="644"/>
     </row>
     <row r="95" spans="1:8" ht="15.75" customHeight="1">
       <c r="A95" s="98" t="s">
@@ -30085,12 +30085,12 @@
       <c r="D95" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E95" s="582"/>
-      <c r="F95" s="583"/>
+      <c r="E95" s="576"/>
+      <c r="F95" s="577"/>
       <c r="G95" s="107" t="s">
         <v>298</v>
       </c>
-      <c r="H95" s="610"/>
+      <c r="H95" s="644"/>
     </row>
     <row r="96" spans="1:8" ht="15.75" customHeight="1">
       <c r="A96" s="98" t="s">
@@ -30105,10 +30105,10 @@
       <c r="D96" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E96" s="582"/>
-      <c r="F96" s="583"/>
+      <c r="E96" s="576"/>
+      <c r="F96" s="577"/>
       <c r="G96" s="105"/>
-      <c r="H96" s="610"/>
+      <c r="H96" s="644"/>
     </row>
     <row r="97" spans="1:8" ht="15.75" customHeight="1">
       <c r="A97" s="98" t="s">
@@ -30123,10 +30123,10 @@
       <c r="D97" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E97" s="582"/>
-      <c r="F97" s="583"/>
+      <c r="E97" s="576"/>
+      <c r="F97" s="577"/>
       <c r="G97" s="105"/>
-      <c r="H97" s="610"/>
+      <c r="H97" s="644"/>
     </row>
     <row r="98" spans="1:8" ht="15.75" customHeight="1">
       <c r="A98" s="98" t="s">
@@ -30141,12 +30141,12 @@
       <c r="D98" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E98" s="582"/>
-      <c r="F98" s="583"/>
+      <c r="E98" s="576"/>
+      <c r="F98" s="577"/>
       <c r="G98" s="107" t="s">
         <v>302</v>
       </c>
-      <c r="H98" s="610"/>
+      <c r="H98" s="644"/>
     </row>
     <row r="99" spans="1:8" ht="15.75" customHeight="1">
       <c r="A99" s="98" t="s">
@@ -30161,10 +30161,10 @@
       <c r="D99" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E99" s="582"/>
-      <c r="F99" s="583"/>
+      <c r="E99" s="576"/>
+      <c r="F99" s="577"/>
       <c r="G99" s="105"/>
-      <c r="H99" s="610"/>
+      <c r="H99" s="644"/>
     </row>
     <row r="100" spans="1:8" ht="15.75" customHeight="1">
       <c r="A100" s="98" t="s">
@@ -30179,12 +30179,12 @@
       <c r="D100" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E100" s="582"/>
-      <c r="F100" s="583"/>
+      <c r="E100" s="576"/>
+      <c r="F100" s="577"/>
       <c r="G100" s="107" t="s">
         <v>305</v>
       </c>
-      <c r="H100" s="610"/>
+      <c r="H100" s="644"/>
     </row>
     <row r="101" spans="1:8" ht="15.75" customHeight="1">
       <c r="A101" s="98" t="s">
@@ -30199,10 +30199,10 @@
       <c r="D101" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E101" s="582"/>
-      <c r="F101" s="583"/>
+      <c r="E101" s="576"/>
+      <c r="F101" s="577"/>
       <c r="G101" s="105"/>
-      <c r="H101" s="610"/>
+      <c r="H101" s="644"/>
     </row>
     <row r="102" spans="1:8" ht="15.75" customHeight="1">
       <c r="A102" s="98" t="s">
@@ -30217,10 +30217,10 @@
       <c r="D102" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E102" s="582"/>
-      <c r="F102" s="583"/>
+      <c r="E102" s="576"/>
+      <c r="F102" s="577"/>
       <c r="G102" s="105"/>
-      <c r="H102" s="610"/>
+      <c r="H102" s="644"/>
     </row>
     <row r="103" spans="1:8" ht="15.75" customHeight="1">
       <c r="A103" s="98" t="s">
@@ -30235,10 +30235,10 @@
       <c r="D103" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E103" s="582"/>
-      <c r="F103" s="583"/>
+      <c r="E103" s="576"/>
+      <c r="F103" s="577"/>
       <c r="G103" s="105"/>
-      <c r="H103" s="610"/>
+      <c r="H103" s="644"/>
     </row>
     <row r="104" spans="1:8" ht="15.75" customHeight="1">
       <c r="A104" s="98" t="s">
@@ -30253,10 +30253,10 @@
       <c r="D104" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E104" s="582"/>
-      <c r="F104" s="583"/>
+      <c r="E104" s="576"/>
+      <c r="F104" s="577"/>
       <c r="G104" s="105"/>
-      <c r="H104" s="610"/>
+      <c r="H104" s="644"/>
     </row>
     <row r="105" spans="1:8" ht="15.75" customHeight="1">
       <c r="A105" s="98" t="s">
@@ -30268,13 +30268,13 @@
       <c r="C105" s="106" t="s">
         <v>311</v>
       </c>
-      <c r="D105" s="632" t="s">
+      <c r="D105" s="628" t="s">
         <v>172</v>
       </c>
-      <c r="E105" s="582"/>
-      <c r="F105" s="583"/>
+      <c r="E105" s="576"/>
+      <c r="F105" s="577"/>
       <c r="G105" s="110"/>
-      <c r="H105" s="610"/>
+      <c r="H105" s="644"/>
     </row>
     <row r="106" spans="1:8" ht="15.75" customHeight="1">
       <c r="A106" s="98" t="s">
@@ -30289,10 +30289,10 @@
       <c r="D106" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E106" s="582"/>
-      <c r="F106" s="583"/>
+      <c r="E106" s="576"/>
+      <c r="F106" s="577"/>
       <c r="G106" s="114"/>
-      <c r="H106" s="610"/>
+      <c r="H106" s="644"/>
     </row>
     <row r="107" spans="1:8" ht="15.75" customHeight="1">
       <c r="A107" s="98" t="s">
@@ -30307,12 +30307,12 @@
       <c r="D107" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E107" s="582"/>
-      <c r="F107" s="583"/>
+      <c r="E107" s="576"/>
+      <c r="F107" s="577"/>
       <c r="G107" s="115" t="s">
         <v>316</v>
       </c>
-      <c r="H107" s="610"/>
+      <c r="H107" s="644"/>
     </row>
     <row r="108" spans="1:8" ht="15.75" customHeight="1">
       <c r="A108" s="98" t="s">
@@ -30327,12 +30327,12 @@
       <c r="D108" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E108" s="582"/>
-      <c r="F108" s="583"/>
+      <c r="E108" s="576"/>
+      <c r="F108" s="577"/>
       <c r="G108" s="108" t="s">
         <v>318</v>
       </c>
-      <c r="H108" s="610"/>
+      <c r="H108" s="644"/>
     </row>
     <row r="109" spans="1:8" ht="15.75" customHeight="1">
       <c r="A109" s="98" t="s">
@@ -30347,10 +30347,10 @@
       <c r="D109" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E109" s="582"/>
-      <c r="F109" s="583"/>
+      <c r="E109" s="576"/>
+      <c r="F109" s="577"/>
       <c r="G109" s="105"/>
-      <c r="H109" s="610"/>
+      <c r="H109" s="644"/>
     </row>
     <row r="110" spans="1:8" ht="15.75" customHeight="1">
       <c r="A110" s="98" t="s">
@@ -30365,10 +30365,10 @@
       <c r="D110" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E110" s="582"/>
-      <c r="F110" s="583"/>
+      <c r="E110" s="576"/>
+      <c r="F110" s="577"/>
       <c r="G110" s="105"/>
-      <c r="H110" s="610"/>
+      <c r="H110" s="644"/>
     </row>
     <row r="111" spans="1:8" ht="15.75" customHeight="1">
       <c r="A111" s="98" t="s">
@@ -30383,10 +30383,10 @@
       <c r="D111" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E111" s="582"/>
-      <c r="F111" s="583"/>
+      <c r="E111" s="576"/>
+      <c r="F111" s="577"/>
       <c r="G111" s="114"/>
-      <c r="H111" s="610"/>
+      <c r="H111" s="644"/>
     </row>
     <row r="112" spans="1:8" ht="15.75" customHeight="1">
       <c r="A112" s="98" t="s">
@@ -30401,12 +30401,12 @@
       <c r="D112" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E112" s="582"/>
-      <c r="F112" s="583"/>
+      <c r="E112" s="576"/>
+      <c r="F112" s="577"/>
       <c r="G112" s="105" t="s">
         <v>327</v>
       </c>
-      <c r="H112" s="610"/>
+      <c r="H112" s="644"/>
     </row>
     <row r="113" spans="1:8" ht="15.75" customHeight="1">
       <c r="A113" s="98" t="s">
@@ -30421,12 +30421,12 @@
       <c r="D113" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E113" s="582"/>
-      <c r="F113" s="583"/>
+      <c r="E113" s="576"/>
+      <c r="F113" s="577"/>
       <c r="G113" s="116" t="s">
         <v>330</v>
       </c>
-      <c r="H113" s="610"/>
+      <c r="H113" s="644"/>
     </row>
     <row r="114" spans="1:8" ht="15.75" customHeight="1">
       <c r="A114" s="98" t="s">
@@ -30441,12 +30441,12 @@
       <c r="D114" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E114" s="582"/>
-      <c r="F114" s="583"/>
+      <c r="E114" s="576"/>
+      <c r="F114" s="577"/>
       <c r="G114" s="116" t="s">
         <v>332</v>
       </c>
-      <c r="H114" s="610"/>
+      <c r="H114" s="644"/>
     </row>
     <row r="115" spans="1:8" ht="15.75" customHeight="1">
       <c r="A115" s="98" t="s">
@@ -30461,12 +30461,12 @@
       <c r="D115" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E115" s="582"/>
-      <c r="F115" s="583"/>
+      <c r="E115" s="576"/>
+      <c r="F115" s="577"/>
       <c r="G115" s="117" t="s">
         <v>334</v>
       </c>
-      <c r="H115" s="610"/>
+      <c r="H115" s="644"/>
     </row>
     <row r="116" spans="1:8" ht="15.75" customHeight="1">
       <c r="A116" s="98" t="s">
@@ -30481,12 +30481,12 @@
       <c r="D116" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E116" s="582"/>
-      <c r="F116" s="583"/>
+      <c r="E116" s="576"/>
+      <c r="F116" s="577"/>
       <c r="G116" s="116" t="s">
         <v>336</v>
       </c>
-      <c r="H116" s="610"/>
+      <c r="H116" s="644"/>
     </row>
     <row r="117" spans="1:8" ht="15.75" customHeight="1">
       <c r="A117" s="98" t="s">
@@ -30501,10 +30501,10 @@
       <c r="D117" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E117" s="582"/>
-      <c r="F117" s="583"/>
+      <c r="E117" s="576"/>
+      <c r="F117" s="577"/>
       <c r="G117" s="118"/>
-      <c r="H117" s="610"/>
+      <c r="H117" s="644"/>
     </row>
     <row r="118" spans="1:8" ht="15.75" customHeight="1">
       <c r="A118" s="98" t="s">
@@ -30519,12 +30519,12 @@
       <c r="D118" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E118" s="582"/>
-      <c r="F118" s="583"/>
+      <c r="E118" s="576"/>
+      <c r="F118" s="577"/>
       <c r="G118" s="116" t="s">
         <v>339</v>
       </c>
-      <c r="H118" s="610"/>
+      <c r="H118" s="644"/>
     </row>
     <row r="119" spans="1:8" ht="15.75" customHeight="1">
       <c r="A119" s="98" t="s">
@@ -30539,12 +30539,12 @@
       <c r="D119" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E119" s="582"/>
-      <c r="F119" s="583"/>
+      <c r="E119" s="576"/>
+      <c r="F119" s="577"/>
       <c r="G119" s="116" t="s">
         <v>341</v>
       </c>
-      <c r="H119" s="610"/>
+      <c r="H119" s="644"/>
     </row>
     <row r="120" spans="1:8" ht="15.75" customHeight="1">
       <c r="A120" s="98" t="s">
@@ -30559,12 +30559,12 @@
       <c r="D120" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E120" s="582"/>
-      <c r="F120" s="583"/>
+      <c r="E120" s="576"/>
+      <c r="F120" s="577"/>
       <c r="G120" s="116" t="s">
         <v>343</v>
       </c>
-      <c r="H120" s="610"/>
+      <c r="H120" s="644"/>
     </row>
     <row r="121" spans="1:8" ht="15.75" customHeight="1">
       <c r="A121" s="98" t="s">
@@ -30579,12 +30579,12 @@
       <c r="D121" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E121" s="582"/>
-      <c r="F121" s="583"/>
+      <c r="E121" s="576"/>
+      <c r="F121" s="577"/>
       <c r="G121" s="116" t="s">
         <v>345</v>
       </c>
-      <c r="H121" s="610"/>
+      <c r="H121" s="644"/>
     </row>
     <row r="122" spans="1:8" ht="15.75" customHeight="1">
       <c r="A122" s="98" t="s">
@@ -30599,12 +30599,12 @@
       <c r="D122" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E122" s="582"/>
-      <c r="F122" s="583"/>
+      <c r="E122" s="576"/>
+      <c r="F122" s="577"/>
       <c r="G122" s="116" t="s">
         <v>347</v>
       </c>
-      <c r="H122" s="610"/>
+      <c r="H122" s="644"/>
     </row>
     <row r="123" spans="1:8" ht="15.75" customHeight="1">
       <c r="A123" s="98" t="s">
@@ -30619,12 +30619,12 @@
       <c r="D123" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E123" s="582"/>
-      <c r="F123" s="583"/>
+      <c r="E123" s="576"/>
+      <c r="F123" s="577"/>
       <c r="G123" s="116" t="s">
         <v>349</v>
       </c>
-      <c r="H123" s="610"/>
+      <c r="H123" s="644"/>
     </row>
     <row r="124" spans="1:8" ht="15.75" customHeight="1">
       <c r="A124" s="98" t="s">
@@ -30639,12 +30639,12 @@
       <c r="D124" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E124" s="582"/>
-      <c r="F124" s="583"/>
+      <c r="E124" s="576"/>
+      <c r="F124" s="577"/>
       <c r="G124" s="105" t="s">
         <v>351</v>
       </c>
-      <c r="H124" s="610"/>
+      <c r="H124" s="644"/>
     </row>
     <row r="125" spans="1:8" ht="15.75" customHeight="1">
       <c r="A125" s="98" t="s">
@@ -30659,10 +30659,10 @@
       <c r="D125" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E125" s="582"/>
-      <c r="F125" s="583"/>
+      <c r="E125" s="576"/>
+      <c r="F125" s="577"/>
       <c r="G125" s="105"/>
-      <c r="H125" s="610"/>
+      <c r="H125" s="644"/>
     </row>
     <row r="126" spans="1:8" ht="15.75" customHeight="1">
       <c r="A126" s="98" t="s">
@@ -30677,10 +30677,10 @@
       <c r="D126" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E126" s="582"/>
-      <c r="F126" s="583"/>
+      <c r="E126" s="576"/>
+      <c r="F126" s="577"/>
       <c r="G126" s="105"/>
-      <c r="H126" s="610"/>
+      <c r="H126" s="644"/>
     </row>
     <row r="127" spans="1:8" ht="15.75" customHeight="1">
       <c r="A127" s="98" t="s">
@@ -30695,12 +30695,12 @@
       <c r="D127" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E127" s="582"/>
-      <c r="F127" s="583"/>
+      <c r="E127" s="576"/>
+      <c r="F127" s="577"/>
       <c r="G127" s="116" t="s">
         <v>355</v>
       </c>
-      <c r="H127" s="610"/>
+      <c r="H127" s="644"/>
     </row>
     <row r="128" spans="1:8" ht="15.75" customHeight="1">
       <c r="A128" s="98" t="s">
@@ -30715,12 +30715,12 @@
       <c r="D128" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E128" s="582"/>
-      <c r="F128" s="583"/>
+      <c r="E128" s="576"/>
+      <c r="F128" s="577"/>
       <c r="G128" s="116" t="s">
         <v>357</v>
       </c>
-      <c r="H128" s="610"/>
+      <c r="H128" s="644"/>
     </row>
     <row r="129" spans="1:8" ht="15.75" customHeight="1">
       <c r="A129" s="98" t="s">
@@ -30735,12 +30735,12 @@
       <c r="D129" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E129" s="582"/>
-      <c r="F129" s="583"/>
+      <c r="E129" s="576"/>
+      <c r="F129" s="577"/>
       <c r="G129" s="116" t="s">
         <v>359</v>
       </c>
-      <c r="H129" s="610"/>
+      <c r="H129" s="644"/>
     </row>
     <row r="130" spans="1:8" ht="15.75" customHeight="1">
       <c r="A130" s="98" t="s">
@@ -30755,12 +30755,12 @@
       <c r="D130" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E130" s="582"/>
-      <c r="F130" s="583"/>
+      <c r="E130" s="576"/>
+      <c r="F130" s="577"/>
       <c r="G130" s="116" t="s">
         <v>349</v>
       </c>
-      <c r="H130" s="610"/>
+      <c r="H130" s="644"/>
     </row>
     <row r="131" spans="1:8" ht="15.75" customHeight="1">
       <c r="A131" s="98" t="s">
@@ -30775,12 +30775,12 @@
       <c r="D131" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E131" s="582"/>
-      <c r="F131" s="583"/>
+      <c r="E131" s="576"/>
+      <c r="F131" s="577"/>
       <c r="G131" s="116" t="s">
         <v>362</v>
       </c>
-      <c r="H131" s="610"/>
+      <c r="H131" s="644"/>
     </row>
     <row r="132" spans="1:8" ht="15.75" customHeight="1">
       <c r="A132" s="98" t="s">
@@ -30795,10 +30795,10 @@
       <c r="D132" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E132" s="582"/>
-      <c r="F132" s="583"/>
+      <c r="E132" s="576"/>
+      <c r="F132" s="577"/>
       <c r="G132" s="105"/>
-      <c r="H132" s="610"/>
+      <c r="H132" s="644"/>
     </row>
     <row r="133" spans="1:8" ht="15.75" customHeight="1">
       <c r="A133" s="98" t="s">
@@ -30813,12 +30813,12 @@
       <c r="D133" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E133" s="582"/>
-      <c r="F133" s="583"/>
+      <c r="E133" s="576"/>
+      <c r="F133" s="577"/>
       <c r="G133" s="116" t="s">
         <v>365</v>
       </c>
-      <c r="H133" s="610"/>
+      <c r="H133" s="644"/>
     </row>
     <row r="134" spans="1:8" ht="15.75" customHeight="1">
       <c r="A134" s="98" t="s">
@@ -30833,12 +30833,12 @@
       <c r="D134" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E134" s="582"/>
-      <c r="F134" s="583"/>
+      <c r="E134" s="576"/>
+      <c r="F134" s="577"/>
       <c r="G134" s="116" t="s">
         <v>367</v>
       </c>
-      <c r="H134" s="610"/>
+      <c r="H134" s="644"/>
     </row>
     <row r="135" spans="1:8" ht="15.75" customHeight="1">
       <c r="A135" s="98" t="s">
@@ -30853,12 +30853,12 @@
       <c r="D135" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E135" s="582"/>
-      <c r="F135" s="583"/>
+      <c r="E135" s="576"/>
+      <c r="F135" s="577"/>
       <c r="G135" s="116" t="s">
         <v>369</v>
       </c>
-      <c r="H135" s="610"/>
+      <c r="H135" s="644"/>
     </row>
     <row r="136" spans="1:8" ht="15.75" customHeight="1">
       <c r="A136" s="98" t="s">
@@ -30873,12 +30873,12 @@
       <c r="D136" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E136" s="582"/>
-      <c r="F136" s="583"/>
+      <c r="E136" s="576"/>
+      <c r="F136" s="577"/>
       <c r="G136" s="116" t="s">
         <v>371</v>
       </c>
-      <c r="H136" s="610"/>
+      <c r="H136" s="644"/>
     </row>
     <row r="137" spans="1:8" ht="15.75" customHeight="1">
       <c r="A137" s="98" t="s">
@@ -30893,12 +30893,12 @@
       <c r="D137" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E137" s="582"/>
-      <c r="F137" s="583"/>
+      <c r="E137" s="576"/>
+      <c r="F137" s="577"/>
       <c r="G137" s="116" t="s">
         <v>373</v>
       </c>
-      <c r="H137" s="610"/>
+      <c r="H137" s="644"/>
     </row>
     <row r="138" spans="1:8" ht="15.75" customHeight="1">
       <c r="A138" s="98" t="s">
@@ -30913,10 +30913,10 @@
       <c r="D138" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E138" s="582"/>
-      <c r="F138" s="583"/>
+      <c r="E138" s="576"/>
+      <c r="F138" s="577"/>
       <c r="G138" s="105"/>
-      <c r="H138" s="610"/>
+      <c r="H138" s="644"/>
     </row>
     <row r="139" spans="1:8" ht="15.75" customHeight="1">
       <c r="A139" s="98" t="s">
@@ -30931,12 +30931,12 @@
       <c r="D139" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E139" s="582"/>
-      <c r="F139" s="583"/>
+      <c r="E139" s="576"/>
+      <c r="F139" s="577"/>
       <c r="G139" s="116" t="s">
         <v>376</v>
       </c>
-      <c r="H139" s="610"/>
+      <c r="H139" s="644"/>
     </row>
     <row r="140" spans="1:8" ht="15.75" customHeight="1">
       <c r="A140" s="98" t="s">
@@ -30951,12 +30951,12 @@
       <c r="D140" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E140" s="582"/>
-      <c r="F140" s="583"/>
+      <c r="E140" s="576"/>
+      <c r="F140" s="577"/>
       <c r="G140" s="116" t="s">
         <v>378</v>
       </c>
-      <c r="H140" s="610"/>
+      <c r="H140" s="644"/>
     </row>
     <row r="141" spans="1:8" ht="25.5" customHeight="1">
       <c r="A141" s="98" t="s">
@@ -30971,12 +30971,12 @@
       <c r="D141" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E141" s="582"/>
-      <c r="F141" s="583"/>
+      <c r="E141" s="576"/>
+      <c r="F141" s="577"/>
       <c r="G141" s="116" t="s">
         <v>381</v>
       </c>
-      <c r="H141" s="610"/>
+      <c r="H141" s="644"/>
     </row>
     <row r="142" spans="1:8" ht="25.5" customHeight="1">
       <c r="A142" s="98" t="s">
@@ -30991,12 +30991,12 @@
       <c r="D142" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E142" s="582"/>
-      <c r="F142" s="583"/>
+      <c r="E142" s="576"/>
+      <c r="F142" s="577"/>
       <c r="G142" s="105" t="s">
         <v>216</v>
       </c>
-      <c r="H142" s="610"/>
+      <c r="H142" s="644"/>
     </row>
     <row r="143" spans="1:8" ht="15.75" customHeight="1">
       <c r="A143" s="98" t="s">
@@ -31011,12 +31011,12 @@
       <c r="D143" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E143" s="582"/>
-      <c r="F143" s="583"/>
+      <c r="E143" s="576"/>
+      <c r="F143" s="577"/>
       <c r="G143" s="116" t="s">
         <v>385</v>
       </c>
-      <c r="H143" s="610"/>
+      <c r="H143" s="644"/>
     </row>
     <row r="144" spans="1:8" ht="15.75" customHeight="1">
       <c r="A144" s="98" t="s">
@@ -31031,12 +31031,12 @@
       <c r="D144" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E144" s="582"/>
-      <c r="F144" s="583"/>
+      <c r="E144" s="576"/>
+      <c r="F144" s="577"/>
       <c r="G144" s="116" t="s">
         <v>387</v>
       </c>
-      <c r="H144" s="610"/>
+      <c r="H144" s="644"/>
     </row>
     <row r="145" spans="1:8" ht="15.75" customHeight="1">
       <c r="A145" s="98" t="s">
@@ -31051,12 +31051,12 @@
       <c r="D145" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E145" s="582"/>
-      <c r="F145" s="583"/>
+      <c r="E145" s="576"/>
+      <c r="F145" s="577"/>
       <c r="G145" s="116" t="s">
         <v>390</v>
       </c>
-      <c r="H145" s="610"/>
+      <c r="H145" s="644"/>
     </row>
     <row r="146" spans="1:8" ht="15.75" customHeight="1">
       <c r="A146" s="98" t="s">
@@ -31071,12 +31071,12 @@
       <c r="D146" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E146" s="582"/>
-      <c r="F146" s="583"/>
+      <c r="E146" s="576"/>
+      <c r="F146" s="577"/>
       <c r="G146" s="116" t="s">
         <v>219</v>
       </c>
-      <c r="H146" s="610"/>
+      <c r="H146" s="644"/>
     </row>
     <row r="147" spans="1:8" ht="15.75" customHeight="1">
       <c r="A147" s="98" t="s">
@@ -31091,10 +31091,10 @@
       <c r="D147" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E147" s="582"/>
-      <c r="F147" s="583"/>
+      <c r="E147" s="576"/>
+      <c r="F147" s="577"/>
       <c r="G147" s="113"/>
-      <c r="H147" s="610"/>
+      <c r="H147" s="644"/>
     </row>
     <row r="148" spans="1:8" ht="15.75" customHeight="1">
       <c r="A148" s="98" t="s">
@@ -31109,10 +31109,10 @@
       <c r="D148" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E148" s="582"/>
-      <c r="F148" s="583"/>
+      <c r="E148" s="576"/>
+      <c r="F148" s="577"/>
       <c r="G148" s="105"/>
-      <c r="H148" s="610"/>
+      <c r="H148" s="644"/>
     </row>
     <row r="149" spans="1:8" ht="15.75" customHeight="1">
       <c r="A149" s="98" t="s">
@@ -31127,10 +31127,10 @@
       <c r="D149" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E149" s="582"/>
-      <c r="F149" s="583"/>
+      <c r="E149" s="576"/>
+      <c r="F149" s="577"/>
       <c r="G149" s="105"/>
-      <c r="H149" s="610"/>
+      <c r="H149" s="644"/>
     </row>
     <row r="150" spans="1:8" ht="15.75" customHeight="1">
       <c r="A150" s="98" t="s">
@@ -31145,10 +31145,10 @@
       <c r="D150" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E150" s="582"/>
-      <c r="F150" s="583"/>
+      <c r="E150" s="576"/>
+      <c r="F150" s="577"/>
       <c r="G150" s="105"/>
-      <c r="H150" s="610"/>
+      <c r="H150" s="644"/>
     </row>
     <row r="151" spans="1:8" ht="15.75" customHeight="1">
       <c r="A151" s="98" t="s">
@@ -31163,10 +31163,10 @@
       <c r="D151" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E151" s="582"/>
-      <c r="F151" s="583"/>
+      <c r="E151" s="576"/>
+      <c r="F151" s="577"/>
       <c r="G151" s="105"/>
-      <c r="H151" s="610"/>
+      <c r="H151" s="644"/>
     </row>
     <row r="152" spans="1:8" ht="15.75" customHeight="1">
       <c r="A152" s="98" t="s">
@@ -31181,12 +31181,12 @@
       <c r="D152" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E152" s="582"/>
-      <c r="F152" s="583"/>
+      <c r="E152" s="576"/>
+      <c r="F152" s="577"/>
       <c r="G152" s="116" t="s">
         <v>399</v>
       </c>
-      <c r="H152" s="610"/>
+      <c r="H152" s="644"/>
     </row>
     <row r="153" spans="1:8" ht="15.75" customHeight="1">
       <c r="A153" s="98" t="s">
@@ -31201,10 +31201,10 @@
       <c r="D153" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E153" s="582"/>
-      <c r="F153" s="583"/>
+      <c r="E153" s="576"/>
+      <c r="F153" s="577"/>
       <c r="G153" s="105"/>
-      <c r="H153" s="610"/>
+      <c r="H153" s="644"/>
     </row>
     <row r="154" spans="1:8" ht="15.75" customHeight="1">
       <c r="A154" s="98" t="s">
@@ -31219,12 +31219,12 @@
       <c r="D154" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E154" s="582"/>
-      <c r="F154" s="583"/>
+      <c r="E154" s="576"/>
+      <c r="F154" s="577"/>
       <c r="G154" s="116" t="s">
         <v>402</v>
       </c>
-      <c r="H154" s="610"/>
+      <c r="H154" s="644"/>
     </row>
     <row r="155" spans="1:8" ht="15.75" customHeight="1">
       <c r="A155" s="98" t="s">
@@ -31239,12 +31239,12 @@
       <c r="D155" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E155" s="582"/>
-      <c r="F155" s="583"/>
+      <c r="E155" s="576"/>
+      <c r="F155" s="577"/>
       <c r="G155" s="116" t="s">
         <v>404</v>
       </c>
-      <c r="H155" s="610"/>
+      <c r="H155" s="644"/>
     </row>
     <row r="156" spans="1:8" ht="15.75" customHeight="1">
       <c r="A156" s="98" t="s">
@@ -31259,17 +31259,17 @@
       <c r="D156" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E156" s="582"/>
-      <c r="F156" s="583"/>
+      <c r="E156" s="576"/>
+      <c r="F156" s="577"/>
       <c r="G156" s="119"/>
-      <c r="H156" s="610"/>
+      <c r="H156" s="644"/>
     </row>
     <row r="157" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A157" s="633" t="s">
+      <c r="A157" s="608" t="s">
         <v>406</v>
       </c>
-      <c r="B157" s="604"/>
-      <c r="C157" s="641">
+      <c r="B157" s="593"/>
+      <c r="C157" s="618">
         <f>COUNTIFS($A24:$A156,"*",$C24:$C156,"*",$D24:$D156,"*")</f>
         <v>133</v>
       </c>
@@ -31283,12 +31283,12 @@
         <v>178</v>
       </c>
       <c r="G157" s="122"/>
-      <c r="H157" s="610"/>
+      <c r="H157" s="644"/>
     </row>
     <row r="158" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A158" s="639"/>
-      <c r="B158" s="640"/>
-      <c r="C158" s="642"/>
+      <c r="A158" s="616"/>
+      <c r="B158" s="617"/>
+      <c r="C158" s="619"/>
       <c r="D158" s="123">
         <f>COUNTIFS($A24:$A156,"*",$C24:$C156,"*",$D24:$D156, "Employed")</f>
         <v>75</v>
@@ -31302,19 +31302,19 @@
         <v>35</v>
       </c>
       <c r="G158" s="124"/>
-      <c r="H158" s="610"/>
+      <c r="H158" s="644"/>
     </row>
     <row r="159" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A159" s="643" t="s">
+      <c r="A159" s="620" t="s">
         <v>148</v>
       </c>
-      <c r="B159" s="582"/>
-      <c r="C159" s="582"/>
-      <c r="D159" s="582"/>
-      <c r="E159" s="582"/>
-      <c r="F159" s="582"/>
-      <c r="G159" s="583"/>
-      <c r="H159" s="610"/>
+      <c r="B159" s="576"/>
+      <c r="C159" s="576"/>
+      <c r="D159" s="576"/>
+      <c r="E159" s="576"/>
+      <c r="F159" s="576"/>
+      <c r="G159" s="577"/>
+      <c r="H159" s="644"/>
     </row>
     <row r="160" spans="1:8" ht="15.75" customHeight="1">
       <c r="A160" s="125" t="s">
@@ -31329,10 +31329,10 @@
       <c r="D160" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E160" s="582"/>
-      <c r="F160" s="583"/>
+      <c r="E160" s="576"/>
+      <c r="F160" s="577"/>
       <c r="G160" s="125"/>
-      <c r="H160" s="610"/>
+      <c r="H160" s="644"/>
     </row>
     <row r="161" spans="1:8" ht="15.75" customHeight="1">
       <c r="A161" s="125" t="s">
@@ -31347,10 +31347,10 @@
       <c r="D161" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E161" s="582"/>
-      <c r="F161" s="583"/>
+      <c r="E161" s="576"/>
+      <c r="F161" s="577"/>
       <c r="G161" s="127"/>
-      <c r="H161" s="610"/>
+      <c r="H161" s="644"/>
     </row>
     <row r="162" spans="1:8" ht="15.75" customHeight="1">
       <c r="A162" s="125" t="s">
@@ -31365,10 +31365,10 @@
       <c r="D162" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E162" s="582"/>
-      <c r="F162" s="583"/>
+      <c r="E162" s="576"/>
+      <c r="F162" s="577"/>
       <c r="G162" s="127"/>
-      <c r="H162" s="610"/>
+      <c r="H162" s="644"/>
     </row>
     <row r="163" spans="1:8" ht="15.75" customHeight="1">
       <c r="A163" s="125" t="s">
@@ -31383,10 +31383,10 @@
       <c r="D163" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E163" s="582"/>
-      <c r="F163" s="583"/>
+      <c r="E163" s="576"/>
+      <c r="F163" s="577"/>
       <c r="G163" s="127"/>
-      <c r="H163" s="610"/>
+      <c r="H163" s="644"/>
     </row>
     <row r="164" spans="1:8" ht="15.75" customHeight="1">
       <c r="A164" s="125" t="s">
@@ -31401,10 +31401,10 @@
       <c r="D164" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E164" s="582"/>
-      <c r="F164" s="583"/>
+      <c r="E164" s="576"/>
+      <c r="F164" s="577"/>
       <c r="G164" s="127"/>
-      <c r="H164" s="610"/>
+      <c r="H164" s="644"/>
     </row>
     <row r="165" spans="1:8" ht="15.75" customHeight="1">
       <c r="A165" s="125" t="s">
@@ -31419,10 +31419,10 @@
       <c r="D165" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E165" s="582"/>
-      <c r="F165" s="583"/>
+      <c r="E165" s="576"/>
+      <c r="F165" s="577"/>
       <c r="G165" s="127"/>
-      <c r="H165" s="610"/>
+      <c r="H165" s="644"/>
     </row>
     <row r="166" spans="1:8" ht="15.75" customHeight="1">
       <c r="A166" s="125" t="s">
@@ -31437,10 +31437,10 @@
       <c r="D166" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E166" s="582"/>
-      <c r="F166" s="583"/>
+      <c r="E166" s="576"/>
+      <c r="F166" s="577"/>
       <c r="G166" s="125"/>
-      <c r="H166" s="610"/>
+      <c r="H166" s="644"/>
     </row>
     <row r="167" spans="1:8" ht="15.75" customHeight="1">
       <c r="A167" s="125" t="s">
@@ -31455,10 +31455,10 @@
       <c r="D167" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E167" s="582"/>
-      <c r="F167" s="583"/>
+      <c r="E167" s="576"/>
+      <c r="F167" s="577"/>
       <c r="G167" s="125"/>
-      <c r="H167" s="610"/>
+      <c r="H167" s="644"/>
     </row>
     <row r="168" spans="1:8" ht="15.75" customHeight="1">
       <c r="A168" s="125" t="s">
@@ -31473,10 +31473,10 @@
       <c r="D168" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E168" s="582"/>
-      <c r="F168" s="583"/>
+      <c r="E168" s="576"/>
+      <c r="F168" s="577"/>
       <c r="G168" s="125"/>
-      <c r="H168" s="610"/>
+      <c r="H168" s="644"/>
     </row>
     <row r="169" spans="1:8" ht="15.75" customHeight="1">
       <c r="A169" s="125" t="s">
@@ -31491,10 +31491,10 @@
       <c r="D169" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E169" s="582"/>
-      <c r="F169" s="583"/>
+      <c r="E169" s="576"/>
+      <c r="F169" s="577"/>
       <c r="G169" s="125"/>
-      <c r="H169" s="610"/>
+      <c r="H169" s="644"/>
     </row>
     <row r="170" spans="1:8" ht="15.75" customHeight="1">
       <c r="A170" s="125" t="s">
@@ -31509,10 +31509,10 @@
       <c r="D170" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E170" s="582"/>
-      <c r="F170" s="583"/>
+      <c r="E170" s="576"/>
+      <c r="F170" s="577"/>
       <c r="G170" s="125"/>
-      <c r="H170" s="610"/>
+      <c r="H170" s="644"/>
     </row>
     <row r="171" spans="1:8" ht="15.75" customHeight="1">
       <c r="A171" s="125" t="s">
@@ -31527,12 +31527,12 @@
       <c r="D171" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E171" s="582"/>
-      <c r="F171" s="583"/>
+      <c r="E171" s="576"/>
+      <c r="F171" s="577"/>
       <c r="G171" s="131" t="s">
         <v>421</v>
       </c>
-      <c r="H171" s="610"/>
+      <c r="H171" s="644"/>
     </row>
     <row r="172" spans="1:8" ht="15.75" customHeight="1">
       <c r="A172" s="125" t="s">
@@ -31547,12 +31547,12 @@
       <c r="D172" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E172" s="582"/>
-      <c r="F172" s="583"/>
+      <c r="E172" s="576"/>
+      <c r="F172" s="577"/>
       <c r="G172" s="125" t="s">
         <v>423</v>
       </c>
-      <c r="H172" s="610"/>
+      <c r="H172" s="644"/>
     </row>
     <row r="173" spans="1:8" ht="15.75" customHeight="1">
       <c r="A173" s="125" t="s">
@@ -31567,10 +31567,10 @@
       <c r="D173" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E173" s="582"/>
-      <c r="F173" s="583"/>
+      <c r="E173" s="576"/>
+      <c r="F173" s="577"/>
       <c r="G173" s="125"/>
-      <c r="H173" s="610"/>
+      <c r="H173" s="644"/>
     </row>
     <row r="174" spans="1:8" ht="15.75" customHeight="1">
       <c r="A174" s="125" t="s">
@@ -31585,10 +31585,10 @@
       <c r="D174" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E174" s="582"/>
-      <c r="F174" s="583"/>
+      <c r="E174" s="576"/>
+      <c r="F174" s="577"/>
       <c r="G174" s="125"/>
-      <c r="H174" s="610"/>
+      <c r="H174" s="644"/>
     </row>
     <row r="175" spans="1:8" ht="15.75" customHeight="1">
       <c r="A175" s="125" t="s">
@@ -31603,10 +31603,10 @@
       <c r="D175" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E175" s="582"/>
-      <c r="F175" s="583"/>
+      <c r="E175" s="576"/>
+      <c r="F175" s="577"/>
       <c r="G175" s="125"/>
-      <c r="H175" s="610"/>
+      <c r="H175" s="644"/>
     </row>
     <row r="176" spans="1:8" ht="15.75" customHeight="1">
       <c r="A176" s="125" t="s">
@@ -31621,10 +31621,10 @@
       <c r="D176" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E176" s="582"/>
-      <c r="F176" s="583"/>
+      <c r="E176" s="576"/>
+      <c r="F176" s="577"/>
       <c r="G176" s="125"/>
-      <c r="H176" s="610"/>
+      <c r="H176" s="644"/>
     </row>
     <row r="177" spans="1:8" ht="15.75" customHeight="1">
       <c r="A177" s="125" t="s">
@@ -31639,10 +31639,10 @@
       <c r="D177" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E177" s="582"/>
-      <c r="F177" s="583"/>
+      <c r="E177" s="576"/>
+      <c r="F177" s="577"/>
       <c r="G177" s="125"/>
-      <c r="H177" s="610"/>
+      <c r="H177" s="644"/>
     </row>
     <row r="178" spans="1:8" ht="15.75" customHeight="1">
       <c r="A178" s="125" t="s">
@@ -31657,10 +31657,10 @@
       <c r="D178" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E178" s="582"/>
-      <c r="F178" s="583"/>
+      <c r="E178" s="576"/>
+      <c r="F178" s="577"/>
       <c r="G178" s="125"/>
-      <c r="H178" s="610"/>
+      <c r="H178" s="644"/>
     </row>
     <row r="179" spans="1:8" ht="15.75" customHeight="1">
       <c r="A179" s="125" t="s">
@@ -31675,12 +31675,12 @@
       <c r="D179" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E179" s="582"/>
-      <c r="F179" s="583"/>
+      <c r="E179" s="576"/>
+      <c r="F179" s="577"/>
       <c r="G179" s="132" t="s">
         <v>431</v>
       </c>
-      <c r="H179" s="610"/>
+      <c r="H179" s="644"/>
     </row>
     <row r="180" spans="1:8" ht="15.75" customHeight="1">
       <c r="A180" s="125" t="s">
@@ -31695,10 +31695,10 @@
       <c r="D180" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E180" s="582"/>
-      <c r="F180" s="583"/>
+      <c r="E180" s="576"/>
+      <c r="F180" s="577"/>
       <c r="G180" s="125"/>
-      <c r="H180" s="610"/>
+      <c r="H180" s="644"/>
     </row>
     <row r="181" spans="1:8" ht="15.75" customHeight="1">
       <c r="A181" s="125" t="s">
@@ -31713,10 +31713,10 @@
       <c r="D181" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E181" s="582"/>
-      <c r="F181" s="583"/>
+      <c r="E181" s="576"/>
+      <c r="F181" s="577"/>
       <c r="G181" s="125"/>
-      <c r="H181" s="610"/>
+      <c r="H181" s="644"/>
     </row>
     <row r="182" spans="1:8" ht="15.75" customHeight="1">
       <c r="A182" s="125" t="s">
@@ -31731,10 +31731,10 @@
       <c r="D182" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E182" s="582"/>
-      <c r="F182" s="583"/>
+      <c r="E182" s="576"/>
+      <c r="F182" s="577"/>
       <c r="G182" s="125"/>
-      <c r="H182" s="610"/>
+      <c r="H182" s="644"/>
     </row>
     <row r="183" spans="1:8" ht="15.75" customHeight="1">
       <c r="A183" s="125" t="s">
@@ -31749,10 +31749,10 @@
       <c r="D183" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E183" s="582"/>
-      <c r="F183" s="583"/>
+      <c r="E183" s="576"/>
+      <c r="F183" s="577"/>
       <c r="G183" s="125"/>
-      <c r="H183" s="610"/>
+      <c r="H183" s="644"/>
     </row>
     <row r="184" spans="1:8" ht="15.75" customHeight="1">
       <c r="A184" s="125" t="s">
@@ -31767,10 +31767,10 @@
       <c r="D184" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E184" s="582"/>
-      <c r="F184" s="583"/>
+      <c r="E184" s="576"/>
+      <c r="F184" s="577"/>
       <c r="G184" s="125"/>
-      <c r="H184" s="610"/>
+      <c r="H184" s="644"/>
     </row>
     <row r="185" spans="1:8" ht="15.75" customHeight="1">
       <c r="A185" s="125" t="s">
@@ -31785,10 +31785,10 @@
       <c r="D185" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E185" s="582"/>
-      <c r="F185" s="583"/>
+      <c r="E185" s="576"/>
+      <c r="F185" s="577"/>
       <c r="G185" s="125"/>
-      <c r="H185" s="610"/>
+      <c r="H185" s="644"/>
     </row>
     <row r="186" spans="1:8" ht="15.75" customHeight="1">
       <c r="A186" s="125" t="s">
@@ -31803,10 +31803,10 @@
       <c r="D186" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E186" s="582"/>
-      <c r="F186" s="583"/>
+      <c r="E186" s="576"/>
+      <c r="F186" s="577"/>
       <c r="G186" s="125"/>
-      <c r="H186" s="610"/>
+      <c r="H186" s="644"/>
     </row>
     <row r="187" spans="1:8" ht="15.75" customHeight="1">
       <c r="A187" s="125" t="s">
@@ -31821,12 +31821,12 @@
       <c r="D187" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E187" s="582"/>
-      <c r="F187" s="583"/>
+      <c r="E187" s="576"/>
+      <c r="F187" s="577"/>
       <c r="G187" s="133" t="s">
         <v>440</v>
       </c>
-      <c r="H187" s="610"/>
+      <c r="H187" s="644"/>
     </row>
     <row r="188" spans="1:8" ht="15.75" customHeight="1">
       <c r="A188" s="125" t="s">
@@ -31841,10 +31841,10 @@
       <c r="D188" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E188" s="582"/>
-      <c r="F188" s="583"/>
+      <c r="E188" s="576"/>
+      <c r="F188" s="577"/>
       <c r="G188" s="125"/>
-      <c r="H188" s="610"/>
+      <c r="H188" s="644"/>
     </row>
     <row r="189" spans="1:8" ht="15.75" customHeight="1">
       <c r="A189" s="125" t="s">
@@ -31859,10 +31859,10 @@
       <c r="D189" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E189" s="582"/>
-      <c r="F189" s="583"/>
+      <c r="E189" s="576"/>
+      <c r="F189" s="577"/>
       <c r="G189" s="125"/>
-      <c r="H189" s="610"/>
+      <c r="H189" s="644"/>
     </row>
     <row r="190" spans="1:8" ht="15.75" customHeight="1">
       <c r="A190" s="125" t="s">
@@ -31877,10 +31877,10 @@
       <c r="D190" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E190" s="582"/>
-      <c r="F190" s="583"/>
+      <c r="E190" s="576"/>
+      <c r="F190" s="577"/>
       <c r="G190" s="125"/>
-      <c r="H190" s="610"/>
+      <c r="H190" s="644"/>
     </row>
     <row r="191" spans="1:8" ht="15.75" customHeight="1">
       <c r="A191" s="125" t="s">
@@ -31895,10 +31895,10 @@
       <c r="D191" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E191" s="582"/>
-      <c r="F191" s="583"/>
+      <c r="E191" s="576"/>
+      <c r="F191" s="577"/>
       <c r="G191" s="125"/>
-      <c r="H191" s="610"/>
+      <c r="H191" s="644"/>
     </row>
     <row r="192" spans="1:8" ht="15.75" customHeight="1">
       <c r="A192" s="125" t="s">
@@ -31913,10 +31913,10 @@
       <c r="D192" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E192" s="582"/>
-      <c r="F192" s="583"/>
+      <c r="E192" s="576"/>
+      <c r="F192" s="577"/>
       <c r="G192" s="125"/>
-      <c r="H192" s="610"/>
+      <c r="H192" s="644"/>
     </row>
     <row r="193" spans="1:8" ht="15.75" customHeight="1">
       <c r="A193" s="125" t="s">
@@ -31931,10 +31931,10 @@
       <c r="D193" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E193" s="582"/>
-      <c r="F193" s="583"/>
+      <c r="E193" s="576"/>
+      <c r="F193" s="577"/>
       <c r="G193" s="125"/>
-      <c r="H193" s="610"/>
+      <c r="H193" s="644"/>
     </row>
     <row r="194" spans="1:8" ht="15.75" customHeight="1">
       <c r="A194" s="125" t="s">
@@ -31949,12 +31949,12 @@
       <c r="D194" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E194" s="582"/>
-      <c r="F194" s="583"/>
+      <c r="E194" s="576"/>
+      <c r="F194" s="577"/>
       <c r="G194" s="133" t="s">
         <v>170</v>
       </c>
-      <c r="H194" s="610"/>
+      <c r="H194" s="644"/>
     </row>
     <row r="195" spans="1:8" ht="15.75" customHeight="1">
       <c r="A195" s="125" t="s">
@@ -31969,10 +31969,10 @@
       <c r="D195" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E195" s="582"/>
-      <c r="F195" s="583"/>
+      <c r="E195" s="576"/>
+      <c r="F195" s="577"/>
       <c r="G195" s="125"/>
-      <c r="H195" s="610"/>
+      <c r="H195" s="644"/>
     </row>
     <row r="196" spans="1:8" ht="15.75" customHeight="1">
       <c r="A196" s="125" t="s">
@@ -31987,12 +31987,12 @@
       <c r="D196" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E196" s="582"/>
-      <c r="F196" s="583"/>
+      <c r="E196" s="576"/>
+      <c r="F196" s="577"/>
       <c r="G196" s="133" t="s">
         <v>170</v>
       </c>
-      <c r="H196" s="610"/>
+      <c r="H196" s="644"/>
     </row>
     <row r="197" spans="1:8" ht="15.75" customHeight="1">
       <c r="A197" s="125" t="s">
@@ -32007,12 +32007,12 @@
       <c r="D197" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E197" s="582"/>
-      <c r="F197" s="583"/>
+      <c r="E197" s="576"/>
+      <c r="F197" s="577"/>
       <c r="G197" s="133" t="s">
         <v>451</v>
       </c>
-      <c r="H197" s="610"/>
+      <c r="H197" s="644"/>
     </row>
     <row r="198" spans="1:8" ht="15.75" customHeight="1">
       <c r="A198" s="125" t="s">
@@ -32027,10 +32027,10 @@
       <c r="D198" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E198" s="582"/>
-      <c r="F198" s="583"/>
+      <c r="E198" s="576"/>
+      <c r="F198" s="577"/>
       <c r="G198" s="125"/>
-      <c r="H198" s="610"/>
+      <c r="H198" s="644"/>
     </row>
     <row r="199" spans="1:8" ht="15.75" customHeight="1">
       <c r="A199" s="125" t="s">
@@ -32045,10 +32045,10 @@
       <c r="D199" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E199" s="582"/>
-      <c r="F199" s="583"/>
+      <c r="E199" s="576"/>
+      <c r="F199" s="577"/>
       <c r="G199" s="125"/>
-      <c r="H199" s="610"/>
+      <c r="H199" s="644"/>
     </row>
     <row r="200" spans="1:8" ht="15.75" customHeight="1">
       <c r="A200" s="127" t="s">
@@ -32063,10 +32063,10 @@
       <c r="D200" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E200" s="582"/>
-      <c r="F200" s="583"/>
+      <c r="E200" s="576"/>
+      <c r="F200" s="577"/>
       <c r="G200" s="125"/>
-      <c r="H200" s="610"/>
+      <c r="H200" s="644"/>
     </row>
     <row r="201" spans="1:8" ht="15.75" customHeight="1">
       <c r="A201" s="127" t="s">
@@ -32081,10 +32081,10 @@
       <c r="D201" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E201" s="582"/>
-      <c r="F201" s="583"/>
+      <c r="E201" s="576"/>
+      <c r="F201" s="577"/>
       <c r="G201" s="125"/>
-      <c r="H201" s="610"/>
+      <c r="H201" s="644"/>
     </row>
     <row r="202" spans="1:8" ht="15.75" customHeight="1">
       <c r="A202" s="127" t="s">
@@ -32099,10 +32099,10 @@
       <c r="D202" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E202" s="582"/>
-      <c r="F202" s="583"/>
+      <c r="E202" s="576"/>
+      <c r="F202" s="577"/>
       <c r="G202" s="125"/>
-      <c r="H202" s="610"/>
+      <c r="H202" s="644"/>
     </row>
     <row r="203" spans="1:8" ht="15.75" customHeight="1">
       <c r="A203" s="127" t="s">
@@ -32117,10 +32117,10 @@
       <c r="D203" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E203" s="582"/>
-      <c r="F203" s="583"/>
+      <c r="E203" s="576"/>
+      <c r="F203" s="577"/>
       <c r="G203" s="125"/>
-      <c r="H203" s="610"/>
+      <c r="H203" s="644"/>
     </row>
     <row r="204" spans="1:8" ht="15.75" customHeight="1">
       <c r="A204" s="127" t="s">
@@ -32135,10 +32135,10 @@
       <c r="D204" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E204" s="582"/>
-      <c r="F204" s="583"/>
+      <c r="E204" s="576"/>
+      <c r="F204" s="577"/>
       <c r="G204" s="125"/>
-      <c r="H204" s="610"/>
+      <c r="H204" s="644"/>
     </row>
     <row r="205" spans="1:8" ht="15.75" customHeight="1">
       <c r="A205" s="127" t="s">
@@ -32153,10 +32153,10 @@
       <c r="D205" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E205" s="582"/>
-      <c r="F205" s="583"/>
+      <c r="E205" s="576"/>
+      <c r="F205" s="577"/>
       <c r="G205" s="125"/>
-      <c r="H205" s="610"/>
+      <c r="H205" s="644"/>
     </row>
     <row r="206" spans="1:8" ht="15.75" customHeight="1">
       <c r="A206" s="127" t="s">
@@ -32171,10 +32171,10 @@
       <c r="D206" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E206" s="582"/>
-      <c r="F206" s="583"/>
+      <c r="E206" s="576"/>
+      <c r="F206" s="577"/>
       <c r="G206" s="125"/>
-      <c r="H206" s="610"/>
+      <c r="H206" s="644"/>
     </row>
     <row r="207" spans="1:8" ht="15.75" customHeight="1">
       <c r="A207" s="127" t="s">
@@ -32189,10 +32189,10 @@
       <c r="D207" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E207" s="582"/>
-      <c r="F207" s="583"/>
+      <c r="E207" s="576"/>
+      <c r="F207" s="577"/>
       <c r="G207" s="125"/>
-      <c r="H207" s="610"/>
+      <c r="H207" s="644"/>
     </row>
     <row r="208" spans="1:8" ht="15.75" customHeight="1">
       <c r="A208" s="127" t="s">
@@ -32207,17 +32207,17 @@
       <c r="D208" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E208" s="582"/>
-      <c r="F208" s="583"/>
+      <c r="E208" s="576"/>
+      <c r="F208" s="577"/>
       <c r="G208" s="125"/>
-      <c r="H208" s="610"/>
+      <c r="H208" s="644"/>
     </row>
     <row r="209" spans="1:8" ht="12.75" customHeight="1">
-      <c r="A209" s="633" t="s">
+      <c r="A209" s="608" t="s">
         <v>464</v>
       </c>
-      <c r="B209" s="604"/>
-      <c r="C209" s="644">
+      <c r="B209" s="593"/>
+      <c r="C209" s="621">
         <f>COUNTIFS($A160:$A208,"*",$C160:$C208,"*",$D160:$D208,"*")</f>
         <v>49</v>
       </c>
@@ -32231,12 +32231,12 @@
         <v>178</v>
       </c>
       <c r="G209" s="136"/>
-      <c r="H209" s="610"/>
+      <c r="H209" s="644"/>
     </row>
     <row r="210" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A210" s="615"/>
-      <c r="B210" s="616"/>
-      <c r="C210" s="645"/>
+      <c r="A210" s="609"/>
+      <c r="B210" s="610"/>
+      <c r="C210" s="622"/>
       <c r="D210" s="123">
         <f>COUNTIFS($A160:$A208,"*",$C160:$C208,"*",$D160:$D208, "Employed")</f>
         <v>7</v>
@@ -32250,26 +32250,26 @@
         <v>13</v>
       </c>
       <c r="G210" s="124"/>
-      <c r="H210" s="610"/>
+      <c r="H210" s="644"/>
     </row>
     <row r="211" spans="1:8" ht="12.75" customHeight="1">
-      <c r="A211" s="646"/>
-      <c r="B211" s="647"/>
-      <c r="C211" s="647"/>
-      <c r="D211" s="647"/>
-      <c r="E211" s="647"/>
-      <c r="F211" s="648"/>
+      <c r="A211" s="623"/>
+      <c r="B211" s="624"/>
+      <c r="C211" s="624"/>
+      <c r="D211" s="624"/>
+      <c r="E211" s="624"/>
+      <c r="F211" s="625"/>
       <c r="G211" s="137" t="s">
         <v>152</v>
       </c>
       <c r="H211" s="64"/>
     </row>
     <row r="212" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A212" s="634" t="s">
+      <c r="A212" s="611" t="s">
         <v>465</v>
       </c>
-      <c r="B212" s="635"/>
-      <c r="C212" s="637">
+      <c r="B212" s="612"/>
+      <c r="C212" s="614">
         <f>SUM(D213:F213)</f>
         <v>182</v>
       </c>
@@ -32282,16 +32282,16 @@
       <c r="F212" s="138" t="s">
         <v>178</v>
       </c>
-      <c r="G212" s="649">
+      <c r="G212" s="626">
         <f>D213/C212</f>
         <v>0.45054945054945056</v>
       </c>
       <c r="H212" s="64"/>
     </row>
     <row r="213" spans="1:8" ht="17.25" customHeight="1">
-      <c r="A213" s="615"/>
-      <c r="B213" s="636"/>
-      <c r="C213" s="638"/>
+      <c r="A213" s="609"/>
+      <c r="B213" s="613"/>
+      <c r="C213" s="615"/>
       <c r="D213" s="139">
         <f>COUNTIFS($A23:$A210,"*",$C23:$C210,"*",$D23:$D210, "Employed")</f>
         <v>82</v>
@@ -32304,7 +32304,7 @@
         <f>COUNTIFS($A23:$A210,"*",$C23:$C210,"*",$D23:$D210, "Not Tracked")</f>
         <v>48</v>
       </c>
-      <c r="G213" s="650"/>
+      <c r="G213" s="627"/>
       <c r="H213" s="64"/>
     </row>
     <row r="214" spans="1:8" ht="15.75" customHeight="1">
@@ -33233,144 +33233,62 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="218">
-    <mergeCell ref="D109:F109"/>
-    <mergeCell ref="D110:F110"/>
-    <mergeCell ref="D111:F111"/>
-    <mergeCell ref="D112:F112"/>
-    <mergeCell ref="D113:F113"/>
-    <mergeCell ref="D114:F114"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="A209:B210"/>
-    <mergeCell ref="A212:B213"/>
-    <mergeCell ref="C212:C213"/>
-    <mergeCell ref="D116:F116"/>
-    <mergeCell ref="D117:F117"/>
-    <mergeCell ref="A157:B158"/>
-    <mergeCell ref="C157:C158"/>
-    <mergeCell ref="A159:G159"/>
-    <mergeCell ref="C209:C210"/>
-    <mergeCell ref="A211:F211"/>
-    <mergeCell ref="G212:G213"/>
-    <mergeCell ref="D100:F100"/>
-    <mergeCell ref="D101:F101"/>
-    <mergeCell ref="D102:F102"/>
-    <mergeCell ref="D103:F103"/>
-    <mergeCell ref="D104:F104"/>
-    <mergeCell ref="D105:F105"/>
-    <mergeCell ref="D106:F106"/>
-    <mergeCell ref="D107:F107"/>
-    <mergeCell ref="D108:F108"/>
-    <mergeCell ref="D91:F91"/>
-    <mergeCell ref="D92:F92"/>
-    <mergeCell ref="D93:F93"/>
-    <mergeCell ref="D94:F94"/>
-    <mergeCell ref="D95:F95"/>
-    <mergeCell ref="D96:F96"/>
-    <mergeCell ref="D97:F97"/>
-    <mergeCell ref="D98:F98"/>
-    <mergeCell ref="D99:F99"/>
-    <mergeCell ref="D82:F82"/>
-    <mergeCell ref="D83:F83"/>
-    <mergeCell ref="D84:F84"/>
-    <mergeCell ref="D85:F85"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D87:F87"/>
-    <mergeCell ref="D88:F88"/>
-    <mergeCell ref="D89:F89"/>
-    <mergeCell ref="D90:F90"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="D76:F76"/>
-    <mergeCell ref="D77:F77"/>
-    <mergeCell ref="D78:F78"/>
-    <mergeCell ref="D79:F79"/>
-    <mergeCell ref="D80:F80"/>
-    <mergeCell ref="D81:F81"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="D67:F67"/>
-    <mergeCell ref="D68:F68"/>
-    <mergeCell ref="D69:F69"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D11:F11"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="H12:H19"/>
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B4:H4"/>
-    <mergeCell ref="B5:H5"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:H7"/>
-    <mergeCell ref="D13:F13"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D207:F207"/>
-    <mergeCell ref="D208:F208"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="H23:H210"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D193:F193"/>
-    <mergeCell ref="D194:F194"/>
-    <mergeCell ref="D195:F195"/>
-    <mergeCell ref="D196:F196"/>
-    <mergeCell ref="D197:F197"/>
-    <mergeCell ref="D198:F198"/>
-    <mergeCell ref="D199:F199"/>
+    <mergeCell ref="D118:F118"/>
+    <mergeCell ref="D119:F119"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="D121:F121"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="D123:F123"/>
+    <mergeCell ref="D124:F124"/>
+    <mergeCell ref="D125:F125"/>
+    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="D128:F128"/>
+    <mergeCell ref="D129:F129"/>
+    <mergeCell ref="D130:F130"/>
+    <mergeCell ref="D131:F131"/>
+    <mergeCell ref="D132:F132"/>
+    <mergeCell ref="D133:F133"/>
+    <mergeCell ref="D134:F134"/>
+    <mergeCell ref="D135:F135"/>
+    <mergeCell ref="D136:F136"/>
+    <mergeCell ref="D137:F137"/>
+    <mergeCell ref="D138:F138"/>
+    <mergeCell ref="D139:F139"/>
+    <mergeCell ref="D140:F140"/>
+    <mergeCell ref="D141:F141"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="D148:F148"/>
+    <mergeCell ref="D149:F149"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="D151:F151"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D155:F155"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D184:F184"/>
+    <mergeCell ref="D185:F185"/>
+    <mergeCell ref="D168:F168"/>
+    <mergeCell ref="D169:F169"/>
+    <mergeCell ref="D170:F170"/>
+    <mergeCell ref="D171:F171"/>
+    <mergeCell ref="D172:F172"/>
+    <mergeCell ref="D173:F173"/>
+    <mergeCell ref="D174:F174"/>
+    <mergeCell ref="D175:F175"/>
+    <mergeCell ref="D176:F176"/>
     <mergeCell ref="D200:F200"/>
     <mergeCell ref="D201:F201"/>
     <mergeCell ref="D202:F202"/>
@@ -33395,62 +33313,144 @@
     <mergeCell ref="D181:F181"/>
     <mergeCell ref="D182:F182"/>
     <mergeCell ref="D183:F183"/>
-    <mergeCell ref="D184:F184"/>
-    <mergeCell ref="D185:F185"/>
-    <mergeCell ref="D168:F168"/>
-    <mergeCell ref="D169:F169"/>
-    <mergeCell ref="D170:F170"/>
-    <mergeCell ref="D171:F171"/>
-    <mergeCell ref="D172:F172"/>
-    <mergeCell ref="D173:F173"/>
-    <mergeCell ref="D174:F174"/>
-    <mergeCell ref="D175:F175"/>
-    <mergeCell ref="D176:F176"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D155:F155"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="D148:F148"/>
-    <mergeCell ref="D149:F149"/>
-    <mergeCell ref="D150:F150"/>
-    <mergeCell ref="D151:F151"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="D136:F136"/>
-    <mergeCell ref="D137:F137"/>
-    <mergeCell ref="D138:F138"/>
-    <mergeCell ref="D139:F139"/>
-    <mergeCell ref="D140:F140"/>
-    <mergeCell ref="D141:F141"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="D127:F127"/>
-    <mergeCell ref="D128:F128"/>
-    <mergeCell ref="D129:F129"/>
-    <mergeCell ref="D130:F130"/>
-    <mergeCell ref="D131:F131"/>
-    <mergeCell ref="D132:F132"/>
-    <mergeCell ref="D133:F133"/>
-    <mergeCell ref="D134:F134"/>
-    <mergeCell ref="D135:F135"/>
-    <mergeCell ref="D118:F118"/>
-    <mergeCell ref="D119:F119"/>
-    <mergeCell ref="D120:F120"/>
-    <mergeCell ref="D121:F121"/>
-    <mergeCell ref="D122:F122"/>
-    <mergeCell ref="D123:F123"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="D125:F125"/>
-    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H4"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:H7"/>
+    <mergeCell ref="D13:F13"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="C18:C19"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="D11:F11"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="H12:H19"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="H23:H210"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="D193:F193"/>
+    <mergeCell ref="D194:F194"/>
+    <mergeCell ref="D195:F195"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D33:F33"/>
+    <mergeCell ref="D34:F34"/>
+    <mergeCell ref="D35:F35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="D37:F37"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="D67:F67"/>
+    <mergeCell ref="D68:F68"/>
+    <mergeCell ref="D69:F69"/>
+    <mergeCell ref="D70:F70"/>
+    <mergeCell ref="D71:F71"/>
+    <mergeCell ref="D72:F72"/>
+    <mergeCell ref="D73:F73"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="D76:F76"/>
+    <mergeCell ref="D77:F77"/>
+    <mergeCell ref="D78:F78"/>
+    <mergeCell ref="D79:F79"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="D81:F81"/>
+    <mergeCell ref="D82:F82"/>
+    <mergeCell ref="D83:F83"/>
+    <mergeCell ref="D84:F84"/>
+    <mergeCell ref="D85:F85"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="D88:F88"/>
+    <mergeCell ref="D89:F89"/>
+    <mergeCell ref="D90:F90"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="D93:F93"/>
+    <mergeCell ref="D94:F94"/>
+    <mergeCell ref="D95:F95"/>
+    <mergeCell ref="D96:F96"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="D98:F98"/>
+    <mergeCell ref="D99:F99"/>
+    <mergeCell ref="D100:F100"/>
+    <mergeCell ref="D101:F101"/>
+    <mergeCell ref="D102:F102"/>
+    <mergeCell ref="D103:F103"/>
+    <mergeCell ref="D104:F104"/>
+    <mergeCell ref="D105:F105"/>
+    <mergeCell ref="D106:F106"/>
+    <mergeCell ref="D107:F107"/>
+    <mergeCell ref="D108:F108"/>
+    <mergeCell ref="D109:F109"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="D111:F111"/>
+    <mergeCell ref="D112:F112"/>
+    <mergeCell ref="D113:F113"/>
+    <mergeCell ref="D114:F114"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="A209:B210"/>
+    <mergeCell ref="A212:B213"/>
+    <mergeCell ref="C212:C213"/>
+    <mergeCell ref="D116:F116"/>
+    <mergeCell ref="D117:F117"/>
+    <mergeCell ref="A157:B158"/>
+    <mergeCell ref="C157:C158"/>
+    <mergeCell ref="A159:G159"/>
+    <mergeCell ref="C209:C210"/>
+    <mergeCell ref="A211:F211"/>
+    <mergeCell ref="G212:G213"/>
+    <mergeCell ref="D207:F207"/>
+    <mergeCell ref="D208:F208"/>
+    <mergeCell ref="D196:F196"/>
+    <mergeCell ref="D197:F197"/>
+    <mergeCell ref="D198:F198"/>
+    <mergeCell ref="D199:F199"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -33480,51 +33480,51 @@
       <c r="B1" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="584" t="s">
+      <c r="C1" s="604" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="585"/>
-      <c r="E1" s="586"/>
+      <c r="D1" s="595"/>
+      <c r="E1" s="605"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="12"/>
       <c r="B2" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="587" t="s">
+      <c r="C2" s="606" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="588"/>
-      <c r="E2" s="589"/>
+      <c r="E2" s="597"/>
     </row>
     <row r="3" spans="1:5" ht="27.75" customHeight="1">
       <c r="A3" s="14"/>
       <c r="B3" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="590" t="s">
+      <c r="C3" s="587" t="s">
         <v>469</v>
       </c>
       <c r="D3" s="588"/>
-      <c r="E3" s="589"/>
+      <c r="E3" s="597"/>
     </row>
     <row r="4" spans="1:5" ht="103.5" customHeight="1">
       <c r="A4" s="17"/>
       <c r="B4" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="590" t="s">
+      <c r="C4" s="587" t="s">
         <v>470</v>
       </c>
       <c r="D4" s="588"/>
-      <c r="E4" s="589"/>
+      <c r="E4" s="597"/>
     </row>
     <row r="5" spans="1:5" ht="66" customHeight="1">
       <c r="A5" s="12"/>
       <c r="B5" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="590" t="str">
+      <c r="C5" s="587" t="str">
         <f>'Reference Matrix'!$E8</f>
         <v>References in determining the disciplines/programs identified as priority offerings:
 a. CMO No. 5, s. 2019
@@ -33533,14 +33533,14 @@
 d. RDC Resolutions</v>
       </c>
       <c r="D5" s="588"/>
-      <c r="E5" s="589"/>
+      <c r="E5" s="597"/>
     </row>
     <row r="6" spans="1:5" ht="103.5" customHeight="1">
       <c r="A6" s="12"/>
       <c r="B6" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="590" t="str">
+      <c r="C6" s="587" t="str">
         <f>'Reference Matrix'!$F8</f>
         <v>1. Duly certified enrollment report for the 1st Semester of AY 2023-2024 per campus
 2. Summary of Enrolment by identified priority undergraduate programs, and all other programs per campus
@@ -33548,80 +33548,80 @@
 4. For programs considered priority outside those identified by CHED, submit certification, resolution from RDC or similar Government Councils, etc.</v>
       </c>
       <c r="D6" s="588"/>
-      <c r="E6" s="589"/>
+      <c r="E6" s="597"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1">
       <c r="A7" s="18"/>
       <c r="B7" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="591" t="s">
+      <c r="C7" s="598" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="592"/>
-      <c r="E7" s="593"/>
+      <c r="D7" s="599"/>
+      <c r="E7" s="586"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="20"/>
       <c r="B8" s="20"/>
-      <c r="C8" s="590"/>
+      <c r="C8" s="587"/>
       <c r="D8" s="588"/>
       <c r="E8" s="588"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A9" s="601" t="s">
+      <c r="A9" s="589" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="576"/>
-      <c r="C9" s="576"/>
-      <c r="D9" s="576"/>
-      <c r="E9" s="577"/>
+      <c r="B9" s="579"/>
+      <c r="C9" s="579"/>
+      <c r="D9" s="579"/>
+      <c r="E9" s="580"/>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A10" s="602">
+      <c r="A10" s="590">
         <v>1</v>
       </c>
-      <c r="B10" s="595"/>
-      <c r="C10" s="651">
+      <c r="B10" s="591"/>
+      <c r="C10" s="662">
         <v>2</v>
       </c>
-      <c r="D10" s="595"/>
+      <c r="D10" s="591"/>
       <c r="E10" s="23">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A11" s="603" t="s">
+      <c r="A11" s="592" t="s">
         <v>117</v>
       </c>
-      <c r="B11" s="604"/>
-      <c r="C11" s="654" t="s">
+      <c r="B11" s="593"/>
+      <c r="C11" s="660" t="s">
         <v>471</v>
       </c>
-      <c r="D11" s="583"/>
-      <c r="E11" s="655" t="s">
+      <c r="D11" s="577"/>
+      <c r="E11" s="661" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A12" s="652"/>
-      <c r="B12" s="653"/>
+      <c r="A12" s="654"/>
+      <c r="B12" s="655"/>
       <c r="C12" s="146" t="s">
         <v>472</v>
       </c>
       <c r="D12" s="146" t="s">
         <v>473</v>
       </c>
-      <c r="E12" s="631"/>
+      <c r="E12" s="645"/>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A13" s="605" t="s">
+      <c r="A13" s="594" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="585"/>
-      <c r="C13" s="585"/>
-      <c r="D13" s="595"/>
-      <c r="E13" s="606" t="s">
+      <c r="B13" s="595"/>
+      <c r="C13" s="595"/>
+      <c r="D13" s="591"/>
+      <c r="E13" s="596" t="s">
         <v>474</v>
       </c>
     </row>
@@ -33636,7 +33636,7 @@
       <c r="D14" s="30">
         <v>85</v>
       </c>
-      <c r="E14" s="589"/>
+      <c r="E14" s="597"/>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1">
       <c r="A15" s="31">
@@ -33649,7 +33649,7 @@
         <v>165</v>
       </c>
       <c r="D15" s="30"/>
-      <c r="E15" s="589"/>
+      <c r="E15" s="597"/>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1">
       <c r="A16" s="31">
@@ -33662,7 +33662,7 @@
         <v>134</v>
       </c>
       <c r="D16" s="30"/>
-      <c r="E16" s="589"/>
+      <c r="E16" s="597"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1">
       <c r="A17" s="31">
@@ -33675,7 +33675,7 @@
         <v>199</v>
       </c>
       <c r="D17" s="30"/>
-      <c r="E17" s="589"/>
+      <c r="E17" s="597"/>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1">
       <c r="A18" s="31">
@@ -33688,7 +33688,7 @@
         <v>223</v>
       </c>
       <c r="D18" s="30"/>
-      <c r="E18" s="589"/>
+      <c r="E18" s="597"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1">
       <c r="A19" s="33">
@@ -33701,60 +33701,60 @@
         <v>321</v>
       </c>
       <c r="D19" s="36"/>
-      <c r="E19" s="580"/>
+      <c r="E19" s="583"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1">
       <c r="A20" s="20"/>
       <c r="B20" s="20"/>
-      <c r="C20" s="590"/>
+      <c r="C20" s="587"/>
       <c r="D20" s="588"/>
       <c r="E20" s="588"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A21" s="594">
+      <c r="A21" s="600">
         <v>1</v>
       </c>
-      <c r="B21" s="595"/>
-      <c r="C21" s="656">
+      <c r="B21" s="591"/>
+      <c r="C21" s="657">
         <v>2</v>
       </c>
-      <c r="D21" s="595"/>
+      <c r="D21" s="591"/>
       <c r="E21" s="39">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="661" t="s">
+      <c r="A22" s="653" t="s">
         <v>117</v>
       </c>
-      <c r="B22" s="604"/>
-      <c r="C22" s="657" t="s">
+      <c r="B22" s="593"/>
+      <c r="C22" s="658" t="s">
         <v>471</v>
       </c>
-      <c r="D22" s="640"/>
-      <c r="E22" s="658" t="s">
+      <c r="D22" s="617"/>
+      <c r="E22" s="659" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="652"/>
-      <c r="B23" s="653"/>
+      <c r="A23" s="654"/>
+      <c r="B23" s="655"/>
       <c r="C23" s="148" t="s">
         <v>472</v>
       </c>
       <c r="D23" s="149" t="s">
         <v>473</v>
       </c>
-      <c r="E23" s="631"/>
+      <c r="E23" s="645"/>
     </row>
     <row r="24" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A24" s="598" t="s">
+      <c r="A24" s="603" t="s">
         <v>476</v>
       </c>
-      <c r="B24" s="585"/>
-      <c r="C24" s="585"/>
-      <c r="D24" s="595"/>
-      <c r="E24" s="662"/>
+      <c r="B24" s="595"/>
+      <c r="C24" s="595"/>
+      <c r="D24" s="591"/>
+      <c r="E24" s="656"/>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1">
       <c r="A25" s="150">
@@ -33767,7 +33767,7 @@
         <v>431</v>
       </c>
       <c r="D25" s="151"/>
-      <c r="E25" s="610"/>
+      <c r="E25" s="644"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1">
       <c r="A26" s="150">
@@ -33780,7 +33780,7 @@
         <v>144</v>
       </c>
       <c r="D26" s="151"/>
-      <c r="E26" s="610"/>
+      <c r="E26" s="644"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1">
       <c r="A27" s="150">
@@ -33793,7 +33793,7 @@
         <v>161</v>
       </c>
       <c r="D27" s="151"/>
-      <c r="E27" s="610"/>
+      <c r="E27" s="644"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1">
       <c r="A28" s="150">
@@ -33806,7 +33806,7 @@
         <v>94</v>
       </c>
       <c r="D28" s="151"/>
-      <c r="E28" s="610"/>
+      <c r="E28" s="644"/>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1">
       <c r="A29" s="150">
@@ -33819,7 +33819,7 @@
         <v>161</v>
       </c>
       <c r="D29" s="151"/>
-      <c r="E29" s="610"/>
+      <c r="E29" s="644"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" customHeight="1">
       <c r="A30" s="150">
@@ -33832,7 +33832,7 @@
         <v>1673</v>
       </c>
       <c r="D30" s="151"/>
-      <c r="E30" s="610"/>
+      <c r="E30" s="644"/>
     </row>
     <row r="31" spans="1:5" ht="15.75" customHeight="1">
       <c r="A31" s="150">
@@ -33845,7 +33845,7 @@
         <v>729</v>
       </c>
       <c r="D31" s="151"/>
-      <c r="E31" s="610"/>
+      <c r="E31" s="644"/>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1">
       <c r="A32" s="150">
@@ -33858,7 +33858,7 @@
         <v>248</v>
       </c>
       <c r="D32" s="151"/>
-      <c r="E32" s="610"/>
+      <c r="E32" s="644"/>
     </row>
     <row r="33" spans="1:5" ht="15.75" customHeight="1">
       <c r="A33" s="150">
@@ -33871,7 +33871,7 @@
         <v>306</v>
       </c>
       <c r="D33" s="151"/>
-      <c r="E33" s="610"/>
+      <c r="E33" s="644"/>
     </row>
     <row r="34" spans="1:5" ht="15.75" customHeight="1">
       <c r="A34" s="150">
@@ -33884,7 +33884,7 @@
         <v>103</v>
       </c>
       <c r="D34" s="151"/>
-      <c r="E34" s="610"/>
+      <c r="E34" s="644"/>
     </row>
     <row r="35" spans="1:5" ht="15.75" customHeight="1">
       <c r="A35" s="150">
@@ -33897,7 +33897,7 @@
         <v>103</v>
       </c>
       <c r="D35" s="151"/>
-      <c r="E35" s="610"/>
+      <c r="E35" s="644"/>
     </row>
     <row r="36" spans="1:5" ht="15.75" customHeight="1">
       <c r="A36" s="150">
@@ -33910,7 +33910,7 @@
       <c r="D36" s="151">
         <v>162</v>
       </c>
-      <c r="E36" s="610"/>
+      <c r="E36" s="644"/>
     </row>
     <row r="37" spans="1:5" ht="15.75" customHeight="1">
       <c r="A37" s="150">
@@ -33923,7 +33923,7 @@
         <v>233</v>
       </c>
       <c r="D37" s="151"/>
-      <c r="E37" s="610"/>
+      <c r="E37" s="644"/>
     </row>
     <row r="38" spans="1:5" ht="15.75" customHeight="1">
       <c r="A38" s="150">
@@ -33936,7 +33936,7 @@
         <v>280</v>
       </c>
       <c r="D38" s="151"/>
-      <c r="E38" s="610"/>
+      <c r="E38" s="644"/>
     </row>
     <row r="39" spans="1:5" ht="15.75" customHeight="1">
       <c r="A39" s="150">
@@ -33949,7 +33949,7 @@
         <v>248</v>
       </c>
       <c r="D39" s="151"/>
-      <c r="E39" s="610"/>
+      <c r="E39" s="644"/>
     </row>
     <row r="40" spans="1:5" ht="15.75" customHeight="1">
       <c r="A40" s="150">
@@ -33962,7 +33962,7 @@
         <v>855</v>
       </c>
       <c r="D40" s="151"/>
-      <c r="E40" s="610"/>
+      <c r="E40" s="644"/>
     </row>
     <row r="41" spans="1:5" ht="15.75" customHeight="1">
       <c r="A41" s="150">
@@ -33975,7 +33975,7 @@
         <v>103</v>
       </c>
       <c r="D41" s="151"/>
-      <c r="E41" s="610"/>
+      <c r="E41" s="644"/>
     </row>
     <row r="42" spans="1:5" ht="15.75" customHeight="1">
       <c r="A42" s="150">
@@ -33988,7 +33988,7 @@
       <c r="D42" s="151">
         <v>290</v>
       </c>
-      <c r="E42" s="610"/>
+      <c r="E42" s="644"/>
     </row>
     <row r="43" spans="1:5" ht="15.75" customHeight="1">
       <c r="A43" s="150">
@@ -34001,7 +34001,7 @@
       <c r="D43" s="151">
         <v>304</v>
       </c>
-      <c r="E43" s="610"/>
+      <c r="E43" s="644"/>
     </row>
     <row r="44" spans="1:5" ht="15.75" customHeight="1">
       <c r="A44" s="150">
@@ -34014,7 +34014,7 @@
         <v>200</v>
       </c>
       <c r="D44" s="151"/>
-      <c r="E44" s="610"/>
+      <c r="E44" s="644"/>
     </row>
     <row r="45" spans="1:5" ht="15.75" customHeight="1">
       <c r="A45" s="150">
@@ -34027,7 +34027,7 @@
         <v>428</v>
       </c>
       <c r="D45" s="151"/>
-      <c r="E45" s="610"/>
+      <c r="E45" s="644"/>
     </row>
     <row r="46" spans="1:5" ht="15.75" customHeight="1">
       <c r="A46" s="150">
@@ -34040,7 +34040,7 @@
         <v>65</v>
       </c>
       <c r="D46" s="151"/>
-      <c r="E46" s="610"/>
+      <c r="E46" s="644"/>
     </row>
     <row r="47" spans="1:5" ht="15.75" customHeight="1">
       <c r="A47" s="150">
@@ -34051,16 +34051,16 @@
       </c>
       <c r="C47" s="151"/>
       <c r="D47" s="151"/>
-      <c r="E47" s="610"/>
+      <c r="E47" s="644"/>
     </row>
     <row r="48" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A48" s="643" t="s">
+      <c r="A48" s="620" t="s">
         <v>493</v>
       </c>
-      <c r="B48" s="582"/>
-      <c r="C48" s="582"/>
-      <c r="D48" s="583"/>
-      <c r="E48" s="609"/>
+      <c r="B48" s="576"/>
+      <c r="C48" s="576"/>
+      <c r="D48" s="577"/>
+      <c r="E48" s="650"/>
     </row>
     <row r="49" spans="1:5" ht="15.75" customHeight="1">
       <c r="A49" s="150">
@@ -34073,16 +34073,16 @@
         <v>393</v>
       </c>
       <c r="D49" s="43"/>
-      <c r="E49" s="610"/>
+      <c r="E49" s="644"/>
     </row>
     <row r="50" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A50" s="643" t="s">
+      <c r="A50" s="620" t="s">
         <v>494</v>
       </c>
-      <c r="B50" s="582"/>
-      <c r="C50" s="582"/>
-      <c r="D50" s="583"/>
-      <c r="E50" s="609"/>
+      <c r="B50" s="576"/>
+      <c r="C50" s="576"/>
+      <c r="D50" s="577"/>
+      <c r="E50" s="650"/>
     </row>
     <row r="51" spans="1:5" ht="15.75" customHeight="1">
       <c r="A51" s="150">
@@ -34095,7 +34095,7 @@
         <v>121</v>
       </c>
       <c r="D51" s="43"/>
-      <c r="E51" s="610"/>
+      <c r="E51" s="644"/>
     </row>
     <row r="52" spans="1:5" ht="15.75" customHeight="1">
       <c r="A52" s="150">
@@ -34108,7 +34108,7 @@
       <c r="D52" s="151">
         <v>222</v>
       </c>
-      <c r="E52" s="610"/>
+      <c r="E52" s="644"/>
     </row>
     <row r="53" spans="1:5" ht="15.75" customHeight="1">
       <c r="A53" s="150">
@@ -34121,7 +34121,7 @@
         <v>98</v>
       </c>
       <c r="D53" s="43"/>
-      <c r="E53" s="610"/>
+      <c r="E53" s="644"/>
     </row>
     <row r="54" spans="1:5" ht="15.75" customHeight="1">
       <c r="A54" s="150">
@@ -34134,7 +34134,7 @@
         <v>399</v>
       </c>
       <c r="D54" s="43"/>
-      <c r="E54" s="610"/>
+      <c r="E54" s="644"/>
     </row>
     <row r="55" spans="1:5" ht="15.75" customHeight="1">
       <c r="A55" s="54">
@@ -34147,16 +34147,16 @@
         <v>145</v>
       </c>
       <c r="D55" s="57"/>
-      <c r="E55" s="631"/>
+      <c r="E55" s="645"/>
     </row>
     <row r="56" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A56" s="643" t="s">
+      <c r="A56" s="620" t="s">
         <v>498</v>
       </c>
-      <c r="B56" s="582"/>
-      <c r="C56" s="582"/>
-      <c r="D56" s="583"/>
-      <c r="E56" s="609"/>
+      <c r="B56" s="576"/>
+      <c r="C56" s="576"/>
+      <c r="D56" s="577"/>
+      <c r="E56" s="650"/>
     </row>
     <row r="57" spans="1:5" ht="15.75" customHeight="1">
       <c r="A57" s="150">
@@ -34169,7 +34169,7 @@
       <c r="D57" s="151">
         <v>145</v>
       </c>
-      <c r="E57" s="610"/>
+      <c r="E57" s="644"/>
     </row>
     <row r="58" spans="1:5" ht="15.75" customHeight="1">
       <c r="A58" s="150">
@@ -34182,7 +34182,7 @@
         <v>96</v>
       </c>
       <c r="D58" s="43"/>
-      <c r="E58" s="610"/>
+      <c r="E58" s="644"/>
     </row>
     <row r="59" spans="1:5" ht="15.75" customHeight="1">
       <c r="A59" s="150">
@@ -34195,7 +34195,7 @@
         <v>1</v>
       </c>
       <c r="D59" s="43"/>
-      <c r="E59" s="610"/>
+      <c r="E59" s="644"/>
     </row>
     <row r="60" spans="1:5" ht="15.75" customHeight="1">
       <c r="A60" s="150">
@@ -34206,7 +34206,7 @@
       </c>
       <c r="C60" s="151"/>
       <c r="D60" s="151"/>
-      <c r="E60" s="610"/>
+      <c r="E60" s="644"/>
     </row>
     <row r="61" spans="1:5" ht="15.75" customHeight="1">
       <c r="A61" s="54">
@@ -34217,7 +34217,7 @@
       </c>
       <c r="C61" s="151"/>
       <c r="D61" s="151"/>
-      <c r="E61" s="631"/>
+      <c r="E61" s="645"/>
     </row>
     <row r="62" spans="1:5" ht="12.75" hidden="1" customHeight="1">
       <c r="A62" s="54"/>
@@ -34246,11 +34246,11 @@
       <c r="B64" s="156" t="s">
         <v>503</v>
       </c>
-      <c r="C64" s="659">
+      <c r="C64" s="651">
         <f>SUM(C63:D63)</f>
         <v>8941</v>
       </c>
-      <c r="D64" s="660"/>
+      <c r="D64" s="652"/>
       <c r="E64" s="61"/>
     </row>
     <row r="65" spans="1:5" ht="15" customHeight="1">
@@ -34258,11 +34258,11 @@
       <c r="B65" s="63" t="s">
         <v>152</v>
       </c>
-      <c r="C65" s="600">
+      <c r="C65" s="585">
         <f>C63/C64</f>
         <v>0.87439883681914776</v>
       </c>
-      <c r="D65" s="593"/>
+      <c r="D65" s="586"/>
       <c r="E65" s="61"/>
     </row>
     <row r="66" spans="1:5" ht="15.75" customHeight="1">
@@ -35300,6 +35300,27 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:B12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="E13:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:E23"/>
     <mergeCell ref="E50:E55"/>
     <mergeCell ref="E56:E61"/>
     <mergeCell ref="C64:D64"/>
@@ -35311,27 +35332,6 @@
     <mergeCell ref="E48:E49"/>
     <mergeCell ref="A50:D50"/>
     <mergeCell ref="A56:D56"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="A11:B12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="E13:E19"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -35362,13 +35362,13 @@
       <c r="B1" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="584" t="s">
+      <c r="C1" s="604" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="585"/>
-      <c r="E1" s="585"/>
-      <c r="F1" s="585"/>
-      <c r="G1" s="586"/>
+      <c r="D1" s="595"/>
+      <c r="E1" s="595"/>
+      <c r="F1" s="595"/>
+      <c r="G1" s="605"/>
       <c r="H1" s="157"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1">
@@ -35376,13 +35376,13 @@
       <c r="B2" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="587" t="s">
+      <c r="C2" s="606" t="s">
         <v>8</v>
       </c>
       <c r="D2" s="588"/>
       <c r="E2" s="588"/>
       <c r="F2" s="588"/>
-      <c r="G2" s="589"/>
+      <c r="G2" s="597"/>
       <c r="H2" s="157"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
@@ -35390,13 +35390,13 @@
       <c r="B3" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="590" t="s">
+      <c r="C3" s="587" t="s">
         <v>506</v>
       </c>
       <c r="D3" s="588"/>
       <c r="E3" s="588"/>
       <c r="F3" s="588"/>
-      <c r="G3" s="589"/>
+      <c r="G3" s="597"/>
       <c r="H3" s="157"/>
     </row>
     <row r="4" spans="1:8" ht="66" customHeight="1">
@@ -35404,13 +35404,13 @@
       <c r="B4" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="590" t="s">
+      <c r="C4" s="587" t="s">
         <v>507</v>
       </c>
       <c r="D4" s="588"/>
       <c r="E4" s="588"/>
       <c r="F4" s="588"/>
-      <c r="G4" s="589"/>
+      <c r="G4" s="597"/>
       <c r="H4" s="157"/>
     </row>
     <row r="5" spans="1:8" ht="27" customHeight="1">
@@ -35418,14 +35418,14 @@
       <c r="B5" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="590" t="str">
+      <c r="C5" s="587" t="str">
         <f>'Reference Matrix'!$E9</f>
         <v>Accreditation includes those issued by local and international bodies recognized by CHED; CMO No. 1, s. 2005; AACCUP (Level 1 - Level 4)</v>
       </c>
       <c r="D5" s="588"/>
       <c r="E5" s="588"/>
       <c r="F5" s="588"/>
-      <c r="G5" s="589"/>
+      <c r="G5" s="597"/>
       <c r="H5" s="157"/>
     </row>
     <row r="6" spans="1:8" ht="41.25" customHeight="1">
@@ -35433,7 +35433,7 @@
       <c r="B6" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="590" t="str">
+      <c r="C6" s="587" t="str">
         <f>'Reference Matrix'!$F9</f>
         <v>1. Accreditation Certificates
 2. List of all undergraduate programs per campus with accreditation (include date of validity) or without accreditation (include reasons for non-accreditation), and indicate year of initial operation of each of the programs being offered</v>
@@ -35441,7 +35441,7 @@
       <c r="D6" s="588"/>
       <c r="E6" s="588"/>
       <c r="F6" s="588"/>
-      <c r="G6" s="589"/>
+      <c r="G6" s="597"/>
       <c r="H6" s="157"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
@@ -35449,19 +35449,19 @@
       <c r="B7" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="591" t="s">
+      <c r="C7" s="598" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="592"/>
-      <c r="E7" s="592"/>
-      <c r="F7" s="592"/>
-      <c r="G7" s="593"/>
+      <c r="D7" s="599"/>
+      <c r="E7" s="599"/>
+      <c r="F7" s="599"/>
+      <c r="G7" s="586"/>
       <c r="H7" s="157"/>
     </row>
     <row r="8" spans="1:8" ht="15.75" customHeight="1">
       <c r="A8" s="20"/>
       <c r="B8" s="20"/>
-      <c r="C8" s="590"/>
+      <c r="C8" s="587"/>
       <c r="D8" s="588"/>
       <c r="E8" s="588"/>
       <c r="F8" s="588"/>
@@ -35469,81 +35469,81 @@
       <c r="H8" s="157"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A9" s="601" t="s">
+      <c r="A9" s="589" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="576"/>
-      <c r="C9" s="576"/>
-      <c r="D9" s="576"/>
-      <c r="E9" s="576"/>
-      <c r="F9" s="576"/>
-      <c r="G9" s="577"/>
+      <c r="B9" s="579"/>
+      <c r="C9" s="579"/>
+      <c r="D9" s="579"/>
+      <c r="E9" s="579"/>
+      <c r="F9" s="579"/>
+      <c r="G9" s="580"/>
       <c r="H9" s="157"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A10" s="602">
+      <c r="A10" s="590">
         <v>1</v>
       </c>
-      <c r="B10" s="595"/>
+      <c r="B10" s="591"/>
       <c r="C10" s="21">
         <v>2</v>
       </c>
       <c r="D10" s="22">
         <v>3</v>
       </c>
-      <c r="E10" s="651">
+      <c r="E10" s="662">
         <v>4</v>
       </c>
-      <c r="F10" s="585"/>
+      <c r="F10" s="595"/>
       <c r="G10" s="23">
         <v>5</v>
       </c>
       <c r="H10" s="157"/>
     </row>
     <row r="11" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A11" s="603" t="s">
+      <c r="A11" s="592" t="s">
         <v>508</v>
       </c>
-      <c r="B11" s="604"/>
-      <c r="C11" s="663" t="s">
+      <c r="B11" s="593"/>
+      <c r="C11" s="679" t="s">
         <v>509</v>
       </c>
-      <c r="D11" s="663" t="s">
+      <c r="D11" s="679" t="s">
         <v>510</v>
       </c>
-      <c r="E11" s="666" t="s">
+      <c r="E11" s="676" t="s">
         <v>511</v>
       </c>
       <c r="F11" s="588"/>
-      <c r="G11" s="655" t="s">
+      <c r="G11" s="661" t="s">
         <v>512</v>
       </c>
       <c r="H11" s="157"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A12" s="652"/>
-      <c r="B12" s="653"/>
-      <c r="C12" s="664"/>
-      <c r="D12" s="664"/>
+      <c r="A12" s="654"/>
+      <c r="B12" s="655"/>
+      <c r="C12" s="673"/>
+      <c r="D12" s="673"/>
       <c r="E12" s="158" t="s">
         <v>513</v>
       </c>
       <c r="F12" s="158" t="s">
         <v>514</v>
       </c>
-      <c r="G12" s="631"/>
+      <c r="G12" s="645"/>
       <c r="H12" s="157"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A13" s="605" t="s">
+      <c r="A13" s="594" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="585"/>
-      <c r="C13" s="585"/>
-      <c r="D13" s="585"/>
-      <c r="E13" s="585"/>
-      <c r="F13" s="585"/>
-      <c r="G13" s="586"/>
+      <c r="B13" s="595"/>
+      <c r="C13" s="595"/>
+      <c r="D13" s="595"/>
+      <c r="E13" s="595"/>
+      <c r="F13" s="595"/>
+      <c r="G13" s="605"/>
       <c r="H13" s="157"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
@@ -35685,7 +35685,7 @@
     <row r="20" spans="1:8" ht="15.75" customHeight="1">
       <c r="A20" s="20"/>
       <c r="B20" s="20"/>
-      <c r="C20" s="590"/>
+      <c r="C20" s="587"/>
       <c r="D20" s="588"/>
       <c r="E20" s="588"/>
       <c r="F20" s="588"/>
@@ -35693,69 +35693,69 @@
       <c r="H20" s="157"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A21" s="594">
+      <c r="A21" s="600">
         <v>1</v>
       </c>
-      <c r="B21" s="595"/>
+      <c r="B21" s="591"/>
       <c r="C21" s="37">
         <v>2</v>
       </c>
       <c r="D21" s="38">
         <v>3</v>
       </c>
-      <c r="E21" s="656">
+      <c r="E21" s="657">
         <v>4</v>
       </c>
-      <c r="F21" s="585"/>
+      <c r="F21" s="595"/>
       <c r="G21" s="39">
         <v>5</v>
       </c>
       <c r="H21" s="157"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A22" s="674" t="s">
+      <c r="A22" s="671" t="s">
         <v>508</v>
       </c>
-      <c r="B22" s="604"/>
-      <c r="C22" s="667" t="s">
+      <c r="B22" s="593"/>
+      <c r="C22" s="677" t="s">
         <v>509</v>
       </c>
-      <c r="D22" s="667" t="s">
+      <c r="D22" s="677" t="s">
         <v>510</v>
       </c>
-      <c r="E22" s="665" t="s">
+      <c r="E22" s="675" t="s">
         <v>525</v>
       </c>
       <c r="F22" s="588"/>
-      <c r="G22" s="668" t="s">
+      <c r="G22" s="678" t="s">
         <v>121</v>
       </c>
       <c r="H22" s="157"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A23" s="652"/>
-      <c r="B23" s="653"/>
-      <c r="C23" s="664"/>
-      <c r="D23" s="664"/>
+      <c r="A23" s="654"/>
+      <c r="B23" s="655"/>
+      <c r="C23" s="673"/>
+      <c r="D23" s="673"/>
       <c r="E23" s="169" t="s">
         <v>526</v>
       </c>
       <c r="F23" s="169" t="s">
         <v>527</v>
       </c>
-      <c r="G23" s="631"/>
+      <c r="G23" s="645"/>
       <c r="H23" s="157"/>
     </row>
     <row r="24" spans="1:8" ht="16.5" customHeight="1">
-      <c r="A24" s="598" t="s">
+      <c r="A24" s="603" t="s">
         <v>528</v>
       </c>
-      <c r="B24" s="585"/>
-      <c r="C24" s="585"/>
-      <c r="D24" s="585"/>
-      <c r="E24" s="585"/>
-      <c r="F24" s="585"/>
-      <c r="G24" s="586"/>
+      <c r="B24" s="595"/>
+      <c r="C24" s="595"/>
+      <c r="D24" s="595"/>
+      <c r="E24" s="595"/>
+      <c r="F24" s="595"/>
+      <c r="G24" s="605"/>
       <c r="H24" s="157"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
@@ -36287,15 +36287,15 @@
       <c r="H46" s="157"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A47" s="675" t="s">
+      <c r="A47" s="664" t="s">
         <v>592</v>
       </c>
-      <c r="B47" s="582"/>
-      <c r="C47" s="582"/>
-      <c r="D47" s="582"/>
-      <c r="E47" s="582"/>
-      <c r="F47" s="582"/>
-      <c r="G47" s="676"/>
+      <c r="B47" s="576"/>
+      <c r="C47" s="576"/>
+      <c r="D47" s="576"/>
+      <c r="E47" s="576"/>
+      <c r="F47" s="576"/>
+      <c r="G47" s="665"/>
       <c r="H47" s="157"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1">
@@ -36317,10 +36317,10 @@
       <c r="F48" s="199" t="s">
         <v>596</v>
       </c>
-      <c r="G48" s="677" t="s">
+      <c r="G48" s="672" t="s">
         <v>597</v>
       </c>
-      <c r="H48" s="679"/>
+      <c r="H48" s="663"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" customHeight="1">
       <c r="A49" s="150">
@@ -36341,7 +36341,7 @@
       <c r="F49" s="189">
         <v>45170</v>
       </c>
-      <c r="G49" s="664"/>
+      <c r="G49" s="673"/>
       <c r="H49" s="588"/>
     </row>
     <row r="50" spans="1:8" ht="15.75" customHeight="1">
@@ -36363,7 +36363,7 @@
       <c r="F50" s="189">
         <v>46174</v>
       </c>
-      <c r="G50" s="678"/>
+      <c r="G50" s="674"/>
       <c r="H50" s="588"/>
     </row>
     <row r="51" spans="1:8" ht="15.75" customHeight="1">
@@ -36391,15 +36391,15 @@
       <c r="H51" s="157"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A52" s="675" t="s">
+      <c r="A52" s="664" t="s">
         <v>451</v>
       </c>
-      <c r="B52" s="582"/>
-      <c r="C52" s="582"/>
-      <c r="D52" s="582"/>
-      <c r="E52" s="582"/>
-      <c r="F52" s="582"/>
-      <c r="G52" s="676"/>
+      <c r="B52" s="576"/>
+      <c r="C52" s="576"/>
+      <c r="D52" s="576"/>
+      <c r="E52" s="576"/>
+      <c r="F52" s="576"/>
+      <c r="G52" s="665"/>
       <c r="H52" s="157"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1">
@@ -36475,15 +36475,15 @@
       <c r="H55" s="157"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A56" s="675" t="s">
+      <c r="A56" s="664" t="s">
         <v>611</v>
       </c>
-      <c r="B56" s="582"/>
-      <c r="C56" s="582"/>
-      <c r="D56" s="582"/>
-      <c r="E56" s="582"/>
-      <c r="F56" s="582"/>
-      <c r="G56" s="676"/>
+      <c r="B56" s="576"/>
+      <c r="C56" s="576"/>
+      <c r="D56" s="576"/>
+      <c r="E56" s="576"/>
+      <c r="F56" s="576"/>
+      <c r="G56" s="665"/>
       <c r="H56" s="157"/>
     </row>
     <row r="57" spans="1:8" ht="15.75" customHeight="1">
@@ -36522,10 +36522,10 @@
     </row>
     <row r="59" spans="1:8" ht="15" customHeight="1">
       <c r="A59" s="211"/>
-      <c r="B59" s="669" t="s">
+      <c r="B59" s="666" t="s">
         <v>615</v>
       </c>
-      <c r="C59" s="648"/>
+      <c r="C59" s="625"/>
       <c r="D59" s="212">
         <f>COUNTIFS($B25:B58,"&lt;&gt;",D25:D58,"&lt;&gt;")</f>
         <v>30</v>
@@ -36537,10 +36537,10 @@
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1">
       <c r="A60" s="214"/>
-      <c r="B60" s="670" t="s">
+      <c r="B60" s="667" t="s">
         <v>616</v>
       </c>
-      <c r="C60" s="671"/>
+      <c r="C60" s="668"/>
       <c r="D60" s="215">
         <v>23</v>
       </c>
@@ -36551,10 +36551,10 @@
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1">
       <c r="A61" s="214"/>
-      <c r="B61" s="670" t="s">
+      <c r="B61" s="667" t="s">
         <v>617</v>
       </c>
-      <c r="C61" s="671"/>
+      <c r="C61" s="668"/>
       <c r="D61" s="215">
         <v>30</v>
       </c>
@@ -36565,10 +36565,10 @@
     </row>
     <row r="62" spans="1:8" ht="15" customHeight="1">
       <c r="A62" s="216"/>
-      <c r="B62" s="672" t="s">
+      <c r="B62" s="669" t="s">
         <v>152</v>
       </c>
-      <c r="C62" s="673"/>
+      <c r="C62" s="670"/>
       <c r="D62" s="217">
         <f>D60/D61</f>
         <v>0.76666666666666672</v>
@@ -39505,18 +39505,17 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="H48:H50"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="B59:C59"/>
-    <mergeCell ref="B60:C60"/>
-    <mergeCell ref="B61:C61"/>
-    <mergeCell ref="B62:C62"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="G48:G50"/>
-    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="E10:F10"/>
     <mergeCell ref="E11:F11"/>
     <mergeCell ref="G11:G12"/>
     <mergeCell ref="C20:G20"/>
@@ -39529,17 +39528,18 @@
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="A13:G13"/>
     <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="B61:C61"/>
+    <mergeCell ref="B62:C62"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="G48:G50"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="H48:H50"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="B59:C59"/>
+    <mergeCell ref="B60:C60"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D58" xr:uid="{00000000-0002-0000-0400-000000000000}">
@@ -39606,101 +39606,101 @@
       <c r="B1" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="584" t="s">
+      <c r="C1" s="604" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="585"/>
-      <c r="E1" s="586"/>
+      <c r="D1" s="595"/>
+      <c r="E1" s="605"/>
     </row>
     <row r="2" spans="1:5" ht="12.75" customHeight="1">
       <c r="A2" s="12"/>
       <c r="B2" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="587" t="s">
+      <c r="C2" s="606" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="588"/>
-      <c r="E2" s="589"/>
+      <c r="E2" s="597"/>
     </row>
     <row r="3" spans="1:5" ht="92.25" customHeight="1">
       <c r="A3" s="14"/>
       <c r="B3" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="590" t="s">
+      <c r="C3" s="587" t="s">
         <v>620</v>
       </c>
       <c r="D3" s="588"/>
-      <c r="E3" s="589"/>
+      <c r="E3" s="597"/>
     </row>
     <row r="4" spans="1:5" ht="66" customHeight="1">
       <c r="A4" s="17"/>
       <c r="B4" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="590" t="s">
+      <c r="C4" s="587" t="s">
         <v>621</v>
       </c>
       <c r="D4" s="588"/>
-      <c r="E4" s="589"/>
+      <c r="E4" s="597"/>
     </row>
     <row r="5" spans="1:5" ht="54" customHeight="1">
       <c r="A5" s="12"/>
       <c r="B5" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="590">
+      <c r="C5" s="587">
         <f>'[1]Reference Matrix'!$E11</f>
         <v>0</v>
       </c>
       <c r="D5" s="588"/>
-      <c r="E5" s="589"/>
+      <c r="E5" s="597"/>
     </row>
     <row r="6" spans="1:5" ht="12.75" customHeight="1">
       <c r="A6" s="12"/>
       <c r="B6" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="590">
+      <c r="C6" s="587">
         <f>'[1]Reference Matrix'!$F11</f>
         <v>0</v>
       </c>
       <c r="D6" s="588"/>
-      <c r="E6" s="589"/>
+      <c r="E6" s="597"/>
     </row>
     <row r="7" spans="1:5" ht="12.75" customHeight="1">
       <c r="A7" s="18"/>
       <c r="B7" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="591" t="s">
+      <c r="C7" s="598" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="592"/>
-      <c r="E7" s="593"/>
+      <c r="D7" s="599"/>
+      <c r="E7" s="586"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="20"/>
       <c r="B8" s="20"/>
-      <c r="C8" s="590"/>
+      <c r="C8" s="587"/>
       <c r="D8" s="588"/>
       <c r="E8" s="588"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A9" s="601" t="s">
+      <c r="A9" s="589" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="576"/>
-      <c r="C9" s="576"/>
-      <c r="D9" s="576"/>
-      <c r="E9" s="577"/>
+      <c r="B9" s="579"/>
+      <c r="C9" s="579"/>
+      <c r="D9" s="579"/>
+      <c r="E9" s="580"/>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A10" s="602">
+      <c r="A10" s="590">
         <v>1</v>
       </c>
-      <c r="B10" s="595"/>
+      <c r="B10" s="591"/>
       <c r="C10" s="21">
         <v>2</v>
       </c>
@@ -39712,10 +39712,10 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="40.5" customHeight="1">
-      <c r="A11" s="625" t="s">
+      <c r="A11" s="638" t="s">
         <v>622</v>
       </c>
-      <c r="B11" s="597"/>
+      <c r="B11" s="602"/>
       <c r="C11" s="218" t="s">
         <v>623</v>
       </c>
@@ -39829,15 +39829,15 @@
     <row r="18" spans="1:5" ht="15.75" customHeight="1">
       <c r="A18" s="20"/>
       <c r="B18" s="20"/>
-      <c r="C18" s="590"/>
+      <c r="C18" s="587"/>
       <c r="D18" s="588"/>
       <c r="E18" s="588"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A19" s="594">
+      <c r="A19" s="600">
         <v>1</v>
       </c>
-      <c r="B19" s="595"/>
+      <c r="B19" s="591"/>
       <c r="C19" s="37">
         <v>2</v>
       </c>
@@ -39849,10 +39849,10 @@
       </c>
     </row>
     <row r="20" spans="1:5" ht="25.5" customHeight="1">
-      <c r="A20" s="596" t="s">
+      <c r="A20" s="601" t="s">
         <v>622</v>
       </c>
-      <c r="B20" s="597"/>
+      <c r="B20" s="602"/>
       <c r="C20" s="226" t="s">
         <v>623</v>
       </c>
@@ -41363,51 +41363,51 @@
       <c r="B1" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="584" t="s">
+      <c r="C1" s="604" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="585"/>
-      <c r="E1" s="586"/>
+      <c r="D1" s="595"/>
+      <c r="E1" s="605"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
       <c r="A2" s="12"/>
       <c r="B2" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="587" t="s">
+      <c r="C2" s="606" t="s">
         <v>681</v>
       </c>
       <c r="D2" s="588"/>
-      <c r="E2" s="589"/>
+      <c r="E2" s="597"/>
     </row>
     <row r="3" spans="1:5" ht="40.5" customHeight="1">
       <c r="A3" s="14"/>
       <c r="B3" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="587" t="s">
+      <c r="C3" s="606" t="s">
         <v>682</v>
       </c>
       <c r="D3" s="588"/>
-      <c r="E3" s="589"/>
+      <c r="E3" s="597"/>
     </row>
     <row r="4" spans="1:5" ht="103.5" customHeight="1">
       <c r="A4" s="17"/>
       <c r="B4" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="590" t="s">
+      <c r="C4" s="587" t="s">
         <v>683</v>
       </c>
       <c r="D4" s="588"/>
-      <c r="E4" s="589"/>
+      <c r="E4" s="597"/>
     </row>
     <row r="5" spans="1:5" ht="77.25" customHeight="1">
       <c r="A5" s="12"/>
       <c r="B5" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="590" t="str">
+      <c r="C5" s="587" t="str">
         <f t="array" ref="C5">"For State Colleges and Professional Institutes:"&amp;CHAR(10)&amp;'Reference Matrix'!$E13</f>
         <v>For State Colleges and Professional Institutes:
 References in determining the disciplines/programs identified as priority offerings:
@@ -41417,14 +41417,14 @@
 d. RDC Resolutions</v>
       </c>
       <c r="D5" s="588"/>
-      <c r="E5" s="589"/>
+      <c r="E5" s="597"/>
     </row>
     <row r="6" spans="1:5" ht="78" customHeight="1">
       <c r="A6" s="12"/>
       <c r="B6" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="590" t="str">
+      <c r="C6" s="587" t="str">
         <f t="array" ref="C6">"For State Colleges and Professional Institutes:"&amp;CHAR(10)&amp;'Reference Matrix'!$F13</f>
         <v>For State Colleges and Professional Institutes:
 1. Duly certified enrollment report
@@ -41432,80 +41432,80 @@
 3. For programs considered priority outside those identified by the CHED, submit certification, resolution from RDC or similar Government Councils, etc.</v>
       </c>
       <c r="D6" s="588"/>
-      <c r="E6" s="589"/>
+      <c r="E6" s="597"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1">
       <c r="A7" s="18"/>
       <c r="B7" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="591" t="s">
+      <c r="C7" s="598" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="592"/>
-      <c r="E7" s="593"/>
+      <c r="D7" s="599"/>
+      <c r="E7" s="586"/>
     </row>
     <row r="8" spans="1:5" ht="15.75" customHeight="1">
       <c r="A8" s="20"/>
       <c r="B8" s="20"/>
-      <c r="C8" s="590"/>
+      <c r="C8" s="587"/>
       <c r="D8" s="588"/>
       <c r="E8" s="588"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A9" s="601" t="s">
+      <c r="A9" s="589" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="576"/>
-      <c r="C9" s="576"/>
-      <c r="D9" s="576"/>
-      <c r="E9" s="577"/>
+      <c r="B9" s="579"/>
+      <c r="C9" s="579"/>
+      <c r="D9" s="579"/>
+      <c r="E9" s="580"/>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A10" s="602">
+      <c r="A10" s="590">
         <v>1</v>
       </c>
-      <c r="B10" s="595"/>
-      <c r="C10" s="651">
+      <c r="B10" s="591"/>
+      <c r="C10" s="662">
         <v>2</v>
       </c>
-      <c r="D10" s="595"/>
+      <c r="D10" s="591"/>
       <c r="E10" s="23">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A11" s="603" t="s">
+      <c r="A11" s="592" t="s">
         <v>117</v>
       </c>
-      <c r="B11" s="604"/>
-      <c r="C11" s="654" t="s">
+      <c r="B11" s="593"/>
+      <c r="C11" s="660" t="s">
         <v>471</v>
       </c>
-      <c r="D11" s="583"/>
-      <c r="E11" s="655" t="s">
+      <c r="D11" s="577"/>
+      <c r="E11" s="661" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A12" s="652"/>
-      <c r="B12" s="653"/>
+      <c r="A12" s="654"/>
+      <c r="B12" s="655"/>
       <c r="C12" s="146" t="s">
         <v>472</v>
       </c>
       <c r="D12" s="146" t="s">
         <v>473</v>
       </c>
-      <c r="E12" s="631"/>
+      <c r="E12" s="645"/>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A13" s="605" t="s">
+      <c r="A13" s="594" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="585"/>
-      <c r="C13" s="585"/>
-      <c r="D13" s="595"/>
-      <c r="E13" s="606" t="s">
+      <c r="B13" s="595"/>
+      <c r="C13" s="595"/>
+      <c r="D13" s="591"/>
+      <c r="E13" s="596" t="s">
         <v>684</v>
       </c>
     </row>
@@ -41520,7 +41520,7 @@
         <v>88</v>
       </c>
       <c r="D14" s="30"/>
-      <c r="E14" s="589"/>
+      <c r="E14" s="597"/>
     </row>
     <row r="15" spans="1:5" ht="15.75" customHeight="1">
       <c r="A15" s="31">
@@ -41533,7 +41533,7 @@
         <v>78</v>
       </c>
       <c r="D15" s="30"/>
-      <c r="E15" s="589"/>
+      <c r="E15" s="597"/>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1">
       <c r="A16" s="31">
@@ -41546,7 +41546,7 @@
       <c r="D16" s="30">
         <v>112</v>
       </c>
-      <c r="E16" s="589"/>
+      <c r="E16" s="597"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1">
       <c r="A17" s="31">
@@ -41559,7 +41559,7 @@
         <v>10</v>
       </c>
       <c r="D17" s="30"/>
-      <c r="E17" s="589"/>
+      <c r="E17" s="597"/>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1">
       <c r="A18" s="31">
@@ -41572,7 +41572,7 @@
       <c r="D18" s="30">
         <v>89</v>
       </c>
-      <c r="E18" s="589"/>
+      <c r="E18" s="597"/>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1">
       <c r="A19" s="33">
@@ -41585,60 +41585,60 @@
         <v>90</v>
       </c>
       <c r="D19" s="36"/>
-      <c r="E19" s="580"/>
+      <c r="E19" s="583"/>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1">
       <c r="A20" s="20"/>
       <c r="B20" s="20"/>
-      <c r="C20" s="590"/>
+      <c r="C20" s="587"/>
       <c r="D20" s="588"/>
       <c r="E20" s="588"/>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A21" s="594">
+      <c r="A21" s="600">
         <v>1</v>
       </c>
-      <c r="B21" s="595"/>
-      <c r="C21" s="656">
+      <c r="B21" s="591"/>
+      <c r="C21" s="657">
         <v>2</v>
       </c>
-      <c r="D21" s="595"/>
+      <c r="D21" s="591"/>
       <c r="E21" s="39">
         <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="661" t="s">
+      <c r="A22" s="653" t="s">
         <v>117</v>
       </c>
-      <c r="B22" s="604"/>
-      <c r="C22" s="657" t="s">
+      <c r="B22" s="593"/>
+      <c r="C22" s="658" t="s">
         <v>471</v>
       </c>
-      <c r="D22" s="640"/>
-      <c r="E22" s="658" t="s">
+      <c r="D22" s="617"/>
+      <c r="E22" s="659" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="652"/>
-      <c r="B23" s="653"/>
+      <c r="A23" s="654"/>
+      <c r="B23" s="655"/>
       <c r="C23" s="148" t="s">
         <v>472</v>
       </c>
       <c r="D23" s="149" t="s">
         <v>473</v>
       </c>
-      <c r="E23" s="631"/>
+      <c r="E23" s="645"/>
     </row>
     <row r="24" spans="1:5" ht="16.5" customHeight="1">
-      <c r="A24" s="598" t="s">
+      <c r="A24" s="603" t="s">
         <v>691</v>
       </c>
-      <c r="B24" s="585"/>
-      <c r="C24" s="585"/>
-      <c r="D24" s="595"/>
-      <c r="E24" s="662"/>
+      <c r="B24" s="595"/>
+      <c r="C24" s="595"/>
+      <c r="D24" s="591"/>
+      <c r="E24" s="656"/>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1">
       <c r="A25" s="150">
@@ -41651,7 +41651,7 @@
         <v>43</v>
       </c>
       <c r="D25" s="151"/>
-      <c r="E25" s="610"/>
+      <c r="E25" s="644"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1">
       <c r="A26" s="150">
@@ -41664,7 +41664,7 @@
         <v>457</v>
       </c>
       <c r="D26" s="151"/>
-      <c r="E26" s="610"/>
+      <c r="E26" s="644"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1">
       <c r="A27" s="150">
@@ -41679,7 +41679,7 @@
       <c r="D27" s="151">
         <v>30</v>
       </c>
-      <c r="E27" s="610"/>
+      <c r="E27" s="644"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1">
       <c r="A28" s="150">
@@ -41692,7 +41692,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="151"/>
-      <c r="E28" s="610"/>
+      <c r="E28" s="644"/>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1">
       <c r="A29" s="150">
@@ -41701,7 +41701,7 @@
       <c r="B29" s="43"/>
       <c r="C29" s="151"/>
       <c r="D29" s="151"/>
-      <c r="E29" s="610"/>
+      <c r="E29" s="644"/>
     </row>
     <row r="30" spans="1:5" ht="12.75" hidden="1" customHeight="1">
       <c r="A30" s="54"/>
@@ -41730,11 +41730,11 @@
       <c r="B32" s="156" t="s">
         <v>503</v>
       </c>
-      <c r="C32" s="659">
+      <c r="C32" s="651">
         <f>SUM(C31:D31)</f>
         <v>582</v>
       </c>
-      <c r="D32" s="660"/>
+      <c r="D32" s="652"/>
       <c r="E32" s="61"/>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1">
@@ -41742,11 +41742,11 @@
       <c r="B33" s="63" t="s">
         <v>152</v>
       </c>
-      <c r="C33" s="600">
+      <c r="C33" s="585">
         <f>C31/C32</f>
         <v>0.94845360824742264</v>
       </c>
-      <c r="D33" s="593"/>
+      <c r="D33" s="586"/>
       <c r="E33" s="61"/>
     </row>
     <row r="34" spans="1:5" ht="15.75" customHeight="1">
@@ -42816,6 +42816,23 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="C3:E3"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="A9:E9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="A11:B12"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A21:B21"/>
     <mergeCell ref="E24:E29"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
@@ -42825,23 +42842,6 @@
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="C22:D22"/>
     <mergeCell ref="E22:E23"/>
-    <mergeCell ref="A11:B12"/>
-    <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="A24:D24"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C1:E1"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C3:E3"/>
-    <mergeCell ref="C4:E4"/>
-    <mergeCell ref="C5:E5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -42872,73 +42872,73 @@
       <c r="B1" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="584" t="s">
+      <c r="C1" s="604" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="585"/>
-      <c r="E1" s="585"/>
-      <c r="F1" s="585"/>
-      <c r="G1" s="586"/>
+      <c r="D1" s="595"/>
+      <c r="E1" s="595"/>
+      <c r="F1" s="595"/>
+      <c r="G1" s="605"/>
     </row>
     <row r="2" spans="1:7" ht="15.75" customHeight="1">
       <c r="A2" s="12"/>
       <c r="B2" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="587" t="s">
+      <c r="C2" s="606" t="s">
         <v>30</v>
       </c>
       <c r="D2" s="588"/>
       <c r="E2" s="588"/>
       <c r="F2" s="588"/>
-      <c r="G2" s="589"/>
+      <c r="G2" s="597"/>
     </row>
     <row r="3" spans="1:7" ht="15.75" customHeight="1">
       <c r="A3" s="14"/>
       <c r="B3" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="590" t="s">
+      <c r="C3" s="587" t="s">
         <v>694</v>
       </c>
       <c r="D3" s="588"/>
       <c r="E3" s="588"/>
       <c r="F3" s="588"/>
-      <c r="G3" s="589"/>
+      <c r="G3" s="597"/>
     </row>
     <row r="4" spans="1:7" ht="67.5" customHeight="1">
       <c r="A4" s="17"/>
       <c r="B4" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="590" t="s">
+      <c r="C4" s="587" t="s">
         <v>695</v>
       </c>
       <c r="D4" s="588"/>
       <c r="E4" s="588"/>
       <c r="F4" s="588"/>
-      <c r="G4" s="589"/>
+      <c r="G4" s="597"/>
     </row>
     <row r="5" spans="1:7" ht="15.75" customHeight="1">
       <c r="A5" s="12"/>
       <c r="B5" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="590" t="str">
+      <c r="C5" s="587" t="str">
         <f>'Reference Matrix'!$E14</f>
         <v>Accreditation includes those issued by local and international bodies recognized by CHED; AACCUP (Level 1 - Level 4)</v>
       </c>
       <c r="D5" s="588"/>
       <c r="E5" s="588"/>
       <c r="F5" s="588"/>
-      <c r="G5" s="589"/>
+      <c r="G5" s="597"/>
     </row>
     <row r="6" spans="1:7" ht="40.5" customHeight="1">
       <c r="A6" s="12"/>
       <c r="B6" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="590" t="str">
+      <c r="C6" s="587" t="str">
         <f>'Reference Matrix'!$F14</f>
         <v>1. Accreditation Certificates
 2. List of all graduate programs per campus with or without accreditation (include reasons for non-accreditation), indicate year of initial operation</v>
@@ -42946,102 +42946,102 @@
       <c r="D6" s="588"/>
       <c r="E6" s="588"/>
       <c r="F6" s="588"/>
-      <c r="G6" s="589"/>
+      <c r="G6" s="597"/>
     </row>
     <row r="7" spans="1:7" ht="12.75" customHeight="1">
       <c r="A7" s="18"/>
       <c r="B7" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="591" t="s">
+      <c r="C7" s="598" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="592"/>
-      <c r="E7" s="592"/>
-      <c r="F7" s="592"/>
-      <c r="G7" s="593"/>
+      <c r="D7" s="599"/>
+      <c r="E7" s="599"/>
+      <c r="F7" s="599"/>
+      <c r="G7" s="586"/>
     </row>
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="20"/>
       <c r="B8" s="20"/>
-      <c r="C8" s="680"/>
-      <c r="D8" s="681"/>
-      <c r="E8" s="681"/>
-      <c r="F8" s="681"/>
-      <c r="G8" s="681"/>
+      <c r="C8" s="682"/>
+      <c r="D8" s="683"/>
+      <c r="E8" s="683"/>
+      <c r="F8" s="683"/>
+      <c r="G8" s="683"/>
     </row>
     <row r="9" spans="1:7" ht="12.75" customHeight="1">
-      <c r="A9" s="682" t="s">
+      <c r="A9" s="684" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="681"/>
-      <c r="C9" s="681"/>
-      <c r="D9" s="681"/>
-      <c r="E9" s="681"/>
-      <c r="F9" s="681"/>
-      <c r="G9" s="683"/>
+      <c r="B9" s="683"/>
+      <c r="C9" s="683"/>
+      <c r="D9" s="683"/>
+      <c r="E9" s="683"/>
+      <c r="F9" s="683"/>
+      <c r="G9" s="685"/>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A10" s="602">
+      <c r="A10" s="590">
         <v>1</v>
       </c>
-      <c r="B10" s="595"/>
+      <c r="B10" s="591"/>
       <c r="C10" s="21">
         <v>2</v>
       </c>
       <c r="D10" s="22">
         <v>3</v>
       </c>
-      <c r="E10" s="651">
+      <c r="E10" s="662">
         <v>4</v>
       </c>
-      <c r="F10" s="595"/>
+      <c r="F10" s="591"/>
       <c r="G10" s="23">
         <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="12.75" customHeight="1">
-      <c r="A11" s="603" t="s">
+      <c r="A11" s="592" t="s">
         <v>508</v>
       </c>
-      <c r="B11" s="604"/>
-      <c r="C11" s="684" t="s">
+      <c r="B11" s="593"/>
+      <c r="C11" s="681" t="s">
         <v>509</v>
       </c>
-      <c r="D11" s="684" t="s">
+      <c r="D11" s="681" t="s">
         <v>510</v>
       </c>
-      <c r="E11" s="685" t="s">
+      <c r="E11" s="680" t="s">
         <v>696</v>
       </c>
-      <c r="F11" s="604"/>
-      <c r="G11" s="655" t="s">
+      <c r="F11" s="593"/>
+      <c r="G11" s="661" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A12" s="615"/>
-      <c r="B12" s="616"/>
-      <c r="C12" s="645"/>
-      <c r="D12" s="645"/>
+      <c r="A12" s="609"/>
+      <c r="B12" s="610"/>
+      <c r="C12" s="622"/>
+      <c r="D12" s="622"/>
       <c r="E12" s="158" t="s">
         <v>697</v>
       </c>
       <c r="F12" s="158" t="s">
         <v>698</v>
       </c>
-      <c r="G12" s="631"/>
+      <c r="G12" s="645"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A13" s="605" t="s">
+      <c r="A13" s="594" t="s">
         <v>122</v>
       </c>
-      <c r="B13" s="585"/>
-      <c r="C13" s="585"/>
-      <c r="D13" s="585"/>
-      <c r="E13" s="585"/>
-      <c r="F13" s="585"/>
-      <c r="G13" s="586"/>
+      <c r="B13" s="595"/>
+      <c r="C13" s="595"/>
+      <c r="D13" s="595"/>
+      <c r="E13" s="595"/>
+      <c r="F13" s="595"/>
+      <c r="G13" s="605"/>
     </row>
     <row r="14" spans="1:7" ht="15.75" customHeight="1">
       <c r="A14" s="27">
@@ -43176,73 +43176,73 @@
     <row r="20" spans="1:7" ht="15.75" customHeight="1">
       <c r="A20" s="20"/>
       <c r="B20" s="20"/>
-      <c r="C20" s="590"/>
+      <c r="C20" s="587"/>
       <c r="D20" s="588"/>
       <c r="E20" s="588"/>
       <c r="F20" s="588"/>
       <c r="G20" s="588"/>
     </row>
     <row r="21" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A21" s="594">
+      <c r="A21" s="600">
         <v>1</v>
       </c>
-      <c r="B21" s="595"/>
+      <c r="B21" s="591"/>
       <c r="C21" s="37">
         <v>2</v>
       </c>
       <c r="D21" s="38">
         <v>3</v>
       </c>
-      <c r="E21" s="656">
+      <c r="E21" s="657">
         <v>4</v>
       </c>
-      <c r="F21" s="585"/>
+      <c r="F21" s="595"/>
       <c r="G21" s="39">
         <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A22" s="674" t="s">
+      <c r="A22" s="671" t="s">
         <v>508</v>
       </c>
-      <c r="B22" s="604"/>
-      <c r="C22" s="667" t="s">
+      <c r="B22" s="593"/>
+      <c r="C22" s="677" t="s">
         <v>509</v>
       </c>
-      <c r="D22" s="667" t="s">
+      <c r="D22" s="677" t="s">
         <v>510</v>
       </c>
-      <c r="E22" s="665" t="s">
+      <c r="E22" s="675" t="s">
         <v>701</v>
       </c>
       <c r="F22" s="588"/>
-      <c r="G22" s="668" t="s">
+      <c r="G22" s="678" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A23" s="652"/>
-      <c r="B23" s="653"/>
-      <c r="C23" s="664"/>
-      <c r="D23" s="664"/>
+      <c r="A23" s="654"/>
+      <c r="B23" s="655"/>
+      <c r="C23" s="673"/>
+      <c r="D23" s="673"/>
       <c r="E23" s="169" t="s">
         <v>702</v>
       </c>
       <c r="F23" s="169" t="s">
         <v>703</v>
       </c>
-      <c r="G23" s="631"/>
+      <c r="G23" s="645"/>
     </row>
     <row r="24" spans="1:7" ht="16.5" customHeight="1">
-      <c r="A24" s="598" t="s">
+      <c r="A24" s="603" t="s">
         <v>528</v>
       </c>
-      <c r="B24" s="585"/>
-      <c r="C24" s="585"/>
-      <c r="D24" s="585"/>
-      <c r="E24" s="585"/>
-      <c r="F24" s="585"/>
-      <c r="G24" s="586"/>
+      <c r="B24" s="595"/>
+      <c r="C24" s="595"/>
+      <c r="D24" s="595"/>
+      <c r="E24" s="595"/>
+      <c r="F24" s="595"/>
+      <c r="G24" s="605"/>
     </row>
     <row r="25" spans="1:7" ht="15.75" customHeight="1">
       <c r="A25" s="150">
@@ -43324,10 +43324,10 @@
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1">
       <c r="A29" s="211"/>
-      <c r="B29" s="669" t="s">
+      <c r="B29" s="666" t="s">
         <v>615</v>
       </c>
-      <c r="C29" s="648"/>
+      <c r="C29" s="625"/>
       <c r="D29" s="212">
         <f>COUNTIFS($B25:B28,"&lt;&gt;",D25:D28,"&lt;&gt;")</f>
         <v>3</v>
@@ -43338,10 +43338,10 @@
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1">
       <c r="A30" s="214"/>
-      <c r="B30" s="670" t="s">
+      <c r="B30" s="667" t="s">
         <v>616</v>
       </c>
-      <c r="C30" s="671"/>
+      <c r="C30" s="668"/>
       <c r="D30" s="215">
         <v>3</v>
       </c>
@@ -43351,10 +43351,10 @@
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1">
       <c r="A31" s="214"/>
-      <c r="B31" s="670" t="s">
+      <c r="B31" s="667" t="s">
         <v>617</v>
       </c>
-      <c r="C31" s="671"/>
+      <c r="C31" s="668"/>
       <c r="D31" s="215">
         <f>D29-COUNTIF(D25:D28,"Not Accreditable")</f>
         <v>3</v>
@@ -43365,10 +43365,10 @@
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1">
       <c r="A32" s="216"/>
-      <c r="B32" s="672" t="s">
+      <c r="B32" s="669" t="s">
         <v>152</v>
       </c>
-      <c r="C32" s="673"/>
+      <c r="C32" s="670"/>
       <c r="D32" s="217">
         <f>D30/D31</f>
         <v>1</v>
@@ -44475,6 +44475,20 @@
     <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="30">
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C3:G3"/>
+    <mergeCell ref="C4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="D11:D12"/>
+    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="A9:G9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="E10:F10"/>
     <mergeCell ref="B31:C31"/>
     <mergeCell ref="B32:C32"/>
     <mergeCell ref="E11:F11"/>
@@ -44491,20 +44505,6 @@
     <mergeCell ref="B30:C30"/>
     <mergeCell ref="A11:B12"/>
     <mergeCell ref="C11:C12"/>
-    <mergeCell ref="D11:D12"/>
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="A9:G9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="C1:G1"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="C3:G3"/>
-    <mergeCell ref="C4:G4"/>
-    <mergeCell ref="C5:G5"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D28" xr:uid="{00000000-0002-0000-0700-000000000000}">
@@ -44564,14 +44564,14 @@
       <c r="B1" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="584" t="s">
+      <c r="C1" s="604" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="585"/>
-      <c r="E1" s="585"/>
-      <c r="F1" s="585"/>
-      <c r="G1" s="585"/>
-      <c r="H1" s="686"/>
+      <c r="D1" s="595"/>
+      <c r="E1" s="595"/>
+      <c r="F1" s="595"/>
+      <c r="G1" s="595"/>
+      <c r="H1" s="709"/>
       <c r="I1" s="246"/>
       <c r="J1" s="246"/>
       <c r="K1" s="246"/>
@@ -44589,7 +44589,7 @@
       <c r="B2" s="13" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="587" t="s">
+      <c r="C2" s="606" t="s">
         <v>51</v>
       </c>
       <c r="D2" s="588"/>
@@ -44602,7 +44602,7 @@
       <c r="K2" s="588"/>
       <c r="L2" s="588"/>
       <c r="M2" s="588"/>
-      <c r="N2" s="589"/>
+      <c r="N2" s="597"/>
       <c r="O2" s="249"/>
       <c r="P2" s="249"/>
       <c r="Q2" s="249"/>
@@ -44614,7 +44614,7 @@
       <c r="B3" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="590" t="s">
+      <c r="C3" s="587" t="s">
         <v>712</v>
       </c>
       <c r="D3" s="588"/>
@@ -44627,7 +44627,7 @@
       <c r="K3" s="588"/>
       <c r="L3" s="588"/>
       <c r="M3" s="588"/>
-      <c r="N3" s="589"/>
+      <c r="N3" s="597"/>
       <c r="O3" s="249"/>
       <c r="P3" s="249"/>
       <c r="Q3" s="249"/>
@@ -44639,7 +44639,7 @@
       <c r="B4" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="590" t="s">
+      <c r="C4" s="587" t="s">
         <v>713</v>
       </c>
       <c r="D4" s="588"/>
@@ -44652,7 +44652,7 @@
       <c r="K4" s="588"/>
       <c r="L4" s="588"/>
       <c r="M4" s="588"/>
-      <c r="N4" s="589"/>
+      <c r="N4" s="597"/>
       <c r="O4" s="249"/>
       <c r="P4" s="249"/>
       <c r="Q4" s="249"/>
@@ -44664,7 +44664,7 @@
       <c r="B5" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="590" t="str">
+      <c r="C5" s="587" t="str">
         <f t="array" ref="C5">"For Outcome Indicator 1:"&amp;CHAR(10)&amp;'Reference Matrix'!$E16&amp;CHAR(10)&amp;CHAR(10)&amp;"For Output Indicator 1:"&amp;CHAR(10)&amp;'Reference Matrix'!$E17&amp;CHAR(10)&amp;CHAR(10)&amp;"For Outcome Indicator 2 (State Universities):"&amp;CHAR(10)&amp;'Reference Matrix'!$E18&amp;CHAR(10)&amp;CHAR(10)&amp;"For Outcome Indicator 2 (State Colleges and Professional Institutes):"&amp;CHAR(10)&amp;'Reference Matrix'!$E19</f>
         <v>For Outcome Indicator 1:
 Utilized by industry or other beneficiaries refers to the adopters/partners/communities, external to the institution
@@ -44691,7 +44691,7 @@
       <c r="K5" s="588"/>
       <c r="L5" s="588"/>
       <c r="M5" s="588"/>
-      <c r="N5" s="589"/>
+      <c r="N5" s="597"/>
       <c r="O5" s="249"/>
       <c r="P5" s="249"/>
       <c r="Q5" s="249"/>
@@ -44703,7 +44703,7 @@
       <c r="B6" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="C6" s="590" t="str">
+      <c r="C6" s="587" t="str">
         <f>"For Outcome Indicator 1:"&amp;CHAR(10)&amp;'Reference Matrix'!$F16&amp;CHAR(10)&amp;CHAR(10)&amp;"For Output Indicator 1:"&amp;CHAR(10)&amp;'Reference Matrix'!$F17&amp;CHAR(10)&amp;CHAR(10)&amp;"For Outcome Indicator 2 (State Universities):"&amp;CHAR(10)&amp;'Reference Matrix'!$F18&amp;CHAR(10)&amp;CHAR(10)&amp;"For Outcome Indicator 2 (State Colleges and Professional Institutes):"&amp;CHAR(10)&amp;'Reference Matrix'!$F19</f>
         <v>For Outcome Indicator 1:
 1. Proof that the research output was utilized by identified stakeholders/beneficiaries
@@ -44730,7 +44730,7 @@
       <c r="K6" s="588"/>
       <c r="L6" s="588"/>
       <c r="M6" s="588"/>
-      <c r="N6" s="589"/>
+      <c r="N6" s="597"/>
       <c r="O6" s="249"/>
       <c r="P6" s="249"/>
       <c r="Q6" s="249"/>
@@ -44742,20 +44742,20 @@
       <c r="B7" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C7" s="591" t="s">
+      <c r="C7" s="598" t="s">
         <v>115</v>
       </c>
-      <c r="D7" s="592"/>
-      <c r="E7" s="592"/>
-      <c r="F7" s="592"/>
-      <c r="G7" s="592"/>
-      <c r="H7" s="592"/>
-      <c r="I7" s="592"/>
-      <c r="J7" s="592"/>
-      <c r="K7" s="592"/>
-      <c r="L7" s="592"/>
-      <c r="M7" s="592"/>
-      <c r="N7" s="593"/>
+      <c r="D7" s="599"/>
+      <c r="E7" s="599"/>
+      <c r="F7" s="599"/>
+      <c r="G7" s="599"/>
+      <c r="H7" s="599"/>
+      <c r="I7" s="599"/>
+      <c r="J7" s="599"/>
+      <c r="K7" s="599"/>
+      <c r="L7" s="599"/>
+      <c r="M7" s="599"/>
+      <c r="N7" s="586"/>
       <c r="O7" s="249"/>
       <c r="P7" s="249"/>
       <c r="Q7" s="249"/>
@@ -44784,136 +44784,136 @@
       <c r="S8" s="249"/>
     </row>
     <row r="9" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A9" s="601" t="s">
+      <c r="A9" s="589" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="576"/>
-      <c r="C9" s="576"/>
-      <c r="D9" s="576"/>
-      <c r="E9" s="576"/>
-      <c r="F9" s="576"/>
-      <c r="G9" s="576"/>
-      <c r="H9" s="576"/>
-      <c r="I9" s="576"/>
-      <c r="J9" s="576"/>
-      <c r="K9" s="576"/>
-      <c r="L9" s="576"/>
-      <c r="M9" s="576"/>
-      <c r="N9" s="576"/>
-      <c r="O9" s="576"/>
-      <c r="P9" s="576"/>
-      <c r="Q9" s="576"/>
-      <c r="R9" s="576"/>
-      <c r="S9" s="577"/>
+      <c r="B9" s="579"/>
+      <c r="C9" s="579"/>
+      <c r="D9" s="579"/>
+      <c r="E9" s="579"/>
+      <c r="F9" s="579"/>
+      <c r="G9" s="579"/>
+      <c r="H9" s="579"/>
+      <c r="I9" s="579"/>
+      <c r="J9" s="579"/>
+      <c r="K9" s="579"/>
+      <c r="L9" s="579"/>
+      <c r="M9" s="579"/>
+      <c r="N9" s="579"/>
+      <c r="O9" s="579"/>
+      <c r="P9" s="579"/>
+      <c r="Q9" s="579"/>
+      <c r="R9" s="579"/>
+      <c r="S9" s="580"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A10" s="690" t="s">
+      <c r="A10" s="705" t="s">
         <v>714</v>
       </c>
-      <c r="B10" s="585"/>
-      <c r="C10" s="585"/>
-      <c r="D10" s="585"/>
-      <c r="E10" s="585"/>
-      <c r="F10" s="586"/>
-      <c r="G10" s="691" t="s">
+      <c r="B10" s="595"/>
+      <c r="C10" s="595"/>
+      <c r="D10" s="595"/>
+      <c r="E10" s="595"/>
+      <c r="F10" s="605"/>
+      <c r="G10" s="706" t="s">
         <v>715</v>
       </c>
-      <c r="H10" s="585"/>
-      <c r="I10" s="585"/>
-      <c r="J10" s="586"/>
-      <c r="K10" s="691" t="s">
+      <c r="H10" s="595"/>
+      <c r="I10" s="595"/>
+      <c r="J10" s="605"/>
+      <c r="K10" s="706" t="s">
         <v>716</v>
       </c>
-      <c r="L10" s="585"/>
-      <c r="M10" s="585"/>
-      <c r="N10" s="585"/>
-      <c r="O10" s="585"/>
-      <c r="P10" s="586"/>
-      <c r="Q10" s="692" t="s">
+      <c r="L10" s="595"/>
+      <c r="M10" s="595"/>
+      <c r="N10" s="595"/>
+      <c r="O10" s="595"/>
+      <c r="P10" s="605"/>
+      <c r="Q10" s="707" t="s">
         <v>717</v>
       </c>
-      <c r="R10" s="585"/>
-      <c r="S10" s="586"/>
+      <c r="R10" s="595"/>
+      <c r="S10" s="605"/>
     </row>
     <row r="11" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A11" s="603" t="s">
+      <c r="A11" s="592" t="s">
         <v>718</v>
       </c>
-      <c r="B11" s="604"/>
-      <c r="C11" s="684" t="s">
+      <c r="B11" s="593"/>
+      <c r="C11" s="681" t="s">
         <v>719</v>
       </c>
-      <c r="D11" s="684" t="s">
+      <c r="D11" s="681" t="s">
         <v>720</v>
       </c>
-      <c r="E11" s="654" t="s">
+      <c r="E11" s="660" t="s">
         <v>721</v>
       </c>
-      <c r="F11" s="676"/>
-      <c r="G11" s="687" t="s">
+      <c r="F11" s="665"/>
+      <c r="G11" s="708" t="s">
         <v>722</v>
       </c>
-      <c r="H11" s="684" t="s">
+      <c r="H11" s="681" t="s">
         <v>723</v>
       </c>
-      <c r="I11" s="684" t="s">
+      <c r="I11" s="681" t="s">
         <v>724</v>
       </c>
-      <c r="J11" s="655" t="s">
+      <c r="J11" s="661" t="s">
         <v>725</v>
       </c>
-      <c r="K11" s="687" t="s">
+      <c r="K11" s="708" t="s">
         <v>726</v>
       </c>
-      <c r="L11" s="684" t="s">
+      <c r="L11" s="681" t="s">
         <v>727</v>
       </c>
-      <c r="M11" s="684" t="s">
+      <c r="M11" s="681" t="s">
         <v>728</v>
       </c>
-      <c r="N11" s="684" t="s">
+      <c r="N11" s="681" t="s">
         <v>729</v>
       </c>
-      <c r="O11" s="684" t="s">
+      <c r="O11" s="681" t="s">
         <v>730</v>
       </c>
-      <c r="P11" s="655" t="s">
+      <c r="P11" s="661" t="s">
         <v>731</v>
       </c>
-      <c r="Q11" s="689" t="s">
+      <c r="Q11" s="704" t="s">
         <v>732</v>
       </c>
-      <c r="R11" s="684" t="s">
+      <c r="R11" s="681" t="s">
         <v>733</v>
       </c>
-      <c r="S11" s="655" t="s">
+      <c r="S11" s="661" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A12" s="615"/>
-      <c r="B12" s="616"/>
-      <c r="C12" s="645"/>
-      <c r="D12" s="645"/>
+      <c r="A12" s="609"/>
+      <c r="B12" s="610"/>
+      <c r="C12" s="622"/>
+      <c r="D12" s="622"/>
       <c r="E12" s="84" t="s">
         <v>735</v>
       </c>
       <c r="F12" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="G12" s="688"/>
-      <c r="H12" s="645"/>
-      <c r="I12" s="645"/>
-      <c r="J12" s="631"/>
-      <c r="K12" s="688"/>
-      <c r="L12" s="645"/>
-      <c r="M12" s="645"/>
-      <c r="N12" s="645"/>
-      <c r="O12" s="645"/>
-      <c r="P12" s="631"/>
-      <c r="Q12" s="616"/>
-      <c r="R12" s="645"/>
-      <c r="S12" s="631"/>
+      <c r="G12" s="687"/>
+      <c r="H12" s="622"/>
+      <c r="I12" s="622"/>
+      <c r="J12" s="645"/>
+      <c r="K12" s="687"/>
+      <c r="L12" s="622"/>
+      <c r="M12" s="622"/>
+      <c r="N12" s="622"/>
+      <c r="O12" s="622"/>
+      <c r="P12" s="645"/>
+      <c r="Q12" s="610"/>
+      <c r="R12" s="622"/>
+      <c r="S12" s="645"/>
     </row>
     <row r="13" spans="1:19" ht="15.75" customHeight="1">
       <c r="A13" s="253">
@@ -45204,113 +45204,113 @@
       <c r="S18" s="249"/>
     </row>
     <row r="19" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A19" s="695" t="s">
+      <c r="A19" s="699" t="s">
         <v>714</v>
       </c>
-      <c r="B19" s="585"/>
-      <c r="C19" s="585"/>
-      <c r="D19" s="585"/>
-      <c r="E19" s="585"/>
-      <c r="F19" s="586"/>
-      <c r="G19" s="696" t="s">
+      <c r="B19" s="595"/>
+      <c r="C19" s="595"/>
+      <c r="D19" s="595"/>
+      <c r="E19" s="595"/>
+      <c r="F19" s="605"/>
+      <c r="G19" s="700" t="s">
         <v>715</v>
       </c>
-      <c r="H19" s="585"/>
-      <c r="I19" s="585"/>
-      <c r="J19" s="595"/>
-      <c r="K19" s="697" t="s">
+      <c r="H19" s="595"/>
+      <c r="I19" s="595"/>
+      <c r="J19" s="591"/>
+      <c r="K19" s="701" t="s">
         <v>716</v>
       </c>
-      <c r="L19" s="585"/>
-      <c r="M19" s="585"/>
-      <c r="N19" s="585"/>
-      <c r="O19" s="585"/>
-      <c r="P19" s="586"/>
-      <c r="Q19" s="697" t="s">
+      <c r="L19" s="595"/>
+      <c r="M19" s="595"/>
+      <c r="N19" s="595"/>
+      <c r="O19" s="595"/>
+      <c r="P19" s="605"/>
+      <c r="Q19" s="701" t="s">
         <v>717</v>
       </c>
-      <c r="R19" s="585"/>
-      <c r="S19" s="586"/>
+      <c r="R19" s="595"/>
+      <c r="S19" s="605"/>
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A20" s="698" t="s">
+      <c r="A20" s="702" t="s">
         <v>718</v>
       </c>
-      <c r="B20" s="653"/>
-      <c r="C20" s="693" t="s">
+      <c r="B20" s="655"/>
+      <c r="C20" s="688" t="s">
         <v>719</v>
       </c>
-      <c r="D20" s="693" t="s">
+      <c r="D20" s="688" t="s">
         <v>720</v>
       </c>
-      <c r="E20" s="704" t="s">
+      <c r="E20" s="695" t="s">
         <v>721</v>
       </c>
-      <c r="F20" s="705"/>
-      <c r="G20" s="693" t="s">
+      <c r="F20" s="696"/>
+      <c r="G20" s="688" t="s">
         <v>722</v>
       </c>
-      <c r="H20" s="693" t="s">
+      <c r="H20" s="688" t="s">
         <v>723</v>
       </c>
-      <c r="I20" s="693" t="s">
+      <c r="I20" s="688" t="s">
         <v>724</v>
       </c>
-      <c r="J20" s="708" t="s">
+      <c r="J20" s="703" t="s">
         <v>760</v>
       </c>
-      <c r="K20" s="709" t="s">
+      <c r="K20" s="686" t="s">
         <v>726</v>
       </c>
-      <c r="L20" s="693" t="s">
+      <c r="L20" s="688" t="s">
         <v>761</v>
       </c>
-      <c r="M20" s="693" t="s">
+      <c r="M20" s="688" t="s">
         <v>728</v>
       </c>
-      <c r="N20" s="693" t="s">
+      <c r="N20" s="688" t="s">
         <v>729</v>
       </c>
-      <c r="O20" s="693" t="s">
+      <c r="O20" s="688" t="s">
         <v>730</v>
       </c>
-      <c r="P20" s="694" t="s">
+      <c r="P20" s="689" t="s">
         <v>731</v>
       </c>
-      <c r="Q20" s="709" t="s">
+      <c r="Q20" s="686" t="s">
         <v>732</v>
       </c>
-      <c r="R20" s="693" t="s">
+      <c r="R20" s="688" t="s">
         <v>733</v>
       </c>
-      <c r="S20" s="694" t="s">
+      <c r="S20" s="689" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A21" s="615"/>
-      <c r="B21" s="616"/>
-      <c r="C21" s="616"/>
-      <c r="D21" s="616"/>
+      <c r="A21" s="609"/>
+      <c r="B21" s="610"/>
+      <c r="C21" s="610"/>
+      <c r="D21" s="610"/>
       <c r="E21" s="273" t="s">
         <v>762</v>
       </c>
       <c r="F21" s="274" t="s">
         <v>763</v>
       </c>
-      <c r="G21" s="616"/>
-      <c r="H21" s="616"/>
-      <c r="I21" s="616"/>
-      <c r="J21" s="579"/>
-      <c r="K21" s="688"/>
-      <c r="L21" s="616"/>
-      <c r="M21" s="616"/>
-      <c r="N21" s="616"/>
-      <c r="O21" s="616"/>
-      <c r="P21" s="580"/>
-      <c r="Q21" s="688"/>
-      <c r="R21" s="616"/>
-      <c r="S21" s="580"/>
+      <c r="G21" s="610"/>
+      <c r="H21" s="610"/>
+      <c r="I21" s="610"/>
+      <c r="J21" s="582"/>
+      <c r="K21" s="687"/>
+      <c r="L21" s="610"/>
+      <c r="M21" s="610"/>
+      <c r="N21" s="610"/>
+      <c r="O21" s="610"/>
+      <c r="P21" s="583"/>
+      <c r="Q21" s="687"/>
+      <c r="R21" s="610"/>
+      <c r="S21" s="583"/>
     </row>
     <row r="22" spans="1:26" ht="15.75" customHeight="1">
       <c r="A22" s="275"/>
@@ -54245,18 +54245,18 @@
     </row>
     <row r="210" spans="1:26" ht="15.75" customHeight="1">
       <c r="A210" s="386"/>
-      <c r="B210" s="699" t="s">
+      <c r="B210" s="690" t="s">
         <v>1373</v>
       </c>
-      <c r="C210" s="671"/>
+      <c r="C210" s="668"/>
       <c r="D210" s="387">
         <v>55</v>
       </c>
       <c r="E210" s="388"/>
-      <c r="F210" s="706" t="s">
+      <c r="F210" s="697" t="s">
         <v>1374</v>
       </c>
-      <c r="G210" s="671"/>
+      <c r="G210" s="668"/>
       <c r="H210" s="389">
         <f>COUNTIFS(B23:B208,"*",C23:C208,"*",D23:D208,"Completed",F23:F208,"&lt;="&amp;VALUE("12/31/23"),G23:G208,"*",J23:J208,"&gt;="&amp;VALUE("1/1/23"),J23:J208,"&lt;="&amp;VALUE("12/31/23"))</f>
         <v>0</v>
@@ -54288,18 +54288,18 @@
     </row>
     <row r="211" spans="1:26" ht="12.75" customHeight="1">
       <c r="A211" s="386"/>
-      <c r="B211" s="700" t="s">
+      <c r="B211" s="691" t="s">
         <v>1375</v>
       </c>
-      <c r="C211" s="635"/>
-      <c r="D211" s="702">
+      <c r="C211" s="612"/>
+      <c r="D211" s="693">
         <v>180</v>
       </c>
       <c r="E211" s="388"/>
-      <c r="F211" s="706" t="s">
+      <c r="F211" s="697" t="s">
         <v>1376</v>
       </c>
-      <c r="G211" s="671"/>
+      <c r="G211" s="668"/>
       <c r="H211" s="389">
         <f>COUNTIFS(B23:B208,"*",C23:C208,"*",D23:D208,"Completed",F23:F208,"&lt;="&amp;VALUE("12/31/23"),K23:K208,"*",L23:L208,"&gt;="&amp;VALUE("1/1/23"),L23:L208,"&lt;="&amp;VALUE("12/31/23"),M23:M208,"*",N23:N208,"*")</f>
         <v>0</v>
@@ -54331,14 +54331,14 @@
     </row>
     <row r="212" spans="1:26" ht="15.75" customHeight="1">
       <c r="A212" s="392"/>
-      <c r="B212" s="701"/>
-      <c r="C212" s="636"/>
-      <c r="D212" s="638"/>
+      <c r="B212" s="692"/>
+      <c r="C212" s="613"/>
+      <c r="D212" s="615"/>
       <c r="E212" s="393"/>
-      <c r="F212" s="707" t="s">
+      <c r="F212" s="698" t="s">
         <v>1377</v>
       </c>
-      <c r="G212" s="673"/>
+      <c r="G212" s="670"/>
       <c r="H212" s="394">
         <v>11</v>
       </c>
@@ -54363,8 +54363,8 @@
     </row>
     <row r="213" spans="1:26" ht="15.75" customHeight="1">
       <c r="A213" s="249"/>
-      <c r="B213" s="703"/>
-      <c r="C213" s="576"/>
+      <c r="B213" s="694"/>
+      <c r="C213" s="579"/>
       <c r="D213" s="249"/>
       <c r="E213" s="391"/>
       <c r="F213" s="391"/>
@@ -55453,20 +55453,33 @@
     <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="57">
-    <mergeCell ref="Q20:Q21"/>
-    <mergeCell ref="L20:L21"/>
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="N20:N21"/>
-    <mergeCell ref="O20:O21"/>
-    <mergeCell ref="P20:P21"/>
-    <mergeCell ref="B210:C210"/>
-    <mergeCell ref="B211:C212"/>
-    <mergeCell ref="D211:D212"/>
-    <mergeCell ref="B213:C213"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="F210:G210"/>
-    <mergeCell ref="F211:G211"/>
-    <mergeCell ref="F212:G212"/>
+    <mergeCell ref="C1:H1"/>
+    <mergeCell ref="C2:N2"/>
+    <mergeCell ref="C3:N3"/>
+    <mergeCell ref="C4:N4"/>
+    <mergeCell ref="C5:N5"/>
+    <mergeCell ref="C6:N6"/>
+    <mergeCell ref="C7:N7"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
+    <mergeCell ref="M11:M12"/>
+    <mergeCell ref="N11:N12"/>
+    <mergeCell ref="O11:O12"/>
+    <mergeCell ref="P11:P12"/>
+    <mergeCell ref="Q11:Q12"/>
+    <mergeCell ref="R11:R12"/>
+    <mergeCell ref="A9:S9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="K10:P10"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="A11:B12"/>
+    <mergeCell ref="C11:C12"/>
+    <mergeCell ref="S11:S12"/>
     <mergeCell ref="R20:R21"/>
     <mergeCell ref="S20:S21"/>
     <mergeCell ref="D11:D12"/>
@@ -55483,33 +55496,20 @@
     <mergeCell ref="I20:I21"/>
     <mergeCell ref="J20:J21"/>
     <mergeCell ref="K20:K21"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="Q11:Q12"/>
-    <mergeCell ref="R11:R12"/>
-    <mergeCell ref="A9:S9"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="K10:P10"/>
-    <mergeCell ref="Q10:S10"/>
-    <mergeCell ref="A11:B12"/>
-    <mergeCell ref="C11:C12"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="C6:N6"/>
-    <mergeCell ref="C7:N7"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
-    <mergeCell ref="M11:M12"/>
-    <mergeCell ref="N11:N12"/>
-    <mergeCell ref="C1:H1"/>
-    <mergeCell ref="C2:N2"/>
-    <mergeCell ref="C3:N3"/>
-    <mergeCell ref="C4:N4"/>
-    <mergeCell ref="C5:N5"/>
+    <mergeCell ref="B210:C210"/>
+    <mergeCell ref="B211:C212"/>
+    <mergeCell ref="D211:D212"/>
+    <mergeCell ref="B213:C213"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="F210:G210"/>
+    <mergeCell ref="F211:G211"/>
+    <mergeCell ref="F212:G212"/>
+    <mergeCell ref="Q20:Q21"/>
+    <mergeCell ref="L20:L21"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="O20:O21"/>
+    <mergeCell ref="P20:P21"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D144:D154 D156:D165 D167:D180 D182:D188 D191:D205" xr:uid="{00000000-0002-0000-0800-000000000000}">

--- a/marsu-pwa-dashboard/py_scripts/PBB FY 2023.xlsx
+++ b/marsu-pwa-dashboard/py_scripts/PBB FY 2023.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\marsu-dasboard-rev2\marsu-pwa-dashboard\py_scripts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C61C01BE-A0C4-444F-8107-8C1F974E523F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EE6232B-F62D-4C14-8B18-AF6F6451A01C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="690" yWindow="690" windowWidth="12030" windowHeight="10800" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="12900" yWindow="345" windowWidth="7935" windowHeight="10800" firstSheet="3" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Reference Matrix" sheetId="1" r:id="rId1"/>
@@ -8633,7 +8633,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="124">
+  <borders count="116">
     <border>
       <left/>
       <right/>
@@ -9240,48 +9240,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right style="thin">
         <color rgb="FF000000"/>
@@ -9290,17 +9248,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -9360,15 +9307,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -9394,17 +9332,6 @@
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
       <top/>
       <bottom style="thin">
         <color rgb="FF000000"/>
@@ -9472,9 +9399,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
+      <left/>
       <right/>
       <top/>
       <bottom/>
@@ -9491,22 +9416,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
@@ -9515,17 +9424,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
       <top/>
       <bottom style="medium">
         <color rgb="FF000000"/>
@@ -10024,11 +9922,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="756">
+  <cellXfs count="801">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -10285,7 +10203,7 @@
     <xf numFmtId="0" fontId="17" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10297,7 +10215,7 @@
     <xf numFmtId="0" fontId="30" fillId="9" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10309,7 +10227,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10330,13 +10248,13 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10354,10 +10272,10 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10366,22 +10284,22 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10412,16 +10330,16 @@
     <xf numFmtId="0" fontId="31" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="8" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="8" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="68" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10446,7 +10364,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10461,19 +10379,19 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -10497,7 +10415,7 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10573,13 +10491,13 @@
     <xf numFmtId="166" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10588,7 +10506,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10603,10 +10521,10 @@
     <xf numFmtId="166" fontId="9" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10615,13 +10533,13 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10633,28 +10551,28 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="10" fontId="13" fillId="7" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="13" fillId="7" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10666,13 +10584,13 @@
     <xf numFmtId="0" fontId="43" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10687,7 +10605,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10696,7 +10614,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10705,19 +10623,19 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="13" fillId="7" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="13" fillId="7" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10726,13 +10644,13 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="10" fontId="10" fillId="7" borderId="94" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="10" fillId="7" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="46" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10743,7 +10661,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -10755,10 +10673,10 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10773,7 +10691,7 @@
     <xf numFmtId="166" fontId="19" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="78" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10788,7 +10706,7 @@
     <xf numFmtId="166" fontId="19" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10797,16 +10715,16 @@
     <xf numFmtId="166" fontId="19" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="90" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="19" fillId="0" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="90" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10818,21 +10736,21 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="93" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="94" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="103" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -10857,7 +10775,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -10866,13 +10784,13 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
@@ -10960,7 +10878,7 @@
     <xf numFmtId="168" fontId="21" fillId="0" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="0" borderId="80" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="21" fillId="0" borderId="70" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10978,10 +10896,10 @@
     <xf numFmtId="166" fontId="21" fillId="13" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="13" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="21" fillId="13" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="21" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -10990,7 +10908,7 @@
     <xf numFmtId="0" fontId="21" fillId="13" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="21" fillId="14" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11012,7 +10930,7 @@
     <xf numFmtId="14" fontId="21" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="13" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11027,10 +10945,10 @@
     <xf numFmtId="166" fontId="21" fillId="13" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="168" fontId="21" fillId="13" borderId="68" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="21" fillId="13" borderId="61" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="21" fillId="13" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -11039,7 +10957,7 @@
     <xf numFmtId="0" fontId="21" fillId="13" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11054,7 +10972,7 @@
     <xf numFmtId="0" fontId="13" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11075,7 +10993,7 @@
     <xf numFmtId="168" fontId="21" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="76" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11087,7 +11005,7 @@
     <xf numFmtId="166" fontId="21" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="168" fontId="21" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11108,22 +11026,22 @@
     <xf numFmtId="0" fontId="31" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="21" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="82" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="168" fontId="21" fillId="7" borderId="67" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="21" fillId="15" borderId="92" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="21" fillId="7" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="21" fillId="15" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="21" fillId="7" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="94" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -11133,7 +11051,7 @@
     <xf numFmtId="0" fontId="21" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="65" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11155,7 +11073,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11164,10 +11082,10 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11180,16 +11098,16 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="19" fillId="0" borderId="101" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="91" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="19" fillId="0" borderId="35" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11232,16 +11150,16 @@
     <xf numFmtId="0" fontId="31" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="60" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="55" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="21" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11250,7 +11168,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="21" fillId="0" borderId="85" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="21" fillId="0" borderId="75" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="21" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11259,16 +11177,16 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="102" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="92" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="103" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="93" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="109" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11280,10 +11198,10 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="21" fillId="16" borderId="110" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="21" fillId="16" borderId="100" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11295,7 +11213,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="13" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11322,13 +11240,13 @@
     <xf numFmtId="169" fontId="21" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="109" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="21" fillId="0" borderId="98" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="21" fillId="0" borderId="88" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="111" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11340,7 +11258,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="109" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11372,7 +11290,7 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="13" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="52" fillId="13" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -11382,25 +11300,25 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="19" fillId="0" borderId="65" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="59" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="166" fontId="19" fillId="0" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11421,13 +11339,13 @@
     <xf numFmtId="166" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="116" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11487,7 +11405,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="111" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -11497,7 +11415,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11512,13 +11430,13 @@
     <xf numFmtId="166" fontId="19" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="53" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11616,7 +11534,7 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11628,11 +11546,11 @@
     <xf numFmtId="166" fontId="21" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="122" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="123" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="112" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="121" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="111" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -11704,290 +11622,442 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="105" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="72" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="105" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="104" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="103" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="7" borderId="82" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="10" fillId="7" borderId="84" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="105" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="100" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="89" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="114" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="84" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="83" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="87" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="95" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="67" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="73" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="31" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="102" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="103" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="31" fillId="7" borderId="103" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="10" fillId="7" borderId="76" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="31" fillId="7" borderId="104" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="105" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="80" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="88" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="93" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="97" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="105" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="106" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="75" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="99" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="112" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="113" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="31" fillId="7" borderId="113" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="31" fillId="7" borderId="114" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="115" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="10" fontId="31" fillId="7" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="98" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="90" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -12002,45 +12072,42 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="89" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="101" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="96" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="91" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="86" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="120" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="110" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="95" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="117" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="107" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="118" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="119" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="108" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="109" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="31" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -12049,7 +12116,7 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -12058,10 +12125,10 @@
     <xf numFmtId="0" fontId="11" fillId="4" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="96" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="69" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -16255,15 +16322,15 @@
       <c r="B1" s="145" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="725" t="s">
+      <c r="C1" s="768" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="624"/>
-      <c r="E1" s="624"/>
-      <c r="F1" s="624"/>
-      <c r="G1" s="624"/>
-      <c r="H1" s="624"/>
-      <c r="I1" s="625"/>
+      <c r="D1" s="769"/>
+      <c r="E1" s="769"/>
+      <c r="F1" s="769"/>
+      <c r="G1" s="769"/>
+      <c r="H1" s="769"/>
+      <c r="I1" s="703"/>
       <c r="J1" s="398"/>
       <c r="K1" s="398"/>
       <c r="L1" s="398"/>
@@ -16295,7 +16362,7 @@
       <c r="B3" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="C3" s="648" t="s">
+      <c r="C3" s="770" t="s">
         <v>1380</v>
       </c>
       <c r="D3" s="588"/>
@@ -16315,7 +16382,7 @@
       <c r="B4" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="648" t="s">
+      <c r="C4" s="770" t="s">
         <v>1381</v>
       </c>
       <c r="D4" s="588"/>
@@ -16407,33 +16474,33 @@
       <c r="N8" s="408"/>
     </row>
     <row r="9" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A9" s="726" t="s">
+      <c r="A9" s="772" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="683"/>
-      <c r="C9" s="683"/>
-      <c r="D9" s="683"/>
-      <c r="E9" s="683"/>
-      <c r="F9" s="683"/>
-      <c r="G9" s="683"/>
-      <c r="H9" s="683"/>
-      <c r="I9" s="683"/>
-      <c r="J9" s="683"/>
-      <c r="K9" s="683"/>
-      <c r="L9" s="683"/>
-      <c r="M9" s="683"/>
-      <c r="N9" s="685"/>
+      <c r="B9" s="723"/>
+      <c r="C9" s="723"/>
+      <c r="D9" s="723"/>
+      <c r="E9" s="723"/>
+      <c r="F9" s="723"/>
+      <c r="G9" s="723"/>
+      <c r="H9" s="723"/>
+      <c r="I9" s="723"/>
+      <c r="J9" s="723"/>
+      <c r="K9" s="723"/>
+      <c r="L9" s="723"/>
+      <c r="M9" s="723"/>
+      <c r="N9" s="725"/>
     </row>
     <row r="10" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A10" s="727">
+      <c r="A10" s="773">
         <v>1</v>
       </c>
       <c r="B10" s="591"/>
-      <c r="C10" s="728">
+      <c r="C10" s="774">
         <v>2</v>
       </c>
       <c r="D10" s="591"/>
-      <c r="E10" s="729">
+      <c r="E10" s="775">
         <v>3</v>
       </c>
       <c r="F10" s="591"/>
@@ -16446,7 +16513,7 @@
       <c r="I10" s="411">
         <v>6</v>
       </c>
-      <c r="J10" s="729">
+      <c r="J10" s="775">
         <v>7</v>
       </c>
       <c r="K10" s="595"/>
@@ -16455,51 +16522,51 @@
       <c r="N10" s="605"/>
     </row>
     <row r="11" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A11" s="730" t="s">
+      <c r="A11" s="776" t="s">
         <v>1384</v>
       </c>
-      <c r="B11" s="655"/>
-      <c r="C11" s="731" t="s">
+      <c r="B11" s="691"/>
+      <c r="C11" s="777" t="s">
         <v>1385</v>
       </c>
-      <c r="D11" s="617"/>
-      <c r="E11" s="732" t="s">
+      <c r="D11" s="694"/>
+      <c r="E11" s="778" t="s">
         <v>1386</v>
       </c>
-      <c r="F11" s="732" t="s">
+      <c r="F11" s="778" t="s">
         <v>1387</v>
       </c>
-      <c r="G11" s="732" t="s">
+      <c r="G11" s="778" t="s">
         <v>1388</v>
       </c>
-      <c r="H11" s="733" t="s">
+      <c r="H11" s="779" t="s">
         <v>1389</v>
       </c>
-      <c r="I11" s="734" t="s">
+      <c r="I11" s="780" t="s">
         <v>1390</v>
       </c>
-      <c r="J11" s="736" t="s">
+      <c r="J11" s="782" t="s">
         <v>1391</v>
       </c>
-      <c r="K11" s="737"/>
-      <c r="L11" s="737"/>
-      <c r="M11" s="737"/>
-      <c r="N11" s="696"/>
+      <c r="K11" s="783"/>
+      <c r="L11" s="783"/>
+      <c r="M11" s="783"/>
+      <c r="N11" s="739"/>
     </row>
     <row r="12" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A12" s="654"/>
-      <c r="B12" s="655"/>
-      <c r="C12" s="679" t="s">
+      <c r="A12" s="690"/>
+      <c r="B12" s="691"/>
+      <c r="C12" s="716" t="s">
         <v>1392</v>
       </c>
-      <c r="D12" s="679" t="s">
+      <c r="D12" s="716" t="s">
         <v>1393</v>
       </c>
-      <c r="E12" s="655"/>
-      <c r="F12" s="655"/>
-      <c r="G12" s="655"/>
+      <c r="E12" s="691"/>
+      <c r="F12" s="691"/>
+      <c r="G12" s="691"/>
       <c r="H12" s="588"/>
-      <c r="I12" s="735"/>
+      <c r="I12" s="781"/>
       <c r="J12" s="412">
         <v>1</v>
       </c>
@@ -16517,15 +16584,15 @@
       </c>
     </row>
     <row r="13" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A13" s="609"/>
-      <c r="B13" s="610"/>
-      <c r="C13" s="622"/>
-      <c r="D13" s="622"/>
-      <c r="E13" s="610"/>
-      <c r="F13" s="610"/>
-      <c r="G13" s="610"/>
+      <c r="A13" s="718"/>
+      <c r="B13" s="719"/>
+      <c r="C13" s="721"/>
+      <c r="D13" s="721"/>
+      <c r="E13" s="719"/>
+      <c r="F13" s="719"/>
+      <c r="G13" s="719"/>
       <c r="H13" s="582"/>
-      <c r="I13" s="687"/>
+      <c r="I13" s="727"/>
       <c r="J13" s="414" t="s">
         <v>1394</v>
       </c>
@@ -16760,15 +16827,15 @@
       <c r="N19" s="407"/>
     </row>
     <row r="20" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A20" s="711">
+      <c r="A20" s="754">
         <v>1</v>
       </c>
       <c r="B20" s="591"/>
-      <c r="C20" s="712">
+      <c r="C20" s="755">
         <v>2</v>
       </c>
       <c r="D20" s="591"/>
-      <c r="E20" s="712">
+      <c r="E20" s="755">
         <v>3</v>
       </c>
       <c r="F20" s="591"/>
@@ -16781,7 +16848,7 @@
       <c r="I20" s="431">
         <v>6</v>
       </c>
-      <c r="J20" s="738">
+      <c r="J20" s="771">
         <v>7</v>
       </c>
       <c r="K20" s="579"/>
@@ -16790,51 +16857,51 @@
       <c r="N20" s="580"/>
     </row>
     <row r="21" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A21" s="653" t="s">
+      <c r="A21" s="689" t="s">
         <v>1384</v>
       </c>
       <c r="B21" s="593"/>
-      <c r="C21" s="710" t="s">
+      <c r="C21" s="753" t="s">
         <v>1385</v>
       </c>
       <c r="D21" s="577"/>
-      <c r="E21" s="720" t="s">
+      <c r="E21" s="757" t="s">
         <v>1386</v>
       </c>
-      <c r="F21" s="720" t="s">
+      <c r="F21" s="757" t="s">
         <v>1387</v>
       </c>
-      <c r="G21" s="720" t="s">
+      <c r="G21" s="757" t="s">
         <v>1388</v>
       </c>
-      <c r="H21" s="721" t="s">
+      <c r="H21" s="759" t="s">
         <v>1389</v>
       </c>
-      <c r="I21" s="653" t="s">
+      <c r="I21" s="689" t="s">
         <v>1390</v>
       </c>
-      <c r="J21" s="710" t="s">
+      <c r="J21" s="753" t="s">
         <v>1391</v>
       </c>
       <c r="K21" s="576"/>
       <c r="L21" s="576"/>
       <c r="M21" s="576"/>
-      <c r="N21" s="665"/>
+      <c r="N21" s="701"/>
     </row>
     <row r="22" spans="1:14" ht="12.75" customHeight="1">
-      <c r="A22" s="654"/>
-      <c r="B22" s="655"/>
-      <c r="C22" s="724" t="s">
+      <c r="A22" s="690"/>
+      <c r="B22" s="691"/>
+      <c r="C22" s="756" t="s">
         <v>1403</v>
       </c>
-      <c r="D22" s="720" t="s">
+      <c r="D22" s="757" t="s">
         <v>1404</v>
       </c>
-      <c r="E22" s="673"/>
-      <c r="F22" s="673"/>
-      <c r="G22" s="673"/>
-      <c r="H22" s="722"/>
-      <c r="I22" s="654"/>
+      <c r="E22" s="710"/>
+      <c r="F22" s="710"/>
+      <c r="G22" s="710"/>
+      <c r="H22" s="760"/>
+      <c r="I22" s="690"/>
       <c r="J22" s="434">
         <v>1</v>
       </c>
@@ -16852,15 +16919,15 @@
       </c>
     </row>
     <row r="23" spans="1:14" ht="15.75" customHeight="1">
-      <c r="A23" s="609"/>
-      <c r="B23" s="610"/>
-      <c r="C23" s="610"/>
-      <c r="D23" s="622"/>
-      <c r="E23" s="622"/>
-      <c r="F23" s="622"/>
-      <c r="G23" s="622"/>
-      <c r="H23" s="723"/>
-      <c r="I23" s="609"/>
+      <c r="A23" s="718"/>
+      <c r="B23" s="719"/>
+      <c r="C23" s="719"/>
+      <c r="D23" s="721"/>
+      <c r="E23" s="721"/>
+      <c r="F23" s="721"/>
+      <c r="G23" s="721"/>
+      <c r="H23" s="761"/>
+      <c r="I23" s="718"/>
       <c r="J23" s="149" t="s">
         <v>1394</v>
       </c>
@@ -18911,19 +18978,19 @@
       <c r="B69" s="405"/>
       <c r="C69" s="405"/>
       <c r="D69" s="405"/>
-      <c r="E69" s="713" t="s">
+      <c r="E69" s="762" t="s">
         <v>1447</v>
       </c>
-      <c r="F69" s="714"/>
-      <c r="G69" s="715">
+      <c r="F69" s="763"/>
+      <c r="G69" s="764">
         <f t="shared" ref="G69:H69" si="6">SUM(G25:G68)</f>
         <v>2657</v>
       </c>
-      <c r="H69" s="716" t="e">
+      <c r="H69" s="765" t="e">
         <f t="shared" ca="1" si="6"/>
         <v>#NAME?</v>
       </c>
-      <c r="I69" s="717">
+      <c r="I69" s="766">
         <f>SUM(I24:I68)</f>
         <v>2657</v>
       </c>
@@ -18950,12 +19017,12 @@
       <c r="B70" s="475"/>
       <c r="C70" s="476"/>
       <c r="D70" s="476"/>
-      <c r="E70" s="609"/>
-      <c r="F70" s="613"/>
-      <c r="G70" s="615"/>
-      <c r="H70" s="615"/>
-      <c r="I70" s="718"/>
-      <c r="J70" s="719">
+      <c r="E70" s="718"/>
+      <c r="F70" s="734"/>
+      <c r="G70" s="736"/>
+      <c r="H70" s="736"/>
+      <c r="I70" s="767"/>
+      <c r="J70" s="758">
         <f>SUM(M69:N69)/I69</f>
         <v>1</v>
       </c>
@@ -22876,6 +22943,7 @@
     <mergeCell ref="I11:I13"/>
     <mergeCell ref="J10:N10"/>
     <mergeCell ref="J11:N11"/>
+    <mergeCell ref="E20:F20"/>
     <mergeCell ref="C1:I1"/>
     <mergeCell ref="C2:N2"/>
     <mergeCell ref="C3:N3"/>
@@ -22887,7 +22955,6 @@
     <mergeCell ref="H21:H23"/>
     <mergeCell ref="I21:I23"/>
     <mergeCell ref="J21:N21"/>
-    <mergeCell ref="E20:F20"/>
     <mergeCell ref="E69:F70"/>
     <mergeCell ref="G69:G70"/>
     <mergeCell ref="H69:H70"/>
@@ -22950,7 +23017,7 @@
       <c r="A3" s="79" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="648" t="s">
+      <c r="B3" s="770" t="s">
         <v>1448</v>
       </c>
       <c r="C3" s="588"/>
@@ -22961,7 +23028,7 @@
       <c r="A4" s="485" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="648" t="s">
+      <c r="B4" s="770" t="s">
         <v>1449</v>
       </c>
       <c r="C4" s="588"/>
@@ -23009,7 +23076,7 @@
       <c r="E8" s="249"/>
     </row>
     <row r="9" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A9" s="741" t="s">
+      <c r="A9" s="786" t="s">
         <v>116</v>
       </c>
       <c r="B9" s="579"/>
@@ -23021,23 +23088,23 @@
       <c r="A10" s="487">
         <v>1</v>
       </c>
-      <c r="B10" s="742">
+      <c r="B10" s="787">
         <v>2</v>
       </c>
-      <c r="C10" s="743"/>
-      <c r="D10" s="742">
+      <c r="C10" s="788"/>
+      <c r="D10" s="787">
         <v>3</v>
       </c>
-      <c r="E10" s="685"/>
+      <c r="E10" s="725"/>
     </row>
     <row r="11" spans="1:5" ht="38.25" customHeight="1">
       <c r="A11" s="488" t="s">
         <v>1452</v>
       </c>
-      <c r="B11" s="744" t="s">
+      <c r="B11" s="789" t="s">
         <v>1453</v>
       </c>
-      <c r="C11" s="610"/>
+      <c r="C11" s="719"/>
       <c r="D11" s="414" t="s">
         <v>1454</v>
       </c>
@@ -23141,20 +23208,20 @@
       <c r="A18" s="500">
         <v>1</v>
       </c>
-      <c r="B18" s="745">
+      <c r="B18" s="790">
         <v>2</v>
       </c>
-      <c r="C18" s="746"/>
-      <c r="D18" s="747">
+      <c r="C18" s="791"/>
+      <c r="D18" s="792">
         <v>3</v>
       </c>
-      <c r="E18" s="685"/>
+      <c r="E18" s="725"/>
     </row>
     <row r="19" spans="1:5" ht="38.25" customHeight="1">
       <c r="A19" s="501" t="s">
         <v>1452</v>
       </c>
-      <c r="B19" s="748" t="s">
+      <c r="B19" s="793" t="s">
         <v>1453</v>
       </c>
       <c r="C19" s="580"/>
@@ -23258,10 +23325,10 @@
       <c r="E25" s="378"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A26" s="739" t="s">
+      <c r="A26" s="784" t="s">
         <v>1469</v>
       </c>
-      <c r="B26" s="740"/>
+      <c r="B26" s="785"/>
       <c r="C26" s="522">
         <v>5</v>
       </c>
@@ -24379,10 +24446,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A1" s="754" t="s">
+      <c r="A1" s="799" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="625"/>
+      <c r="B1" s="703"/>
       <c r="C1" s="604" t="s">
         <v>106</v>
       </c>
@@ -24390,7 +24457,7 @@
       <c r="E1" s="605"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A2" s="751" t="s">
+      <c r="A2" s="796" t="s">
         <v>107</v>
       </c>
       <c r="B2" s="588"/>
@@ -24401,29 +24468,29 @@
       <c r="E2" s="597"/>
     </row>
     <row r="3" spans="1:5" ht="29.25" customHeight="1">
-      <c r="A3" s="755" t="s">
+      <c r="A3" s="800" t="s">
         <v>108</v>
       </c>
       <c r="B3" s="588"/>
-      <c r="C3" s="648" t="s">
+      <c r="C3" s="770" t="s">
         <v>1470</v>
       </c>
       <c r="D3" s="588"/>
       <c r="E3" s="597"/>
     </row>
     <row r="4" spans="1:5" ht="54.75" customHeight="1">
-      <c r="A4" s="751" t="s">
+      <c r="A4" s="796" t="s">
         <v>110</v>
       </c>
       <c r="B4" s="588"/>
-      <c r="C4" s="648" t="s">
+      <c r="C4" s="770" t="s">
         <v>1471</v>
       </c>
       <c r="D4" s="588"/>
       <c r="E4" s="597"/>
     </row>
     <row r="5" spans="1:5" ht="24.75" customHeight="1">
-      <c r="A5" s="751" t="s">
+      <c r="A5" s="796" t="s">
         <v>112</v>
       </c>
       <c r="B5" s="588"/>
@@ -24434,7 +24501,7 @@
       <c r="E5" s="404"/>
     </row>
     <row r="6" spans="1:5" ht="51.75" customHeight="1">
-      <c r="A6" s="751" t="s">
+      <c r="A6" s="796" t="s">
         <v>113</v>
       </c>
       <c r="B6" s="588"/>
@@ -24445,10 +24512,10 @@
       <c r="E6" s="404"/>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A7" s="752" t="s">
+      <c r="A7" s="797" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="670"/>
+      <c r="B7" s="707"/>
       <c r="C7" s="598" t="s">
         <v>115</v>
       </c>
@@ -24470,20 +24537,20 @@
       <c r="E9" s="525"/>
     </row>
     <row r="10" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A10" s="753">
+      <c r="A10" s="798">
         <v>1</v>
       </c>
-      <c r="B10" s="685"/>
+      <c r="B10" s="725"/>
       <c r="C10" s="526">
         <v>2</v>
       </c>
-      <c r="D10" s="742">
+      <c r="D10" s="787">
         <v>3</v>
       </c>
-      <c r="E10" s="685"/>
+      <c r="E10" s="725"/>
     </row>
     <row r="11" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A11" s="749" t="s">
+      <c r="A11" s="794" t="s">
         <v>1474</v>
       </c>
       <c r="B11" s="583"/>
@@ -24556,23 +24623,23 @@
       <c r="E15" s="525"/>
     </row>
     <row r="16" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A16" s="750">
+      <c r="A16" s="795">
         <v>1</v>
       </c>
-      <c r="B16" s="743"/>
+      <c r="B16" s="788"/>
       <c r="C16" s="531">
         <v>2</v>
       </c>
-      <c r="D16" s="747">
+      <c r="D16" s="792">
         <v>3</v>
       </c>
-      <c r="E16" s="685"/>
+      <c r="E16" s="725"/>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A17" s="748" t="s">
+      <c r="A17" s="793" t="s">
         <v>1474</v>
       </c>
-      <c r="B17" s="746"/>
+      <c r="B17" s="791"/>
       <c r="C17" s="532" t="s">
         <v>1475</v>
       </c>
@@ -28348,105 +28415,105 @@
       <c r="A1" s="78" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="604" t="s">
+      <c r="B1" s="672" t="s">
         <v>160</v>
       </c>
-      <c r="C1" s="595"/>
-      <c r="D1" s="595"/>
-      <c r="E1" s="595"/>
-      <c r="F1" s="595"/>
-      <c r="G1" s="595"/>
-      <c r="H1" s="605"/>
+      <c r="C1" s="672"/>
+      <c r="D1" s="672"/>
+      <c r="E1" s="672"/>
+      <c r="F1" s="672"/>
+      <c r="G1" s="672"/>
+      <c r="H1" s="673"/>
     </row>
     <row r="2" spans="1:8" ht="15.75" customHeight="1">
       <c r="A2" s="79" t="s">
         <v>107</v>
       </c>
-      <c r="B2" s="646" t="s">
+      <c r="B2" s="674" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="588"/>
-      <c r="D2" s="588"/>
-      <c r="E2" s="588"/>
-      <c r="F2" s="588"/>
-      <c r="G2" s="588"/>
-      <c r="H2" s="597"/>
+      <c r="C2" s="674"/>
+      <c r="D2" s="674"/>
+      <c r="E2" s="674"/>
+      <c r="F2" s="674"/>
+      <c r="G2" s="674"/>
+      <c r="H2" s="675"/>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1">
       <c r="A3" s="79" t="s">
         <v>108</v>
       </c>
-      <c r="B3" s="647" t="s">
+      <c r="B3" s="676" t="s">
         <v>161</v>
       </c>
-      <c r="C3" s="588"/>
-      <c r="D3" s="588"/>
-      <c r="E3" s="588"/>
-      <c r="F3" s="588"/>
-      <c r="G3" s="588"/>
-      <c r="H3" s="597"/>
+      <c r="C3" s="676"/>
+      <c r="D3" s="676"/>
+      <c r="E3" s="676"/>
+      <c r="F3" s="676"/>
+      <c r="G3" s="676"/>
+      <c r="H3" s="677"/>
     </row>
     <row r="4" spans="1:8" ht="78.75" customHeight="1">
       <c r="A4" s="79" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="648" t="s">
+      <c r="B4" s="678" t="s">
         <v>162</v>
       </c>
-      <c r="C4" s="588"/>
-      <c r="D4" s="588"/>
-      <c r="E4" s="588"/>
-      <c r="F4" s="588"/>
-      <c r="G4" s="588"/>
-      <c r="H4" s="597"/>
+      <c r="C4" s="678"/>
+      <c r="D4" s="678"/>
+      <c r="E4" s="678"/>
+      <c r="F4" s="678"/>
+      <c r="G4" s="678"/>
+      <c r="H4" s="679"/>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1">
       <c r="A5" s="79" t="s">
         <v>112</v>
       </c>
-      <c r="B5" s="647" t="str">
+      <c r="B5" s="676" t="str">
         <f>'Reference Matrix'!$E7</f>
         <v>Summary Sheets</v>
       </c>
-      <c r="C5" s="588"/>
-      <c r="D5" s="588"/>
-      <c r="E5" s="588"/>
-      <c r="F5" s="588"/>
-      <c r="G5" s="588"/>
-      <c r="H5" s="597"/>
+      <c r="C5" s="676"/>
+      <c r="D5" s="676"/>
+      <c r="E5" s="676"/>
+      <c r="F5" s="676"/>
+      <c r="G5" s="676"/>
+      <c r="H5" s="677"/>
     </row>
     <row r="6" spans="1:8" ht="39.75" customHeight="1">
       <c r="A6" s="79" t="s">
         <v>113</v>
       </c>
-      <c r="B6" s="587" t="str">
+      <c r="B6" s="680" t="str">
         <f>'Reference Matrix'!$F7</f>
         <v>1. Graduate tracer study
 2. Result of survey of employed from the graduates in the 1st semester of FY 2021-2022, certified by the Registrar
 3. Total Enrolment in the 1st Semester of AY 2021-2022, certified by the Registrar</v>
       </c>
-      <c r="C6" s="588"/>
-      <c r="D6" s="588"/>
-      <c r="E6" s="588"/>
-      <c r="F6" s="588"/>
-      <c r="G6" s="588"/>
-      <c r="H6" s="597"/>
+      <c r="C6" s="680"/>
+      <c r="D6" s="680"/>
+      <c r="E6" s="680"/>
+      <c r="F6" s="680"/>
+      <c r="G6" s="680"/>
+      <c r="H6" s="681"/>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1">
       <c r="A7" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="B7" s="598" t="s">
+      <c r="B7" s="682" t="s">
         <v>115</v>
       </c>
-      <c r="C7" s="599"/>
-      <c r="D7" s="599"/>
-      <c r="E7" s="599"/>
-      <c r="F7" s="599"/>
-      <c r="G7" s="599"/>
-      <c r="H7" s="586"/>
-    </row>
-    <row r="8" spans="1:8" ht="12.75" customHeight="1">
+      <c r="C7" s="682"/>
+      <c r="D7" s="682"/>
+      <c r="E7" s="682"/>
+      <c r="F7" s="682"/>
+      <c r="G7" s="682"/>
+      <c r="H7" s="683"/>
+    </row>
+    <row r="8" spans="1:8" ht="12.75" customHeight="1" thickBot="1">
       <c r="A8" s="80"/>
       <c r="B8" s="64"/>
       <c r="C8" s="64"/>
@@ -28457,30 +28524,30 @@
       <c r="H8" s="64"/>
     </row>
     <row r="9" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A9" s="589" t="s">
+      <c r="A9" s="650" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="579"/>
-      <c r="C9" s="579"/>
-      <c r="D9" s="579"/>
-      <c r="E9" s="579"/>
-      <c r="F9" s="579"/>
-      <c r="G9" s="579"/>
-      <c r="H9" s="580"/>
+      <c r="B9" s="651"/>
+      <c r="C9" s="651"/>
+      <c r="D9" s="651"/>
+      <c r="E9" s="651"/>
+      <c r="F9" s="651"/>
+      <c r="G9" s="651"/>
+      <c r="H9" s="652"/>
     </row>
     <row r="10" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A10" s="636">
+      <c r="A10" s="653">
         <v>1</v>
       </c>
-      <c r="B10" s="577"/>
+      <c r="B10" s="654"/>
       <c r="C10" s="82">
         <v>2</v>
       </c>
-      <c r="D10" s="637">
+      <c r="D10" s="655">
         <v>3</v>
       </c>
-      <c r="E10" s="576"/>
-      <c r="F10" s="577"/>
+      <c r="E10" s="656"/>
+      <c r="F10" s="654"/>
       <c r="G10" s="82">
         <v>4</v>
       </c>
@@ -28488,19 +28555,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A11" s="638" t="s">
+    <row r="11" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A11" s="657" t="s">
         <v>163</v>
       </c>
-      <c r="B11" s="602"/>
+      <c r="B11" s="658"/>
       <c r="C11" s="84" t="s">
         <v>164</v>
       </c>
-      <c r="D11" s="639" t="s">
+      <c r="D11" s="659" t="s">
         <v>165</v>
       </c>
-      <c r="E11" s="635"/>
-      <c r="F11" s="602"/>
+      <c r="E11" s="660"/>
+      <c r="F11" s="658"/>
       <c r="G11" s="84" t="s">
         <v>166</v>
       </c>
@@ -28509,16 +28576,16 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A12" s="640" t="s">
+      <c r="A12" s="661" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="641"/>
-      <c r="C12" s="641"/>
-      <c r="D12" s="641"/>
-      <c r="E12" s="641"/>
-      <c r="F12" s="641"/>
-      <c r="G12" s="642"/>
-      <c r="H12" s="643" t="s">
+      <c r="B12" s="662"/>
+      <c r="C12" s="662"/>
+      <c r="D12" s="662"/>
+      <c r="E12" s="662"/>
+      <c r="F12" s="662"/>
+      <c r="G12" s="663"/>
+      <c r="H12" s="664" t="s">
         <v>167</v>
       </c>
     </row>
@@ -28532,15 +28599,15 @@
       <c r="C13" s="87" t="s">
         <v>168</v>
       </c>
-      <c r="D13" s="649" t="s">
+      <c r="D13" s="667" t="s">
         <v>169</v>
       </c>
-      <c r="E13" s="576"/>
-      <c r="F13" s="577"/>
+      <c r="E13" s="668"/>
+      <c r="F13" s="669"/>
       <c r="G13" s="88" t="s">
         <v>170</v>
       </c>
-      <c r="H13" s="644"/>
+      <c r="H13" s="665"/>
     </row>
     <row r="14" spans="1:8" ht="15.75" customHeight="1">
       <c r="A14" s="85" t="s">
@@ -28552,13 +28619,13 @@
       <c r="C14" s="87" t="s">
         <v>168</v>
       </c>
-      <c r="D14" s="649" t="s">
+      <c r="D14" s="667" t="s">
         <v>171</v>
       </c>
-      <c r="E14" s="576"/>
-      <c r="F14" s="577"/>
+      <c r="E14" s="668"/>
+      <c r="F14" s="669"/>
       <c r="G14" s="88"/>
-      <c r="H14" s="644"/>
+      <c r="H14" s="665"/>
     </row>
     <row r="15" spans="1:8" ht="15.75" customHeight="1">
       <c r="A15" s="85" t="s">
@@ -28570,13 +28637,13 @@
       <c r="C15" s="87" t="s">
         <v>168</v>
       </c>
-      <c r="D15" s="649" t="s">
+      <c r="D15" s="667" t="s">
         <v>172</v>
       </c>
-      <c r="E15" s="576"/>
-      <c r="F15" s="577"/>
+      <c r="E15" s="668"/>
+      <c r="F15" s="669"/>
       <c r="G15" s="88"/>
-      <c r="H15" s="644"/>
+      <c r="H15" s="665"/>
     </row>
     <row r="16" spans="1:8" ht="15.75" customHeight="1">
       <c r="A16" s="85" t="s">
@@ -28588,15 +28655,15 @@
       <c r="C16" s="87" t="s">
         <v>168</v>
       </c>
-      <c r="D16" s="649" t="s">
+      <c r="D16" s="667" t="s">
         <v>169</v>
       </c>
-      <c r="E16" s="576"/>
-      <c r="F16" s="577"/>
+      <c r="E16" s="668"/>
+      <c r="F16" s="669"/>
       <c r="G16" s="88" t="s">
         <v>173</v>
       </c>
-      <c r="H16" s="644"/>
+      <c r="H16" s="665"/>
     </row>
     <row r="17" spans="1:8" ht="15.75" customHeight="1">
       <c r="A17" s="85" t="s">
@@ -28608,22 +28675,22 @@
       <c r="C17" s="87" t="s">
         <v>168</v>
       </c>
-      <c r="D17" s="649" t="s">
+      <c r="D17" s="667" t="s">
         <v>169</v>
       </c>
-      <c r="E17" s="576"/>
-      <c r="F17" s="577"/>
+      <c r="E17" s="668"/>
+      <c r="F17" s="669"/>
       <c r="G17" s="88" t="s">
         <v>174</v>
       </c>
-      <c r="H17" s="644"/>
+      <c r="H17" s="665"/>
     </row>
     <row r="18" spans="1:8" ht="13.5" customHeight="1">
-      <c r="A18" s="629" t="s">
+      <c r="A18" s="635" t="s">
         <v>175</v>
       </c>
-      <c r="B18" s="593"/>
-      <c r="C18" s="630">
+      <c r="B18" s="636"/>
+      <c r="C18" s="639">
         <f>COUNTIFS($A13:$A17,"*",$C13:$C17,"*",$D13:$D17,"*")</f>
         <v>5</v>
       </c>
@@ -28637,12 +28704,12 @@
         <v>178</v>
       </c>
       <c r="G18" s="91"/>
-      <c r="H18" s="644"/>
-    </row>
-    <row r="19" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A19" s="609"/>
-      <c r="B19" s="610"/>
-      <c r="C19" s="631"/>
+      <c r="H18" s="665"/>
+    </row>
+    <row r="19" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A19" s="637"/>
+      <c r="B19" s="638"/>
+      <c r="C19" s="640"/>
       <c r="D19" s="92">
         <f>COUNTIFS($A13:$A17,"*",$C13:$C17,"*",$D13:$D17, "Employed")</f>
         <v>3</v>
@@ -28656,9 +28723,9 @@
         <v>1</v>
       </c>
       <c r="G19" s="93"/>
-      <c r="H19" s="645"/>
-    </row>
-    <row r="20" spans="1:8" ht="13.5" customHeight="1">
+      <c r="H19" s="666"/>
+    </row>
+    <row r="20" spans="1:8" ht="13.5" customHeight="1" thickBot="1">
       <c r="A20" s="77"/>
       <c r="B20" s="64"/>
       <c r="C20" s="77"/>
@@ -28669,18 +28736,18 @@
       <c r="H20" s="77"/>
     </row>
     <row r="21" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A21" s="632">
+      <c r="A21" s="641">
         <v>1</v>
       </c>
-      <c r="B21" s="591"/>
+      <c r="B21" s="642"/>
       <c r="C21" s="94">
         <v>2</v>
       </c>
-      <c r="D21" s="633">
+      <c r="D21" s="643">
         <v>3</v>
       </c>
-      <c r="E21" s="595"/>
-      <c r="F21" s="591"/>
+      <c r="E21" s="644"/>
+      <c r="F21" s="642"/>
       <c r="G21" s="95">
         <v>4</v>
       </c>
@@ -28688,19 +28755,19 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15.75" customHeight="1">
+    <row r="22" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
       <c r="A22" s="601" t="s">
         <v>163</v>
       </c>
-      <c r="B22" s="602"/>
+      <c r="B22" s="645"/>
       <c r="C22" s="97" t="s">
         <v>164</v>
       </c>
-      <c r="D22" s="634" t="s">
+      <c r="D22" s="646" t="s">
         <v>179</v>
       </c>
-      <c r="E22" s="635"/>
-      <c r="F22" s="602"/>
+      <c r="E22" s="647"/>
+      <c r="F22" s="645"/>
       <c r="G22" s="97" t="s">
         <v>166</v>
       </c>
@@ -28712,13 +28779,13 @@
       <c r="A23" s="603" t="s">
         <v>130</v>
       </c>
-      <c r="B23" s="595"/>
-      <c r="C23" s="595"/>
-      <c r="D23" s="595"/>
-      <c r="E23" s="595"/>
-      <c r="F23" s="595"/>
-      <c r="G23" s="591"/>
-      <c r="H23" s="650"/>
+      <c r="B23" s="648"/>
+      <c r="C23" s="648"/>
+      <c r="D23" s="648"/>
+      <c r="E23" s="648"/>
+      <c r="F23" s="648"/>
+      <c r="G23" s="649"/>
+      <c r="H23" s="670"/>
     </row>
     <row r="24" spans="1:8" ht="15.75" customHeight="1">
       <c r="A24" s="98" t="s">
@@ -28733,12 +28800,12 @@
       <c r="D24" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E24" s="576"/>
-      <c r="F24" s="577"/>
+      <c r="E24" s="608"/>
+      <c r="F24" s="609"/>
       <c r="G24" s="101" t="s">
         <v>181</v>
       </c>
-      <c r="H24" s="644"/>
+      <c r="H24" s="671"/>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1">
       <c r="A25" s="98" t="s">
@@ -28753,10 +28820,10 @@
       <c r="D25" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E25" s="576"/>
-      <c r="F25" s="577"/>
+      <c r="E25" s="608"/>
+      <c r="F25" s="609"/>
       <c r="G25" s="101"/>
-      <c r="H25" s="644"/>
+      <c r="H25" s="671"/>
     </row>
     <row r="26" spans="1:8" ht="15.75" customHeight="1">
       <c r="A26" s="98" t="s">
@@ -28771,12 +28838,12 @@
       <c r="D26" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E26" s="576"/>
-      <c r="F26" s="577"/>
+      <c r="E26" s="608"/>
+      <c r="F26" s="609"/>
       <c r="G26" s="102" t="s">
         <v>184</v>
       </c>
-      <c r="H26" s="644"/>
+      <c r="H26" s="671"/>
     </row>
     <row r="27" spans="1:8" ht="15.75" customHeight="1">
       <c r="A27" s="98" t="s">
@@ -28791,12 +28858,12 @@
       <c r="D27" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E27" s="576"/>
-      <c r="F27" s="577"/>
+      <c r="E27" s="608"/>
+      <c r="F27" s="609"/>
       <c r="G27" s="102" t="s">
         <v>186</v>
       </c>
-      <c r="H27" s="644"/>
+      <c r="H27" s="671"/>
     </row>
     <row r="28" spans="1:8" ht="15.75" customHeight="1">
       <c r="A28" s="98" t="s">
@@ -28811,10 +28878,10 @@
       <c r="D28" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E28" s="576"/>
-      <c r="F28" s="577"/>
+      <c r="E28" s="608"/>
+      <c r="F28" s="609"/>
       <c r="G28" s="101"/>
-      <c r="H28" s="644"/>
+      <c r="H28" s="671"/>
     </row>
     <row r="29" spans="1:8" ht="15.75" customHeight="1">
       <c r="A29" s="98" t="s">
@@ -28829,10 +28896,10 @@
       <c r="D29" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E29" s="576"/>
-      <c r="F29" s="577"/>
+      <c r="E29" s="608"/>
+      <c r="F29" s="609"/>
       <c r="G29" s="101"/>
-      <c r="H29" s="644"/>
+      <c r="H29" s="671"/>
     </row>
     <row r="30" spans="1:8" ht="15.75" customHeight="1">
       <c r="A30" s="98" t="s">
@@ -28847,10 +28914,10 @@
       <c r="D30" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E30" s="576"/>
-      <c r="F30" s="577"/>
+      <c r="E30" s="608"/>
+      <c r="F30" s="609"/>
       <c r="G30" s="101"/>
-      <c r="H30" s="644"/>
+      <c r="H30" s="671"/>
     </row>
     <row r="31" spans="1:8" ht="15.75" customHeight="1">
       <c r="A31" s="98" t="s">
@@ -28865,10 +28932,10 @@
       <c r="D31" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E31" s="576"/>
-      <c r="F31" s="577"/>
+      <c r="E31" s="608"/>
+      <c r="F31" s="609"/>
       <c r="G31" s="101"/>
-      <c r="H31" s="644"/>
+      <c r="H31" s="671"/>
     </row>
     <row r="32" spans="1:8" ht="15.75" customHeight="1">
       <c r="A32" s="98" t="s">
@@ -28883,10 +28950,10 @@
       <c r="D32" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E32" s="576"/>
-      <c r="F32" s="577"/>
+      <c r="E32" s="608"/>
+      <c r="F32" s="609"/>
       <c r="G32" s="105"/>
-      <c r="H32" s="644"/>
+      <c r="H32" s="671"/>
     </row>
     <row r="33" spans="1:8" ht="15.75" customHeight="1">
       <c r="A33" s="98" t="s">
@@ -28901,12 +28968,12 @@
       <c r="D33" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E33" s="576"/>
-      <c r="F33" s="577"/>
+      <c r="E33" s="608"/>
+      <c r="F33" s="609"/>
       <c r="G33" s="107" t="s">
         <v>195</v>
       </c>
-      <c r="H33" s="644"/>
+      <c r="H33" s="671"/>
     </row>
     <row r="34" spans="1:8" ht="15.75" customHeight="1">
       <c r="A34" s="98" t="s">
@@ -28921,10 +28988,10 @@
       <c r="D34" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E34" s="576"/>
-      <c r="F34" s="577"/>
+      <c r="E34" s="608"/>
+      <c r="F34" s="609"/>
       <c r="G34" s="105"/>
-      <c r="H34" s="644"/>
+      <c r="H34" s="671"/>
     </row>
     <row r="35" spans="1:8" ht="15.75" customHeight="1">
       <c r="A35" s="98" t="s">
@@ -28939,10 +29006,10 @@
       <c r="D35" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E35" s="576"/>
-      <c r="F35" s="577"/>
+      <c r="E35" s="608"/>
+      <c r="F35" s="609"/>
       <c r="G35" s="105"/>
-      <c r="H35" s="644"/>
+      <c r="H35" s="671"/>
     </row>
     <row r="36" spans="1:8" ht="15.75" customHeight="1">
       <c r="A36" s="98" t="s">
@@ -28957,12 +29024,12 @@
       <c r="D36" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E36" s="576"/>
-      <c r="F36" s="577"/>
+      <c r="E36" s="608"/>
+      <c r="F36" s="609"/>
       <c r="G36" s="108" t="s">
         <v>200</v>
       </c>
-      <c r="H36" s="644"/>
+      <c r="H36" s="671"/>
     </row>
     <row r="37" spans="1:8" ht="15.75" customHeight="1">
       <c r="A37" s="98" t="s">
@@ -28977,10 +29044,10 @@
       <c r="D37" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E37" s="576"/>
-      <c r="F37" s="577"/>
+      <c r="E37" s="608"/>
+      <c r="F37" s="609"/>
       <c r="G37" s="105"/>
-      <c r="H37" s="644"/>
+      <c r="H37" s="671"/>
     </row>
     <row r="38" spans="1:8" ht="15.75" customHeight="1">
       <c r="A38" s="98" t="s">
@@ -28995,12 +29062,12 @@
       <c r="D38" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E38" s="576"/>
-      <c r="F38" s="577"/>
+      <c r="E38" s="608"/>
+      <c r="F38" s="609"/>
       <c r="G38" s="108" t="s">
         <v>204</v>
       </c>
-      <c r="H38" s="644"/>
+      <c r="H38" s="671"/>
     </row>
     <row r="39" spans="1:8" ht="15.75" customHeight="1">
       <c r="A39" s="98" t="s">
@@ -29015,10 +29082,10 @@
       <c r="D39" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E39" s="576"/>
-      <c r="F39" s="577"/>
+      <c r="E39" s="608"/>
+      <c r="F39" s="609"/>
       <c r="G39" s="105"/>
-      <c r="H39" s="644"/>
+      <c r="H39" s="671"/>
     </row>
     <row r="40" spans="1:8" ht="15.75" customHeight="1">
       <c r="A40" s="98" t="s">
@@ -29033,12 +29100,12 @@
       <c r="D40" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E40" s="576"/>
-      <c r="F40" s="577"/>
+      <c r="E40" s="608"/>
+      <c r="F40" s="609"/>
       <c r="G40" s="108" t="s">
         <v>208</v>
       </c>
-      <c r="H40" s="644"/>
+      <c r="H40" s="671"/>
     </row>
     <row r="41" spans="1:8" ht="15.75" customHeight="1">
       <c r="A41" s="98" t="s">
@@ -29053,12 +29120,12 @@
       <c r="D41" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E41" s="576"/>
-      <c r="F41" s="577"/>
+      <c r="E41" s="608"/>
+      <c r="F41" s="609"/>
       <c r="G41" s="108" t="s">
         <v>210</v>
       </c>
-      <c r="H41" s="644"/>
+      <c r="H41" s="671"/>
     </row>
     <row r="42" spans="1:8" ht="15.75" customHeight="1">
       <c r="A42" s="98" t="s">
@@ -29073,12 +29140,12 @@
       <c r="D42" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E42" s="576"/>
-      <c r="F42" s="577"/>
+      <c r="E42" s="608"/>
+      <c r="F42" s="609"/>
       <c r="G42" s="108" t="s">
         <v>212</v>
       </c>
-      <c r="H42" s="644"/>
+      <c r="H42" s="671"/>
     </row>
     <row r="43" spans="1:8" ht="15.75" customHeight="1">
       <c r="A43" s="98" t="s">
@@ -29093,10 +29160,10 @@
       <c r="D43" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E43" s="576"/>
-      <c r="F43" s="577"/>
+      <c r="E43" s="608"/>
+      <c r="F43" s="609"/>
       <c r="G43" s="105"/>
-      <c r="H43" s="644"/>
+      <c r="H43" s="671"/>
     </row>
     <row r="44" spans="1:8" ht="15.75" customHeight="1">
       <c r="A44" s="98" t="s">
@@ -29111,10 +29178,10 @@
       <c r="D44" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E44" s="576"/>
-      <c r="F44" s="577"/>
+      <c r="E44" s="608"/>
+      <c r="F44" s="609"/>
       <c r="G44" s="109"/>
-      <c r="H44" s="644"/>
+      <c r="H44" s="671"/>
     </row>
     <row r="45" spans="1:8" ht="15.75" customHeight="1">
       <c r="A45" s="98" t="s">
@@ -29129,12 +29196,12 @@
       <c r="D45" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E45" s="576"/>
-      <c r="F45" s="577"/>
+      <c r="E45" s="608"/>
+      <c r="F45" s="609"/>
       <c r="G45" s="108" t="s">
         <v>216</v>
       </c>
-      <c r="H45" s="644"/>
+      <c r="H45" s="671"/>
     </row>
     <row r="46" spans="1:8" ht="15.75" customHeight="1">
       <c r="A46" s="98" t="s">
@@ -29149,12 +29216,12 @@
       <c r="D46" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E46" s="576"/>
-      <c r="F46" s="577"/>
+      <c r="E46" s="608"/>
+      <c r="F46" s="609"/>
       <c r="G46" s="108" t="s">
         <v>219</v>
       </c>
-      <c r="H46" s="644"/>
+      <c r="H46" s="671"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1">
       <c r="A47" s="98" t="s">
@@ -29169,12 +29236,12 @@
       <c r="D47" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E47" s="576"/>
-      <c r="F47" s="577"/>
+      <c r="E47" s="608"/>
+      <c r="F47" s="609"/>
       <c r="G47" s="108" t="s">
         <v>221</v>
       </c>
-      <c r="H47" s="644"/>
+      <c r="H47" s="671"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1">
       <c r="A48" s="98" t="s">
@@ -29186,13 +29253,13 @@
       <c r="C48" s="106" t="s">
         <v>222</v>
       </c>
-      <c r="D48" s="628" t="s">
+      <c r="D48" s="632" t="s">
         <v>172</v>
       </c>
-      <c r="E48" s="576"/>
-      <c r="F48" s="577"/>
+      <c r="E48" s="633"/>
+      <c r="F48" s="634"/>
       <c r="G48" s="110"/>
-      <c r="H48" s="644"/>
+      <c r="H48" s="671"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" customHeight="1">
       <c r="A49" s="98" t="s">
@@ -29207,12 +29274,12 @@
       <c r="D49" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E49" s="576"/>
-      <c r="F49" s="577"/>
+      <c r="E49" s="608"/>
+      <c r="F49" s="609"/>
       <c r="G49" s="108" t="s">
         <v>224</v>
       </c>
-      <c r="H49" s="644"/>
+      <c r="H49" s="671"/>
     </row>
     <row r="50" spans="1:8" ht="15.75" customHeight="1">
       <c r="A50" s="98" t="s">
@@ -29227,10 +29294,10 @@
       <c r="D50" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E50" s="576"/>
-      <c r="F50" s="577"/>
+      <c r="E50" s="608"/>
+      <c r="F50" s="609"/>
       <c r="G50" s="109"/>
-      <c r="H50" s="644"/>
+      <c r="H50" s="671"/>
     </row>
     <row r="51" spans="1:8" ht="15.75" customHeight="1">
       <c r="A51" s="98" t="s">
@@ -29245,12 +29312,12 @@
       <c r="D51" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E51" s="576"/>
-      <c r="F51" s="577"/>
+      <c r="E51" s="608"/>
+      <c r="F51" s="609"/>
       <c r="G51" s="107" t="s">
         <v>227</v>
       </c>
-      <c r="H51" s="644"/>
+      <c r="H51" s="671"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" customHeight="1">
       <c r="A52" s="98" t="s">
@@ -29265,12 +29332,12 @@
       <c r="D52" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E52" s="576"/>
-      <c r="F52" s="577"/>
+      <c r="E52" s="608"/>
+      <c r="F52" s="609"/>
       <c r="G52" s="108" t="s">
         <v>229</v>
       </c>
-      <c r="H52" s="644"/>
+      <c r="H52" s="671"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1">
       <c r="A53" s="98" t="s">
@@ -29285,10 +29352,10 @@
       <c r="D53" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E53" s="576"/>
-      <c r="F53" s="577"/>
+      <c r="E53" s="608"/>
+      <c r="F53" s="609"/>
       <c r="G53" s="105"/>
-      <c r="H53" s="644"/>
+      <c r="H53" s="671"/>
     </row>
     <row r="54" spans="1:8" ht="15.75" customHeight="1">
       <c r="A54" s="98" t="s">
@@ -29303,12 +29370,12 @@
       <c r="D54" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E54" s="576"/>
-      <c r="F54" s="577"/>
+      <c r="E54" s="608"/>
+      <c r="F54" s="609"/>
       <c r="G54" s="108" t="s">
         <v>233</v>
       </c>
-      <c r="H54" s="644"/>
+      <c r="H54" s="671"/>
     </row>
     <row r="55" spans="1:8" ht="15.75" customHeight="1">
       <c r="A55" s="98" t="s">
@@ -29323,12 +29390,12 @@
       <c r="D55" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E55" s="576"/>
-      <c r="F55" s="577"/>
+      <c r="E55" s="608"/>
+      <c r="F55" s="609"/>
       <c r="G55" s="108" t="s">
         <v>235</v>
       </c>
-      <c r="H55" s="644"/>
+      <c r="H55" s="671"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" customHeight="1">
       <c r="A56" s="98" t="s">
@@ -29343,10 +29410,10 @@
       <c r="D56" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E56" s="576"/>
-      <c r="F56" s="577"/>
+      <c r="E56" s="608"/>
+      <c r="F56" s="609"/>
       <c r="G56" s="105"/>
-      <c r="H56" s="644"/>
+      <c r="H56" s="671"/>
     </row>
     <row r="57" spans="1:8" ht="15.75" customHeight="1">
       <c r="A57" s="98" t="s">
@@ -29361,12 +29428,12 @@
       <c r="D57" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E57" s="576"/>
-      <c r="F57" s="577"/>
+      <c r="E57" s="608"/>
+      <c r="F57" s="609"/>
       <c r="G57" s="108" t="s">
         <v>238</v>
       </c>
-      <c r="H57" s="644"/>
+      <c r="H57" s="671"/>
     </row>
     <row r="58" spans="1:8" ht="15.75" customHeight="1">
       <c r="A58" s="98" t="s">
@@ -29381,12 +29448,12 @@
       <c r="D58" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E58" s="576"/>
-      <c r="F58" s="577"/>
+      <c r="E58" s="608"/>
+      <c r="F58" s="609"/>
       <c r="G58" s="108" t="s">
         <v>240</v>
       </c>
-      <c r="H58" s="644"/>
+      <c r="H58" s="671"/>
     </row>
     <row r="59" spans="1:8" ht="15.75" customHeight="1">
       <c r="A59" s="98" t="s">
@@ -29401,10 +29468,10 @@
       <c r="D59" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E59" s="576"/>
-      <c r="F59" s="577"/>
+      <c r="E59" s="608"/>
+      <c r="F59" s="609"/>
       <c r="G59" s="105"/>
-      <c r="H59" s="644"/>
+      <c r="H59" s="671"/>
     </row>
     <row r="60" spans="1:8" ht="15.75" customHeight="1">
       <c r="A60" s="98" t="s">
@@ -29419,12 +29486,12 @@
       <c r="D60" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E60" s="576"/>
-      <c r="F60" s="577"/>
+      <c r="E60" s="608"/>
+      <c r="F60" s="609"/>
       <c r="G60" s="107" t="s">
         <v>243</v>
       </c>
-      <c r="H60" s="644"/>
+      <c r="H60" s="671"/>
     </row>
     <row r="61" spans="1:8" ht="15.75" customHeight="1">
       <c r="A61" s="98" t="s">
@@ -29439,10 +29506,10 @@
       <c r="D61" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E61" s="576"/>
-      <c r="F61" s="577"/>
+      <c r="E61" s="608"/>
+      <c r="F61" s="609"/>
       <c r="G61" s="105"/>
-      <c r="H61" s="644"/>
+      <c r="H61" s="671"/>
     </row>
     <row r="62" spans="1:8" ht="15.75" customHeight="1">
       <c r="A62" s="98" t="s">
@@ -29457,10 +29524,10 @@
       <c r="D62" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E62" s="576"/>
-      <c r="F62" s="577"/>
+      <c r="E62" s="608"/>
+      <c r="F62" s="609"/>
       <c r="G62" s="105"/>
-      <c r="H62" s="644"/>
+      <c r="H62" s="671"/>
     </row>
     <row r="63" spans="1:8" ht="15.75" customHeight="1">
       <c r="A63" s="98" t="s">
@@ -29475,10 +29542,10 @@
       <c r="D63" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E63" s="576"/>
-      <c r="F63" s="577"/>
+      <c r="E63" s="608"/>
+      <c r="F63" s="609"/>
       <c r="G63" s="105"/>
-      <c r="H63" s="644"/>
+      <c r="H63" s="671"/>
     </row>
     <row r="64" spans="1:8" ht="15.75" customHeight="1">
       <c r="A64" s="98" t="s">
@@ -29493,12 +29560,12 @@
       <c r="D64" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E64" s="576"/>
-      <c r="F64" s="577"/>
+      <c r="E64" s="608"/>
+      <c r="F64" s="609"/>
       <c r="G64" s="108" t="s">
         <v>248</v>
       </c>
-      <c r="H64" s="644"/>
+      <c r="H64" s="671"/>
     </row>
     <row r="65" spans="1:8" ht="15.75" customHeight="1">
       <c r="A65" s="98" t="s">
@@ -29513,10 +29580,10 @@
       <c r="D65" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E65" s="576"/>
-      <c r="F65" s="577"/>
+      <c r="E65" s="608"/>
+      <c r="F65" s="609"/>
       <c r="G65" s="105"/>
-      <c r="H65" s="644"/>
+      <c r="H65" s="671"/>
     </row>
     <row r="66" spans="1:8" ht="15.75" customHeight="1">
       <c r="A66" s="98" t="s">
@@ -29531,12 +29598,12 @@
       <c r="D66" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E66" s="576"/>
-      <c r="F66" s="577"/>
+      <c r="E66" s="608"/>
+      <c r="F66" s="609"/>
       <c r="G66" s="108" t="s">
         <v>251</v>
       </c>
-      <c r="H66" s="644"/>
+      <c r="H66" s="671"/>
     </row>
     <row r="67" spans="1:8" ht="15.75" customHeight="1">
       <c r="A67" s="98" t="s">
@@ -29551,12 +29618,12 @@
       <c r="D67" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E67" s="576"/>
-      <c r="F67" s="577"/>
+      <c r="E67" s="608"/>
+      <c r="F67" s="609"/>
       <c r="G67" s="108" t="s">
         <v>253</v>
       </c>
-      <c r="H67" s="644"/>
+      <c r="H67" s="671"/>
     </row>
     <row r="68" spans="1:8" ht="15.75" customHeight="1">
       <c r="A68" s="98" t="s">
@@ -29571,10 +29638,10 @@
       <c r="D68" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E68" s="576"/>
-      <c r="F68" s="577"/>
+      <c r="E68" s="608"/>
+      <c r="F68" s="609"/>
       <c r="G68" s="105"/>
-      <c r="H68" s="644"/>
+      <c r="H68" s="671"/>
     </row>
     <row r="69" spans="1:8" ht="15.75" customHeight="1">
       <c r="A69" s="98" t="s">
@@ -29589,12 +29656,12 @@
       <c r="D69" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E69" s="576"/>
-      <c r="F69" s="577"/>
+      <c r="E69" s="608"/>
+      <c r="F69" s="609"/>
       <c r="G69" s="108" t="s">
         <v>256</v>
       </c>
-      <c r="H69" s="644"/>
+      <c r="H69" s="671"/>
     </row>
     <row r="70" spans="1:8" ht="15.75" customHeight="1">
       <c r="A70" s="98" t="s">
@@ -29609,10 +29676,10 @@
       <c r="D70" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E70" s="576"/>
-      <c r="F70" s="577"/>
+      <c r="E70" s="608"/>
+      <c r="F70" s="609"/>
       <c r="G70" s="105"/>
-      <c r="H70" s="644"/>
+      <c r="H70" s="671"/>
     </row>
     <row r="71" spans="1:8" ht="15.75" customHeight="1">
       <c r="A71" s="98" t="s">
@@ -29627,10 +29694,10 @@
       <c r="D71" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E71" s="576"/>
-      <c r="F71" s="577"/>
+      <c r="E71" s="608"/>
+      <c r="F71" s="609"/>
       <c r="G71" s="105"/>
-      <c r="H71" s="644"/>
+      <c r="H71" s="671"/>
     </row>
     <row r="72" spans="1:8" ht="15.75" customHeight="1">
       <c r="A72" s="98" t="s">
@@ -29645,12 +29712,12 @@
       <c r="D72" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E72" s="576"/>
-      <c r="F72" s="577"/>
+      <c r="E72" s="608"/>
+      <c r="F72" s="609"/>
       <c r="G72" s="108" t="s">
         <v>260</v>
       </c>
-      <c r="H72" s="644"/>
+      <c r="H72" s="671"/>
     </row>
     <row r="73" spans="1:8" ht="15.75" customHeight="1">
       <c r="A73" s="98" t="s">
@@ -29665,10 +29732,10 @@
       <c r="D73" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E73" s="576"/>
-      <c r="F73" s="577"/>
+      <c r="E73" s="608"/>
+      <c r="F73" s="609"/>
       <c r="G73" s="112"/>
-      <c r="H73" s="644"/>
+      <c r="H73" s="671"/>
     </row>
     <row r="74" spans="1:8" ht="15.75" customHeight="1">
       <c r="A74" s="98" t="s">
@@ -29683,12 +29750,12 @@
       <c r="D74" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E74" s="576"/>
-      <c r="F74" s="577"/>
+      <c r="E74" s="608"/>
+      <c r="F74" s="609"/>
       <c r="G74" s="108" t="s">
         <v>263</v>
       </c>
-      <c r="H74" s="644"/>
+      <c r="H74" s="671"/>
     </row>
     <row r="75" spans="1:8" ht="15.75" customHeight="1">
       <c r="A75" s="98" t="s">
@@ -29703,12 +29770,12 @@
       <c r="D75" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E75" s="576"/>
-      <c r="F75" s="577"/>
+      <c r="E75" s="608"/>
+      <c r="F75" s="609"/>
       <c r="G75" s="108" t="s">
         <v>265</v>
       </c>
-      <c r="H75" s="644"/>
+      <c r="H75" s="671"/>
     </row>
     <row r="76" spans="1:8" ht="15.75" customHeight="1">
       <c r="A76" s="98" t="s">
@@ -29723,12 +29790,12 @@
       <c r="D76" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E76" s="576"/>
-      <c r="F76" s="577"/>
+      <c r="E76" s="608"/>
+      <c r="F76" s="609"/>
       <c r="G76" s="108" t="s">
         <v>268</v>
       </c>
-      <c r="H76" s="644"/>
+      <c r="H76" s="671"/>
     </row>
     <row r="77" spans="1:8" ht="15.75" customHeight="1">
       <c r="A77" s="98" t="s">
@@ -29743,12 +29810,12 @@
       <c r="D77" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E77" s="576"/>
-      <c r="F77" s="577"/>
+      <c r="E77" s="608"/>
+      <c r="F77" s="609"/>
       <c r="G77" s="107" t="s">
         <v>270</v>
       </c>
-      <c r="H77" s="644"/>
+      <c r="H77" s="671"/>
     </row>
     <row r="78" spans="1:8" ht="15.75" customHeight="1">
       <c r="A78" s="98" t="s">
@@ -29763,12 +29830,12 @@
       <c r="D78" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E78" s="576"/>
-      <c r="F78" s="577"/>
+      <c r="E78" s="608"/>
+      <c r="F78" s="609"/>
       <c r="G78" s="107" t="s">
         <v>272</v>
       </c>
-      <c r="H78" s="644"/>
+      <c r="H78" s="671"/>
     </row>
     <row r="79" spans="1:8" ht="15.75" customHeight="1">
       <c r="A79" s="98" t="s">
@@ -29783,12 +29850,12 @@
       <c r="D79" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E79" s="576"/>
-      <c r="F79" s="577"/>
+      <c r="E79" s="608"/>
+      <c r="F79" s="609"/>
       <c r="G79" s="105" t="s">
         <v>274</v>
       </c>
-      <c r="H79" s="644"/>
+      <c r="H79" s="671"/>
     </row>
     <row r="80" spans="1:8" ht="15.75" customHeight="1">
       <c r="A80" s="98" t="s">
@@ -29803,10 +29870,10 @@
       <c r="D80" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E80" s="576"/>
-      <c r="F80" s="577"/>
+      <c r="E80" s="608"/>
+      <c r="F80" s="609"/>
       <c r="G80" s="105"/>
-      <c r="H80" s="644"/>
+      <c r="H80" s="671"/>
     </row>
     <row r="81" spans="1:8" ht="15.75" customHeight="1">
       <c r="A81" s="98" t="s">
@@ -29818,15 +29885,15 @@
       <c r="C81" s="106" t="s">
         <v>277</v>
       </c>
-      <c r="D81" s="628" t="s">
+      <c r="D81" s="632" t="s">
         <v>169</v>
       </c>
-      <c r="E81" s="576"/>
-      <c r="F81" s="577"/>
+      <c r="E81" s="633"/>
+      <c r="F81" s="634"/>
       <c r="G81" s="107" t="s">
         <v>278</v>
       </c>
-      <c r="H81" s="644"/>
+      <c r="H81" s="671"/>
     </row>
     <row r="82" spans="1:8" ht="15.75" customHeight="1">
       <c r="A82" s="98" t="s">
@@ -29838,13 +29905,13 @@
       <c r="C82" s="106" t="s">
         <v>279</v>
       </c>
-      <c r="D82" s="628" t="s">
+      <c r="D82" s="632" t="s">
         <v>171</v>
       </c>
-      <c r="E82" s="576"/>
-      <c r="F82" s="577"/>
+      <c r="E82" s="633"/>
+      <c r="F82" s="634"/>
       <c r="G82" s="113"/>
-      <c r="H82" s="644"/>
+      <c r="H82" s="671"/>
     </row>
     <row r="83" spans="1:8" ht="15.75" customHeight="1">
       <c r="A83" s="98" t="s">
@@ -29859,12 +29926,12 @@
       <c r="D83" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E83" s="576"/>
-      <c r="F83" s="577"/>
+      <c r="E83" s="608"/>
+      <c r="F83" s="609"/>
       <c r="G83" s="108" t="s">
         <v>281</v>
       </c>
-      <c r="H83" s="644"/>
+      <c r="H83" s="671"/>
     </row>
     <row r="84" spans="1:8" ht="15.75" customHeight="1">
       <c r="A84" s="98" t="s">
@@ -29879,12 +29946,12 @@
       <c r="D84" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E84" s="576"/>
-      <c r="F84" s="577"/>
+      <c r="E84" s="608"/>
+      <c r="F84" s="609"/>
       <c r="G84" s="107" t="s">
         <v>283</v>
       </c>
-      <c r="H84" s="644"/>
+      <c r="H84" s="671"/>
     </row>
     <row r="85" spans="1:8" ht="15.75" customHeight="1">
       <c r="A85" s="98" t="s">
@@ -29899,12 +29966,12 @@
       <c r="D85" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E85" s="576"/>
-      <c r="F85" s="577"/>
+      <c r="E85" s="608"/>
+      <c r="F85" s="609"/>
       <c r="G85" s="107" t="s">
         <v>285</v>
       </c>
-      <c r="H85" s="644"/>
+      <c r="H85" s="671"/>
     </row>
     <row r="86" spans="1:8" ht="15.75" customHeight="1">
       <c r="A86" s="98" t="s">
@@ -29919,10 +29986,10 @@
       <c r="D86" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E86" s="576"/>
-      <c r="F86" s="577"/>
+      <c r="E86" s="608"/>
+      <c r="F86" s="609"/>
       <c r="G86" s="105"/>
-      <c r="H86" s="644"/>
+      <c r="H86" s="671"/>
     </row>
     <row r="87" spans="1:8" ht="15.75" customHeight="1">
       <c r="A87" s="98" t="s">
@@ -29937,10 +30004,10 @@
       <c r="D87" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E87" s="576"/>
-      <c r="F87" s="577"/>
+      <c r="E87" s="608"/>
+      <c r="F87" s="609"/>
       <c r="G87" s="105"/>
-      <c r="H87" s="644"/>
+      <c r="H87" s="671"/>
     </row>
     <row r="88" spans="1:8" ht="15.75" customHeight="1">
       <c r="A88" s="98" t="s">
@@ -29955,10 +30022,10 @@
       <c r="D88" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E88" s="576"/>
-      <c r="F88" s="577"/>
+      <c r="E88" s="608"/>
+      <c r="F88" s="609"/>
       <c r="G88" s="105"/>
-      <c r="H88" s="644"/>
+      <c r="H88" s="671"/>
     </row>
     <row r="89" spans="1:8" ht="15.75" customHeight="1">
       <c r="A89" s="98" t="s">
@@ -29973,12 +30040,12 @@
       <c r="D89" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E89" s="576"/>
-      <c r="F89" s="577"/>
+      <c r="E89" s="608"/>
+      <c r="F89" s="609"/>
       <c r="G89" s="107" t="s">
         <v>290</v>
       </c>
-      <c r="H89" s="644"/>
+      <c r="H89" s="671"/>
     </row>
     <row r="90" spans="1:8" ht="15.75" customHeight="1">
       <c r="A90" s="98" t="s">
@@ -29993,12 +30060,12 @@
       <c r="D90" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E90" s="576"/>
-      <c r="F90" s="577"/>
+      <c r="E90" s="608"/>
+      <c r="F90" s="609"/>
       <c r="G90" s="107" t="s">
         <v>292</v>
       </c>
-      <c r="H90" s="644"/>
+      <c r="H90" s="671"/>
     </row>
     <row r="91" spans="1:8" ht="15.75" customHeight="1">
       <c r="A91" s="98" t="s">
@@ -30013,10 +30080,10 @@
       <c r="D91" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E91" s="576"/>
-      <c r="F91" s="577"/>
+      <c r="E91" s="608"/>
+      <c r="F91" s="609"/>
       <c r="G91" s="105"/>
-      <c r="H91" s="644"/>
+      <c r="H91" s="671"/>
     </row>
     <row r="92" spans="1:8" ht="15.75" customHeight="1">
       <c r="A92" s="98" t="s">
@@ -30031,10 +30098,10 @@
       <c r="D92" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E92" s="576"/>
-      <c r="F92" s="577"/>
+      <c r="E92" s="608"/>
+      <c r="F92" s="609"/>
       <c r="G92" s="105"/>
-      <c r="H92" s="644"/>
+      <c r="H92" s="671"/>
     </row>
     <row r="93" spans="1:8" ht="15.75" customHeight="1">
       <c r="A93" s="98" t="s">
@@ -30049,10 +30116,10 @@
       <c r="D93" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E93" s="576"/>
-      <c r="F93" s="577"/>
+      <c r="E93" s="608"/>
+      <c r="F93" s="609"/>
       <c r="G93" s="105"/>
-      <c r="H93" s="644"/>
+      <c r="H93" s="671"/>
     </row>
     <row r="94" spans="1:8" ht="15.75" customHeight="1">
       <c r="A94" s="98" t="s">
@@ -30067,10 +30134,10 @@
       <c r="D94" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E94" s="576"/>
-      <c r="F94" s="577"/>
+      <c r="E94" s="608"/>
+      <c r="F94" s="609"/>
       <c r="G94" s="105"/>
-      <c r="H94" s="644"/>
+      <c r="H94" s="671"/>
     </row>
     <row r="95" spans="1:8" ht="15.75" customHeight="1">
       <c r="A95" s="98" t="s">
@@ -30085,12 +30152,12 @@
       <c r="D95" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E95" s="576"/>
-      <c r="F95" s="577"/>
+      <c r="E95" s="608"/>
+      <c r="F95" s="609"/>
       <c r="G95" s="107" t="s">
         <v>298</v>
       </c>
-      <c r="H95" s="644"/>
+      <c r="H95" s="671"/>
     </row>
     <row r="96" spans="1:8" ht="15.75" customHeight="1">
       <c r="A96" s="98" t="s">
@@ -30105,10 +30172,10 @@
       <c r="D96" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E96" s="576"/>
-      <c r="F96" s="577"/>
+      <c r="E96" s="608"/>
+      <c r="F96" s="609"/>
       <c r="G96" s="105"/>
-      <c r="H96" s="644"/>
+      <c r="H96" s="671"/>
     </row>
     <row r="97" spans="1:8" ht="15.75" customHeight="1">
       <c r="A97" s="98" t="s">
@@ -30123,10 +30190,10 @@
       <c r="D97" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E97" s="576"/>
-      <c r="F97" s="577"/>
+      <c r="E97" s="608"/>
+      <c r="F97" s="609"/>
       <c r="G97" s="105"/>
-      <c r="H97" s="644"/>
+      <c r="H97" s="671"/>
     </row>
     <row r="98" spans="1:8" ht="15.75" customHeight="1">
       <c r="A98" s="98" t="s">
@@ -30141,12 +30208,12 @@
       <c r="D98" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E98" s="576"/>
-      <c r="F98" s="577"/>
+      <c r="E98" s="608"/>
+      <c r="F98" s="609"/>
       <c r="G98" s="107" t="s">
         <v>302</v>
       </c>
-      <c r="H98" s="644"/>
+      <c r="H98" s="671"/>
     </row>
     <row r="99" spans="1:8" ht="15.75" customHeight="1">
       <c r="A99" s="98" t="s">
@@ -30161,10 +30228,10 @@
       <c r="D99" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E99" s="576"/>
-      <c r="F99" s="577"/>
+      <c r="E99" s="608"/>
+      <c r="F99" s="609"/>
       <c r="G99" s="105"/>
-      <c r="H99" s="644"/>
+      <c r="H99" s="671"/>
     </row>
     <row r="100" spans="1:8" ht="15.75" customHeight="1">
       <c r="A100" s="98" t="s">
@@ -30179,12 +30246,12 @@
       <c r="D100" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E100" s="576"/>
-      <c r="F100" s="577"/>
+      <c r="E100" s="608"/>
+      <c r="F100" s="609"/>
       <c r="G100" s="107" t="s">
         <v>305</v>
       </c>
-      <c r="H100" s="644"/>
+      <c r="H100" s="671"/>
     </row>
     <row r="101" spans="1:8" ht="15.75" customHeight="1">
       <c r="A101" s="98" t="s">
@@ -30199,10 +30266,10 @@
       <c r="D101" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E101" s="576"/>
-      <c r="F101" s="577"/>
+      <c r="E101" s="608"/>
+      <c r="F101" s="609"/>
       <c r="G101" s="105"/>
-      <c r="H101" s="644"/>
+      <c r="H101" s="671"/>
     </row>
     <row r="102" spans="1:8" ht="15.75" customHeight="1">
       <c r="A102" s="98" t="s">
@@ -30217,10 +30284,10 @@
       <c r="D102" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E102" s="576"/>
-      <c r="F102" s="577"/>
+      <c r="E102" s="608"/>
+      <c r="F102" s="609"/>
       <c r="G102" s="105"/>
-      <c r="H102" s="644"/>
+      <c r="H102" s="671"/>
     </row>
     <row r="103" spans="1:8" ht="15.75" customHeight="1">
       <c r="A103" s="98" t="s">
@@ -30235,10 +30302,10 @@
       <c r="D103" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E103" s="576"/>
-      <c r="F103" s="577"/>
+      <c r="E103" s="608"/>
+      <c r="F103" s="609"/>
       <c r="G103" s="105"/>
-      <c r="H103" s="644"/>
+      <c r="H103" s="671"/>
     </row>
     <row r="104" spans="1:8" ht="15.75" customHeight="1">
       <c r="A104" s="98" t="s">
@@ -30253,10 +30320,10 @@
       <c r="D104" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E104" s="576"/>
-      <c r="F104" s="577"/>
+      <c r="E104" s="608"/>
+      <c r="F104" s="609"/>
       <c r="G104" s="105"/>
-      <c r="H104" s="644"/>
+      <c r="H104" s="671"/>
     </row>
     <row r="105" spans="1:8" ht="15.75" customHeight="1">
       <c r="A105" s="98" t="s">
@@ -30268,13 +30335,13 @@
       <c r="C105" s="106" t="s">
         <v>311</v>
       </c>
-      <c r="D105" s="628" t="s">
+      <c r="D105" s="632" t="s">
         <v>172</v>
       </c>
-      <c r="E105" s="576"/>
-      <c r="F105" s="577"/>
+      <c r="E105" s="633"/>
+      <c r="F105" s="634"/>
       <c r="G105" s="110"/>
-      <c r="H105" s="644"/>
+      <c r="H105" s="671"/>
     </row>
     <row r="106" spans="1:8" ht="15.75" customHeight="1">
       <c r="A106" s="98" t="s">
@@ -30289,10 +30356,10 @@
       <c r="D106" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E106" s="576"/>
-      <c r="F106" s="577"/>
+      <c r="E106" s="608"/>
+      <c r="F106" s="609"/>
       <c r="G106" s="114"/>
-      <c r="H106" s="644"/>
+      <c r="H106" s="671"/>
     </row>
     <row r="107" spans="1:8" ht="15.75" customHeight="1">
       <c r="A107" s="98" t="s">
@@ -30307,12 +30374,12 @@
       <c r="D107" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E107" s="576"/>
-      <c r="F107" s="577"/>
+      <c r="E107" s="608"/>
+      <c r="F107" s="609"/>
       <c r="G107" s="115" t="s">
         <v>316</v>
       </c>
-      <c r="H107" s="644"/>
+      <c r="H107" s="671"/>
     </row>
     <row r="108" spans="1:8" ht="15.75" customHeight="1">
       <c r="A108" s="98" t="s">
@@ -30327,12 +30394,12 @@
       <c r="D108" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E108" s="576"/>
-      <c r="F108" s="577"/>
+      <c r="E108" s="608"/>
+      <c r="F108" s="609"/>
       <c r="G108" s="108" t="s">
         <v>318</v>
       </c>
-      <c r="H108" s="644"/>
+      <c r="H108" s="671"/>
     </row>
     <row r="109" spans="1:8" ht="15.75" customHeight="1">
       <c r="A109" s="98" t="s">
@@ -30347,10 +30414,10 @@
       <c r="D109" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E109" s="576"/>
-      <c r="F109" s="577"/>
+      <c r="E109" s="608"/>
+      <c r="F109" s="609"/>
       <c r="G109" s="105"/>
-      <c r="H109" s="644"/>
+      <c r="H109" s="671"/>
     </row>
     <row r="110" spans="1:8" ht="15.75" customHeight="1">
       <c r="A110" s="98" t="s">
@@ -30365,10 +30432,10 @@
       <c r="D110" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E110" s="576"/>
-      <c r="F110" s="577"/>
+      <c r="E110" s="608"/>
+      <c r="F110" s="609"/>
       <c r="G110" s="105"/>
-      <c r="H110" s="644"/>
+      <c r="H110" s="671"/>
     </row>
     <row r="111" spans="1:8" ht="15.75" customHeight="1">
       <c r="A111" s="98" t="s">
@@ -30383,10 +30450,10 @@
       <c r="D111" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E111" s="576"/>
-      <c r="F111" s="577"/>
+      <c r="E111" s="608"/>
+      <c r="F111" s="609"/>
       <c r="G111" s="114"/>
-      <c r="H111" s="644"/>
+      <c r="H111" s="671"/>
     </row>
     <row r="112" spans="1:8" ht="15.75" customHeight="1">
       <c r="A112" s="98" t="s">
@@ -30401,12 +30468,12 @@
       <c r="D112" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E112" s="576"/>
-      <c r="F112" s="577"/>
+      <c r="E112" s="608"/>
+      <c r="F112" s="609"/>
       <c r="G112" s="105" t="s">
         <v>327</v>
       </c>
-      <c r="H112" s="644"/>
+      <c r="H112" s="671"/>
     </row>
     <row r="113" spans="1:8" ht="15.75" customHeight="1">
       <c r="A113" s="98" t="s">
@@ -30421,12 +30488,12 @@
       <c r="D113" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E113" s="576"/>
-      <c r="F113" s="577"/>
+      <c r="E113" s="608"/>
+      <c r="F113" s="609"/>
       <c r="G113" s="116" t="s">
         <v>330</v>
       </c>
-      <c r="H113" s="644"/>
+      <c r="H113" s="671"/>
     </row>
     <row r="114" spans="1:8" ht="15.75" customHeight="1">
       <c r="A114" s="98" t="s">
@@ -30441,12 +30508,12 @@
       <c r="D114" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E114" s="576"/>
-      <c r="F114" s="577"/>
+      <c r="E114" s="608"/>
+      <c r="F114" s="609"/>
       <c r="G114" s="116" t="s">
         <v>332</v>
       </c>
-      <c r="H114" s="644"/>
+      <c r="H114" s="671"/>
     </row>
     <row r="115" spans="1:8" ht="15.75" customHeight="1">
       <c r="A115" s="98" t="s">
@@ -30461,12 +30528,12 @@
       <c r="D115" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E115" s="576"/>
-      <c r="F115" s="577"/>
+      <c r="E115" s="608"/>
+      <c r="F115" s="609"/>
       <c r="G115" s="117" t="s">
         <v>334</v>
       </c>
-      <c r="H115" s="644"/>
+      <c r="H115" s="671"/>
     </row>
     <row r="116" spans="1:8" ht="15.75" customHeight="1">
       <c r="A116" s="98" t="s">
@@ -30481,12 +30548,12 @@
       <c r="D116" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E116" s="576"/>
-      <c r="F116" s="577"/>
+      <c r="E116" s="608"/>
+      <c r="F116" s="609"/>
       <c r="G116" s="116" t="s">
         <v>336</v>
       </c>
-      <c r="H116" s="644"/>
+      <c r="H116" s="671"/>
     </row>
     <row r="117" spans="1:8" ht="15.75" customHeight="1">
       <c r="A117" s="98" t="s">
@@ -30501,10 +30568,10 @@
       <c r="D117" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E117" s="576"/>
-      <c r="F117" s="577"/>
+      <c r="E117" s="608"/>
+      <c r="F117" s="609"/>
       <c r="G117" s="118"/>
-      <c r="H117" s="644"/>
+      <c r="H117" s="671"/>
     </row>
     <row r="118" spans="1:8" ht="15.75" customHeight="1">
       <c r="A118" s="98" t="s">
@@ -30519,12 +30586,12 @@
       <c r="D118" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E118" s="576"/>
-      <c r="F118" s="577"/>
+      <c r="E118" s="608"/>
+      <c r="F118" s="609"/>
       <c r="G118" s="116" t="s">
         <v>339</v>
       </c>
-      <c r="H118" s="644"/>
+      <c r="H118" s="671"/>
     </row>
     <row r="119" spans="1:8" ht="15.75" customHeight="1">
       <c r="A119" s="98" t="s">
@@ -30539,12 +30606,12 @@
       <c r="D119" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E119" s="576"/>
-      <c r="F119" s="577"/>
+      <c r="E119" s="608"/>
+      <c r="F119" s="609"/>
       <c r="G119" s="116" t="s">
         <v>341</v>
       </c>
-      <c r="H119" s="644"/>
+      <c r="H119" s="671"/>
     </row>
     <row r="120" spans="1:8" ht="15.75" customHeight="1">
       <c r="A120" s="98" t="s">
@@ -30559,12 +30626,12 @@
       <c r="D120" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E120" s="576"/>
-      <c r="F120" s="577"/>
+      <c r="E120" s="608"/>
+      <c r="F120" s="609"/>
       <c r="G120" s="116" t="s">
         <v>343</v>
       </c>
-      <c r="H120" s="644"/>
+      <c r="H120" s="671"/>
     </row>
     <row r="121" spans="1:8" ht="15.75" customHeight="1">
       <c r="A121" s="98" t="s">
@@ -30579,12 +30646,12 @@
       <c r="D121" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E121" s="576"/>
-      <c r="F121" s="577"/>
+      <c r="E121" s="608"/>
+      <c r="F121" s="609"/>
       <c r="G121" s="116" t="s">
         <v>345</v>
       </c>
-      <c r="H121" s="644"/>
+      <c r="H121" s="671"/>
     </row>
     <row r="122" spans="1:8" ht="15.75" customHeight="1">
       <c r="A122" s="98" t="s">
@@ -30599,12 +30666,12 @@
       <c r="D122" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E122" s="576"/>
-      <c r="F122" s="577"/>
+      <c r="E122" s="608"/>
+      <c r="F122" s="609"/>
       <c r="G122" s="116" t="s">
         <v>347</v>
       </c>
-      <c r="H122" s="644"/>
+      <c r="H122" s="671"/>
     </row>
     <row r="123" spans="1:8" ht="15.75" customHeight="1">
       <c r="A123" s="98" t="s">
@@ -30619,12 +30686,12 @@
       <c r="D123" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E123" s="576"/>
-      <c r="F123" s="577"/>
+      <c r="E123" s="608"/>
+      <c r="F123" s="609"/>
       <c r="G123" s="116" t="s">
         <v>349</v>
       </c>
-      <c r="H123" s="644"/>
+      <c r="H123" s="671"/>
     </row>
     <row r="124" spans="1:8" ht="15.75" customHeight="1">
       <c r="A124" s="98" t="s">
@@ -30639,12 +30706,12 @@
       <c r="D124" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E124" s="576"/>
-      <c r="F124" s="577"/>
+      <c r="E124" s="608"/>
+      <c r="F124" s="609"/>
       <c r="G124" s="105" t="s">
         <v>351</v>
       </c>
-      <c r="H124" s="644"/>
+      <c r="H124" s="671"/>
     </row>
     <row r="125" spans="1:8" ht="15.75" customHeight="1">
       <c r="A125" s="98" t="s">
@@ -30659,10 +30726,10 @@
       <c r="D125" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E125" s="576"/>
-      <c r="F125" s="577"/>
+      <c r="E125" s="608"/>
+      <c r="F125" s="609"/>
       <c r="G125" s="105"/>
-      <c r="H125" s="644"/>
+      <c r="H125" s="671"/>
     </row>
     <row r="126" spans="1:8" ht="15.75" customHeight="1">
       <c r="A126" s="98" t="s">
@@ -30677,10 +30744,10 @@
       <c r="D126" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E126" s="576"/>
-      <c r="F126" s="577"/>
+      <c r="E126" s="608"/>
+      <c r="F126" s="609"/>
       <c r="G126" s="105"/>
-      <c r="H126" s="644"/>
+      <c r="H126" s="671"/>
     </row>
     <row r="127" spans="1:8" ht="15.75" customHeight="1">
       <c r="A127" s="98" t="s">
@@ -30695,12 +30762,12 @@
       <c r="D127" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E127" s="576"/>
-      <c r="F127" s="577"/>
+      <c r="E127" s="608"/>
+      <c r="F127" s="609"/>
       <c r="G127" s="116" t="s">
         <v>355</v>
       </c>
-      <c r="H127" s="644"/>
+      <c r="H127" s="671"/>
     </row>
     <row r="128" spans="1:8" ht="15.75" customHeight="1">
       <c r="A128" s="98" t="s">
@@ -30715,12 +30782,12 @@
       <c r="D128" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E128" s="576"/>
-      <c r="F128" s="577"/>
+      <c r="E128" s="608"/>
+      <c r="F128" s="609"/>
       <c r="G128" s="116" t="s">
         <v>357</v>
       </c>
-      <c r="H128" s="644"/>
+      <c r="H128" s="671"/>
     </row>
     <row r="129" spans="1:8" ht="15.75" customHeight="1">
       <c r="A129" s="98" t="s">
@@ -30735,12 +30802,12 @@
       <c r="D129" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E129" s="576"/>
-      <c r="F129" s="577"/>
+      <c r="E129" s="608"/>
+      <c r="F129" s="609"/>
       <c r="G129" s="116" t="s">
         <v>359</v>
       </c>
-      <c r="H129" s="644"/>
+      <c r="H129" s="671"/>
     </row>
     <row r="130" spans="1:8" ht="15.75" customHeight="1">
       <c r="A130" s="98" t="s">
@@ -30755,12 +30822,12 @@
       <c r="D130" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E130" s="576"/>
-      <c r="F130" s="577"/>
+      <c r="E130" s="608"/>
+      <c r="F130" s="609"/>
       <c r="G130" s="116" t="s">
         <v>349</v>
       </c>
-      <c r="H130" s="644"/>
+      <c r="H130" s="671"/>
     </row>
     <row r="131" spans="1:8" ht="15.75" customHeight="1">
       <c r="A131" s="98" t="s">
@@ -30775,12 +30842,12 @@
       <c r="D131" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E131" s="576"/>
-      <c r="F131" s="577"/>
+      <c r="E131" s="608"/>
+      <c r="F131" s="609"/>
       <c r="G131" s="116" t="s">
         <v>362</v>
       </c>
-      <c r="H131" s="644"/>
+      <c r="H131" s="671"/>
     </row>
     <row r="132" spans="1:8" ht="15.75" customHeight="1">
       <c r="A132" s="98" t="s">
@@ -30795,10 +30862,10 @@
       <c r="D132" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E132" s="576"/>
-      <c r="F132" s="577"/>
+      <c r="E132" s="608"/>
+      <c r="F132" s="609"/>
       <c r="G132" s="105"/>
-      <c r="H132" s="644"/>
+      <c r="H132" s="671"/>
     </row>
     <row r="133" spans="1:8" ht="15.75" customHeight="1">
       <c r="A133" s="98" t="s">
@@ -30813,12 +30880,12 @@
       <c r="D133" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E133" s="576"/>
-      <c r="F133" s="577"/>
+      <c r="E133" s="608"/>
+      <c r="F133" s="609"/>
       <c r="G133" s="116" t="s">
         <v>365</v>
       </c>
-      <c r="H133" s="644"/>
+      <c r="H133" s="671"/>
     </row>
     <row r="134" spans="1:8" ht="15.75" customHeight="1">
       <c r="A134" s="98" t="s">
@@ -30833,12 +30900,12 @@
       <c r="D134" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E134" s="576"/>
-      <c r="F134" s="577"/>
+      <c r="E134" s="608"/>
+      <c r="F134" s="609"/>
       <c r="G134" s="116" t="s">
         <v>367</v>
       </c>
-      <c r="H134" s="644"/>
+      <c r="H134" s="671"/>
     </row>
     <row r="135" spans="1:8" ht="15.75" customHeight="1">
       <c r="A135" s="98" t="s">
@@ -30853,12 +30920,12 @@
       <c r="D135" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E135" s="576"/>
-      <c r="F135" s="577"/>
+      <c r="E135" s="608"/>
+      <c r="F135" s="609"/>
       <c r="G135" s="116" t="s">
         <v>369</v>
       </c>
-      <c r="H135" s="644"/>
+      <c r="H135" s="671"/>
     </row>
     <row r="136" spans="1:8" ht="15.75" customHeight="1">
       <c r="A136" s="98" t="s">
@@ -30873,12 +30940,12 @@
       <c r="D136" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E136" s="576"/>
-      <c r="F136" s="577"/>
+      <c r="E136" s="608"/>
+      <c r="F136" s="609"/>
       <c r="G136" s="116" t="s">
         <v>371</v>
       </c>
-      <c r="H136" s="644"/>
+      <c r="H136" s="671"/>
     </row>
     <row r="137" spans="1:8" ht="15.75" customHeight="1">
       <c r="A137" s="98" t="s">
@@ -30893,12 +30960,12 @@
       <c r="D137" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E137" s="576"/>
-      <c r="F137" s="577"/>
+      <c r="E137" s="608"/>
+      <c r="F137" s="609"/>
       <c r="G137" s="116" t="s">
         <v>373</v>
       </c>
-      <c r="H137" s="644"/>
+      <c r="H137" s="671"/>
     </row>
     <row r="138" spans="1:8" ht="15.75" customHeight="1">
       <c r="A138" s="98" t="s">
@@ -30913,10 +30980,10 @@
       <c r="D138" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E138" s="576"/>
-      <c r="F138" s="577"/>
+      <c r="E138" s="608"/>
+      <c r="F138" s="609"/>
       <c r="G138" s="105"/>
-      <c r="H138" s="644"/>
+      <c r="H138" s="671"/>
     </row>
     <row r="139" spans="1:8" ht="15.75" customHeight="1">
       <c r="A139" s="98" t="s">
@@ -30931,12 +30998,12 @@
       <c r="D139" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E139" s="576"/>
-      <c r="F139" s="577"/>
+      <c r="E139" s="608"/>
+      <c r="F139" s="609"/>
       <c r="G139" s="116" t="s">
         <v>376</v>
       </c>
-      <c r="H139" s="644"/>
+      <c r="H139" s="671"/>
     </row>
     <row r="140" spans="1:8" ht="15.75" customHeight="1">
       <c r="A140" s="98" t="s">
@@ -30951,12 +31018,12 @@
       <c r="D140" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E140" s="576"/>
-      <c r="F140" s="577"/>
+      <c r="E140" s="608"/>
+      <c r="F140" s="609"/>
       <c r="G140" s="116" t="s">
         <v>378</v>
       </c>
-      <c r="H140" s="644"/>
+      <c r="H140" s="671"/>
     </row>
     <row r="141" spans="1:8" ht="25.5" customHeight="1">
       <c r="A141" s="98" t="s">
@@ -30971,12 +31038,12 @@
       <c r="D141" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E141" s="576"/>
-      <c r="F141" s="577"/>
+      <c r="E141" s="608"/>
+      <c r="F141" s="609"/>
       <c r="G141" s="116" t="s">
         <v>381</v>
       </c>
-      <c r="H141" s="644"/>
+      <c r="H141" s="671"/>
     </row>
     <row r="142" spans="1:8" ht="25.5" customHeight="1">
       <c r="A142" s="98" t="s">
@@ -30991,12 +31058,12 @@
       <c r="D142" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E142" s="576"/>
-      <c r="F142" s="577"/>
+      <c r="E142" s="608"/>
+      <c r="F142" s="609"/>
       <c r="G142" s="105" t="s">
         <v>216</v>
       </c>
-      <c r="H142" s="644"/>
+      <c r="H142" s="671"/>
     </row>
     <row r="143" spans="1:8" ht="15.75" customHeight="1">
       <c r="A143" s="98" t="s">
@@ -31011,12 +31078,12 @@
       <c r="D143" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E143" s="576"/>
-      <c r="F143" s="577"/>
+      <c r="E143" s="608"/>
+      <c r="F143" s="609"/>
       <c r="G143" s="116" t="s">
         <v>385</v>
       </c>
-      <c r="H143" s="644"/>
+      <c r="H143" s="671"/>
     </row>
     <row r="144" spans="1:8" ht="15.75" customHeight="1">
       <c r="A144" s="98" t="s">
@@ -31031,12 +31098,12 @@
       <c r="D144" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E144" s="576"/>
-      <c r="F144" s="577"/>
+      <c r="E144" s="608"/>
+      <c r="F144" s="609"/>
       <c r="G144" s="116" t="s">
         <v>387</v>
       </c>
-      <c r="H144" s="644"/>
+      <c r="H144" s="671"/>
     </row>
     <row r="145" spans="1:8" ht="15.75" customHeight="1">
       <c r="A145" s="98" t="s">
@@ -31051,12 +31118,12 @@
       <c r="D145" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E145" s="576"/>
-      <c r="F145" s="577"/>
+      <c r="E145" s="608"/>
+      <c r="F145" s="609"/>
       <c r="G145" s="116" t="s">
         <v>390</v>
       </c>
-      <c r="H145" s="644"/>
+      <c r="H145" s="671"/>
     </row>
     <row r="146" spans="1:8" ht="15.75" customHeight="1">
       <c r="A146" s="98" t="s">
@@ -31071,12 +31138,12 @@
       <c r="D146" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E146" s="576"/>
-      <c r="F146" s="577"/>
+      <c r="E146" s="608"/>
+      <c r="F146" s="609"/>
       <c r="G146" s="116" t="s">
         <v>219</v>
       </c>
-      <c r="H146" s="644"/>
+      <c r="H146" s="671"/>
     </row>
     <row r="147" spans="1:8" ht="15.75" customHeight="1">
       <c r="A147" s="98" t="s">
@@ -31091,10 +31158,10 @@
       <c r="D147" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E147" s="576"/>
-      <c r="F147" s="577"/>
+      <c r="E147" s="608"/>
+      <c r="F147" s="609"/>
       <c r="G147" s="113"/>
-      <c r="H147" s="644"/>
+      <c r="H147" s="671"/>
     </row>
     <row r="148" spans="1:8" ht="15.75" customHeight="1">
       <c r="A148" s="98" t="s">
@@ -31109,10 +31176,10 @@
       <c r="D148" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E148" s="576"/>
-      <c r="F148" s="577"/>
+      <c r="E148" s="608"/>
+      <c r="F148" s="609"/>
       <c r="G148" s="105"/>
-      <c r="H148" s="644"/>
+      <c r="H148" s="671"/>
     </row>
     <row r="149" spans="1:8" ht="15.75" customHeight="1">
       <c r="A149" s="98" t="s">
@@ -31127,10 +31194,10 @@
       <c r="D149" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E149" s="576"/>
-      <c r="F149" s="577"/>
+      <c r="E149" s="608"/>
+      <c r="F149" s="609"/>
       <c r="G149" s="105"/>
-      <c r="H149" s="644"/>
+      <c r="H149" s="671"/>
     </row>
     <row r="150" spans="1:8" ht="15.75" customHeight="1">
       <c r="A150" s="98" t="s">
@@ -31145,10 +31212,10 @@
       <c r="D150" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E150" s="576"/>
-      <c r="F150" s="577"/>
+      <c r="E150" s="608"/>
+      <c r="F150" s="609"/>
       <c r="G150" s="105"/>
-      <c r="H150" s="644"/>
+      <c r="H150" s="671"/>
     </row>
     <row r="151" spans="1:8" ht="15.75" customHeight="1">
       <c r="A151" s="98" t="s">
@@ -31163,10 +31230,10 @@
       <c r="D151" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E151" s="576"/>
-      <c r="F151" s="577"/>
+      <c r="E151" s="608"/>
+      <c r="F151" s="609"/>
       <c r="G151" s="105"/>
-      <c r="H151" s="644"/>
+      <c r="H151" s="671"/>
     </row>
     <row r="152" spans="1:8" ht="15.75" customHeight="1">
       <c r="A152" s="98" t="s">
@@ -31181,12 +31248,12 @@
       <c r="D152" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E152" s="576"/>
-      <c r="F152" s="577"/>
+      <c r="E152" s="608"/>
+      <c r="F152" s="609"/>
       <c r="G152" s="116" t="s">
         <v>399</v>
       </c>
-      <c r="H152" s="644"/>
+      <c r="H152" s="671"/>
     </row>
     <row r="153" spans="1:8" ht="15.75" customHeight="1">
       <c r="A153" s="98" t="s">
@@ -31201,10 +31268,10 @@
       <c r="D153" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E153" s="576"/>
-      <c r="F153" s="577"/>
+      <c r="E153" s="608"/>
+      <c r="F153" s="609"/>
       <c r="G153" s="105"/>
-      <c r="H153" s="644"/>
+      <c r="H153" s="671"/>
     </row>
     <row r="154" spans="1:8" ht="15.75" customHeight="1">
       <c r="A154" s="98" t="s">
@@ -31219,12 +31286,12 @@
       <c r="D154" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E154" s="576"/>
-      <c r="F154" s="577"/>
+      <c r="E154" s="608"/>
+      <c r="F154" s="609"/>
       <c r="G154" s="116" t="s">
         <v>402</v>
       </c>
-      <c r="H154" s="644"/>
+      <c r="H154" s="671"/>
     </row>
     <row r="155" spans="1:8" ht="15.75" customHeight="1">
       <c r="A155" s="98" t="s">
@@ -31239,12 +31306,12 @@
       <c r="D155" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E155" s="576"/>
-      <c r="F155" s="577"/>
+      <c r="E155" s="608"/>
+      <c r="F155" s="609"/>
       <c r="G155" s="116" t="s">
         <v>404</v>
       </c>
-      <c r="H155" s="644"/>
+      <c r="H155" s="671"/>
     </row>
     <row r="156" spans="1:8" ht="15.75" customHeight="1">
       <c r="A156" s="98" t="s">
@@ -31259,17 +31326,17 @@
       <c r="D156" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E156" s="576"/>
-      <c r="F156" s="577"/>
+      <c r="E156" s="608"/>
+      <c r="F156" s="609"/>
       <c r="G156" s="119"/>
-      <c r="H156" s="644"/>
+      <c r="H156" s="671"/>
     </row>
     <row r="157" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A157" s="608" t="s">
+      <c r="A157" s="610" t="s">
         <v>406</v>
       </c>
-      <c r="B157" s="593"/>
-      <c r="C157" s="618">
+      <c r="B157" s="611"/>
+      <c r="C157" s="622">
         <f>COUNTIFS($A24:$A156,"*",$C24:$C156,"*",$D24:$D156,"*")</f>
         <v>133</v>
       </c>
@@ -31283,12 +31350,12 @@
         <v>178</v>
       </c>
       <c r="G157" s="122"/>
-      <c r="H157" s="644"/>
+      <c r="H157" s="671"/>
     </row>
     <row r="158" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A158" s="616"/>
-      <c r="B158" s="617"/>
-      <c r="C158" s="619"/>
+      <c r="A158" s="620"/>
+      <c r="B158" s="621"/>
+      <c r="C158" s="623"/>
       <c r="D158" s="123">
         <f>COUNTIFS($A24:$A156,"*",$C24:$C156,"*",$D24:$D156, "Employed")</f>
         <v>75</v>
@@ -31302,19 +31369,19 @@
         <v>35</v>
       </c>
       <c r="G158" s="124"/>
-      <c r="H158" s="644"/>
+      <c r="H158" s="671"/>
     </row>
     <row r="159" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A159" s="620" t="s">
+      <c r="A159" s="624" t="s">
         <v>148</v>
       </c>
-      <c r="B159" s="576"/>
-      <c r="C159" s="576"/>
-      <c r="D159" s="576"/>
-      <c r="E159" s="576"/>
-      <c r="F159" s="576"/>
-      <c r="G159" s="577"/>
-      <c r="H159" s="644"/>
+      <c r="B159" s="625"/>
+      <c r="C159" s="625"/>
+      <c r="D159" s="625"/>
+      <c r="E159" s="625"/>
+      <c r="F159" s="625"/>
+      <c r="G159" s="626"/>
+      <c r="H159" s="671"/>
     </row>
     <row r="160" spans="1:8" ht="15.75" customHeight="1">
       <c r="A160" s="125" t="s">
@@ -31329,10 +31396,10 @@
       <c r="D160" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E160" s="576"/>
-      <c r="F160" s="577"/>
+      <c r="E160" s="608"/>
+      <c r="F160" s="609"/>
       <c r="G160" s="125"/>
-      <c r="H160" s="644"/>
+      <c r="H160" s="671"/>
     </row>
     <row r="161" spans="1:8" ht="15.75" customHeight="1">
       <c r="A161" s="125" t="s">
@@ -31347,10 +31414,10 @@
       <c r="D161" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E161" s="576"/>
-      <c r="F161" s="577"/>
+      <c r="E161" s="608"/>
+      <c r="F161" s="609"/>
       <c r="G161" s="127"/>
-      <c r="H161" s="644"/>
+      <c r="H161" s="671"/>
     </row>
     <row r="162" spans="1:8" ht="15.75" customHeight="1">
       <c r="A162" s="125" t="s">
@@ -31365,10 +31432,10 @@
       <c r="D162" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E162" s="576"/>
-      <c r="F162" s="577"/>
+      <c r="E162" s="608"/>
+      <c r="F162" s="609"/>
       <c r="G162" s="127"/>
-      <c r="H162" s="644"/>
+      <c r="H162" s="671"/>
     </row>
     <row r="163" spans="1:8" ht="15.75" customHeight="1">
       <c r="A163" s="125" t="s">
@@ -31383,10 +31450,10 @@
       <c r="D163" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E163" s="576"/>
-      <c r="F163" s="577"/>
+      <c r="E163" s="608"/>
+      <c r="F163" s="609"/>
       <c r="G163" s="127"/>
-      <c r="H163" s="644"/>
+      <c r="H163" s="671"/>
     </row>
     <row r="164" spans="1:8" ht="15.75" customHeight="1">
       <c r="A164" s="125" t="s">
@@ -31401,10 +31468,10 @@
       <c r="D164" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E164" s="576"/>
-      <c r="F164" s="577"/>
+      <c r="E164" s="608"/>
+      <c r="F164" s="609"/>
       <c r="G164" s="127"/>
-      <c r="H164" s="644"/>
+      <c r="H164" s="671"/>
     </row>
     <row r="165" spans="1:8" ht="15.75" customHeight="1">
       <c r="A165" s="125" t="s">
@@ -31419,10 +31486,10 @@
       <c r="D165" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E165" s="576"/>
-      <c r="F165" s="577"/>
+      <c r="E165" s="608"/>
+      <c r="F165" s="609"/>
       <c r="G165" s="127"/>
-      <c r="H165" s="644"/>
+      <c r="H165" s="671"/>
     </row>
     <row r="166" spans="1:8" ht="15.75" customHeight="1">
       <c r="A166" s="125" t="s">
@@ -31437,10 +31504,10 @@
       <c r="D166" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E166" s="576"/>
-      <c r="F166" s="577"/>
+      <c r="E166" s="608"/>
+      <c r="F166" s="609"/>
       <c r="G166" s="125"/>
-      <c r="H166" s="644"/>
+      <c r="H166" s="671"/>
     </row>
     <row r="167" spans="1:8" ht="15.75" customHeight="1">
       <c r="A167" s="125" t="s">
@@ -31455,10 +31522,10 @@
       <c r="D167" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E167" s="576"/>
-      <c r="F167" s="577"/>
+      <c r="E167" s="608"/>
+      <c r="F167" s="609"/>
       <c r="G167" s="125"/>
-      <c r="H167" s="644"/>
+      <c r="H167" s="671"/>
     </row>
     <row r="168" spans="1:8" ht="15.75" customHeight="1">
       <c r="A168" s="125" t="s">
@@ -31473,10 +31540,10 @@
       <c r="D168" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E168" s="576"/>
-      <c r="F168" s="577"/>
+      <c r="E168" s="608"/>
+      <c r="F168" s="609"/>
       <c r="G168" s="125"/>
-      <c r="H168" s="644"/>
+      <c r="H168" s="671"/>
     </row>
     <row r="169" spans="1:8" ht="15.75" customHeight="1">
       <c r="A169" s="125" t="s">
@@ -31491,10 +31558,10 @@
       <c r="D169" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E169" s="576"/>
-      <c r="F169" s="577"/>
+      <c r="E169" s="608"/>
+      <c r="F169" s="609"/>
       <c r="G169" s="125"/>
-      <c r="H169" s="644"/>
+      <c r="H169" s="671"/>
     </row>
     <row r="170" spans="1:8" ht="15.75" customHeight="1">
       <c r="A170" s="125" t="s">
@@ -31509,10 +31576,10 @@
       <c r="D170" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E170" s="576"/>
-      <c r="F170" s="577"/>
+      <c r="E170" s="608"/>
+      <c r="F170" s="609"/>
       <c r="G170" s="125"/>
-      <c r="H170" s="644"/>
+      <c r="H170" s="671"/>
     </row>
     <row r="171" spans="1:8" ht="15.75" customHeight="1">
       <c r="A171" s="125" t="s">
@@ -31527,12 +31594,12 @@
       <c r="D171" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E171" s="576"/>
-      <c r="F171" s="577"/>
+      <c r="E171" s="608"/>
+      <c r="F171" s="609"/>
       <c r="G171" s="131" t="s">
         <v>421</v>
       </c>
-      <c r="H171" s="644"/>
+      <c r="H171" s="671"/>
     </row>
     <row r="172" spans="1:8" ht="15.75" customHeight="1">
       <c r="A172" s="125" t="s">
@@ -31547,12 +31614,12 @@
       <c r="D172" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E172" s="576"/>
-      <c r="F172" s="577"/>
+      <c r="E172" s="608"/>
+      <c r="F172" s="609"/>
       <c r="G172" s="125" t="s">
         <v>423</v>
       </c>
-      <c r="H172" s="644"/>
+      <c r="H172" s="671"/>
     </row>
     <row r="173" spans="1:8" ht="15.75" customHeight="1">
       <c r="A173" s="125" t="s">
@@ -31567,10 +31634,10 @@
       <c r="D173" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E173" s="576"/>
-      <c r="F173" s="577"/>
+      <c r="E173" s="608"/>
+      <c r="F173" s="609"/>
       <c r="G173" s="125"/>
-      <c r="H173" s="644"/>
+      <c r="H173" s="671"/>
     </row>
     <row r="174" spans="1:8" ht="15.75" customHeight="1">
       <c r="A174" s="125" t="s">
@@ -31585,10 +31652,10 @@
       <c r="D174" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E174" s="576"/>
-      <c r="F174" s="577"/>
+      <c r="E174" s="608"/>
+      <c r="F174" s="609"/>
       <c r="G174" s="125"/>
-      <c r="H174" s="644"/>
+      <c r="H174" s="671"/>
     </row>
     <row r="175" spans="1:8" ht="15.75" customHeight="1">
       <c r="A175" s="125" t="s">
@@ -31603,10 +31670,10 @@
       <c r="D175" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E175" s="576"/>
-      <c r="F175" s="577"/>
+      <c r="E175" s="608"/>
+      <c r="F175" s="609"/>
       <c r="G175" s="125"/>
-      <c r="H175" s="644"/>
+      <c r="H175" s="671"/>
     </row>
     <row r="176" spans="1:8" ht="15.75" customHeight="1">
       <c r="A176" s="125" t="s">
@@ -31621,10 +31688,10 @@
       <c r="D176" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E176" s="576"/>
-      <c r="F176" s="577"/>
+      <c r="E176" s="608"/>
+      <c r="F176" s="609"/>
       <c r="G176" s="125"/>
-      <c r="H176" s="644"/>
+      <c r="H176" s="671"/>
     </row>
     <row r="177" spans="1:8" ht="15.75" customHeight="1">
       <c r="A177" s="125" t="s">
@@ -31639,10 +31706,10 @@
       <c r="D177" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E177" s="576"/>
-      <c r="F177" s="577"/>
+      <c r="E177" s="608"/>
+      <c r="F177" s="609"/>
       <c r="G177" s="125"/>
-      <c r="H177" s="644"/>
+      <c r="H177" s="671"/>
     </row>
     <row r="178" spans="1:8" ht="15.75" customHeight="1">
       <c r="A178" s="125" t="s">
@@ -31657,10 +31724,10 @@
       <c r="D178" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E178" s="576"/>
-      <c r="F178" s="577"/>
+      <c r="E178" s="608"/>
+      <c r="F178" s="609"/>
       <c r="G178" s="125"/>
-      <c r="H178" s="644"/>
+      <c r="H178" s="671"/>
     </row>
     <row r="179" spans="1:8" ht="15.75" customHeight="1">
       <c r="A179" s="125" t="s">
@@ -31675,12 +31742,12 @@
       <c r="D179" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E179" s="576"/>
-      <c r="F179" s="577"/>
+      <c r="E179" s="608"/>
+      <c r="F179" s="609"/>
       <c r="G179" s="132" t="s">
         <v>431</v>
       </c>
-      <c r="H179" s="644"/>
+      <c r="H179" s="671"/>
     </row>
     <row r="180" spans="1:8" ht="15.75" customHeight="1">
       <c r="A180" s="125" t="s">
@@ -31695,10 +31762,10 @@
       <c r="D180" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E180" s="576"/>
-      <c r="F180" s="577"/>
+      <c r="E180" s="608"/>
+      <c r="F180" s="609"/>
       <c r="G180" s="125"/>
-      <c r="H180" s="644"/>
+      <c r="H180" s="671"/>
     </row>
     <row r="181" spans="1:8" ht="15.75" customHeight="1">
       <c r="A181" s="125" t="s">
@@ -31713,10 +31780,10 @@
       <c r="D181" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E181" s="576"/>
-      <c r="F181" s="577"/>
+      <c r="E181" s="608"/>
+      <c r="F181" s="609"/>
       <c r="G181" s="125"/>
-      <c r="H181" s="644"/>
+      <c r="H181" s="671"/>
     </row>
     <row r="182" spans="1:8" ht="15.75" customHeight="1">
       <c r="A182" s="125" t="s">
@@ -31731,10 +31798,10 @@
       <c r="D182" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E182" s="576"/>
-      <c r="F182" s="577"/>
+      <c r="E182" s="608"/>
+      <c r="F182" s="609"/>
       <c r="G182" s="125"/>
-      <c r="H182" s="644"/>
+      <c r="H182" s="671"/>
     </row>
     <row r="183" spans="1:8" ht="15.75" customHeight="1">
       <c r="A183" s="125" t="s">
@@ -31749,10 +31816,10 @@
       <c r="D183" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E183" s="576"/>
-      <c r="F183" s="577"/>
+      <c r="E183" s="608"/>
+      <c r="F183" s="609"/>
       <c r="G183" s="125"/>
-      <c r="H183" s="644"/>
+      <c r="H183" s="671"/>
     </row>
     <row r="184" spans="1:8" ht="15.75" customHeight="1">
       <c r="A184" s="125" t="s">
@@ -31767,10 +31834,10 @@
       <c r="D184" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E184" s="576"/>
-      <c r="F184" s="577"/>
+      <c r="E184" s="608"/>
+      <c r="F184" s="609"/>
       <c r="G184" s="125"/>
-      <c r="H184" s="644"/>
+      <c r="H184" s="671"/>
     </row>
     <row r="185" spans="1:8" ht="15.75" customHeight="1">
       <c r="A185" s="125" t="s">
@@ -31785,10 +31852,10 @@
       <c r="D185" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E185" s="576"/>
-      <c r="F185" s="577"/>
+      <c r="E185" s="608"/>
+      <c r="F185" s="609"/>
       <c r="G185" s="125"/>
-      <c r="H185" s="644"/>
+      <c r="H185" s="671"/>
     </row>
     <row r="186" spans="1:8" ht="15.75" customHeight="1">
       <c r="A186" s="125" t="s">
@@ -31803,10 +31870,10 @@
       <c r="D186" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E186" s="576"/>
-      <c r="F186" s="577"/>
+      <c r="E186" s="608"/>
+      <c r="F186" s="609"/>
       <c r="G186" s="125"/>
-      <c r="H186" s="644"/>
+      <c r="H186" s="671"/>
     </row>
     <row r="187" spans="1:8" ht="15.75" customHeight="1">
       <c r="A187" s="125" t="s">
@@ -31821,12 +31888,12 @@
       <c r="D187" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E187" s="576"/>
-      <c r="F187" s="577"/>
+      <c r="E187" s="608"/>
+      <c r="F187" s="609"/>
       <c r="G187" s="133" t="s">
         <v>440</v>
       </c>
-      <c r="H187" s="644"/>
+      <c r="H187" s="671"/>
     </row>
     <row r="188" spans="1:8" ht="15.75" customHeight="1">
       <c r="A188" s="125" t="s">
@@ -31841,10 +31908,10 @@
       <c r="D188" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E188" s="576"/>
-      <c r="F188" s="577"/>
+      <c r="E188" s="608"/>
+      <c r="F188" s="609"/>
       <c r="G188" s="125"/>
-      <c r="H188" s="644"/>
+      <c r="H188" s="671"/>
     </row>
     <row r="189" spans="1:8" ht="15.75" customHeight="1">
       <c r="A189" s="125" t="s">
@@ -31859,10 +31926,10 @@
       <c r="D189" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E189" s="576"/>
-      <c r="F189" s="577"/>
+      <c r="E189" s="608"/>
+      <c r="F189" s="609"/>
       <c r="G189" s="125"/>
-      <c r="H189" s="644"/>
+      <c r="H189" s="671"/>
     </row>
     <row r="190" spans="1:8" ht="15.75" customHeight="1">
       <c r="A190" s="125" t="s">
@@ -31877,10 +31944,10 @@
       <c r="D190" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E190" s="576"/>
-      <c r="F190" s="577"/>
+      <c r="E190" s="608"/>
+      <c r="F190" s="609"/>
       <c r="G190" s="125"/>
-      <c r="H190" s="644"/>
+      <c r="H190" s="671"/>
     </row>
     <row r="191" spans="1:8" ht="15.75" customHeight="1">
       <c r="A191" s="125" t="s">
@@ -31895,10 +31962,10 @@
       <c r="D191" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E191" s="576"/>
-      <c r="F191" s="577"/>
+      <c r="E191" s="608"/>
+      <c r="F191" s="609"/>
       <c r="G191" s="125"/>
-      <c r="H191" s="644"/>
+      <c r="H191" s="671"/>
     </row>
     <row r="192" spans="1:8" ht="15.75" customHeight="1">
       <c r="A192" s="125" t="s">
@@ -31913,10 +31980,10 @@
       <c r="D192" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E192" s="576"/>
-      <c r="F192" s="577"/>
+      <c r="E192" s="608"/>
+      <c r="F192" s="609"/>
       <c r="G192" s="125"/>
-      <c r="H192" s="644"/>
+      <c r="H192" s="671"/>
     </row>
     <row r="193" spans="1:8" ht="15.75" customHeight="1">
       <c r="A193" s="125" t="s">
@@ -31931,10 +31998,10 @@
       <c r="D193" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E193" s="576"/>
-      <c r="F193" s="577"/>
+      <c r="E193" s="608"/>
+      <c r="F193" s="609"/>
       <c r="G193" s="125"/>
-      <c r="H193" s="644"/>
+      <c r="H193" s="671"/>
     </row>
     <row r="194" spans="1:8" ht="15.75" customHeight="1">
       <c r="A194" s="125" t="s">
@@ -31949,12 +32016,12 @@
       <c r="D194" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E194" s="576"/>
-      <c r="F194" s="577"/>
+      <c r="E194" s="608"/>
+      <c r="F194" s="609"/>
       <c r="G194" s="133" t="s">
         <v>170</v>
       </c>
-      <c r="H194" s="644"/>
+      <c r="H194" s="671"/>
     </row>
     <row r="195" spans="1:8" ht="15.75" customHeight="1">
       <c r="A195" s="125" t="s">
@@ -31969,10 +32036,10 @@
       <c r="D195" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E195" s="576"/>
-      <c r="F195" s="577"/>
+      <c r="E195" s="608"/>
+      <c r="F195" s="609"/>
       <c r="G195" s="125"/>
-      <c r="H195" s="644"/>
+      <c r="H195" s="671"/>
     </row>
     <row r="196" spans="1:8" ht="15.75" customHeight="1">
       <c r="A196" s="125" t="s">
@@ -31987,12 +32054,12 @@
       <c r="D196" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E196" s="576"/>
-      <c r="F196" s="577"/>
+      <c r="E196" s="608"/>
+      <c r="F196" s="609"/>
       <c r="G196" s="133" t="s">
         <v>170</v>
       </c>
-      <c r="H196" s="644"/>
+      <c r="H196" s="671"/>
     </row>
     <row r="197" spans="1:8" ht="15.75" customHeight="1">
       <c r="A197" s="125" t="s">
@@ -32007,12 +32074,12 @@
       <c r="D197" s="607" t="s">
         <v>169</v>
       </c>
-      <c r="E197" s="576"/>
-      <c r="F197" s="577"/>
+      <c r="E197" s="608"/>
+      <c r="F197" s="609"/>
       <c r="G197" s="133" t="s">
         <v>451</v>
       </c>
-      <c r="H197" s="644"/>
+      <c r="H197" s="671"/>
     </row>
     <row r="198" spans="1:8" ht="15.75" customHeight="1">
       <c r="A198" s="125" t="s">
@@ -32027,10 +32094,10 @@
       <c r="D198" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E198" s="576"/>
-      <c r="F198" s="577"/>
+      <c r="E198" s="608"/>
+      <c r="F198" s="609"/>
       <c r="G198" s="125"/>
-      <c r="H198" s="644"/>
+      <c r="H198" s="671"/>
     </row>
     <row r="199" spans="1:8" ht="15.75" customHeight="1">
       <c r="A199" s="125" t="s">
@@ -32045,10 +32112,10 @@
       <c r="D199" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E199" s="576"/>
-      <c r="F199" s="577"/>
+      <c r="E199" s="608"/>
+      <c r="F199" s="609"/>
       <c r="G199" s="125"/>
-      <c r="H199" s="644"/>
+      <c r="H199" s="671"/>
     </row>
     <row r="200" spans="1:8" ht="15.75" customHeight="1">
       <c r="A200" s="127" t="s">
@@ -32063,10 +32130,10 @@
       <c r="D200" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E200" s="576"/>
-      <c r="F200" s="577"/>
+      <c r="E200" s="608"/>
+      <c r="F200" s="609"/>
       <c r="G200" s="125"/>
-      <c r="H200" s="644"/>
+      <c r="H200" s="671"/>
     </row>
     <row r="201" spans="1:8" ht="15.75" customHeight="1">
       <c r="A201" s="127" t="s">
@@ -32081,10 +32148,10 @@
       <c r="D201" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E201" s="576"/>
-      <c r="F201" s="577"/>
+      <c r="E201" s="608"/>
+      <c r="F201" s="609"/>
       <c r="G201" s="125"/>
-      <c r="H201" s="644"/>
+      <c r="H201" s="671"/>
     </row>
     <row r="202" spans="1:8" ht="15.75" customHeight="1">
       <c r="A202" s="127" t="s">
@@ -32099,10 +32166,10 @@
       <c r="D202" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E202" s="576"/>
-      <c r="F202" s="577"/>
+      <c r="E202" s="608"/>
+      <c r="F202" s="609"/>
       <c r="G202" s="125"/>
-      <c r="H202" s="644"/>
+      <c r="H202" s="671"/>
     </row>
     <row r="203" spans="1:8" ht="15.75" customHeight="1">
       <c r="A203" s="127" t="s">
@@ -32117,10 +32184,10 @@
       <c r="D203" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E203" s="576"/>
-      <c r="F203" s="577"/>
+      <c r="E203" s="608"/>
+      <c r="F203" s="609"/>
       <c r="G203" s="125"/>
-      <c r="H203" s="644"/>
+      <c r="H203" s="671"/>
     </row>
     <row r="204" spans="1:8" ht="15.75" customHeight="1">
       <c r="A204" s="127" t="s">
@@ -32135,10 +32202,10 @@
       <c r="D204" s="607" t="s">
         <v>171</v>
       </c>
-      <c r="E204" s="576"/>
-      <c r="F204" s="577"/>
+      <c r="E204" s="608"/>
+      <c r="F204" s="609"/>
       <c r="G204" s="125"/>
-      <c r="H204" s="644"/>
+      <c r="H204" s="671"/>
     </row>
     <row r="205" spans="1:8" ht="15.75" customHeight="1">
       <c r="A205" s="127" t="s">
@@ -32153,10 +32220,10 @@
       <c r="D205" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E205" s="576"/>
-      <c r="F205" s="577"/>
+      <c r="E205" s="608"/>
+      <c r="F205" s="609"/>
       <c r="G205" s="125"/>
-      <c r="H205" s="644"/>
+      <c r="H205" s="671"/>
     </row>
     <row r="206" spans="1:8" ht="15.75" customHeight="1">
       <c r="A206" s="127" t="s">
@@ -32171,10 +32238,10 @@
       <c r="D206" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E206" s="576"/>
-      <c r="F206" s="577"/>
+      <c r="E206" s="608"/>
+      <c r="F206" s="609"/>
       <c r="G206" s="125"/>
-      <c r="H206" s="644"/>
+      <c r="H206" s="671"/>
     </row>
     <row r="207" spans="1:8" ht="15.75" customHeight="1">
       <c r="A207" s="127" t="s">
@@ -32189,10 +32256,10 @@
       <c r="D207" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E207" s="576"/>
-      <c r="F207" s="577"/>
+      <c r="E207" s="608"/>
+      <c r="F207" s="609"/>
       <c r="G207" s="125"/>
-      <c r="H207" s="644"/>
+      <c r="H207" s="671"/>
     </row>
     <row r="208" spans="1:8" ht="15.75" customHeight="1">
       <c r="A208" s="127" t="s">
@@ -32207,17 +32274,17 @@
       <c r="D208" s="607" t="s">
         <v>172</v>
       </c>
-      <c r="E208" s="576"/>
-      <c r="F208" s="577"/>
+      <c r="E208" s="608"/>
+      <c r="F208" s="609"/>
       <c r="G208" s="125"/>
-      <c r="H208" s="644"/>
+      <c r="H208" s="671"/>
     </row>
     <row r="209" spans="1:8" ht="12.75" customHeight="1">
-      <c r="A209" s="608" t="s">
+      <c r="A209" s="610" t="s">
         <v>464</v>
       </c>
-      <c r="B209" s="593"/>
-      <c r="C209" s="621">
+      <c r="B209" s="611"/>
+      <c r="C209" s="622">
         <f>COUNTIFS($A160:$A208,"*",$C160:$C208,"*",$D160:$D208,"*")</f>
         <v>49</v>
       </c>
@@ -32231,12 +32298,12 @@
         <v>178</v>
       </c>
       <c r="G209" s="136"/>
-      <c r="H209" s="644"/>
-    </row>
-    <row r="210" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A210" s="609"/>
-      <c r="B210" s="610"/>
-      <c r="C210" s="622"/>
+      <c r="H209" s="671"/>
+    </row>
+    <row r="210" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
+      <c r="A210" s="612"/>
+      <c r="B210" s="613"/>
+      <c r="C210" s="627"/>
       <c r="D210" s="123">
         <f>COUNTIFS($A160:$A208,"*",$C160:$C208,"*",$D160:$D208, "Employed")</f>
         <v>7</v>
@@ -32250,26 +32317,26 @@
         <v>13</v>
       </c>
       <c r="G210" s="124"/>
-      <c r="H210" s="644"/>
+      <c r="H210" s="671"/>
     </row>
     <row r="211" spans="1:8" ht="12.75" customHeight="1">
-      <c r="A211" s="623"/>
-      <c r="B211" s="624"/>
-      <c r="C211" s="624"/>
-      <c r="D211" s="624"/>
-      <c r="E211" s="624"/>
-      <c r="F211" s="625"/>
+      <c r="A211" s="628"/>
+      <c r="B211" s="629"/>
+      <c r="C211" s="629"/>
+      <c r="D211" s="629"/>
+      <c r="E211" s="629"/>
+      <c r="F211" s="629"/>
       <c r="G211" s="137" t="s">
         <v>152</v>
       </c>
       <c r="H211" s="64"/>
     </row>
     <row r="212" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A212" s="611" t="s">
+      <c r="A212" s="614" t="s">
         <v>465</v>
       </c>
-      <c r="B212" s="612"/>
-      <c r="C212" s="614">
+      <c r="B212" s="615"/>
+      <c r="C212" s="618">
         <f>SUM(D213:F213)</f>
         <v>182</v>
       </c>
@@ -32282,16 +32349,16 @@
       <c r="F212" s="138" t="s">
         <v>178</v>
       </c>
-      <c r="G212" s="626">
+      <c r="G212" s="630">
         <f>D213/C212</f>
         <v>0.45054945054945056</v>
       </c>
       <c r="H212" s="64"/>
     </row>
-    <row r="213" spans="1:8" ht="17.25" customHeight="1">
-      <c r="A213" s="609"/>
-      <c r="B213" s="613"/>
-      <c r="C213" s="615"/>
+    <row r="213" spans="1:8" ht="17.25" customHeight="1" thickBot="1">
+      <c r="A213" s="616"/>
+      <c r="B213" s="617"/>
+      <c r="C213" s="619"/>
       <c r="D213" s="139">
         <f>COUNTIFS($A23:$A210,"*",$C23:$C210,"*",$D23:$D210, "Employed")</f>
         <v>82</v>
@@ -32304,7 +32371,7 @@
         <f>COUNTIFS($A23:$A210,"*",$C23:$C210,"*",$D23:$D210, "Not Tracked")</f>
         <v>48</v>
       </c>
-      <c r="G213" s="627"/>
+      <c r="G213" s="631"/>
       <c r="H213" s="64"/>
     </row>
     <row r="214" spans="1:8" ht="15.75" customHeight="1">
@@ -33582,7 +33649,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="591"/>
-      <c r="C10" s="662">
+      <c r="C10" s="698">
         <v>2</v>
       </c>
       <c r="D10" s="591"/>
@@ -33595,24 +33662,24 @@
         <v>117</v>
       </c>
       <c r="B11" s="593"/>
-      <c r="C11" s="660" t="s">
+      <c r="C11" s="696" t="s">
         <v>471</v>
       </c>
       <c r="D11" s="577"/>
-      <c r="E11" s="661" t="s">
+      <c r="E11" s="697" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A12" s="654"/>
-      <c r="B12" s="655"/>
+      <c r="A12" s="690"/>
+      <c r="B12" s="691"/>
       <c r="C12" s="146" t="s">
         <v>472</v>
       </c>
       <c r="D12" s="146" t="s">
         <v>473</v>
       </c>
-      <c r="E12" s="645"/>
+      <c r="E12" s="686"/>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1">
       <c r="A13" s="594" t="s">
@@ -33715,7 +33782,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="591"/>
-      <c r="C21" s="657">
+      <c r="C21" s="692">
         <v>2</v>
       </c>
       <c r="D21" s="591"/>
@@ -33724,28 +33791,28 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="653" t="s">
+      <c r="A22" s="689" t="s">
         <v>117</v>
       </c>
       <c r="B22" s="593"/>
-      <c r="C22" s="658" t="s">
+      <c r="C22" s="693" t="s">
         <v>471</v>
       </c>
-      <c r="D22" s="617"/>
-      <c r="E22" s="659" t="s">
+      <c r="D22" s="694"/>
+      <c r="E22" s="695" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="654"/>
-      <c r="B23" s="655"/>
+      <c r="A23" s="690"/>
+      <c r="B23" s="691"/>
       <c r="C23" s="148" t="s">
         <v>472</v>
       </c>
       <c r="D23" s="149" t="s">
         <v>473</v>
       </c>
-      <c r="E23" s="645"/>
+      <c r="E23" s="686"/>
     </row>
     <row r="24" spans="1:5" ht="16.5" customHeight="1">
       <c r="A24" s="603" t="s">
@@ -33754,7 +33821,7 @@
       <c r="B24" s="595"/>
       <c r="C24" s="595"/>
       <c r="D24" s="591"/>
-      <c r="E24" s="656"/>
+      <c r="E24" s="670"/>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1">
       <c r="A25" s="150">
@@ -33767,7 +33834,7 @@
         <v>431</v>
       </c>
       <c r="D25" s="151"/>
-      <c r="E25" s="644"/>
+      <c r="E25" s="685"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1">
       <c r="A26" s="150">
@@ -33780,7 +33847,7 @@
         <v>144</v>
       </c>
       <c r="D26" s="151"/>
-      <c r="E26" s="644"/>
+      <c r="E26" s="685"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1">
       <c r="A27" s="150">
@@ -33793,7 +33860,7 @@
         <v>161</v>
       </c>
       <c r="D27" s="151"/>
-      <c r="E27" s="644"/>
+      <c r="E27" s="685"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1">
       <c r="A28" s="150">
@@ -33806,7 +33873,7 @@
         <v>94</v>
       </c>
       <c r="D28" s="151"/>
-      <c r="E28" s="644"/>
+      <c r="E28" s="685"/>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1">
       <c r="A29" s="150">
@@ -33819,7 +33886,7 @@
         <v>161</v>
       </c>
       <c r="D29" s="151"/>
-      <c r="E29" s="644"/>
+      <c r="E29" s="685"/>
     </row>
     <row r="30" spans="1:5" ht="15.75" customHeight="1">
       <c r="A30" s="150">
@@ -33832,7 +33899,7 @@
         <v>1673</v>
       </c>
       <c r="D30" s="151"/>
-      <c r="E30" s="644"/>
+      <c r="E30" s="685"/>
     </row>
     <row r="31" spans="1:5" ht="15.75" customHeight="1">
       <c r="A31" s="150">
@@ -33845,7 +33912,7 @@
         <v>729</v>
       </c>
       <c r="D31" s="151"/>
-      <c r="E31" s="644"/>
+      <c r="E31" s="685"/>
     </row>
     <row r="32" spans="1:5" ht="15.75" customHeight="1">
       <c r="A32" s="150">
@@ -33858,7 +33925,7 @@
         <v>248</v>
       </c>
       <c r="D32" s="151"/>
-      <c r="E32" s="644"/>
+      <c r="E32" s="685"/>
     </row>
     <row r="33" spans="1:5" ht="15.75" customHeight="1">
       <c r="A33" s="150">
@@ -33871,7 +33938,7 @@
         <v>306</v>
       </c>
       <c r="D33" s="151"/>
-      <c r="E33" s="644"/>
+      <c r="E33" s="685"/>
     </row>
     <row r="34" spans="1:5" ht="15.75" customHeight="1">
       <c r="A34" s="150">
@@ -33884,7 +33951,7 @@
         <v>103</v>
       </c>
       <c r="D34" s="151"/>
-      <c r="E34" s="644"/>
+      <c r="E34" s="685"/>
     </row>
     <row r="35" spans="1:5" ht="15.75" customHeight="1">
       <c r="A35" s="150">
@@ -33897,7 +33964,7 @@
         <v>103</v>
       </c>
       <c r="D35" s="151"/>
-      <c r="E35" s="644"/>
+      <c r="E35" s="685"/>
     </row>
     <row r="36" spans="1:5" ht="15.75" customHeight="1">
       <c r="A36" s="150">
@@ -33910,7 +33977,7 @@
       <c r="D36" s="151">
         <v>162</v>
       </c>
-      <c r="E36" s="644"/>
+      <c r="E36" s="685"/>
     </row>
     <row r="37" spans="1:5" ht="15.75" customHeight="1">
       <c r="A37" s="150">
@@ -33923,7 +33990,7 @@
         <v>233</v>
       </c>
       <c r="D37" s="151"/>
-      <c r="E37" s="644"/>
+      <c r="E37" s="685"/>
     </row>
     <row r="38" spans="1:5" ht="15.75" customHeight="1">
       <c r="A38" s="150">
@@ -33936,7 +34003,7 @@
         <v>280</v>
       </c>
       <c r="D38" s="151"/>
-      <c r="E38" s="644"/>
+      <c r="E38" s="685"/>
     </row>
     <row r="39" spans="1:5" ht="15.75" customHeight="1">
       <c r="A39" s="150">
@@ -33949,7 +34016,7 @@
         <v>248</v>
       </c>
       <c r="D39" s="151"/>
-      <c r="E39" s="644"/>
+      <c r="E39" s="685"/>
     </row>
     <row r="40" spans="1:5" ht="15.75" customHeight="1">
       <c r="A40" s="150">
@@ -33962,7 +34029,7 @@
         <v>855</v>
       </c>
       <c r="D40" s="151"/>
-      <c r="E40" s="644"/>
+      <c r="E40" s="685"/>
     </row>
     <row r="41" spans="1:5" ht="15.75" customHeight="1">
       <c r="A41" s="150">
@@ -33975,7 +34042,7 @@
         <v>103</v>
       </c>
       <c r="D41" s="151"/>
-      <c r="E41" s="644"/>
+      <c r="E41" s="685"/>
     </row>
     <row r="42" spans="1:5" ht="15.75" customHeight="1">
       <c r="A42" s="150">
@@ -33988,7 +34055,7 @@
       <c r="D42" s="151">
         <v>290</v>
       </c>
-      <c r="E42" s="644"/>
+      <c r="E42" s="685"/>
     </row>
     <row r="43" spans="1:5" ht="15.75" customHeight="1">
       <c r="A43" s="150">
@@ -34001,7 +34068,7 @@
       <c r="D43" s="151">
         <v>304</v>
       </c>
-      <c r="E43" s="644"/>
+      <c r="E43" s="685"/>
     </row>
     <row r="44" spans="1:5" ht="15.75" customHeight="1">
       <c r="A44" s="150">
@@ -34014,7 +34081,7 @@
         <v>200</v>
       </c>
       <c r="D44" s="151"/>
-      <c r="E44" s="644"/>
+      <c r="E44" s="685"/>
     </row>
     <row r="45" spans="1:5" ht="15.75" customHeight="1">
       <c r="A45" s="150">
@@ -34027,7 +34094,7 @@
         <v>428</v>
       </c>
       <c r="D45" s="151"/>
-      <c r="E45" s="644"/>
+      <c r="E45" s="685"/>
     </row>
     <row r="46" spans="1:5" ht="15.75" customHeight="1">
       <c r="A46" s="150">
@@ -34040,7 +34107,7 @@
         <v>65</v>
       </c>
       <c r="D46" s="151"/>
-      <c r="E46" s="644"/>
+      <c r="E46" s="685"/>
     </row>
     <row r="47" spans="1:5" ht="15.75" customHeight="1">
       <c r="A47" s="150">
@@ -34051,16 +34118,16 @@
       </c>
       <c r="C47" s="151"/>
       <c r="D47" s="151"/>
-      <c r="E47" s="644"/>
+      <c r="E47" s="685"/>
     </row>
     <row r="48" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A48" s="620" t="s">
+      <c r="A48" s="624" t="s">
         <v>493</v>
       </c>
       <c r="B48" s="576"/>
       <c r="C48" s="576"/>
       <c r="D48" s="577"/>
-      <c r="E48" s="650"/>
+      <c r="E48" s="684"/>
     </row>
     <row r="49" spans="1:5" ht="15.75" customHeight="1">
       <c r="A49" s="150">
@@ -34073,16 +34140,16 @@
         <v>393</v>
       </c>
       <c r="D49" s="43"/>
-      <c r="E49" s="644"/>
+      <c r="E49" s="685"/>
     </row>
     <row r="50" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A50" s="620" t="s">
+      <c r="A50" s="624" t="s">
         <v>494</v>
       </c>
       <c r="B50" s="576"/>
       <c r="C50" s="576"/>
       <c r="D50" s="577"/>
-      <c r="E50" s="650"/>
+      <c r="E50" s="684"/>
     </row>
     <row r="51" spans="1:5" ht="15.75" customHeight="1">
       <c r="A51" s="150">
@@ -34095,7 +34162,7 @@
         <v>121</v>
       </c>
       <c r="D51" s="43"/>
-      <c r="E51" s="644"/>
+      <c r="E51" s="685"/>
     </row>
     <row r="52" spans="1:5" ht="15.75" customHeight="1">
       <c r="A52" s="150">
@@ -34108,7 +34175,7 @@
       <c r="D52" s="151">
         <v>222</v>
       </c>
-      <c r="E52" s="644"/>
+      <c r="E52" s="685"/>
     </row>
     <row r="53" spans="1:5" ht="15.75" customHeight="1">
       <c r="A53" s="150">
@@ -34121,7 +34188,7 @@
         <v>98</v>
       </c>
       <c r="D53" s="43"/>
-      <c r="E53" s="644"/>
+      <c r="E53" s="685"/>
     </row>
     <row r="54" spans="1:5" ht="15.75" customHeight="1">
       <c r="A54" s="150">
@@ -34134,7 +34201,7 @@
         <v>399</v>
       </c>
       <c r="D54" s="43"/>
-      <c r="E54" s="644"/>
+      <c r="E54" s="685"/>
     </row>
     <row r="55" spans="1:5" ht="15.75" customHeight="1">
       <c r="A55" s="54">
@@ -34147,16 +34214,16 @@
         <v>145</v>
       </c>
       <c r="D55" s="57"/>
-      <c r="E55" s="645"/>
+      <c r="E55" s="686"/>
     </row>
     <row r="56" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A56" s="620" t="s">
+      <c r="A56" s="624" t="s">
         <v>498</v>
       </c>
       <c r="B56" s="576"/>
       <c r="C56" s="576"/>
       <c r="D56" s="577"/>
-      <c r="E56" s="650"/>
+      <c r="E56" s="684"/>
     </row>
     <row r="57" spans="1:5" ht="15.75" customHeight="1">
       <c r="A57" s="150">
@@ -34169,7 +34236,7 @@
       <c r="D57" s="151">
         <v>145</v>
       </c>
-      <c r="E57" s="644"/>
+      <c r="E57" s="685"/>
     </row>
     <row r="58" spans="1:5" ht="15.75" customHeight="1">
       <c r="A58" s="150">
@@ -34182,7 +34249,7 @@
         <v>96</v>
       </c>
       <c r="D58" s="43"/>
-      <c r="E58" s="644"/>
+      <c r="E58" s="685"/>
     </row>
     <row r="59" spans="1:5" ht="15.75" customHeight="1">
       <c r="A59" s="150">
@@ -34195,7 +34262,7 @@
         <v>1</v>
       </c>
       <c r="D59" s="43"/>
-      <c r="E59" s="644"/>
+      <c r="E59" s="685"/>
     </row>
     <row r="60" spans="1:5" ht="15.75" customHeight="1">
       <c r="A60" s="150">
@@ -34206,7 +34273,7 @@
       </c>
       <c r="C60" s="151"/>
       <c r="D60" s="151"/>
-      <c r="E60" s="644"/>
+      <c r="E60" s="685"/>
     </row>
     <row r="61" spans="1:5" ht="15.75" customHeight="1">
       <c r="A61" s="54">
@@ -34217,7 +34284,7 @@
       </c>
       <c r="C61" s="151"/>
       <c r="D61" s="151"/>
-      <c r="E61" s="645"/>
+      <c r="E61" s="686"/>
     </row>
     <row r="62" spans="1:5" ht="12.75" hidden="1" customHeight="1">
       <c r="A62" s="54"/>
@@ -34246,11 +34313,11 @@
       <c r="B64" s="156" t="s">
         <v>503</v>
       </c>
-      <c r="C64" s="651">
+      <c r="C64" s="687">
         <f>SUM(C63:D63)</f>
         <v>8941</v>
       </c>
-      <c r="D64" s="652"/>
+      <c r="D64" s="688"/>
       <c r="E64" s="61"/>
     </row>
     <row r="65" spans="1:5" ht="15" customHeight="1">
@@ -35491,7 +35558,7 @@
       <c r="D10" s="22">
         <v>3</v>
       </c>
-      <c r="E10" s="662">
+      <c r="E10" s="698">
         <v>4</v>
       </c>
       <c r="F10" s="595"/>
@@ -35505,33 +35572,33 @@
         <v>508</v>
       </c>
       <c r="B11" s="593"/>
-      <c r="C11" s="679" t="s">
+      <c r="C11" s="716" t="s">
         <v>509</v>
       </c>
-      <c r="D11" s="679" t="s">
+      <c r="D11" s="716" t="s">
         <v>510</v>
       </c>
-      <c r="E11" s="676" t="s">
+      <c r="E11" s="713" t="s">
         <v>511</v>
       </c>
       <c r="F11" s="588"/>
-      <c r="G11" s="661" t="s">
+      <c r="G11" s="697" t="s">
         <v>512</v>
       </c>
       <c r="H11" s="157"/>
     </row>
     <row r="12" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A12" s="654"/>
-      <c r="B12" s="655"/>
-      <c r="C12" s="673"/>
-      <c r="D12" s="673"/>
+      <c r="A12" s="690"/>
+      <c r="B12" s="691"/>
+      <c r="C12" s="710"/>
+      <c r="D12" s="710"/>
       <c r="E12" s="158" t="s">
         <v>513</v>
       </c>
       <c r="F12" s="158" t="s">
         <v>514</v>
       </c>
-      <c r="G12" s="645"/>
+      <c r="G12" s="686"/>
       <c r="H12" s="157"/>
     </row>
     <row r="13" spans="1:8" ht="15.75" customHeight="1">
@@ -35703,7 +35770,7 @@
       <c r="D21" s="38">
         <v>3</v>
       </c>
-      <c r="E21" s="657">
+      <c r="E21" s="692">
         <v>4</v>
       </c>
       <c r="F21" s="595"/>
@@ -35713,37 +35780,37 @@
       <c r="H21" s="157"/>
     </row>
     <row r="22" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A22" s="671" t="s">
+      <c r="A22" s="708" t="s">
         <v>508</v>
       </c>
       <c r="B22" s="593"/>
-      <c r="C22" s="677" t="s">
+      <c r="C22" s="714" t="s">
         <v>509</v>
       </c>
-      <c r="D22" s="677" t="s">
+      <c r="D22" s="714" t="s">
         <v>510</v>
       </c>
-      <c r="E22" s="675" t="s">
+      <c r="E22" s="712" t="s">
         <v>525</v>
       </c>
       <c r="F22" s="588"/>
-      <c r="G22" s="678" t="s">
+      <c r="G22" s="715" t="s">
         <v>121</v>
       </c>
       <c r="H22" s="157"/>
     </row>
     <row r="23" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A23" s="654"/>
-      <c r="B23" s="655"/>
-      <c r="C23" s="673"/>
-      <c r="D23" s="673"/>
+      <c r="A23" s="690"/>
+      <c r="B23" s="691"/>
+      <c r="C23" s="710"/>
+      <c r="D23" s="710"/>
       <c r="E23" s="169" t="s">
         <v>526</v>
       </c>
       <c r="F23" s="169" t="s">
         <v>527</v>
       </c>
-      <c r="G23" s="645"/>
+      <c r="G23" s="686"/>
       <c r="H23" s="157"/>
     </row>
     <row r="24" spans="1:8" ht="16.5" customHeight="1">
@@ -36287,7 +36354,7 @@
       <c r="H46" s="157"/>
     </row>
     <row r="47" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A47" s="664" t="s">
+      <c r="A47" s="700" t="s">
         <v>592</v>
       </c>
       <c r="B47" s="576"/>
@@ -36295,7 +36362,7 @@
       <c r="D47" s="576"/>
       <c r="E47" s="576"/>
       <c r="F47" s="576"/>
-      <c r="G47" s="665"/>
+      <c r="G47" s="701"/>
       <c r="H47" s="157"/>
     </row>
     <row r="48" spans="1:8" ht="15.75" customHeight="1">
@@ -36317,10 +36384,10 @@
       <c r="F48" s="199" t="s">
         <v>596</v>
       </c>
-      <c r="G48" s="672" t="s">
+      <c r="G48" s="709" t="s">
         <v>597</v>
       </c>
-      <c r="H48" s="663"/>
+      <c r="H48" s="699"/>
     </row>
     <row r="49" spans="1:8" ht="15.75" customHeight="1">
       <c r="A49" s="150">
@@ -36341,7 +36408,7 @@
       <c r="F49" s="189">
         <v>45170</v>
       </c>
-      <c r="G49" s="673"/>
+      <c r="G49" s="710"/>
       <c r="H49" s="588"/>
     </row>
     <row r="50" spans="1:8" ht="15.75" customHeight="1">
@@ -36363,7 +36430,7 @@
       <c r="F50" s="189">
         <v>46174</v>
       </c>
-      <c r="G50" s="674"/>
+      <c r="G50" s="711"/>
       <c r="H50" s="588"/>
     </row>
     <row r="51" spans="1:8" ht="15.75" customHeight="1">
@@ -36391,7 +36458,7 @@
       <c r="H51" s="157"/>
     </row>
     <row r="52" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A52" s="664" t="s">
+      <c r="A52" s="700" t="s">
         <v>451</v>
       </c>
       <c r="B52" s="576"/>
@@ -36399,7 +36466,7 @@
       <c r="D52" s="576"/>
       <c r="E52" s="576"/>
       <c r="F52" s="576"/>
-      <c r="G52" s="665"/>
+      <c r="G52" s="701"/>
       <c r="H52" s="157"/>
     </row>
     <row r="53" spans="1:8" ht="15.75" customHeight="1">
@@ -36475,7 +36542,7 @@
       <c r="H55" s="157"/>
     </row>
     <row r="56" spans="1:8" ht="15.75" customHeight="1">
-      <c r="A56" s="664" t="s">
+      <c r="A56" s="700" t="s">
         <v>611</v>
       </c>
       <c r="B56" s="576"/>
@@ -36483,7 +36550,7 @@
       <c r="D56" s="576"/>
       <c r="E56" s="576"/>
       <c r="F56" s="576"/>
-      <c r="G56" s="665"/>
+      <c r="G56" s="701"/>
       <c r="H56" s="157"/>
     </row>
     <row r="57" spans="1:8" ht="15.75" customHeight="1">
@@ -36522,10 +36589,10 @@
     </row>
     <row r="59" spans="1:8" ht="15" customHeight="1">
       <c r="A59" s="211"/>
-      <c r="B59" s="666" t="s">
+      <c r="B59" s="702" t="s">
         <v>615</v>
       </c>
-      <c r="C59" s="625"/>
+      <c r="C59" s="703"/>
       <c r="D59" s="212">
         <f>COUNTIFS($B25:B58,"&lt;&gt;",D25:D58,"&lt;&gt;")</f>
         <v>30</v>
@@ -36537,10 +36604,10 @@
     </row>
     <row r="60" spans="1:8" ht="15" customHeight="1">
       <c r="A60" s="214"/>
-      <c r="B60" s="667" t="s">
+      <c r="B60" s="704" t="s">
         <v>616</v>
       </c>
-      <c r="C60" s="668"/>
+      <c r="C60" s="705"/>
       <c r="D60" s="215">
         <v>23</v>
       </c>
@@ -36551,10 +36618,10 @@
     </row>
     <row r="61" spans="1:8" ht="15" customHeight="1">
       <c r="A61" s="214"/>
-      <c r="B61" s="667" t="s">
+      <c r="B61" s="704" t="s">
         <v>617</v>
       </c>
-      <c r="C61" s="668"/>
+      <c r="C61" s="705"/>
       <c r="D61" s="215">
         <v>30</v>
       </c>
@@ -36565,10 +36632,10 @@
     </row>
     <row r="62" spans="1:8" ht="15" customHeight="1">
       <c r="A62" s="216"/>
-      <c r="B62" s="669" t="s">
+      <c r="B62" s="706" t="s">
         <v>152</v>
       </c>
-      <c r="C62" s="670"/>
+      <c r="C62" s="707"/>
       <c r="D62" s="217">
         <f>D60/D61</f>
         <v>0.76666666666666672</v>
@@ -39712,7 +39779,7 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="40.5" customHeight="1">
-      <c r="A11" s="638" t="s">
+      <c r="A11" s="657" t="s">
         <v>622</v>
       </c>
       <c r="B11" s="602"/>
@@ -41466,7 +41533,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="591"/>
-      <c r="C10" s="662">
+      <c r="C10" s="698">
         <v>2</v>
       </c>
       <c r="D10" s="591"/>
@@ -41479,24 +41546,24 @@
         <v>117</v>
       </c>
       <c r="B11" s="593"/>
-      <c r="C11" s="660" t="s">
+      <c r="C11" s="696" t="s">
         <v>471</v>
       </c>
       <c r="D11" s="577"/>
-      <c r="E11" s="661" t="s">
+      <c r="E11" s="697" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A12" s="654"/>
-      <c r="B12" s="655"/>
+      <c r="A12" s="690"/>
+      <c r="B12" s="691"/>
       <c r="C12" s="146" t="s">
         <v>472</v>
       </c>
       <c r="D12" s="146" t="s">
         <v>473</v>
       </c>
-      <c r="E12" s="645"/>
+      <c r="E12" s="686"/>
     </row>
     <row r="13" spans="1:5" ht="15.75" customHeight="1">
       <c r="A13" s="594" t="s">
@@ -41599,7 +41666,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="591"/>
-      <c r="C21" s="657">
+      <c r="C21" s="692">
         <v>2</v>
       </c>
       <c r="D21" s="591"/>
@@ -41608,28 +41675,28 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A22" s="653" t="s">
+      <c r="A22" s="689" t="s">
         <v>117</v>
       </c>
       <c r="B22" s="593"/>
-      <c r="C22" s="658" t="s">
+      <c r="C22" s="693" t="s">
         <v>471</v>
       </c>
-      <c r="D22" s="617"/>
-      <c r="E22" s="659" t="s">
+      <c r="D22" s="694"/>
+      <c r="E22" s="695" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1">
-      <c r="A23" s="654"/>
-      <c r="B23" s="655"/>
+      <c r="A23" s="690"/>
+      <c r="B23" s="691"/>
       <c r="C23" s="148" t="s">
         <v>472</v>
       </c>
       <c r="D23" s="149" t="s">
         <v>473</v>
       </c>
-      <c r="E23" s="645"/>
+      <c r="E23" s="686"/>
     </row>
     <row r="24" spans="1:5" ht="16.5" customHeight="1">
       <c r="A24" s="603" t="s">
@@ -41638,7 +41705,7 @@
       <c r="B24" s="595"/>
       <c r="C24" s="595"/>
       <c r="D24" s="591"/>
-      <c r="E24" s="656"/>
+      <c r="E24" s="670"/>
     </row>
     <row r="25" spans="1:5" ht="15.75" customHeight="1">
       <c r="A25" s="150">
@@ -41651,7 +41718,7 @@
         <v>43</v>
       </c>
       <c r="D25" s="151"/>
-      <c r="E25" s="644"/>
+      <c r="E25" s="685"/>
     </row>
     <row r="26" spans="1:5" ht="15.75" customHeight="1">
       <c r="A26" s="150">
@@ -41664,7 +41731,7 @@
         <v>457</v>
       </c>
       <c r="D26" s="151"/>
-      <c r="E26" s="644"/>
+      <c r="E26" s="685"/>
     </row>
     <row r="27" spans="1:5" ht="15.75" customHeight="1">
       <c r="A27" s="150">
@@ -41679,7 +41746,7 @@
       <c r="D27" s="151">
         <v>30</v>
       </c>
-      <c r="E27" s="644"/>
+      <c r="E27" s="685"/>
     </row>
     <row r="28" spans="1:5" ht="15.75" customHeight="1">
       <c r="A28" s="150">
@@ -41692,7 +41759,7 @@
         <v>7</v>
       </c>
       <c r="D28" s="151"/>
-      <c r="E28" s="644"/>
+      <c r="E28" s="685"/>
     </row>
     <row r="29" spans="1:5" ht="15.75" customHeight="1">
       <c r="A29" s="150">
@@ -41701,7 +41768,7 @@
       <c r="B29" s="43"/>
       <c r="C29" s="151"/>
       <c r="D29" s="151"/>
-      <c r="E29" s="644"/>
+      <c r="E29" s="685"/>
     </row>
     <row r="30" spans="1:5" ht="12.75" hidden="1" customHeight="1">
       <c r="A30" s="54"/>
@@ -41730,11 +41797,11 @@
       <c r="B32" s="156" t="s">
         <v>503</v>
       </c>
-      <c r="C32" s="651">
+      <c r="C32" s="687">
         <f>SUM(C31:D31)</f>
         <v>582</v>
       </c>
-      <c r="D32" s="652"/>
+      <c r="D32" s="688"/>
       <c r="E32" s="61"/>
     </row>
     <row r="33" spans="1:5" ht="15" customHeight="1">
@@ -42964,22 +43031,22 @@
     <row r="8" spans="1:7" ht="15.75" customHeight="1">
       <c r="A8" s="20"/>
       <c r="B8" s="20"/>
-      <c r="C8" s="682"/>
-      <c r="D8" s="683"/>
-      <c r="E8" s="683"/>
-      <c r="F8" s="683"/>
-      <c r="G8" s="683"/>
+      <c r="C8" s="722"/>
+      <c r="D8" s="723"/>
+      <c r="E8" s="723"/>
+      <c r="F8" s="723"/>
+      <c r="G8" s="723"/>
     </row>
     <row r="9" spans="1:7" ht="12.75" customHeight="1">
-      <c r="A9" s="684" t="s">
+      <c r="A9" s="724" t="s">
         <v>116</v>
       </c>
-      <c r="B9" s="683"/>
-      <c r="C9" s="683"/>
-      <c r="D9" s="683"/>
-      <c r="E9" s="683"/>
-      <c r="F9" s="683"/>
-      <c r="G9" s="685"/>
+      <c r="B9" s="723"/>
+      <c r="C9" s="723"/>
+      <c r="D9" s="723"/>
+      <c r="E9" s="723"/>
+      <c r="F9" s="723"/>
+      <c r="G9" s="725"/>
     </row>
     <row r="10" spans="1:7" ht="15.75" customHeight="1">
       <c r="A10" s="590">
@@ -42992,7 +43059,7 @@
       <c r="D10" s="22">
         <v>3</v>
       </c>
-      <c r="E10" s="662">
+      <c r="E10" s="698">
         <v>4</v>
       </c>
       <c r="F10" s="591"/>
@@ -43005,32 +43072,32 @@
         <v>508</v>
       </c>
       <c r="B11" s="593"/>
-      <c r="C11" s="681" t="s">
+      <c r="C11" s="720" t="s">
         <v>509</v>
       </c>
-      <c r="D11" s="681" t="s">
+      <c r="D11" s="720" t="s">
         <v>510</v>
       </c>
-      <c r="E11" s="680" t="s">
+      <c r="E11" s="717" t="s">
         <v>696</v>
       </c>
       <c r="F11" s="593"/>
-      <c r="G11" s="661" t="s">
+      <c r="G11" s="697" t="s">
         <v>512</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A12" s="609"/>
-      <c r="B12" s="610"/>
-      <c r="C12" s="622"/>
-      <c r="D12" s="622"/>
+      <c r="A12" s="718"/>
+      <c r="B12" s="719"/>
+      <c r="C12" s="721"/>
+      <c r="D12" s="721"/>
       <c r="E12" s="158" t="s">
         <v>697</v>
       </c>
       <c r="F12" s="158" t="s">
         <v>698</v>
       </c>
-      <c r="G12" s="645"/>
+      <c r="G12" s="686"/>
     </row>
     <row r="13" spans="1:7" ht="15.75" customHeight="1">
       <c r="A13" s="594" t="s">
@@ -43193,7 +43260,7 @@
       <c r="D21" s="38">
         <v>3</v>
       </c>
-      <c r="E21" s="657">
+      <c r="E21" s="692">
         <v>4</v>
       </c>
       <c r="F21" s="595"/>
@@ -43202,36 +43269,36 @@
       </c>
     </row>
     <row r="22" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A22" s="671" t="s">
+      <c r="A22" s="708" t="s">
         <v>508</v>
       </c>
       <c r="B22" s="593"/>
-      <c r="C22" s="677" t="s">
+      <c r="C22" s="714" t="s">
         <v>509</v>
       </c>
-      <c r="D22" s="677" t="s">
+      <c r="D22" s="714" t="s">
         <v>510</v>
       </c>
-      <c r="E22" s="675" t="s">
+      <c r="E22" s="712" t="s">
         <v>701</v>
       </c>
       <c r="F22" s="588"/>
-      <c r="G22" s="678" t="s">
+      <c r="G22" s="715" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="15.75" customHeight="1">
-      <c r="A23" s="654"/>
-      <c r="B23" s="655"/>
-      <c r="C23" s="673"/>
-      <c r="D23" s="673"/>
+      <c r="A23" s="690"/>
+      <c r="B23" s="691"/>
+      <c r="C23" s="710"/>
+      <c r="D23" s="710"/>
       <c r="E23" s="169" t="s">
         <v>702</v>
       </c>
       <c r="F23" s="169" t="s">
         <v>703</v>
       </c>
-      <c r="G23" s="645"/>
+      <c r="G23" s="686"/>
     </row>
     <row r="24" spans="1:7" ht="16.5" customHeight="1">
       <c r="A24" s="603" t="s">
@@ -43324,10 +43391,10 @@
     </row>
     <row r="29" spans="1:7" ht="15" customHeight="1">
       <c r="A29" s="211"/>
-      <c r="B29" s="666" t="s">
+      <c r="B29" s="702" t="s">
         <v>615</v>
       </c>
-      <c r="C29" s="625"/>
+      <c r="C29" s="703"/>
       <c r="D29" s="212">
         <f>COUNTIFS($B25:B28,"&lt;&gt;",D25:D28,"&lt;&gt;")</f>
         <v>3</v>
@@ -43338,10 +43405,10 @@
     </row>
     <row r="30" spans="1:7" ht="15" customHeight="1">
       <c r="A30" s="214"/>
-      <c r="B30" s="667" t="s">
+      <c r="B30" s="704" t="s">
         <v>616</v>
       </c>
-      <c r="C30" s="668"/>
+      <c r="C30" s="705"/>
       <c r="D30" s="215">
         <v>3</v>
       </c>
@@ -43351,10 +43418,10 @@
     </row>
     <row r="31" spans="1:7" ht="15" customHeight="1">
       <c r="A31" s="214"/>
-      <c r="B31" s="667" t="s">
+      <c r="B31" s="704" t="s">
         <v>617</v>
       </c>
-      <c r="C31" s="668"/>
+      <c r="C31" s="705"/>
       <c r="D31" s="215">
         <f>D29-COUNTIF(D25:D28,"Not Accreditable")</f>
         <v>3</v>
@@ -43365,10 +43432,10 @@
     </row>
     <row r="32" spans="1:7" ht="15" customHeight="1">
       <c r="A32" s="216"/>
-      <c r="B32" s="669" t="s">
+      <c r="B32" s="706" t="s">
         <v>152</v>
       </c>
-      <c r="C32" s="670"/>
+      <c r="C32" s="707"/>
       <c r="D32" s="217">
         <f>D30/D31</f>
         <v>1</v>
@@ -44571,7 +44638,7 @@
       <c r="E1" s="595"/>
       <c r="F1" s="595"/>
       <c r="G1" s="595"/>
-      <c r="H1" s="709"/>
+      <c r="H1" s="752"/>
       <c r="I1" s="246"/>
       <c r="J1" s="246"/>
       <c r="K1" s="246"/>
@@ -44807,7 +44874,7 @@
       <c r="S9" s="580"/>
     </row>
     <row r="10" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A10" s="705" t="s">
+      <c r="A10" s="748" t="s">
         <v>714</v>
       </c>
       <c r="B10" s="595"/>
@@ -44815,13 +44882,13 @@
       <c r="D10" s="595"/>
       <c r="E10" s="595"/>
       <c r="F10" s="605"/>
-      <c r="G10" s="706" t="s">
+      <c r="G10" s="749" t="s">
         <v>715</v>
       </c>
       <c r="H10" s="595"/>
       <c r="I10" s="595"/>
       <c r="J10" s="605"/>
-      <c r="K10" s="706" t="s">
+      <c r="K10" s="749" t="s">
         <v>716</v>
       </c>
       <c r="L10" s="595"/>
@@ -44829,7 +44896,7 @@
       <c r="N10" s="595"/>
       <c r="O10" s="595"/>
       <c r="P10" s="605"/>
-      <c r="Q10" s="707" t="s">
+      <c r="Q10" s="750" t="s">
         <v>717</v>
       </c>
       <c r="R10" s="595"/>
@@ -44840,80 +44907,80 @@
         <v>718</v>
       </c>
       <c r="B11" s="593"/>
-      <c r="C11" s="681" t="s">
+      <c r="C11" s="720" t="s">
         <v>719</v>
       </c>
-      <c r="D11" s="681" t="s">
+      <c r="D11" s="720" t="s">
         <v>720</v>
       </c>
-      <c r="E11" s="660" t="s">
+      <c r="E11" s="696" t="s">
         <v>721</v>
       </c>
-      <c r="F11" s="665"/>
-      <c r="G11" s="708" t="s">
+      <c r="F11" s="701"/>
+      <c r="G11" s="751" t="s">
         <v>722</v>
       </c>
-      <c r="H11" s="681" t="s">
+      <c r="H11" s="720" t="s">
         <v>723</v>
       </c>
-      <c r="I11" s="681" t="s">
+      <c r="I11" s="720" t="s">
         <v>724</v>
       </c>
-      <c r="J11" s="661" t="s">
+      <c r="J11" s="697" t="s">
         <v>725</v>
       </c>
-      <c r="K11" s="708" t="s">
+      <c r="K11" s="751" t="s">
         <v>726</v>
       </c>
-      <c r="L11" s="681" t="s">
+      <c r="L11" s="720" t="s">
         <v>727</v>
       </c>
-      <c r="M11" s="681" t="s">
+      <c r="M11" s="720" t="s">
         <v>728</v>
       </c>
-      <c r="N11" s="681" t="s">
+      <c r="N11" s="720" t="s">
         <v>729</v>
       </c>
-      <c r="O11" s="681" t="s">
+      <c r="O11" s="720" t="s">
         <v>730</v>
       </c>
-      <c r="P11" s="661" t="s">
+      <c r="P11" s="697" t="s">
         <v>731</v>
       </c>
-      <c r="Q11" s="704" t="s">
+      <c r="Q11" s="747" t="s">
         <v>732</v>
       </c>
-      <c r="R11" s="681" t="s">
+      <c r="R11" s="720" t="s">
         <v>733</v>
       </c>
-      <c r="S11" s="661" t="s">
+      <c r="S11" s="697" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="12" spans="1:19" ht="15.75" customHeight="1">
-      <c r="A12" s="609"/>
-      <c r="B12" s="610"/>
-      <c r="C12" s="622"/>
-      <c r="D12" s="622"/>
+      <c r="A12" s="718"/>
+      <c r="B12" s="719"/>
+      <c r="C12" s="721"/>
+      <c r="D12" s="721"/>
       <c r="E12" s="84" t="s">
         <v>735</v>
       </c>
       <c r="F12" s="25" t="s">
         <v>736</v>
       </c>
-      <c r="G12" s="687"/>
-      <c r="H12" s="622"/>
-      <c r="I12" s="622"/>
-      <c r="J12" s="645"/>
-      <c r="K12" s="687"/>
-      <c r="L12" s="622"/>
-      <c r="M12" s="622"/>
-      <c r="N12" s="622"/>
-      <c r="O12" s="622"/>
-      <c r="P12" s="645"/>
-      <c r="Q12" s="610"/>
-      <c r="R12" s="622"/>
-      <c r="S12" s="645"/>
+      <c r="G12" s="727"/>
+      <c r="H12" s="721"/>
+      <c r="I12" s="721"/>
+      <c r="J12" s="686"/>
+      <c r="K12" s="727"/>
+      <c r="L12" s="721"/>
+      <c r="M12" s="721"/>
+      <c r="N12" s="721"/>
+      <c r="O12" s="721"/>
+      <c r="P12" s="686"/>
+      <c r="Q12" s="719"/>
+      <c r="R12" s="721"/>
+      <c r="S12" s="686"/>
     </row>
     <row r="13" spans="1:19" ht="15.75" customHeight="1">
       <c r="A13" s="253">
@@ -45204,7 +45271,7 @@
       <c r="S18" s="249"/>
     </row>
     <row r="19" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A19" s="699" t="s">
+      <c r="A19" s="742" t="s">
         <v>714</v>
       </c>
       <c r="B19" s="595"/>
@@ -45212,13 +45279,13 @@
       <c r="D19" s="595"/>
       <c r="E19" s="595"/>
       <c r="F19" s="605"/>
-      <c r="G19" s="700" t="s">
+      <c r="G19" s="743" t="s">
         <v>715</v>
       </c>
       <c r="H19" s="595"/>
       <c r="I19" s="595"/>
       <c r="J19" s="591"/>
-      <c r="K19" s="701" t="s">
+      <c r="K19" s="744" t="s">
         <v>716</v>
       </c>
       <c r="L19" s="595"/>
@@ -45226,90 +45293,90 @@
       <c r="N19" s="595"/>
       <c r="O19" s="595"/>
       <c r="P19" s="605"/>
-      <c r="Q19" s="701" t="s">
+      <c r="Q19" s="744" t="s">
         <v>717</v>
       </c>
       <c r="R19" s="595"/>
       <c r="S19" s="605"/>
     </row>
     <row r="20" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A20" s="702" t="s">
+      <c r="A20" s="745" t="s">
         <v>718</v>
       </c>
-      <c r="B20" s="655"/>
-      <c r="C20" s="688" t="s">
+      <c r="B20" s="691"/>
+      <c r="C20" s="728" t="s">
         <v>719</v>
       </c>
-      <c r="D20" s="688" t="s">
+      <c r="D20" s="728" t="s">
         <v>720</v>
       </c>
-      <c r="E20" s="695" t="s">
+      <c r="E20" s="738" t="s">
         <v>721</v>
       </c>
-      <c r="F20" s="696"/>
-      <c r="G20" s="688" t="s">
+      <c r="F20" s="739"/>
+      <c r="G20" s="728" t="s">
         <v>722</v>
       </c>
-      <c r="H20" s="688" t="s">
+      <c r="H20" s="728" t="s">
         <v>723</v>
       </c>
-      <c r="I20" s="688" t="s">
+      <c r="I20" s="728" t="s">
         <v>724</v>
       </c>
-      <c r="J20" s="703" t="s">
+      <c r="J20" s="746" t="s">
         <v>760</v>
       </c>
-      <c r="K20" s="686" t="s">
+      <c r="K20" s="726" t="s">
         <v>726</v>
       </c>
-      <c r="L20" s="688" t="s">
+      <c r="L20" s="728" t="s">
         <v>761</v>
       </c>
-      <c r="M20" s="688" t="s">
+      <c r="M20" s="728" t="s">
         <v>728</v>
       </c>
-      <c r="N20" s="688" t="s">
+      <c r="N20" s="728" t="s">
         <v>729</v>
       </c>
-      <c r="O20" s="688" t="s">
+      <c r="O20" s="728" t="s">
         <v>730</v>
       </c>
-      <c r="P20" s="689" t="s">
+      <c r="P20" s="729" t="s">
         <v>731</v>
       </c>
-      <c r="Q20" s="686" t="s">
+      <c r="Q20" s="726" t="s">
         <v>732</v>
       </c>
-      <c r="R20" s="688" t="s">
+      <c r="R20" s="728" t="s">
         <v>733</v>
       </c>
-      <c r="S20" s="689" t="s">
+      <c r="S20" s="729" t="s">
         <v>734</v>
       </c>
     </row>
     <row r="21" spans="1:26" ht="15.75" customHeight="1">
-      <c r="A21" s="609"/>
-      <c r="B21" s="610"/>
-      <c r="C21" s="610"/>
-      <c r="D21" s="610"/>
+      <c r="A21" s="718"/>
+      <c r="B21" s="719"/>
+      <c r="C21" s="719"/>
+      <c r="D21" s="719"/>
       <c r="E21" s="273" t="s">
         <v>762</v>
       </c>
       <c r="F21" s="274" t="s">
         <v>763</v>
       </c>
-      <c r="G21" s="610"/>
-      <c r="H21" s="610"/>
-      <c r="I21" s="610"/>
+      <c r="G21" s="719"/>
+      <c r="H21" s="719"/>
+      <c r="I21" s="719"/>
       <c r="J21" s="582"/>
-      <c r="K21" s="687"/>
-      <c r="L21" s="610"/>
-      <c r="M21" s="610"/>
-      <c r="N21" s="610"/>
-      <c r="O21" s="610"/>
+      <c r="K21" s="727"/>
+      <c r="L21" s="719"/>
+      <c r="M21" s="719"/>
+      <c r="N21" s="719"/>
+      <c r="O21" s="719"/>
       <c r="P21" s="583"/>
-      <c r="Q21" s="687"/>
-      <c r="R21" s="610"/>
+      <c r="Q21" s="727"/>
+      <c r="R21" s="719"/>
       <c r="S21" s="583"/>
     </row>
     <row r="22" spans="1:26" ht="15.75" customHeight="1">
@@ -54245,18 +54312,18 @@
     </row>
     <row r="210" spans="1:26" ht="15.75" customHeight="1">
       <c r="A210" s="386"/>
-      <c r="B210" s="690" t="s">
+      <c r="B210" s="730" t="s">
         <v>1373</v>
       </c>
-      <c r="C210" s="668"/>
+      <c r="C210" s="705"/>
       <c r="D210" s="387">
         <v>55</v>
       </c>
       <c r="E210" s="388"/>
-      <c r="F210" s="697" t="s">
+      <c r="F210" s="740" t="s">
         <v>1374</v>
       </c>
-      <c r="G210" s="668"/>
+      <c r="G210" s="705"/>
       <c r="H210" s="389">
         <f>COUNTIFS(B23:B208,"*",C23:C208,"*",D23:D208,"Completed",F23:F208,"&lt;="&amp;VALUE("12/31/23"),G23:G208,"*",J23:J208,"&gt;="&amp;VALUE("1/1/23"),J23:J208,"&lt;="&amp;VALUE("12/31/23"))</f>
         <v>0</v>
@@ -54288,18 +54355,18 @@
     </row>
     <row r="211" spans="1:26" ht="12.75" customHeight="1">
       <c r="A211" s="386"/>
-      <c r="B211" s="691" t="s">
+      <c r="B211" s="731" t="s">
         <v>1375</v>
       </c>
-      <c r="C211" s="612"/>
-      <c r="D211" s="693">
+      <c r="C211" s="732"/>
+      <c r="D211" s="735">
         <v>180</v>
       </c>
       <c r="E211" s="388"/>
-      <c r="F211" s="697" t="s">
+      <c r="F211" s="740" t="s">
         <v>1376</v>
       </c>
-      <c r="G211" s="668"/>
+      <c r="G211" s="705"/>
       <c r="H211" s="389">
         <f>COUNTIFS(B23:B208,"*",C23:C208,"*",D23:D208,"Completed",F23:F208,"&lt;="&amp;VALUE("12/31/23"),K23:K208,"*",L23:L208,"&gt;="&amp;VALUE("1/1/23"),L23:L208,"&lt;="&amp;VALUE("12/31/23"),M23:M208,"*",N23:N208,"*")</f>
         <v>0</v>
@@ -54331,14 +54398,14 @@
     </row>
     <row r="212" spans="1:26" ht="15.75" customHeight="1">
       <c r="A212" s="392"/>
-      <c r="B212" s="692"/>
-      <c r="C212" s="613"/>
-      <c r="D212" s="615"/>
+      <c r="B212" s="733"/>
+      <c r="C212" s="734"/>
+      <c r="D212" s="736"/>
       <c r="E212" s="393"/>
-      <c r="F212" s="698" t="s">
+      <c r="F212" s="741" t="s">
         <v>1377</v>
       </c>
-      <c r="G212" s="670"/>
+      <c r="G212" s="707"/>
       <c r="H212" s="394">
         <v>11</v>
       </c>
@@ -54363,7 +54430,7 @@
     </row>
     <row r="213" spans="1:26" ht="15.75" customHeight="1">
       <c r="A213" s="249"/>
-      <c r="B213" s="694"/>
+      <c r="B213" s="737"/>
       <c r="C213" s="579"/>
       <c r="D213" s="249"/>
       <c r="E213" s="391"/>
